--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4426,6 +4426,9161 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129357161</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>430629</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6795747</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129365279</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>430739</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6795491</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129365287</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>430700</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6795791</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129365285</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>430830</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6795490</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129366858</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>430593</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6795779</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129366877</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>430703</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6795594</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129366831</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>430798</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6795760</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129366857</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>430616</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6795790</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129366830</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>430794</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6795786</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129366846</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>430812</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6795708</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129366886</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>430675</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6795479</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129365284</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>430819</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6795467</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129366863</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>430653</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6795695</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129366873</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>430712</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6795594</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129366884</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>430687</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6795504</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129357147</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>430860</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6795577</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129357149</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>430757</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6795495</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129366841</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>430768</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6795473</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129366871</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>430684</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6795634</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129357164</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>430692</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6795567</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129366845</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>430816</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6795679</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129366860</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>430605</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6795761</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129365281</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>430773</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6795492</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129357151</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>430783</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6795740</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129357150</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>430883</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6795535</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129357155</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>430682</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6795752</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129365288</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>430681</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6795704</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129365278</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>430695</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6795429</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129366883</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>430687</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6795535</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129366856</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>430745</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6795798</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129366866</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>430658</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6795716</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129366853</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>430777</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6795779</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129357167</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>430663</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6795463</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129357163</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>430645</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6795744</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129366882</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>430689</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6795544</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129366852</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>430782</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6795779</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129366837</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>430718</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6795419</v>
+      </c>
+      <c r="S73" t="n">
+        <v>25</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129365286</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>430758</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6795794</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129365290</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>430688</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6795513</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129365291</v>
+      </c>
+      <c r="B76" t="n">
+        <v>78707</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>353</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>430668</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6795504</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129366872</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>430682</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6795626</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129366849</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>430801</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6795776</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129366838</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>430741</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6795432</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129357158</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>430587</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6795787</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129357146</v>
+      </c>
+      <c r="B81" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>430723</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6795733</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129366868</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>430681</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6795699</v>
+      </c>
+      <c r="S82" t="n">
+        <v>25</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129366848</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>430801</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6795771</v>
+      </c>
+      <c r="S83" t="n">
+        <v>25</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129366847</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>430798</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6795788</v>
+      </c>
+      <c r="S84" t="n">
+        <v>25</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129366887</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>430677</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6795456</v>
+      </c>
+      <c r="S85" t="n">
+        <v>25</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129366870</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>430685</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6795636</v>
+      </c>
+      <c r="S86" t="n">
+        <v>25</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129357156</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>430678</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6795768</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129366855</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>430747</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6795794</v>
+      </c>
+      <c r="S88" t="n">
+        <v>25</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129366844</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>430858</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6795532</v>
+      </c>
+      <c r="S89" t="n">
+        <v>25</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129357152</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>430776</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6795730</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>129357157</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>430595</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6795802</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>129357148</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>430712</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6795453</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129366843</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>430875</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6795544</v>
+      </c>
+      <c r="S93" t="n">
+        <v>25</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129366865</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>430656</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6795713</v>
+      </c>
+      <c r="S94" t="n">
+        <v>25</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>129366879</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>430705</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6795565</v>
+      </c>
+      <c r="S95" t="n">
+        <v>25</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>129365277</v>
+      </c>
+      <c r="B96" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>430671</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6795716</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>129357165</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>430697</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6795560</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>129366835</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>430696</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6795393</v>
+      </c>
+      <c r="S98" t="n">
+        <v>25</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>129365282</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>430792</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6795496</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>129365289</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>430687</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6795502</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>129365276</v>
+      </c>
+      <c r="B101" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>430818</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6795676</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>129365274</v>
+      </c>
+      <c r="B102" t="n">
+        <v>83007</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>430645</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6795789</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>129357154</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>430735</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6795766</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>129366861</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>430639</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6795711</v>
+      </c>
+      <c r="S104" t="n">
+        <v>25</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>129366874</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>430713</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6795598</v>
+      </c>
+      <c r="S105" t="n">
+        <v>25</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>129366850</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>430795</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6795788</v>
+      </c>
+      <c r="S106" t="n">
+        <v>25</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>129366833</v>
+      </c>
+      <c r="B107" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>430797</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6795778</v>
+      </c>
+      <c r="S107" t="n">
+        <v>25</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>129366832</v>
+      </c>
+      <c r="B108" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>430802</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6795767</v>
+      </c>
+      <c r="S108" t="n">
+        <v>25</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>129366878</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>430709</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6795590</v>
+      </c>
+      <c r="S109" t="n">
+        <v>25</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>129366885</v>
+      </c>
+      <c r="B110" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>430679</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6795496</v>
+      </c>
+      <c r="S110" t="n">
+        <v>25</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>129366840</v>
+      </c>
+      <c r="B111" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>430748</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6795446</v>
+      </c>
+      <c r="S111" t="n">
+        <v>25</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>129357153</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>430756</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6795808</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>129357160</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>430620</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6795743</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>129366828</v>
+      </c>
+      <c r="B114" t="n">
+        <v>97559</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>430615</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6795799</v>
+      </c>
+      <c r="S114" t="n">
+        <v>25</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Blöt, översilad mark, örtrik.</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>129357166</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>430683</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6795520</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>129366854</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>430775</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6795782</v>
+      </c>
+      <c r="S116" t="n">
+        <v>25</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>129366836</v>
+      </c>
+      <c r="B117" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>430712</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6795414</v>
+      </c>
+      <c r="S117" t="n">
+        <v>25</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>129366862</v>
+      </c>
+      <c r="B118" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>430645</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6795703</v>
+      </c>
+      <c r="S118" t="n">
+        <v>25</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>129365280</v>
+      </c>
+      <c r="B119" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>430749</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6795484</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>129366867</v>
+      </c>
+      <c r="B120" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>430653</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6795711</v>
+      </c>
+      <c r="S120" t="n">
+        <v>25</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>129366875</v>
+      </c>
+      <c r="B121" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>430714</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6795602</v>
+      </c>
+      <c r="S121" t="n">
+        <v>25</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>129366880</v>
+      </c>
+      <c r="B122" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>430701</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6795567</v>
+      </c>
+      <c r="S122" t="n">
+        <v>25</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>129366842</v>
+      </c>
+      <c r="B123" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>430787</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6795507</v>
+      </c>
+      <c r="S123" t="n">
+        <v>25</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>129365283</v>
+      </c>
+      <c r="B124" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>430793</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6795485</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>129357159</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>430603</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6795771</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>129357145</v>
+      </c>
+      <c r="B126" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Sötberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>430763</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6795787</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>129366881</v>
+      </c>
+      <c r="B127" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>430697</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6795563</v>
+      </c>
+      <c r="S127" t="n">
+        <v>25</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>129366864</v>
+      </c>
+      <c r="B128" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>430653</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6795703</v>
+      </c>
+      <c r="S128" t="n">
+        <v>25</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>129366859</v>
+      </c>
+      <c r="B129" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Åsdammen väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>430595</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6795774</v>
+      </c>
+      <c r="S129" t="n">
+        <v>25</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129351746</v>
+        <v>129351772</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>430822</v>
+        <v>430658</v>
       </c>
       <c r="R2" t="n">
-        <v>6795781</v>
+        <v>6795572</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351765</v>
+        <v>129351746</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430609</v>
+        <v>430822</v>
       </c>
       <c r="R3" t="n">
-        <v>6795766</v>
+        <v>6795781</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351772</v>
+        <v>129351765</v>
       </c>
       <c r="B4" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430658</v>
+        <v>430609</v>
       </c>
       <c r="R4" t="n">
-        <v>6795572</v>
+        <v>6795766</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2390,7 +2390,7 @@
         <v>129351734</v>
       </c>
       <c r="B18" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351748</v>
+        <v>129351762</v>
       </c>
       <c r="B21" t="n">
         <v>79041</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>430805</v>
+        <v>430595</v>
       </c>
       <c r="R21" t="n">
-        <v>6795787</v>
+        <v>6795796</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351762</v>
+        <v>129351748</v>
       </c>
       <c r="B22" t="n">
         <v>79041</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430595</v>
+        <v>430805</v>
       </c>
       <c r="R22" t="n">
-        <v>6795796</v>
+        <v>6795787</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351737</v>
+        <v>129351751</v>
       </c>
       <c r="B23" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430757</v>
+        <v>430718</v>
       </c>
       <c r="R23" t="n">
-        <v>6795789</v>
+        <v>6795804</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129351751</v>
+        <v>129351737</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430718</v>
+        <v>430757</v>
       </c>
       <c r="R24" t="n">
-        <v>6795804</v>
+        <v>6795789</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3671,7 +3671,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351745</v>
+        <v>129351771</v>
       </c>
       <c r="B30" t="n">
         <v>79041</v>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>430824</v>
+        <v>430674</v>
       </c>
       <c r="R30" t="n">
-        <v>6795635</v>
+        <v>6795553</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351735</v>
+        <v>129351745</v>
       </c>
       <c r="B31" t="n">
-        <v>91562</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,41 +3789,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norr om Storbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>430608</v>
+        <v>430824</v>
       </c>
       <c r="R31" t="n">
-        <v>6795766</v>
+        <v>6795635</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3865,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3874,7 +3867,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3893,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351771</v>
+        <v>129351735</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3904,34 +3896,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norr om Storbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>430674</v>
+        <v>430608</v>
       </c>
       <c r="R32" t="n">
-        <v>6795553</v>
+        <v>6795766</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3963,7 +3962,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3973,7 +3972,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3982,6 +3981,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4428,10 +4428,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129357161</v>
+        <v>129366831</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4439,37 +4439,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>430629</v>
+        <v>430798</v>
       </c>
       <c r="R37" t="n">
-        <v>6795747</v>
+        <v>6795760</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4513,19 +4513,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129365279</v>
+        <v>129365287</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>430739</v>
+        <v>430700</v>
       </c>
       <c r="R38" t="n">
-        <v>6795491</v>
+        <v>6795791</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129365287</v>
+        <v>129366886</v>
       </c>
       <c r="B39" t="n">
         <v>79041</v>
@@ -4651,19 +4651,22 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>430700</v>
+        <v>430675</v>
       </c>
       <c r="R39" t="n">
-        <v>6795791</v>
+        <v>6795479</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4701,28 +4704,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129365285</v>
+        <v>129366830</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4730,37 +4734,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>430830</v>
+        <v>430794</v>
       </c>
       <c r="R40" t="n">
-        <v>6795490</v>
+        <v>6795786</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4804,19 +4808,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129366858</v>
+        <v>129366846</v>
       </c>
       <c r="B41" t="n">
         <v>79041</v>
@@ -4845,19 +4849,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>430593</v>
+        <v>430812</v>
       </c>
       <c r="R41" t="n">
-        <v>6795779</v>
+        <v>6795708</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4898,7 +4899,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129366831</v>
+        <v>129365285</v>
       </c>
       <c r="B43" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5029,37 +5029,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>430798</v>
+        <v>430830</v>
       </c>
       <c r="R43" t="n">
-        <v>6795760</v>
+        <v>6795490</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5103,12 +5103,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5216,10 +5216,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129366830</v>
+        <v>129357161</v>
       </c>
       <c r="B45" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5227,37 +5227,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>430794</v>
+        <v>430629</v>
       </c>
       <c r="R45" t="n">
-        <v>6795786</v>
+        <v>6795747</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5301,19 +5301,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129366846</v>
+        <v>129365279</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5344,17 +5344,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>430812</v>
+        <v>430739</v>
       </c>
       <c r="R46" t="n">
-        <v>6795708</v>
+        <v>6795491</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5398,19 +5398,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129366886</v>
+        <v>129366858</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>430675</v>
+        <v>430593</v>
       </c>
       <c r="R47" t="n">
-        <v>6795479</v>
+        <v>6795779</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5511,7 +5511,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129365284</v>
+        <v>129366863</v>
       </c>
       <c r="B48" t="n">
         <v>79041</v>
@@ -5540,19 +5540,22 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>430819</v>
+        <v>430653</v>
       </c>
       <c r="R48" t="n">
-        <v>6795467</v>
+        <v>6795695</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5590,25 +5593,26 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129366863</v>
+        <v>129366884</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5646,10 +5650,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>430653</v>
+        <v>430687</v>
       </c>
       <c r="R49" t="n">
-        <v>6795695</v>
+        <v>6795504</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5709,7 +5713,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129366873</v>
+        <v>129365284</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5738,22 +5742,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>430712</v>
+        <v>430819</v>
       </c>
       <c r="R50" t="n">
-        <v>6795594</v>
+        <v>6795467</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5791,26 +5792,25 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129366884</v>
+        <v>129357147</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5839,22 +5839,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>430687</v>
+        <v>430860</v>
       </c>
       <c r="R51" t="n">
-        <v>6795504</v>
+        <v>6795577</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5892,26 +5889,25 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129357147</v>
+        <v>129366873</v>
       </c>
       <c r="B52" t="n">
         <v>79041</v>
@@ -5940,19 +5936,22 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>430860</v>
+        <v>430712</v>
       </c>
       <c r="R52" t="n">
-        <v>6795577</v>
+        <v>6795594</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5990,25 +5989,26 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129357149</v>
+        <v>129366871</v>
       </c>
       <c r="B53" t="n">
         <v>79041</v>
@@ -6037,19 +6037,22 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>430757</v>
+        <v>430684</v>
       </c>
       <c r="R53" t="n">
-        <v>6795495</v>
+        <v>6795634</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6087,18 +6090,19 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6202,7 +6206,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129366871</v>
+        <v>129357149</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -6231,22 +6235,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>430684</v>
+        <v>430757</v>
       </c>
       <c r="R55" t="n">
-        <v>6795634</v>
+        <v>6795495</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6284,26 +6285,25 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129357164</v>
+        <v>129366860</v>
       </c>
       <c r="B56" t="n">
         <v>79041</v>
@@ -6332,19 +6332,22 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>430692</v>
+        <v>430605</v>
       </c>
       <c r="R56" t="n">
-        <v>6795567</v>
+        <v>6795761</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6382,18 +6385,19 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6497,7 +6501,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129366860</v>
+        <v>129357164</v>
       </c>
       <c r="B58" t="n">
         <v>79041</v>
@@ -6526,22 +6530,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>430605</v>
+        <v>430692</v>
       </c>
       <c r="R58" t="n">
-        <v>6795761</v>
+        <v>6795567</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6579,19 +6580,18 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6695,7 +6695,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129357151</v>
+        <v>129365288</v>
       </c>
       <c r="B60" t="n">
         <v>79041</v>
@@ -6730,10 +6730,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>430783</v>
+        <v>430681</v>
       </c>
       <c r="R60" t="n">
-        <v>6795740</v>
+        <v>6795704</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6780,19 +6780,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129357150</v>
+        <v>129357151</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -6827,10 +6827,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>430883</v>
+        <v>430783</v>
       </c>
       <c r="R61" t="n">
-        <v>6795535</v>
+        <v>6795740</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129365288</v>
+        <v>129365278</v>
       </c>
       <c r="B63" t="n">
         <v>79041</v>
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>430681</v>
+        <v>430695</v>
       </c>
       <c r="R63" t="n">
-        <v>6795704</v>
+        <v>6795429</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7083,7 +7083,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129365278</v>
+        <v>129357150</v>
       </c>
       <c r="B64" t="n">
         <v>79041</v>
@@ -7118,10 +7118,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>430695</v>
+        <v>430883</v>
       </c>
       <c r="R64" t="n">
-        <v>6795429</v>
+        <v>6795535</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7168,19 +7168,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129366883</v>
+        <v>129366866</v>
       </c>
       <c r="B65" t="n">
         <v>79041</v>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>430687</v>
+        <v>430658</v>
       </c>
       <c r="R65" t="n">
-        <v>6795535</v>
+        <v>6795716</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7281,7 +7281,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129366856</v>
+        <v>129366883</v>
       </c>
       <c r="B66" t="n">
         <v>79041</v>
@@ -7319,10 +7319,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430745</v>
+        <v>430687</v>
       </c>
       <c r="R66" t="n">
-        <v>6795798</v>
+        <v>6795535</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7382,7 +7382,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129366866</v>
+        <v>129366856</v>
       </c>
       <c r="B67" t="n">
         <v>79041</v>
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>430658</v>
+        <v>430745</v>
       </c>
       <c r="R67" t="n">
-        <v>6795716</v>
+        <v>6795798</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7580,7 +7580,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129357167</v>
+        <v>129366882</v>
       </c>
       <c r="B69" t="n">
         <v>79041</v>
@@ -7609,19 +7609,22 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>430663</v>
+        <v>430689</v>
       </c>
       <c r="R69" t="n">
-        <v>6795463</v>
+        <v>6795544</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7659,18 +7662,19 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7774,7 +7778,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129366882</v>
+        <v>129357167</v>
       </c>
       <c r="B71" t="n">
         <v>79041</v>
@@ -7803,22 +7807,19 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>430689</v>
+        <v>430663</v>
       </c>
       <c r="R71" t="n">
-        <v>6795544</v>
+        <v>6795463</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7856,19 +7857,18 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8069,10 +8069,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129365286</v>
+        <v>129365291</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8080,21 +8080,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8104,10 +8104,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>430758</v>
+        <v>430668</v>
       </c>
       <c r="R74" t="n">
-        <v>6795794</v>
+        <v>6795504</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8166,7 +8166,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129365290</v>
+        <v>129365286</v>
       </c>
       <c r="B75" t="n">
         <v>79041</v>
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>430688</v>
+        <v>430758</v>
       </c>
       <c r="R75" t="n">
-        <v>6795513</v>
+        <v>6795794</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8263,10 +8263,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129365291</v>
+        <v>129366838</v>
       </c>
       <c r="B76" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8274,37 +8274,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>430668</v>
+        <v>430741</v>
       </c>
       <c r="R76" t="n">
-        <v>6795504</v>
+        <v>6795432</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8348,19 +8348,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129366872</v>
+        <v>129366849</v>
       </c>
       <c r="B77" t="n">
         <v>79041</v>
@@ -8389,19 +8389,16 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>430682</v>
+        <v>430801</v>
       </c>
       <c r="R77" t="n">
-        <v>6795626</v>
+        <v>6795776</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8442,7 +8439,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8454,14 +8450,14 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129366849</v>
+        <v>129366872</v>
       </c>
       <c r="B78" t="n">
         <v>79041</v>
@@ -8490,16 +8486,19 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>430801</v>
+        <v>430682</v>
       </c>
       <c r="R78" t="n">
-        <v>6795776</v>
+        <v>6795626</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8540,6 +8539,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8551,14 +8551,14 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129366838</v>
+        <v>129365290</v>
       </c>
       <c r="B79" t="n">
         <v>79041</v>
@@ -8589,17 +8589,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>430741</v>
+        <v>430688</v>
       </c>
       <c r="R79" t="n">
-        <v>6795432</v>
+        <v>6795513</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8643,12 +8643,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8752,10 +8752,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129357146</v>
+        <v>129366868</v>
       </c>
       <c r="B81" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8763,37 +8763,40 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>430723</v>
+        <v>430681</v>
       </c>
       <c r="R81" t="n">
-        <v>6795733</v>
+        <v>6795699</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8831,25 +8834,26 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129366868</v>
+        <v>129366848</v>
       </c>
       <c r="B82" t="n">
         <v>79041</v>
@@ -8878,19 +8882,16 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>430681</v>
+        <v>430801</v>
       </c>
       <c r="R82" t="n">
-        <v>6795699</v>
+        <v>6795771</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8931,7 +8932,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8943,17 +8943,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129366848</v>
+        <v>129357146</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8961,37 +8961,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>430801</v>
+        <v>430723</v>
       </c>
       <c r="R83" t="n">
-        <v>6795771</v>
+        <v>6795733</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9035,19 +9035,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129366847</v>
+        <v>129366870</v>
       </c>
       <c r="B84" t="n">
         <v>79041</v>
@@ -9076,16 +9076,19 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>430798</v>
+        <v>430685</v>
       </c>
       <c r="R84" t="n">
-        <v>6795788</v>
+        <v>6795636</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9126,6 +9129,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9137,7 +9141,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9245,7 +9249,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129366870</v>
+        <v>129366847</v>
       </c>
       <c r="B86" t="n">
         <v>79041</v>
@@ -9274,19 +9278,16 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>430685</v>
+        <v>430798</v>
       </c>
       <c r="R86" t="n">
-        <v>6795636</v>
+        <v>6795788</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9327,7 +9328,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9339,14 +9339,14 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129357156</v>
+        <v>129366844</v>
       </c>
       <c r="B87" t="n">
         <v>79041</v>
@@ -9377,17 +9377,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>430678</v>
+        <v>430858</v>
       </c>
       <c r="R87" t="n">
-        <v>6795768</v>
+        <v>6795532</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9431,12 +9431,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9544,7 +9544,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129366844</v>
+        <v>129357156</v>
       </c>
       <c r="B89" t="n">
         <v>79041</v>
@@ -9575,17 +9575,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>430858</v>
+        <v>430678</v>
       </c>
       <c r="R89" t="n">
-        <v>6795532</v>
+        <v>6795768</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9738,7 +9738,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129357157</v>
+        <v>129357148</v>
       </c>
       <c r="B91" t="n">
         <v>79041</v>
@@ -9773,10 +9773,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>430595</v>
+        <v>430712</v>
       </c>
       <c r="R91" t="n">
-        <v>6795802</v>
+        <v>6795453</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9835,7 +9835,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129357148</v>
+        <v>129357157</v>
       </c>
       <c r="B92" t="n">
         <v>79041</v>
@@ -9870,10 +9870,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>430712</v>
+        <v>430595</v>
       </c>
       <c r="R92" t="n">
-        <v>6795453</v>
+        <v>6795802</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9932,7 +9932,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129366843</v>
+        <v>129366879</v>
       </c>
       <c r="B93" t="n">
         <v>79041</v>
@@ -9961,16 +9961,19 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>430875</v>
+        <v>430705</v>
       </c>
       <c r="R93" t="n">
-        <v>6795544</v>
+        <v>6795565</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10011,6 +10014,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10022,7 +10026,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10130,10 +10134,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129366879</v>
+        <v>129365277</v>
       </c>
       <c r="B95" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10141,40 +10145,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>430705</v>
+        <v>430671</v>
       </c>
       <c r="R95" t="n">
-        <v>6795565</v>
+        <v>6795716</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10212,29 +10213,28 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129365277</v>
+        <v>129366843</v>
       </c>
       <c r="B96" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10242,37 +10242,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>430671</v>
+        <v>430875</v>
       </c>
       <c r="R96" t="n">
-        <v>6795716</v>
+        <v>6795544</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10316,12 +10316,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10425,7 +10425,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129366835</v>
+        <v>129365282</v>
       </c>
       <c r="B98" t="n">
         <v>79041</v>
@@ -10456,17 +10456,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>430696</v>
+        <v>430792</v>
       </c>
       <c r="R98" t="n">
-        <v>6795393</v>
+        <v>6795496</v>
       </c>
       <c r="S98" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10510,19 +10510,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129365282</v>
+        <v>129365289</v>
       </c>
       <c r="B99" t="n">
         <v>79041</v>
@@ -10557,10 +10557,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>430792</v>
+        <v>430687</v>
       </c>
       <c r="R99" t="n">
-        <v>6795496</v>
+        <v>6795502</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10619,10 +10619,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129365289</v>
+        <v>129365276</v>
       </c>
       <c r="B100" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10630,21 +10630,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10654,10 +10654,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>430687</v>
+        <v>430818</v>
       </c>
       <c r="R100" t="n">
-        <v>6795502</v>
+        <v>6795676</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10716,10 +10716,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129365276</v>
+        <v>129366835</v>
       </c>
       <c r="B101" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10727,37 +10727,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>430818</v>
+        <v>430696</v>
       </c>
       <c r="R101" t="n">
-        <v>6795676</v>
+        <v>6795393</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10801,22 +10801,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129365274</v>
+        <v>129366850</v>
       </c>
       <c r="B102" t="n">
-        <v>83007</v>
+        <v>79041</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10824,37 +10824,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>430645</v>
+        <v>430795</v>
       </c>
       <c r="R102" t="n">
-        <v>6795789</v>
+        <v>6795788</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10898,19 +10898,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129357154</v>
+        <v>129366861</v>
       </c>
       <c r="B103" t="n">
         <v>79041</v>
@@ -10939,19 +10939,22 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>430735</v>
+        <v>430639</v>
       </c>
       <c r="R103" t="n">
-        <v>6795766</v>
+        <v>6795711</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10989,25 +10992,26 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129366861</v>
+        <v>129357154</v>
       </c>
       <c r="B104" t="n">
         <v>79041</v>
@@ -11036,22 +11040,19 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>430639</v>
+        <v>430735</v>
       </c>
       <c r="R104" t="n">
-        <v>6795711</v>
+        <v>6795766</v>
       </c>
       <c r="S104" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11089,19 +11090,18 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -11209,7 +11209,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129366850</v>
+        <v>129366878</v>
       </c>
       <c r="B106" t="n">
         <v>79041</v>
@@ -11238,16 +11238,19 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>430795</v>
+        <v>430709</v>
       </c>
       <c r="R106" t="n">
-        <v>6795788</v>
+        <v>6795590</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11288,6 +11291,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11299,14 +11303,14 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129366833</v>
+        <v>129366832</v>
       </c>
       <c r="B107" t="n">
         <v>78798</v>
@@ -11341,10 +11345,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>430797</v>
+        <v>430802</v>
       </c>
       <c r="R107" t="n">
-        <v>6795778</v>
+        <v>6795767</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11403,10 +11407,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129366832</v>
+        <v>129365274</v>
       </c>
       <c r="B108" t="n">
-        <v>78798</v>
+        <v>83007</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11414,37 +11418,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>430802</v>
+        <v>430645</v>
       </c>
       <c r="R108" t="n">
-        <v>6795767</v>
+        <v>6795789</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11488,22 +11492,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129366878</v>
+        <v>129366833</v>
       </c>
       <c r="B109" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11511,37 +11515,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>430709</v>
+        <v>430797</v>
       </c>
       <c r="R109" t="n">
-        <v>6795590</v>
+        <v>6795778</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11582,7 +11583,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11594,14 +11594,14 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129366885</v>
+        <v>129366840</v>
       </c>
       <c r="B110" t="n">
         <v>79041</v>
@@ -11630,19 +11630,16 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>430679</v>
+        <v>430748</v>
       </c>
       <c r="R110" t="n">
-        <v>6795496</v>
+        <v>6795446</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11683,7 +11680,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11695,14 +11691,14 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129366840</v>
+        <v>129366885</v>
       </c>
       <c r="B111" t="n">
         <v>79041</v>
@@ -11731,16 +11727,19 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>430748</v>
+        <v>430679</v>
       </c>
       <c r="R111" t="n">
-        <v>6795446</v>
+        <v>6795496</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11781,6 +11780,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11792,55 +11792,59 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129357153</v>
+        <v>129366828</v>
       </c>
       <c r="B112" t="n">
-        <v>79041</v>
+        <v>97575</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>430756</v>
+        <v>430615</v>
       </c>
       <c r="R112" t="n">
-        <v>6795808</v>
+        <v>6795799</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11872,24 +11876,30 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Blöt, översilad mark, örtrik.</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -11993,52 +12003,48 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129366828</v>
+        <v>129357153</v>
       </c>
       <c r="B114" t="n">
-        <v>97559</v>
+        <v>79041</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>430615</v>
+        <v>430756</v>
       </c>
       <c r="R114" t="n">
-        <v>6795799</v>
+        <v>6795808</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12070,37 +12076,31 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Blöt, översilad mark, örtrik.</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129357166</v>
+        <v>129366854</v>
       </c>
       <c r="B115" t="n">
         <v>79041</v>
@@ -12131,17 +12131,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>430683</v>
+        <v>430775</v>
       </c>
       <c r="R115" t="n">
-        <v>6795520</v>
+        <v>6795782</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12185,19 +12185,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129366854</v>
+        <v>129366836</v>
       </c>
       <c r="B116" t="n">
         <v>79041</v>
@@ -12232,10 +12232,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>430775</v>
+        <v>430712</v>
       </c>
       <c r="R116" t="n">
-        <v>6795782</v>
+        <v>6795414</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12294,7 +12294,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129366836</v>
+        <v>129365280</v>
       </c>
       <c r="B117" t="n">
         <v>79041</v>
@@ -12325,17 +12325,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>430712</v>
+        <v>430749</v>
       </c>
       <c r="R117" t="n">
-        <v>6795414</v>
+        <v>6795484</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12379,12 +12379,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12492,7 +12492,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129365280</v>
+        <v>129357166</v>
       </c>
       <c r="B119" t="n">
         <v>79041</v>
@@ -12527,10 +12527,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>430749</v>
+        <v>430683</v>
       </c>
       <c r="R119" t="n">
-        <v>6795484</v>
+        <v>6795520</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12577,19 +12577,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129366867</v>
+        <v>129366875</v>
       </c>
       <c r="B120" t="n">
         <v>79041</v>
@@ -12627,10 +12627,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>430653</v>
+        <v>430714</v>
       </c>
       <c r="R120" t="n">
-        <v>6795711</v>
+        <v>6795602</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12690,7 +12690,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129366875</v>
+        <v>129366842</v>
       </c>
       <c r="B121" t="n">
         <v>79041</v>
@@ -12719,19 +12719,16 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>430714</v>
+        <v>430787</v>
       </c>
       <c r="R121" t="n">
-        <v>6795602</v>
+        <v>6795507</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -12772,7 +12769,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12784,7 +12780,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -12892,7 +12888,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129366842</v>
+        <v>129366867</v>
       </c>
       <c r="B123" t="n">
         <v>79041</v>
@@ -12921,16 +12917,19 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>430787</v>
+        <v>430653</v>
       </c>
       <c r="R123" t="n">
-        <v>6795507</v>
+        <v>6795711</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -12971,6 +12970,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12982,14 +12982,14 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129365283</v>
+        <v>129366864</v>
       </c>
       <c r="B124" t="n">
         <v>79041</v>
@@ -13018,19 +13018,22 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>430793</v>
+        <v>430653</v>
       </c>
       <c r="R124" t="n">
-        <v>6795485</v>
+        <v>6795703</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13068,25 +13071,26 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129357159</v>
+        <v>129366881</v>
       </c>
       <c r="B125" t="n">
         <v>79041</v>
@@ -13115,19 +13119,22 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>430603</v>
+        <v>430697</v>
       </c>
       <c r="R125" t="n">
-        <v>6795771</v>
+        <v>6795563</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13165,28 +13172,29 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129357145</v>
+        <v>129365283</v>
       </c>
       <c r="B126" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13194,21 +13202,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13218,10 +13226,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>430763</v>
+        <v>430793</v>
       </c>
       <c r="R126" t="n">
-        <v>6795787</v>
+        <v>6795485</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13268,19 +13276,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129366881</v>
+        <v>129366859</v>
       </c>
       <c r="B127" t="n">
         <v>79041</v>
@@ -13318,10 +13326,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>430697</v>
+        <v>430595</v>
       </c>
       <c r="R127" t="n">
-        <v>6795563</v>
+        <v>6795774</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13381,7 +13389,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129366864</v>
+        <v>129357159</v>
       </c>
       <c r="B128" t="n">
         <v>79041</v>
@@ -13410,22 +13418,19 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>430653</v>
+        <v>430603</v>
       </c>
       <c r="R128" t="n">
-        <v>6795703</v>
+        <v>6795771</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13463,29 +13468,28 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129366859</v>
+        <v>129357145</v>
       </c>
       <c r="B129" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13493,40 +13497,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>430595</v>
+        <v>430763</v>
       </c>
       <c r="R129" t="n">
-        <v>6795774</v>
+        <v>6795787</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13564,19 +13565,18 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -2390,7 +2390,7 @@
         <v>129351734</v>
       </c>
       <c r="B18" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351762</v>
+        <v>129351748</v>
       </c>
       <c r="B21" t="n">
         <v>79041</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>430595</v>
+        <v>430805</v>
       </c>
       <c r="R21" t="n">
-        <v>6795796</v>
+        <v>6795787</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351748</v>
+        <v>129351762</v>
       </c>
       <c r="B22" t="n">
         <v>79041</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430805</v>
+        <v>430595</v>
       </c>
       <c r="R22" t="n">
-        <v>6795787</v>
+        <v>6795796</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3671,10 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351771</v>
+        <v>129351735</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>91561</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,34 +3682,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Norr om Storbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>430674</v>
+        <v>430608</v>
       </c>
       <c r="R30" t="n">
-        <v>6795553</v>
+        <v>6795766</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3748,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3758,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3760,6 +3767,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3778,7 +3786,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351745</v>
+        <v>129351771</v>
       </c>
       <c r="B31" t="n">
         <v>79041</v>
@@ -3813,10 +3821,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>430824</v>
+        <v>430674</v>
       </c>
       <c r="R31" t="n">
-        <v>6795635</v>
+        <v>6795553</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3856,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3866,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3893,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351735</v>
+        <v>129351745</v>
       </c>
       <c r="B32" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,41 +3904,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norr om Storbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>430608</v>
+        <v>430824</v>
       </c>
       <c r="R32" t="n">
-        <v>6795766</v>
+        <v>6795635</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3962,7 +3963,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3972,7 +3973,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3981,7 +3982,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4428,10 +4428,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129366831</v>
+        <v>129357161</v>
       </c>
       <c r="B37" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4439,37 +4439,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>430798</v>
+        <v>430629</v>
       </c>
       <c r="R37" t="n">
-        <v>6795760</v>
+        <v>6795747</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4513,22 +4513,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129365287</v>
+        <v>129366831</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,37 +4536,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>430700</v>
+        <v>430798</v>
       </c>
       <c r="R38" t="n">
-        <v>6795791</v>
+        <v>6795760</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4610,12 +4610,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4820,7 +4820,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129366846</v>
+        <v>129365279</v>
       </c>
       <c r="B41" t="n">
         <v>79041</v>
@@ -4851,17 +4851,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>430812</v>
+        <v>430739</v>
       </c>
       <c r="R41" t="n">
-        <v>6795708</v>
+        <v>6795491</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4905,19 +4905,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129366877</v>
+        <v>129366858</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>430703</v>
+        <v>430593</v>
       </c>
       <c r="R42" t="n">
-        <v>6795594</v>
+        <v>6795779</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5018,7 +5018,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129365285</v>
+        <v>129365287</v>
       </c>
       <c r="B43" t="n">
         <v>79041</v>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>430830</v>
+        <v>430700</v>
       </c>
       <c r="R43" t="n">
-        <v>6795490</v>
+        <v>6795791</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5115,7 +5115,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129366857</v>
+        <v>129366846</v>
       </c>
       <c r="B44" t="n">
         <v>79041</v>
@@ -5144,19 +5144,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>430616</v>
+        <v>430812</v>
       </c>
       <c r="R44" t="n">
-        <v>6795790</v>
+        <v>6795708</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5197,7 +5194,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5209,14 +5205,14 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129357161</v>
+        <v>129366877</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5245,19 +5241,22 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>430629</v>
+        <v>430703</v>
       </c>
       <c r="R45" t="n">
-        <v>6795747</v>
+        <v>6795594</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5295,25 +5294,26 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129365279</v>
+        <v>129365285</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5348,10 +5348,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>430739</v>
+        <v>430830</v>
       </c>
       <c r="R46" t="n">
-        <v>6795491</v>
+        <v>6795490</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5410,7 +5410,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129366858</v>
+        <v>129366857</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>430593</v>
+        <v>430616</v>
       </c>
       <c r="R47" t="n">
-        <v>6795779</v>
+        <v>6795790</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5511,7 +5511,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129366863</v>
+        <v>129366884</v>
       </c>
       <c r="B48" t="n">
         <v>79041</v>
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>430653</v>
+        <v>430687</v>
       </c>
       <c r="R48" t="n">
-        <v>6795695</v>
+        <v>6795504</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5612,7 +5612,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129366884</v>
+        <v>129365284</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5641,22 +5641,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>430687</v>
+        <v>430819</v>
       </c>
       <c r="R49" t="n">
-        <v>6795504</v>
+        <v>6795467</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5694,26 +5691,25 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129365284</v>
+        <v>129357147</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5748,10 +5744,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>430819</v>
+        <v>430860</v>
       </c>
       <c r="R50" t="n">
-        <v>6795467</v>
+        <v>6795577</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5798,19 +5794,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129357147</v>
+        <v>129366873</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5839,19 +5835,22 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>430860</v>
+        <v>430712</v>
       </c>
       <c r="R51" t="n">
-        <v>6795577</v>
+        <v>6795594</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5889,25 +5888,26 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129366873</v>
+        <v>129366863</v>
       </c>
       <c r="B52" t="n">
         <v>79041</v>
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>430712</v>
+        <v>430653</v>
       </c>
       <c r="R52" t="n">
-        <v>6795594</v>
+        <v>6795695</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6501,7 +6501,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129357164</v>
+        <v>129365281</v>
       </c>
       <c r="B58" t="n">
         <v>79041</v>
@@ -6536,10 +6536,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>430692</v>
+        <v>430773</v>
       </c>
       <c r="R58" t="n">
-        <v>6795567</v>
+        <v>6795492</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6586,19 +6586,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129365281</v>
+        <v>129357164</v>
       </c>
       <c r="B59" t="n">
         <v>79041</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>430773</v>
+        <v>430692</v>
       </c>
       <c r="R59" t="n">
-        <v>6795492</v>
+        <v>6795567</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6683,12 +6683,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6792,7 +6792,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129357151</v>
+        <v>129365278</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -6827,10 +6827,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>430783</v>
+        <v>430695</v>
       </c>
       <c r="R61" t="n">
-        <v>6795740</v>
+        <v>6795429</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6877,19 +6877,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129357155</v>
+        <v>129366866</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -6918,19 +6918,22 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>430682</v>
+        <v>430658</v>
       </c>
       <c r="R62" t="n">
-        <v>6795752</v>
+        <v>6795716</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6968,25 +6971,26 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129365278</v>
+        <v>129366856</v>
       </c>
       <c r="B63" t="n">
         <v>79041</v>
@@ -7015,19 +7019,22 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>430695</v>
+        <v>430745</v>
       </c>
       <c r="R63" t="n">
-        <v>6795429</v>
+        <v>6795798</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7065,25 +7072,26 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129357150</v>
+        <v>129357151</v>
       </c>
       <c r="B64" t="n">
         <v>79041</v>
@@ -7118,10 +7126,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>430883</v>
+        <v>430783</v>
       </c>
       <c r="R64" t="n">
-        <v>6795535</v>
+        <v>6795740</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7180,7 +7188,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129366866</v>
+        <v>129357155</v>
       </c>
       <c r="B65" t="n">
         <v>79041</v>
@@ -7209,22 +7217,19 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>430658</v>
+        <v>430682</v>
       </c>
       <c r="R65" t="n">
-        <v>6795716</v>
+        <v>6795752</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7262,26 +7267,25 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129366883</v>
+        <v>129357150</v>
       </c>
       <c r="B66" t="n">
         <v>79041</v>
@@ -7310,22 +7314,19 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430687</v>
+        <v>430883</v>
       </c>
       <c r="R66" t="n">
         <v>6795535</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7363,26 +7364,25 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129366856</v>
+        <v>129366883</v>
       </c>
       <c r="B67" t="n">
         <v>79041</v>
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>430745</v>
+        <v>430687</v>
       </c>
       <c r="R67" t="n">
-        <v>6795798</v>
+        <v>6795535</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8263,7 +8263,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129366838</v>
+        <v>129366872</v>
       </c>
       <c r="B76" t="n">
         <v>79041</v>
@@ -8292,16 +8292,19 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>430741</v>
+        <v>430682</v>
       </c>
       <c r="R76" t="n">
-        <v>6795432</v>
+        <v>6795626</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8342,6 +8345,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8353,14 +8357,14 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129366849</v>
+        <v>129365290</v>
       </c>
       <c r="B77" t="n">
         <v>79041</v>
@@ -8391,17 +8395,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>430801</v>
+        <v>430688</v>
       </c>
       <c r="R77" t="n">
-        <v>6795776</v>
+        <v>6795513</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8445,19 +8449,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129366872</v>
+        <v>129366838</v>
       </c>
       <c r="B78" t="n">
         <v>79041</v>
@@ -8486,19 +8490,16 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>430682</v>
+        <v>430741</v>
       </c>
       <c r="R78" t="n">
-        <v>6795626</v>
+        <v>6795432</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8539,7 +8540,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8551,14 +8551,14 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129365290</v>
+        <v>129366849</v>
       </c>
       <c r="B79" t="n">
         <v>79041</v>
@@ -8589,17 +8589,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>430688</v>
+        <v>430801</v>
       </c>
       <c r="R79" t="n">
-        <v>6795513</v>
+        <v>6795776</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8643,12 +8643,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9148,7 +9148,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129366887</v>
+        <v>129366847</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -9177,19 +9177,16 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>430677</v>
+        <v>430798</v>
       </c>
       <c r="R85" t="n">
-        <v>6795456</v>
+        <v>6795788</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9230,7 +9227,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9242,14 +9238,14 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129366847</v>
+        <v>129366887</v>
       </c>
       <c r="B86" t="n">
         <v>79041</v>
@@ -9278,16 +9274,19 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>430798</v>
+        <v>430677</v>
       </c>
       <c r="R86" t="n">
-        <v>6795788</v>
+        <v>6795456</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9328,6 +9327,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9641,7 +9641,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129357152</v>
+        <v>129357157</v>
       </c>
       <c r="B90" t="n">
         <v>79041</v>
@@ -9676,10 +9676,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>430776</v>
+        <v>430595</v>
       </c>
       <c r="R90" t="n">
-        <v>6795730</v>
+        <v>6795802</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9738,7 +9738,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129357148</v>
+        <v>129357152</v>
       </c>
       <c r="B91" t="n">
         <v>79041</v>
@@ -9773,10 +9773,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>430712</v>
+        <v>430776</v>
       </c>
       <c r="R91" t="n">
-        <v>6795453</v>
+        <v>6795730</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9835,7 +9835,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129357157</v>
+        <v>129357148</v>
       </c>
       <c r="B92" t="n">
         <v>79041</v>
@@ -9870,10 +9870,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>430595</v>
+        <v>430712</v>
       </c>
       <c r="R92" t="n">
-        <v>6795802</v>
+        <v>6795453</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9932,10 +9932,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129366879</v>
+        <v>129365277</v>
       </c>
       <c r="B93" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9943,40 +9943,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>430705</v>
+        <v>430671</v>
       </c>
       <c r="R93" t="n">
-        <v>6795565</v>
+        <v>6795716</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10014,26 +10011,25 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129366865</v>
+        <v>129366879</v>
       </c>
       <c r="B94" t="n">
         <v>79041</v>
@@ -10071,10 +10067,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>430656</v>
+        <v>430705</v>
       </c>
       <c r="R94" t="n">
-        <v>6795713</v>
+        <v>6795565</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10134,10 +10130,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129365277</v>
+        <v>129366865</v>
       </c>
       <c r="B95" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10145,37 +10141,40 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>430671</v>
+        <v>430656</v>
       </c>
       <c r="R95" t="n">
-        <v>6795716</v>
+        <v>6795713</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10213,18 +10212,19 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10328,7 +10328,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129357165</v>
+        <v>129365282</v>
       </c>
       <c r="B97" t="n">
         <v>79041</v>
@@ -10363,10 +10363,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>430697</v>
+        <v>430792</v>
       </c>
       <c r="R97" t="n">
-        <v>6795560</v>
+        <v>6795496</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10413,19 +10413,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129365282</v>
+        <v>129365289</v>
       </c>
       <c r="B98" t="n">
         <v>79041</v>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>430792</v>
+        <v>430687</v>
       </c>
       <c r="R98" t="n">
-        <v>6795496</v>
+        <v>6795502</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10522,7 +10522,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129365289</v>
+        <v>129366835</v>
       </c>
       <c r="B99" t="n">
         <v>79041</v>
@@ -10553,17 +10553,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>430687</v>
+        <v>430696</v>
       </c>
       <c r="R99" t="n">
-        <v>6795502</v>
+        <v>6795393</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10607,22 +10607,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129365276</v>
+        <v>129357165</v>
       </c>
       <c r="B100" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10630,21 +10630,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10654,10 +10654,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>430818</v>
+        <v>430697</v>
       </c>
       <c r="R100" t="n">
-        <v>6795676</v>
+        <v>6795560</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10704,22 +10704,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129366835</v>
+        <v>129365276</v>
       </c>
       <c r="B101" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10727,37 +10727,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>430696</v>
+        <v>430818</v>
       </c>
       <c r="R101" t="n">
-        <v>6795393</v>
+        <v>6795676</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -11011,7 +11011,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129357154</v>
+        <v>129366874</v>
       </c>
       <c r="B104" t="n">
         <v>79041</v>
@@ -11040,19 +11040,22 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>430735</v>
+        <v>430713</v>
       </c>
       <c r="R104" t="n">
-        <v>6795766</v>
+        <v>6795598</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11090,25 +11093,26 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129366874</v>
+        <v>129366878</v>
       </c>
       <c r="B105" t="n">
         <v>79041</v>
@@ -11146,10 +11150,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>430713</v>
+        <v>430709</v>
       </c>
       <c r="R105" t="n">
-        <v>6795598</v>
+        <v>6795590</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11209,7 +11213,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129366878</v>
+        <v>129357154</v>
       </c>
       <c r="B106" t="n">
         <v>79041</v>
@@ -11238,22 +11242,19 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>430709</v>
+        <v>430735</v>
       </c>
       <c r="R106" t="n">
-        <v>6795590</v>
+        <v>6795766</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11291,19 +11292,18 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129366840</v>
+        <v>129366885</v>
       </c>
       <c r="B110" t="n">
         <v>79041</v>
@@ -11630,16 +11630,19 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>430748</v>
+        <v>430679</v>
       </c>
       <c r="R110" t="n">
-        <v>6795446</v>
+        <v>6795496</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11680,6 +11683,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11691,14 +11695,14 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129366885</v>
+        <v>129366840</v>
       </c>
       <c r="B111" t="n">
         <v>79041</v>
@@ -11727,19 +11731,16 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>430679</v>
+        <v>430748</v>
       </c>
       <c r="R111" t="n">
-        <v>6795496</v>
+        <v>6795446</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11780,7 +11781,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11792,59 +11792,55 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129366828</v>
+        <v>129357160</v>
       </c>
       <c r="B112" t="n">
-        <v>97575</v>
+        <v>79041</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>430615</v>
+        <v>430620</v>
       </c>
       <c r="R112" t="n">
-        <v>6795799</v>
+        <v>6795743</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11876,37 +11872,31 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Blöt, översilad mark, örtrik.</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129357160</v>
+        <v>129357153</v>
       </c>
       <c r="B113" t="n">
         <v>79041</v>
@@ -11941,10 +11931,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>430620</v>
+        <v>430756</v>
       </c>
       <c r="R113" t="n">
-        <v>6795743</v>
+        <v>6795808</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12003,48 +11993,52 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129357153</v>
+        <v>129366828</v>
       </c>
       <c r="B114" t="n">
-        <v>79041</v>
+        <v>97576</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>430756</v>
+        <v>430615</v>
       </c>
       <c r="R114" t="n">
-        <v>6795808</v>
+        <v>6795799</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12076,24 +12070,30 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Blöt, översilad mark, örtrik.</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12197,7 +12197,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129366836</v>
+        <v>129365280</v>
       </c>
       <c r="B116" t="n">
         <v>79041</v>
@@ -12228,17 +12228,17 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>430712</v>
+        <v>430749</v>
       </c>
       <c r="R116" t="n">
-        <v>6795414</v>
+        <v>6795484</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12282,19 +12282,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129365280</v>
+        <v>129366862</v>
       </c>
       <c r="B117" t="n">
         <v>79041</v>
@@ -12323,19 +12323,22 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>430749</v>
+        <v>430645</v>
       </c>
       <c r="R117" t="n">
-        <v>6795484</v>
+        <v>6795703</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12373,25 +12376,26 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129366862</v>
+        <v>129366836</v>
       </c>
       <c r="B118" t="n">
         <v>79041</v>
@@ -12420,19 +12424,16 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>430645</v>
+        <v>430712</v>
       </c>
       <c r="R118" t="n">
-        <v>6795703</v>
+        <v>6795414</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12473,7 +12474,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12485,7 +12485,7 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -12589,7 +12589,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129366875</v>
+        <v>129366867</v>
       </c>
       <c r="B120" t="n">
         <v>79041</v>
@@ -12627,10 +12627,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>430714</v>
+        <v>430653</v>
       </c>
       <c r="R120" t="n">
-        <v>6795602</v>
+        <v>6795711</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12690,7 +12690,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129366842</v>
+        <v>129366875</v>
       </c>
       <c r="B121" t="n">
         <v>79041</v>
@@ -12719,16 +12719,19 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>430787</v>
+        <v>430714</v>
       </c>
       <c r="R121" t="n">
-        <v>6795507</v>
+        <v>6795602</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -12769,6 +12772,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12780,14 +12784,14 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129366880</v>
+        <v>129366842</v>
       </c>
       <c r="B122" t="n">
         <v>79041</v>
@@ -12816,19 +12820,16 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>430701</v>
+        <v>430787</v>
       </c>
       <c r="R122" t="n">
-        <v>6795567</v>
+        <v>6795507</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -12869,7 +12870,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12881,14 +12881,14 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129366867</v>
+        <v>129366880</v>
       </c>
       <c r="B123" t="n">
         <v>79041</v>
@@ -12926,10 +12926,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>430653</v>
+        <v>430701</v>
       </c>
       <c r="R123" t="n">
-        <v>6795711</v>
+        <v>6795567</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -12989,7 +12989,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129366864</v>
+        <v>129357159</v>
       </c>
       <c r="B124" t="n">
         <v>79041</v>
@@ -13018,22 +13018,19 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>430653</v>
+        <v>430603</v>
       </c>
       <c r="R124" t="n">
-        <v>6795703</v>
+        <v>6795771</v>
       </c>
       <c r="S124" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13071,29 +13068,28 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129366881</v>
+        <v>129357145</v>
       </c>
       <c r="B125" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13101,40 +13097,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>430697</v>
+        <v>430763</v>
       </c>
       <c r="R125" t="n">
-        <v>6795563</v>
+        <v>6795787</v>
       </c>
       <c r="S125" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13172,26 +13165,25 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129365283</v>
+        <v>129366864</v>
       </c>
       <c r="B126" t="n">
         <v>79041</v>
@@ -13220,19 +13212,22 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>430793</v>
+        <v>430653</v>
       </c>
       <c r="R126" t="n">
-        <v>6795485</v>
+        <v>6795703</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13270,25 +13265,26 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129366859</v>
+        <v>129366881</v>
       </c>
       <c r="B127" t="n">
         <v>79041</v>
@@ -13326,10 +13322,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>430595</v>
+        <v>430697</v>
       </c>
       <c r="R127" t="n">
-        <v>6795774</v>
+        <v>6795563</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13389,7 +13385,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129357159</v>
+        <v>129365283</v>
       </c>
       <c r="B128" t="n">
         <v>79041</v>
@@ -13424,10 +13420,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>430603</v>
+        <v>430793</v>
       </c>
       <c r="R128" t="n">
-        <v>6795771</v>
+        <v>6795485</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13474,22 +13470,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129357145</v>
+        <v>129366859</v>
       </c>
       <c r="B129" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13497,37 +13493,40 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>430763</v>
+        <v>430595</v>
       </c>
       <c r="R129" t="n">
-        <v>6795787</v>
+        <v>6795774</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13565,18 +13564,19 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351748</v>
+        <v>129351737</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>430805</v>
+        <v>430757</v>
       </c>
       <c r="R21" t="n">
-        <v>6795787</v>
+        <v>6795789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351762</v>
+        <v>129351748</v>
       </c>
       <c r="B22" t="n">
         <v>79041</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430595</v>
+        <v>430805</v>
       </c>
       <c r="R22" t="n">
-        <v>6795796</v>
+        <v>6795787</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351751</v>
+        <v>129351762</v>
       </c>
       <c r="B23" t="n">
         <v>79041</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430718</v>
+        <v>430595</v>
       </c>
       <c r="R23" t="n">
-        <v>6795804</v>
+        <v>6795796</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129351737</v>
+        <v>129351751</v>
       </c>
       <c r="B24" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430757</v>
+        <v>430718</v>
       </c>
       <c r="R24" t="n">
-        <v>6795789</v>
+        <v>6795804</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4428,10 +4428,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129357161</v>
+        <v>129366831</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4439,37 +4439,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>430629</v>
+        <v>430798</v>
       </c>
       <c r="R37" t="n">
-        <v>6795747</v>
+        <v>6795760</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4513,19 +4513,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129366831</v>
+        <v>129366830</v>
       </c>
       <c r="B38" t="n">
         <v>78798</v>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>430798</v>
+        <v>430794</v>
       </c>
       <c r="R38" t="n">
-        <v>6795760</v>
+        <v>6795786</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4622,7 +4622,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129366886</v>
+        <v>129366857</v>
       </c>
       <c r="B39" t="n">
         <v>79041</v>
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>430675</v>
+        <v>430616</v>
       </c>
       <c r="R39" t="n">
-        <v>6795479</v>
+        <v>6795790</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4723,10 +4723,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129366830</v>
+        <v>129357161</v>
       </c>
       <c r="B40" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4734,37 +4734,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>430794</v>
+        <v>430629</v>
       </c>
       <c r="R40" t="n">
-        <v>6795786</v>
+        <v>6795747</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4808,12 +4808,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5115,7 +5115,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129366846</v>
+        <v>129366886</v>
       </c>
       <c r="B44" t="n">
         <v>79041</v>
@@ -5144,16 +5144,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>430812</v>
+        <v>430675</v>
       </c>
       <c r="R44" t="n">
-        <v>6795708</v>
+        <v>6795479</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5194,6 +5197,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5205,14 +5209,14 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129366877</v>
+        <v>129366846</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5241,19 +5245,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>430703</v>
+        <v>430812</v>
       </c>
       <c r="R45" t="n">
-        <v>6795594</v>
+        <v>6795708</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5294,7 +5295,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5306,14 +5306,14 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129365285</v>
+        <v>129366877</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5342,19 +5342,22 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>430830</v>
+        <v>430703</v>
       </c>
       <c r="R46" t="n">
-        <v>6795490</v>
+        <v>6795594</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5392,25 +5395,26 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129366857</v>
+        <v>129365285</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5439,22 +5443,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>430616</v>
+        <v>430830</v>
       </c>
       <c r="R47" t="n">
-        <v>6795790</v>
+        <v>6795490</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5492,26 +5493,25 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129366884</v>
+        <v>129366863</v>
       </c>
       <c r="B48" t="n">
         <v>79041</v>
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>430687</v>
+        <v>430653</v>
       </c>
       <c r="R48" t="n">
-        <v>6795504</v>
+        <v>6795695</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5612,7 +5612,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129365284</v>
+        <v>129366884</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5641,19 +5641,22 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>430819</v>
+        <v>430687</v>
       </c>
       <c r="R49" t="n">
-        <v>6795467</v>
+        <v>6795504</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5691,25 +5694,26 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129357147</v>
+        <v>129365284</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5744,10 +5748,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>430860</v>
+        <v>430819</v>
       </c>
       <c r="R50" t="n">
-        <v>6795577</v>
+        <v>6795467</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5794,19 +5798,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129366873</v>
+        <v>129357147</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5835,22 +5839,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>430712</v>
+        <v>430860</v>
       </c>
       <c r="R51" t="n">
-        <v>6795594</v>
+        <v>6795577</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5888,26 +5889,25 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129366863</v>
+        <v>129366873</v>
       </c>
       <c r="B52" t="n">
         <v>79041</v>
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>430653</v>
+        <v>430712</v>
       </c>
       <c r="R52" t="n">
-        <v>6795695</v>
+        <v>6795594</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6501,7 +6501,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129365281</v>
+        <v>129357164</v>
       </c>
       <c r="B58" t="n">
         <v>79041</v>
@@ -6536,10 +6536,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>430773</v>
+        <v>430692</v>
       </c>
       <c r="R58" t="n">
-        <v>6795492</v>
+        <v>6795567</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6586,19 +6586,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129357164</v>
+        <v>129365281</v>
       </c>
       <c r="B59" t="n">
         <v>79041</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>430692</v>
+        <v>430773</v>
       </c>
       <c r="R59" t="n">
-        <v>6795567</v>
+        <v>6795492</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6683,12 +6683,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6792,7 +6792,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129365278</v>
+        <v>129357151</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -6827,10 +6827,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>430695</v>
+        <v>430783</v>
       </c>
       <c r="R61" t="n">
-        <v>6795429</v>
+        <v>6795740</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6877,19 +6877,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129366866</v>
+        <v>129357155</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -6918,22 +6918,19 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>430658</v>
+        <v>430682</v>
       </c>
       <c r="R62" t="n">
-        <v>6795716</v>
+        <v>6795752</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6971,26 +6968,25 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129366856</v>
+        <v>129365278</v>
       </c>
       <c r="B63" t="n">
         <v>79041</v>
@@ -7019,22 +7015,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>430745</v>
+        <v>430695</v>
       </c>
       <c r="R63" t="n">
-        <v>6795798</v>
+        <v>6795429</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7072,26 +7065,25 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129357151</v>
+        <v>129357150</v>
       </c>
       <c r="B64" t="n">
         <v>79041</v>
@@ -7126,10 +7118,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>430783</v>
+        <v>430883</v>
       </c>
       <c r="R64" t="n">
-        <v>6795740</v>
+        <v>6795535</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7188,7 +7180,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129357155</v>
+        <v>129366866</v>
       </c>
       <c r="B65" t="n">
         <v>79041</v>
@@ -7217,19 +7209,22 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>430682</v>
+        <v>430658</v>
       </c>
       <c r="R65" t="n">
-        <v>6795752</v>
+        <v>6795716</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7267,25 +7262,26 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129357150</v>
+        <v>129366883</v>
       </c>
       <c r="B66" t="n">
         <v>79041</v>
@@ -7314,19 +7310,22 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430883</v>
+        <v>430687</v>
       </c>
       <c r="R66" t="n">
         <v>6795535</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7364,25 +7363,26 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129366883</v>
+        <v>129366856</v>
       </c>
       <c r="B67" t="n">
         <v>79041</v>
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>430687</v>
+        <v>430745</v>
       </c>
       <c r="R67" t="n">
-        <v>6795535</v>
+        <v>6795798</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7875,7 +7875,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129366852</v>
+        <v>129366837</v>
       </c>
       <c r="B72" t="n">
         <v>79041</v>
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>430782</v>
+        <v>430718</v>
       </c>
       <c r="R72" t="n">
-        <v>6795779</v>
+        <v>6795419</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7972,7 +7972,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129366837</v>
+        <v>129366852</v>
       </c>
       <c r="B73" t="n">
         <v>79041</v>
@@ -8007,10 +8007,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>430718</v>
+        <v>430782</v>
       </c>
       <c r="R73" t="n">
-        <v>6795419</v>
+        <v>6795779</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8069,10 +8069,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129365291</v>
+        <v>129366838</v>
       </c>
       <c r="B74" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8080,37 +8080,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>430668</v>
+        <v>430741</v>
       </c>
       <c r="R74" t="n">
-        <v>6795504</v>
+        <v>6795432</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8154,19 +8154,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129365286</v>
+        <v>129366849</v>
       </c>
       <c r="B75" t="n">
         <v>79041</v>
@@ -8197,17 +8197,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>430758</v>
+        <v>430801</v>
       </c>
       <c r="R75" t="n">
-        <v>6795794</v>
+        <v>6795776</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8251,12 +8251,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8364,10 +8364,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129365290</v>
+        <v>129365291</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8375,21 +8375,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8399,10 +8399,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>430688</v>
+        <v>430668</v>
       </c>
       <c r="R77" t="n">
-        <v>6795513</v>
+        <v>6795504</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8461,7 +8461,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129366838</v>
+        <v>129365286</v>
       </c>
       <c r="B78" t="n">
         <v>79041</v>
@@ -8492,17 +8492,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>430741</v>
+        <v>430758</v>
       </c>
       <c r="R78" t="n">
-        <v>6795432</v>
+        <v>6795794</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8546,19 +8546,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129366849</v>
+        <v>129365290</v>
       </c>
       <c r="B79" t="n">
         <v>79041</v>
@@ -8589,17 +8589,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>430801</v>
+        <v>430688</v>
       </c>
       <c r="R79" t="n">
-        <v>6795776</v>
+        <v>6795513</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8643,19 +8643,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129357158</v>
+        <v>129366868</v>
       </c>
       <c r="B80" t="n">
         <v>79041</v>
@@ -8684,19 +8684,22 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>430587</v>
+        <v>430681</v>
       </c>
       <c r="R80" t="n">
-        <v>6795787</v>
+        <v>6795699</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8734,25 +8737,26 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129366868</v>
+        <v>129366848</v>
       </c>
       <c r="B81" t="n">
         <v>79041</v>
@@ -8781,19 +8785,16 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>430681</v>
+        <v>430801</v>
       </c>
       <c r="R81" t="n">
-        <v>6795699</v>
+        <v>6795771</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8834,7 +8835,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8846,17 +8846,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129366848</v>
+        <v>129357146</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8864,37 +8864,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>430801</v>
+        <v>430723</v>
       </c>
       <c r="R82" t="n">
-        <v>6795771</v>
+        <v>6795733</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8938,22 +8938,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129357146</v>
+        <v>129357158</v>
       </c>
       <c r="B83" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8961,21 +8961,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8985,10 +8985,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>430723</v>
+        <v>430587</v>
       </c>
       <c r="R83" t="n">
-        <v>6795733</v>
+        <v>6795787</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9047,7 +9047,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129366870</v>
+        <v>129366887</v>
       </c>
       <c r="B84" t="n">
         <v>79041</v>
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>430685</v>
+        <v>430677</v>
       </c>
       <c r="R84" t="n">
-        <v>6795636</v>
+        <v>6795456</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9148,7 +9148,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129366847</v>
+        <v>129366870</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -9177,16 +9177,19 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>430798</v>
+        <v>430685</v>
       </c>
       <c r="R85" t="n">
-        <v>6795788</v>
+        <v>6795636</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9227,6 +9230,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9238,14 +9242,14 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129366887</v>
+        <v>129366847</v>
       </c>
       <c r="B86" t="n">
         <v>79041</v>
@@ -9274,19 +9278,16 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>430677</v>
+        <v>430798</v>
       </c>
       <c r="R86" t="n">
-        <v>6795456</v>
+        <v>6795788</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9327,7 +9328,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9443,7 +9443,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129366855</v>
+        <v>129357156</v>
       </c>
       <c r="B88" t="n">
         <v>79041</v>
@@ -9472,22 +9472,19 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>430747</v>
+        <v>430678</v>
       </c>
       <c r="R88" t="n">
-        <v>6795794</v>
+        <v>6795768</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9525,26 +9522,25 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129357156</v>
+        <v>129366855</v>
       </c>
       <c r="B89" t="n">
         <v>79041</v>
@@ -9573,19 +9569,22 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>430678</v>
+        <v>430747</v>
       </c>
       <c r="R89" t="n">
-        <v>6795768</v>
+        <v>6795794</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9623,18 +9622,19 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9932,10 +9932,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129365277</v>
+        <v>129366865</v>
       </c>
       <c r="B93" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9943,37 +9943,40 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>430671</v>
+        <v>430656</v>
       </c>
       <c r="R93" t="n">
-        <v>6795716</v>
+        <v>6795713</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10011,25 +10014,26 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129366879</v>
+        <v>129366843</v>
       </c>
       <c r="B94" t="n">
         <v>79041</v>
@@ -10058,19 +10062,16 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>430705</v>
+        <v>430875</v>
       </c>
       <c r="R94" t="n">
-        <v>6795565</v>
+        <v>6795544</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10111,7 +10112,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10123,14 +10123,14 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129366865</v>
+        <v>129366879</v>
       </c>
       <c r="B95" t="n">
         <v>79041</v>
@@ -10168,10 +10168,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>430656</v>
+        <v>430705</v>
       </c>
       <c r="R95" t="n">
-        <v>6795713</v>
+        <v>6795565</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10231,10 +10231,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129366843</v>
+        <v>129365277</v>
       </c>
       <c r="B96" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10242,37 +10242,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>430875</v>
+        <v>430671</v>
       </c>
       <c r="R96" t="n">
-        <v>6795544</v>
+        <v>6795716</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10316,19 +10316,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129365282</v>
+        <v>129357165</v>
       </c>
       <c r="B97" t="n">
         <v>79041</v>
@@ -10363,10 +10363,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>430792</v>
+        <v>430697</v>
       </c>
       <c r="R97" t="n">
-        <v>6795496</v>
+        <v>6795560</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10413,19 +10413,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129365289</v>
+        <v>129365282</v>
       </c>
       <c r="B98" t="n">
         <v>79041</v>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>430687</v>
+        <v>430792</v>
       </c>
       <c r="R98" t="n">
-        <v>6795502</v>
+        <v>6795496</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10522,7 +10522,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129366835</v>
+        <v>129365289</v>
       </c>
       <c r="B99" t="n">
         <v>79041</v>
@@ -10553,17 +10553,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>430696</v>
+        <v>430687</v>
       </c>
       <c r="R99" t="n">
-        <v>6795393</v>
+        <v>6795502</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10607,19 +10607,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129357165</v>
+        <v>129366835</v>
       </c>
       <c r="B100" t="n">
         <v>79041</v>
@@ -10650,17 +10650,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>430697</v>
+        <v>430696</v>
       </c>
       <c r="R100" t="n">
-        <v>6795560</v>
+        <v>6795393</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10704,12 +10704,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10813,7 +10813,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129366850</v>
+        <v>129366861</v>
       </c>
       <c r="B102" t="n">
         <v>79041</v>
@@ -10842,16 +10842,19 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>430795</v>
+        <v>430639</v>
       </c>
       <c r="R102" t="n">
-        <v>6795788</v>
+        <v>6795711</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -10892,6 +10895,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10903,14 +10907,14 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129366861</v>
+        <v>129357154</v>
       </c>
       <c r="B103" t="n">
         <v>79041</v>
@@ -10939,22 +10943,19 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>430639</v>
+        <v>430735</v>
       </c>
       <c r="R103" t="n">
-        <v>6795711</v>
+        <v>6795766</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10992,19 +10993,18 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11112,7 +11112,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129366878</v>
+        <v>129366850</v>
       </c>
       <c r="B105" t="n">
         <v>79041</v>
@@ -11141,19 +11141,16 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>430709</v>
+        <v>430795</v>
       </c>
       <c r="R105" t="n">
-        <v>6795590</v>
+        <v>6795788</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11194,7 +11191,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11206,14 +11202,14 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129357154</v>
+        <v>129366878</v>
       </c>
       <c r="B106" t="n">
         <v>79041</v>
@@ -11242,19 +11238,22 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>430735</v>
+        <v>430709</v>
       </c>
       <c r="R106" t="n">
-        <v>6795766</v>
+        <v>6795590</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11292,18 +11291,19 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129366885</v>
+        <v>129366840</v>
       </c>
       <c r="B110" t="n">
         <v>79041</v>
@@ -11630,19 +11630,16 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>430679</v>
+        <v>430748</v>
       </c>
       <c r="R110" t="n">
-        <v>6795496</v>
+        <v>6795446</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11683,7 +11680,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11695,14 +11691,14 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129366840</v>
+        <v>129366885</v>
       </c>
       <c r="B111" t="n">
         <v>79041</v>
@@ -11731,16 +11727,19 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>430748</v>
+        <v>430679</v>
       </c>
       <c r="R111" t="n">
-        <v>6795446</v>
+        <v>6795496</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11781,6 +11780,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11792,55 +11792,59 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129357160</v>
+        <v>129366828</v>
       </c>
       <c r="B112" t="n">
-        <v>79041</v>
+        <v>97577</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>430620</v>
+        <v>430615</v>
       </c>
       <c r="R112" t="n">
-        <v>6795743</v>
+        <v>6795799</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11872,31 +11876,37 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Blöt, översilad mark, örtrik.</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129357153</v>
+        <v>129357160</v>
       </c>
       <c r="B113" t="n">
         <v>79041</v>
@@ -11931,10 +11941,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>430756</v>
+        <v>430620</v>
       </c>
       <c r="R113" t="n">
-        <v>6795808</v>
+        <v>6795743</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11993,52 +12003,48 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129366828</v>
+        <v>129357153</v>
       </c>
       <c r="B114" t="n">
-        <v>97576</v>
+        <v>79041</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>430615</v>
+        <v>430756</v>
       </c>
       <c r="R114" t="n">
-        <v>6795799</v>
+        <v>6795808</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12070,30 +12076,24 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Blöt, översilad mark, örtrik.</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12294,7 +12294,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129366862</v>
+        <v>129357166</v>
       </c>
       <c r="B117" t="n">
         <v>79041</v>
@@ -12323,22 +12323,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>430645</v>
+        <v>430683</v>
       </c>
       <c r="R117" t="n">
-        <v>6795703</v>
+        <v>6795520</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12376,19 +12373,18 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12492,7 +12488,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129357166</v>
+        <v>129366862</v>
       </c>
       <c r="B119" t="n">
         <v>79041</v>
@@ -12521,19 +12517,22 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>430683</v>
+        <v>430645</v>
       </c>
       <c r="R119" t="n">
-        <v>6795520</v>
+        <v>6795703</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12571,25 +12570,26 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129366867</v>
+        <v>129366842</v>
       </c>
       <c r="B120" t="n">
         <v>79041</v>
@@ -12618,19 +12618,16 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>430653</v>
+        <v>430787</v>
       </c>
       <c r="R120" t="n">
-        <v>6795711</v>
+        <v>6795507</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12671,7 +12668,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12683,14 +12679,14 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129366875</v>
+        <v>129366880</v>
       </c>
       <c r="B121" t="n">
         <v>79041</v>
@@ -12728,10 +12724,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>430714</v>
+        <v>430701</v>
       </c>
       <c r="R121" t="n">
-        <v>6795602</v>
+        <v>6795567</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -12791,7 +12787,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129366842</v>
+        <v>129366867</v>
       </c>
       <c r="B122" t="n">
         <v>79041</v>
@@ -12820,16 +12816,19 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>430787</v>
+        <v>430653</v>
       </c>
       <c r="R122" t="n">
-        <v>6795507</v>
+        <v>6795711</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -12870,6 +12869,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12881,14 +12881,14 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129366880</v>
+        <v>129366875</v>
       </c>
       <c r="B123" t="n">
         <v>79041</v>
@@ -12926,10 +12926,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>430701</v>
+        <v>430714</v>
       </c>
       <c r="R123" t="n">
-        <v>6795567</v>
+        <v>6795602</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -12989,7 +12989,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129357159</v>
+        <v>129366881</v>
       </c>
       <c r="B124" t="n">
         <v>79041</v>
@@ -13018,19 +13018,22 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>430603</v>
+        <v>430697</v>
       </c>
       <c r="R124" t="n">
-        <v>6795771</v>
+        <v>6795563</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13068,28 +13071,29 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129357145</v>
+        <v>129365283</v>
       </c>
       <c r="B125" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13097,21 +13101,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13121,10 +13125,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>430763</v>
+        <v>430793</v>
       </c>
       <c r="R125" t="n">
-        <v>6795787</v>
+        <v>6795485</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13171,19 +13175,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129366864</v>
+        <v>129366859</v>
       </c>
       <c r="B126" t="n">
         <v>79041</v>
@@ -13221,10 +13225,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>430653</v>
+        <v>430595</v>
       </c>
       <c r="R126" t="n">
-        <v>6795703</v>
+        <v>6795774</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13284,7 +13288,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129366881</v>
+        <v>129357159</v>
       </c>
       <c r="B127" t="n">
         <v>79041</v>
@@ -13313,22 +13317,19 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>430697</v>
+        <v>430603</v>
       </c>
       <c r="R127" t="n">
-        <v>6795563</v>
+        <v>6795771</v>
       </c>
       <c r="S127" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13366,26 +13367,25 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129365283</v>
+        <v>129366864</v>
       </c>
       <c r="B128" t="n">
         <v>79041</v>
@@ -13414,19 +13414,22 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>430793</v>
+        <v>430653</v>
       </c>
       <c r="R128" t="n">
-        <v>6795485</v>
+        <v>6795703</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13464,28 +13467,29 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129366859</v>
+        <v>129357145</v>
       </c>
       <c r="B129" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13493,40 +13497,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>430595</v>
+        <v>430763</v>
       </c>
       <c r="R129" t="n">
-        <v>6795774</v>
+        <v>6795787</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13564,19 +13565,18 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351772</v>
       </c>
       <c r="B2" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129351746</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129351765</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129351740</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129351767</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129351742</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129351754</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129351770</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129351758</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129351760</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129351759</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129351747</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129351744</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>129351763</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129351755</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>129351764</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129351734</v>
       </c>
       <c r="B18" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129351761</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>129351757</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351737</v>
+        <v>129351748</v>
       </c>
       <c r="B21" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>430757</v>
+        <v>430805</v>
       </c>
       <c r="R21" t="n">
-        <v>6795789</v>
+        <v>6795787</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351748</v>
+        <v>129351762</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430805</v>
+        <v>430595</v>
       </c>
       <c r="R22" t="n">
-        <v>6795787</v>
+        <v>6795796</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351762</v>
+        <v>129351751</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430595</v>
+        <v>430718</v>
       </c>
       <c r="R23" t="n">
-        <v>6795796</v>
+        <v>6795804</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129351751</v>
+        <v>129351737</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430718</v>
+        <v>430757</v>
       </c>
       <c r="R24" t="n">
-        <v>6795804</v>
+        <v>6795789</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,7 +3139,7 @@
         <v>129351752</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>129351769</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>129351750</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>129351741</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>129351753</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351735</v>
+        <v>129351771</v>
       </c>
       <c r="B30" t="n">
-        <v>91561</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,41 +3682,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Norr om Storbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>430608</v>
+        <v>430674</v>
       </c>
       <c r="R30" t="n">
-        <v>6795766</v>
+        <v>6795553</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3758,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3767,7 +3760,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3786,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351771</v>
+        <v>129351745</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3821,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>430674</v>
+        <v>430824</v>
       </c>
       <c r="R31" t="n">
-        <v>6795553</v>
+        <v>6795635</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3866,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3893,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351745</v>
+        <v>129351735</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>91564</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3904,34 +3896,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norr om Storbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>430824</v>
+        <v>430608</v>
       </c>
       <c r="R32" t="n">
-        <v>6795635</v>
+        <v>6795766</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3963,7 +3962,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3973,7 +3972,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3982,6 +3981,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>129351766</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>129351749</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>129351743</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>129351768</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4428,10 +4428,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129366831</v>
+        <v>129357161</v>
       </c>
       <c r="B37" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4439,37 +4439,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>430798</v>
+        <v>430629</v>
       </c>
       <c r="R37" t="n">
-        <v>6795760</v>
+        <v>6795747</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4513,22 +4513,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129366830</v>
+        <v>129366846</v>
       </c>
       <c r="B38" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>430794</v>
+        <v>430812</v>
       </c>
       <c r="R38" t="n">
-        <v>6795786</v>
+        <v>6795708</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129366857</v>
+        <v>129365285</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,22 +4651,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>430616</v>
+        <v>430830</v>
       </c>
       <c r="R39" t="n">
-        <v>6795790</v>
+        <v>6795490</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4704,29 +4701,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129357161</v>
+        <v>129365279</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4758,10 +4754,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>430629</v>
+        <v>430739</v>
       </c>
       <c r="R40" t="n">
-        <v>6795747</v>
+        <v>6795491</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4808,22 +4804,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129365279</v>
+        <v>129366831</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4831,37 +4827,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>430739</v>
+        <v>430798</v>
       </c>
       <c r="R41" t="n">
-        <v>6795491</v>
+        <v>6795760</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4905,12 +4901,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4920,7 +4916,7 @@
         <v>129366858</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5021,7 +5017,7 @@
         <v>129365287</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,7 +5114,7 @@
         <v>129366886</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5216,10 +5212,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129366846</v>
+        <v>129366877</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5245,16 +5241,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>430812</v>
+        <v>430703</v>
       </c>
       <c r="R45" t="n">
-        <v>6795708</v>
+        <v>6795594</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5295,6 +5294,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5306,17 +5306,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129366877</v>
+        <v>129366830</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5324,37 +5324,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>430703</v>
+        <v>430794</v>
       </c>
       <c r="R46" t="n">
-        <v>6795594</v>
+        <v>6795786</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5395,7 +5392,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5407,17 +5403,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129365285</v>
+        <v>129366857</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5443,19 +5439,22 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>430830</v>
+        <v>430616</v>
       </c>
       <c r="R47" t="n">
-        <v>6795490</v>
+        <v>6795790</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5493,28 +5492,29 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129366863</v>
+        <v>129365284</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5540,22 +5540,19 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>430653</v>
+        <v>430819</v>
       </c>
       <c r="R48" t="n">
-        <v>6795695</v>
+        <v>6795467</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5593,29 +5590,28 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129366884</v>
+        <v>129357147</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5641,22 +5637,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>430687</v>
+        <v>430860</v>
       </c>
       <c r="R49" t="n">
-        <v>6795504</v>
+        <v>6795577</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5694,29 +5687,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129365284</v>
+        <v>129366863</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5742,19 +5734,22 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>430819</v>
+        <v>430653</v>
       </c>
       <c r="R50" t="n">
-        <v>6795467</v>
+        <v>6795695</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5792,28 +5787,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129357147</v>
+        <v>129366884</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5839,19 +5835,22 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>430860</v>
+        <v>430687</v>
       </c>
       <c r="R51" t="n">
-        <v>6795577</v>
+        <v>6795504</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5889,18 +5888,19 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5910,7 +5910,7 @@
         <v>129366873</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>129366871</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>129366841</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>129357149</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>129366860</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6404,10 +6404,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129366845</v>
+        <v>129357164</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6435,17 +6435,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>430816</v>
+        <v>430692</v>
       </c>
       <c r="R57" t="n">
-        <v>6795679</v>
+        <v>6795567</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6489,22 +6489,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129357164</v>
+        <v>129365281</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6536,10 +6536,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>430692</v>
+        <v>430773</v>
       </c>
       <c r="R58" t="n">
-        <v>6795567</v>
+        <v>6795492</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6586,22 +6586,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129365281</v>
+        <v>129366845</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6629,17 +6629,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>430773</v>
+        <v>430816</v>
       </c>
       <c r="R59" t="n">
-        <v>6795492</v>
+        <v>6795679</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6683,22 +6683,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129365288</v>
+        <v>129365278</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6730,10 +6730,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>430681</v>
+        <v>430695</v>
       </c>
       <c r="R60" t="n">
-        <v>6795704</v>
+        <v>6795429</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6792,10 +6792,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129357151</v>
+        <v>129366856</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6821,19 +6821,22 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>430783</v>
+        <v>430745</v>
       </c>
       <c r="R61" t="n">
-        <v>6795740</v>
+        <v>6795798</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6871,28 +6874,29 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129357155</v>
+        <v>129366853</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6920,17 +6924,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>430682</v>
+        <v>430777</v>
       </c>
       <c r="R62" t="n">
-        <v>6795752</v>
+        <v>6795779</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6974,22 +6978,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129365278</v>
+        <v>129365288</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7021,10 +7025,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>430695</v>
+        <v>430681</v>
       </c>
       <c r="R63" t="n">
-        <v>6795429</v>
+        <v>6795704</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7083,10 +7087,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129357150</v>
+        <v>129357151</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7118,10 +7122,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>430883</v>
+        <v>430783</v>
       </c>
       <c r="R64" t="n">
-        <v>6795535</v>
+        <v>6795740</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7180,10 +7184,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129366866</v>
+        <v>129357155</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7209,22 +7213,19 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>430658</v>
+        <v>430682</v>
       </c>
       <c r="R65" t="n">
-        <v>6795716</v>
+        <v>6795752</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7262,29 +7263,28 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129366883</v>
+        <v>129357150</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7310,22 +7310,19 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430687</v>
+        <v>430883</v>
       </c>
       <c r="R66" t="n">
         <v>6795535</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7363,29 +7360,28 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129366856</v>
+        <v>129366866</v>
       </c>
       <c r="B67" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7420,10 +7416,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>430745</v>
+        <v>430658</v>
       </c>
       <c r="R67" t="n">
-        <v>6795798</v>
+        <v>6795716</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7483,10 +7479,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129366853</v>
+        <v>129366883</v>
       </c>
       <c r="B68" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7512,16 +7508,19 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>430777</v>
+        <v>430687</v>
       </c>
       <c r="R68" t="n">
-        <v>6795779</v>
+        <v>6795535</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7562,6 +7561,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7583,7 +7583,7 @@
         <v>129366882</v>
       </c>
       <c r="B69" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>129357163</v>
       </c>
       <c r="B70" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>129357167</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7875,10 +7875,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129366837</v>
+        <v>129366852</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>430718</v>
+        <v>430782</v>
       </c>
       <c r="R72" t="n">
-        <v>6795419</v>
+        <v>6795779</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7972,10 +7972,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129366852</v>
+        <v>129366837</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8007,10 +8007,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>430782</v>
+        <v>430718</v>
       </c>
       <c r="R73" t="n">
-        <v>6795779</v>
+        <v>6795419</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8069,10 +8069,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129366838</v>
+        <v>129365291</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>78709</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8080,37 +8080,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>430741</v>
+        <v>430668</v>
       </c>
       <c r="R74" t="n">
-        <v>6795432</v>
+        <v>6795504</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8154,22 +8154,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129366849</v>
+        <v>129365286</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8197,17 +8197,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>430801</v>
+        <v>430758</v>
       </c>
       <c r="R75" t="n">
-        <v>6795776</v>
+        <v>6795794</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8251,12 +8251,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8266,7 +8266,7 @@
         <v>129366872</v>
       </c>
       <c r="B76" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8364,10 +8364,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129365291</v>
+        <v>129366838</v>
       </c>
       <c r="B77" t="n">
-        <v>78707</v>
+        <v>79043</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8375,37 +8375,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>430668</v>
+        <v>430741</v>
       </c>
       <c r="R77" t="n">
-        <v>6795504</v>
+        <v>6795432</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8449,22 +8449,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129365286</v>
+        <v>129366849</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8492,17 +8492,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>430758</v>
+        <v>430801</v>
       </c>
       <c r="R78" t="n">
-        <v>6795794</v>
+        <v>6795776</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8546,12 +8546,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8561,7 +8561,7 @@
         <v>129365290</v>
       </c>
       <c r="B79" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>129366868</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8756,10 +8756,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129366848</v>
+        <v>129357146</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8767,37 +8767,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>430801</v>
+        <v>430723</v>
       </c>
       <c r="R81" t="n">
-        <v>6795771</v>
+        <v>6795733</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8841,22 +8841,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129357146</v>
+        <v>129357158</v>
       </c>
       <c r="B82" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8864,21 +8864,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8888,10 +8888,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>430723</v>
+        <v>430587</v>
       </c>
       <c r="R82" t="n">
-        <v>6795733</v>
+        <v>6795787</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8950,10 +8950,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129357158</v>
+        <v>129366848</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8981,17 +8981,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>430587</v>
+        <v>430801</v>
       </c>
       <c r="R83" t="n">
-        <v>6795787</v>
+        <v>6795771</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9035,22 +9035,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129366887</v>
+        <v>129366847</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9076,19 +9076,16 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>430677</v>
+        <v>430798</v>
       </c>
       <c r="R84" t="n">
-        <v>6795456</v>
+        <v>6795788</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9129,7 +9126,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9141,7 +9137,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9151,7 +9147,7 @@
         <v>129366870</v>
       </c>
       <c r="B85" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9249,10 +9245,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129366847</v>
+        <v>129366887</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9278,16 +9274,19 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>430798</v>
+        <v>430677</v>
       </c>
       <c r="R86" t="n">
-        <v>6795788</v>
+        <v>6795456</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9328,6 +9327,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9339,17 +9339,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129366844</v>
+        <v>129357156</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9377,17 +9377,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>430858</v>
+        <v>430678</v>
       </c>
       <c r="R87" t="n">
-        <v>6795532</v>
+        <v>6795768</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9431,22 +9431,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129357156</v>
+        <v>129366844</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9474,17 +9474,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>430678</v>
+        <v>430858</v>
       </c>
       <c r="R88" t="n">
-        <v>6795768</v>
+        <v>6795532</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9528,12 +9528,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9543,7 +9543,7 @@
         <v>129366855</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>129357157</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>129357152</v>
       </c>
       <c r="B91" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>129357148</v>
       </c>
       <c r="B92" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9932,10 +9932,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129366865</v>
+        <v>129366879</v>
       </c>
       <c r="B93" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>430656</v>
+        <v>430705</v>
       </c>
       <c r="R93" t="n">
-        <v>6795713</v>
+        <v>6795565</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10033,10 +10033,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129366843</v>
+        <v>129366865</v>
       </c>
       <c r="B94" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10062,16 +10062,19 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>430875</v>
+        <v>430656</v>
       </c>
       <c r="R94" t="n">
-        <v>6795544</v>
+        <v>6795713</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10112,6 +10115,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10123,17 +10127,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129366879</v>
+        <v>129365277</v>
       </c>
       <c r="B95" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10141,40 +10145,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>430705</v>
+        <v>430671</v>
       </c>
       <c r="R95" t="n">
-        <v>6795565</v>
+        <v>6795716</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10212,29 +10213,28 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129365277</v>
+        <v>129366843</v>
       </c>
       <c r="B96" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10242,37 +10242,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>430671</v>
+        <v>430875</v>
       </c>
       <c r="R96" t="n">
-        <v>6795716</v>
+        <v>6795544</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10316,22 +10316,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129357165</v>
+        <v>129365289</v>
       </c>
       <c r="B97" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10363,10 +10363,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>430697</v>
+        <v>430687</v>
       </c>
       <c r="R97" t="n">
-        <v>6795560</v>
+        <v>6795502</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10413,22 +10413,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129365282</v>
+        <v>129357165</v>
       </c>
       <c r="B98" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>430792</v>
+        <v>430697</v>
       </c>
       <c r="R98" t="n">
-        <v>6795496</v>
+        <v>6795560</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10510,22 +10510,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129365289</v>
+        <v>129365282</v>
       </c>
       <c r="B99" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10557,10 +10557,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>430687</v>
+        <v>430792</v>
       </c>
       <c r="R99" t="n">
-        <v>6795502</v>
+        <v>6795496</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10619,10 +10619,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129366835</v>
+        <v>129365276</v>
       </c>
       <c r="B100" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10630,37 +10630,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>430696</v>
+        <v>430818</v>
       </c>
       <c r="R100" t="n">
-        <v>6795393</v>
+        <v>6795676</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10704,22 +10704,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129365276</v>
+        <v>129366835</v>
       </c>
       <c r="B101" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10727,37 +10727,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>430818</v>
+        <v>430696</v>
       </c>
       <c r="R101" t="n">
-        <v>6795676</v>
+        <v>6795393</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10801,22 +10801,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129366861</v>
+        <v>129357154</v>
       </c>
       <c r="B102" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10842,22 +10842,19 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>430639</v>
+        <v>430735</v>
       </c>
       <c r="R102" t="n">
-        <v>6795711</v>
+        <v>6795766</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10895,29 +10892,28 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129357154</v>
+        <v>129366874</v>
       </c>
       <c r="B103" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10943,19 +10939,22 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>430735</v>
+        <v>430713</v>
       </c>
       <c r="R103" t="n">
-        <v>6795766</v>
+        <v>6795598</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10993,28 +10992,29 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129366874</v>
+        <v>129366850</v>
       </c>
       <c r="B104" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11040,19 +11040,16 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>430713</v>
+        <v>430795</v>
       </c>
       <c r="R104" t="n">
-        <v>6795598</v>
+        <v>6795788</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11093,7 +11090,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11105,17 +11101,17 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129366850</v>
+        <v>129366861</v>
       </c>
       <c r="B105" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11141,16 +11137,19 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>430795</v>
+        <v>430639</v>
       </c>
       <c r="R105" t="n">
-        <v>6795788</v>
+        <v>6795711</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11191,6 +11190,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11212,7 +11212,7 @@
         <v>129366878</v>
       </c>
       <c r="B106" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>129366832</v>
       </c>
       <c r="B107" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>129365274</v>
       </c>
       <c r="B108" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>129366833</v>
       </c>
       <c r="B109" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>129366840</v>
       </c>
       <c r="B110" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>129366885</v>
       </c>
       <c r="B111" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11799,52 +11799,48 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129366828</v>
+        <v>129357160</v>
       </c>
       <c r="B112" t="n">
-        <v>97577</v>
+        <v>79043</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>430615</v>
+        <v>430620</v>
       </c>
       <c r="R112" t="n">
-        <v>6795799</v>
+        <v>6795743</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11876,40 +11872,34 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Blöt, översilad mark, örtrik.</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129357160</v>
+        <v>129357153</v>
       </c>
       <c r="B113" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11941,10 +11931,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>430620</v>
+        <v>430756</v>
       </c>
       <c r="R113" t="n">
-        <v>6795743</v>
+        <v>6795808</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12003,48 +11993,52 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129357153</v>
+        <v>129366828</v>
       </c>
       <c r="B114" t="n">
-        <v>79041</v>
+        <v>97581</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>430756</v>
+        <v>430615</v>
       </c>
       <c r="R114" t="n">
-        <v>6795808</v>
+        <v>6795799</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12076,24 +12070,30 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Blöt, översilad mark, örtrik.</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12103,7 +12103,7 @@
         <v>129366854</v>
       </c>
       <c r="B115" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         <v>129365280</v>
       </c>
       <c r="B116" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>129357166</v>
       </c>
       <c r="B117" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>129366836</v>
       </c>
       <c r="B118" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>129366862</v>
       </c>
       <c r="B119" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12589,10 +12589,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129366842</v>
+        <v>129366875</v>
       </c>
       <c r="B120" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12618,16 +12618,19 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>430787</v>
+        <v>430714</v>
       </c>
       <c r="R120" t="n">
-        <v>6795507</v>
+        <v>6795602</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12668,6 +12671,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12679,17 +12683,17 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129366880</v>
+        <v>129366842</v>
       </c>
       <c r="B121" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12715,19 +12719,16 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>430701</v>
+        <v>430787</v>
       </c>
       <c r="R121" t="n">
-        <v>6795567</v>
+        <v>6795507</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -12768,7 +12769,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12780,7 +12780,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -12790,7 +12790,7 @@
         <v>129366867</v>
       </c>
       <c r="B122" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12888,10 +12888,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129366875</v>
+        <v>129366880</v>
       </c>
       <c r="B123" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12926,10 +12926,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>430714</v>
+        <v>430701</v>
       </c>
       <c r="R123" t="n">
-        <v>6795602</v>
+        <v>6795567</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -12992,7 +12992,7 @@
         <v>129366881</v>
       </c>
       <c r="B124" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>129365283</v>
       </c>
       <c r="B125" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13187,10 +13187,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129366859</v>
+        <v>129357145</v>
       </c>
       <c r="B126" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13198,40 +13198,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>430595</v>
+        <v>430763</v>
       </c>
       <c r="R126" t="n">
-        <v>6795774</v>
+        <v>6795787</v>
       </c>
       <c r="S126" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13269,29 +13266,28 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129357159</v>
+        <v>129366864</v>
       </c>
       <c r="B127" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13317,19 +13313,22 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>430603</v>
+        <v>430653</v>
       </c>
       <c r="R127" t="n">
-        <v>6795771</v>
+        <v>6795703</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13367,28 +13366,29 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129366864</v>
+        <v>129366859</v>
       </c>
       <c r="B128" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13423,10 +13423,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>430653</v>
+        <v>430595</v>
       </c>
       <c r="R128" t="n">
-        <v>6795703</v>
+        <v>6795774</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -13486,10 +13486,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129357145</v>
+        <v>129357159</v>
       </c>
       <c r="B129" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13497,21 +13497,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13521,10 +13521,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>430763</v>
+        <v>430603</v>
       </c>
       <c r="R129" t="n">
-        <v>6795787</v>
+        <v>6795771</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>

--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351772</v>
       </c>
       <c r="B2" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351765</v>
+        <v>129351746</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430609</v>
+        <v>430822</v>
       </c>
       <c r="R3" t="n">
-        <v>6795766</v>
+        <v>6795781</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351746</v>
+        <v>129351765</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430822</v>
+        <v>430609</v>
       </c>
       <c r="R4" t="n">
-        <v>6795781</v>
+        <v>6795766</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>129351740</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129351767</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129351742</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129351754</v>
       </c>
       <c r="B8" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129351770</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129351758</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129351760</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129351759</v>
       </c>
       <c r="B12" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129351747</v>
       </c>
       <c r="B13" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129351744</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351755</v>
+        <v>129351763</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430727</v>
+        <v>430600</v>
       </c>
       <c r="R15" t="n">
-        <v>6795462</v>
+        <v>6795776</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129351763</v>
+        <v>129351755</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>430600</v>
+        <v>430727</v>
       </c>
       <c r="R16" t="n">
-        <v>6795776</v>
+        <v>6795462</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,7 +2283,7 @@
         <v>129351764</v>
       </c>
       <c r="B17" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129351734</v>
       </c>
       <c r="B18" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129351761</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>129351757</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>129351748</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351737</v>
+        <v>129351762</v>
       </c>
       <c r="B22" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430757</v>
+        <v>430595</v>
       </c>
       <c r="R22" t="n">
-        <v>6795789</v>
+        <v>6795796</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351762</v>
+        <v>129351751</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430595</v>
+        <v>430718</v>
       </c>
       <c r="R23" t="n">
-        <v>6795796</v>
+        <v>6795804</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129351751</v>
+        <v>129351737</v>
       </c>
       <c r="B24" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430718</v>
+        <v>430757</v>
       </c>
       <c r="R24" t="n">
-        <v>6795804</v>
+        <v>6795789</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,7 +3139,7 @@
         <v>129351752</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>129351769</v>
       </c>
       <c r="B26" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351741</v>
+        <v>129351750</v>
       </c>
       <c r="B27" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430712</v>
+        <v>430759</v>
       </c>
       <c r="R27" t="n">
-        <v>6795444</v>
+        <v>6795799</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129351750</v>
+        <v>129351741</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430759</v>
+        <v>430712</v>
       </c>
       <c r="R28" t="n">
-        <v>6795799</v>
+        <v>6795444</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3567,7 +3567,7 @@
         <v>129351753</v>
       </c>
       <c r="B29" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351771</v>
+        <v>129351735</v>
       </c>
       <c r="B30" t="n">
-        <v>79070</v>
+        <v>91608</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,34 +3682,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Norr om Storbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>430674</v>
+        <v>430608</v>
       </c>
       <c r="R30" t="n">
-        <v>6795553</v>
+        <v>6795766</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3748,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3758,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3760,6 +3767,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3778,10 +3786,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351745</v>
+        <v>129351771</v>
       </c>
       <c r="B31" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3813,10 +3821,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>430824</v>
+        <v>430674</v>
       </c>
       <c r="R31" t="n">
-        <v>6795635</v>
+        <v>6795553</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3856,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3866,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3893,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351735</v>
+        <v>129351745</v>
       </c>
       <c r="B32" t="n">
-        <v>91602</v>
+        <v>79075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,41 +3904,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norr om Storbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>430608</v>
+        <v>430824</v>
       </c>
       <c r="R32" t="n">
-        <v>6795766</v>
+        <v>6795635</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3962,7 +3963,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3972,7 +3973,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3981,7 +3982,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>129351766</v>
       </c>
       <c r="B33" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351743</v>
+        <v>129351749</v>
       </c>
       <c r="B34" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>430768</v>
+        <v>430826</v>
       </c>
       <c r="R34" t="n">
-        <v>6795443</v>
+        <v>6795750</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4214,10 +4214,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129351749</v>
+        <v>129351743</v>
       </c>
       <c r="B35" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>430826</v>
+        <v>430768</v>
       </c>
       <c r="R35" t="n">
-        <v>6795750</v>
+        <v>6795443</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4324,7 +4324,7 @@
         <v>129351768</v>
       </c>
       <c r="B36" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4428,10 +4428,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129365279</v>
+        <v>129357161</v>
       </c>
       <c r="B37" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4463,10 +4463,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>430739</v>
+        <v>430629</v>
       </c>
       <c r="R37" t="n">
-        <v>6795491</v>
+        <v>6795747</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4513,22 +4513,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129366877</v>
+        <v>129365279</v>
       </c>
       <c r="B38" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4554,22 +4554,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>430703</v>
+        <v>430739</v>
       </c>
       <c r="R38" t="n">
-        <v>6795594</v>
+        <v>6795491</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4607,29 +4604,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129365285</v>
+        <v>129366858</v>
       </c>
       <c r="B39" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4655,19 +4651,22 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>430830</v>
+        <v>430593</v>
       </c>
       <c r="R39" t="n">
-        <v>6795490</v>
+        <v>6795779</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4705,28 +4704,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129357161</v>
+        <v>129365287</v>
       </c>
       <c r="B40" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>430629</v>
+        <v>430700</v>
       </c>
       <c r="R40" t="n">
-        <v>6795747</v>
+        <v>6795791</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4808,22 +4808,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129365287</v>
+        <v>129366886</v>
       </c>
       <c r="B41" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,19 +4849,22 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>430700</v>
+        <v>430675</v>
       </c>
       <c r="R41" t="n">
-        <v>6795791</v>
+        <v>6795479</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4899,18 +4902,19 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4920,7 +4924,7 @@
         <v>129366846</v>
       </c>
       <c r="B42" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5007,17 +5011,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129366830</v>
+        <v>129365285</v>
       </c>
       <c r="B43" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5025,37 +5029,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>430794</v>
+        <v>430830</v>
       </c>
       <c r="R43" t="n">
-        <v>6795786</v>
+        <v>6795490</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5099,22 +5103,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129366858</v>
+        <v>129366857</v>
       </c>
       <c r="B44" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5149,10 +5153,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>430593</v>
+        <v>430616</v>
       </c>
       <c r="R44" t="n">
-        <v>6795779</v>
+        <v>6795790</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5205,17 +5209,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129366886</v>
+        <v>129366831</v>
       </c>
       <c r="B45" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5223,37 +5227,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>430675</v>
+        <v>430798</v>
       </c>
       <c r="R45" t="n">
-        <v>6795479</v>
+        <v>6795760</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5294,7 +5295,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5313,10 +5313,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129366857</v>
+        <v>129366877</v>
       </c>
       <c r="B46" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5351,10 +5351,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>430616</v>
+        <v>430703</v>
       </c>
       <c r="R46" t="n">
-        <v>6795790</v>
+        <v>6795594</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5407,17 +5407,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129366831</v>
+        <v>129366830</v>
       </c>
       <c r="B47" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>430798</v>
+        <v>430794</v>
       </c>
       <c r="R47" t="n">
-        <v>6795760</v>
+        <v>6795786</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5504,17 +5504,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129357147</v>
+        <v>129366884</v>
       </c>
       <c r="B48" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5540,19 +5540,22 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>430860</v>
+        <v>430687</v>
       </c>
       <c r="R48" t="n">
-        <v>6795577</v>
+        <v>6795504</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5590,28 +5593,29 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129365284</v>
+        <v>129366863</v>
       </c>
       <c r="B49" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5637,19 +5641,22 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>430819</v>
+        <v>430653</v>
       </c>
       <c r="R49" t="n">
-        <v>6795467</v>
+        <v>6795695</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5687,28 +5694,29 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129366863</v>
+        <v>129365284</v>
       </c>
       <c r="B50" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5734,22 +5742,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>430653</v>
+        <v>430819</v>
       </c>
       <c r="R50" t="n">
-        <v>6795695</v>
+        <v>6795467</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5787,29 +5792,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129366884</v>
+        <v>129366873</v>
       </c>
       <c r="B51" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5844,10 +5848,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>430687</v>
+        <v>430712</v>
       </c>
       <c r="R51" t="n">
-        <v>6795504</v>
+        <v>6795594</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5900,17 +5904,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129366873</v>
+        <v>129357147</v>
       </c>
       <c r="B52" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5936,22 +5940,19 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>430712</v>
+        <v>430860</v>
       </c>
       <c r="R52" t="n">
-        <v>6795594</v>
+        <v>6795577</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5989,19 +5990,18 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6011,7 +6011,7 @@
         <v>129357149</v>
       </c>
       <c r="B53" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>129366871</v>
       </c>
       <c r="B54" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6209,7 +6209,7 @@
         <v>129366841</v>
       </c>
       <c r="B55" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6296,17 +6296,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129357164</v>
+        <v>129366845</v>
       </c>
       <c r="B56" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6334,17 +6334,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>430692</v>
+        <v>430816</v>
       </c>
       <c r="R56" t="n">
-        <v>6795567</v>
+        <v>6795679</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6388,22 +6388,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129366860</v>
+        <v>129357164</v>
       </c>
       <c r="B57" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6429,22 +6429,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>430605</v>
+        <v>430692</v>
       </c>
       <c r="R57" t="n">
-        <v>6795761</v>
+        <v>6795567</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6482,19 +6479,18 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6504,7 +6500,7 @@
         <v>129365281</v>
       </c>
       <c r="B58" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6598,10 +6594,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129366845</v>
+        <v>129366860</v>
       </c>
       <c r="B59" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6627,16 +6623,19 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>430816</v>
+        <v>430605</v>
       </c>
       <c r="R59" t="n">
-        <v>6795679</v>
+        <v>6795761</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6677,6 +6676,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6695,10 +6695,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129357150</v>
+        <v>129365288</v>
       </c>
       <c r="B60" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6730,10 +6730,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>430883</v>
+        <v>430681</v>
       </c>
       <c r="R60" t="n">
-        <v>6795535</v>
+        <v>6795704</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6780,12 +6780,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6795,7 +6795,7 @@
         <v>129357155</v>
       </c>
       <c r="B61" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6889,10 +6889,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129357151</v>
+        <v>129365278</v>
       </c>
       <c r="B62" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>430783</v>
+        <v>430695</v>
       </c>
       <c r="R62" t="n">
-        <v>6795740</v>
+        <v>6795429</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6974,22 +6974,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129365278</v>
+        <v>129357150</v>
       </c>
       <c r="B63" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>430695</v>
+        <v>430883</v>
       </c>
       <c r="R63" t="n">
-        <v>6795429</v>
+        <v>6795535</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7071,22 +7071,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129365288</v>
+        <v>129366883</v>
       </c>
       <c r="B64" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7112,19 +7112,22 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>430681</v>
+        <v>430687</v>
       </c>
       <c r="R64" t="n">
-        <v>6795704</v>
+        <v>6795535</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7162,28 +7165,29 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129366866</v>
+        <v>129366856</v>
       </c>
       <c r="B65" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7218,10 +7222,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>430658</v>
+        <v>430745</v>
       </c>
       <c r="R65" t="n">
-        <v>6795716</v>
+        <v>6795798</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7274,17 +7278,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129366883</v>
+        <v>129366853</v>
       </c>
       <c r="B66" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7310,19 +7314,16 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430687</v>
+        <v>430777</v>
       </c>
       <c r="R66" t="n">
-        <v>6795535</v>
+        <v>6795779</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7363,7 +7364,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7382,10 +7382,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129366856</v>
+        <v>129357151</v>
       </c>
       <c r="B67" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7411,22 +7411,19 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>430745</v>
+        <v>430783</v>
       </c>
       <c r="R67" t="n">
-        <v>6795798</v>
+        <v>6795740</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7464,29 +7461,28 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129366853</v>
+        <v>129366866</v>
       </c>
       <c r="B68" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7512,16 +7508,19 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>430777</v>
+        <v>430658</v>
       </c>
       <c r="R68" t="n">
-        <v>6795779</v>
+        <v>6795716</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7562,6 +7561,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7580,10 +7580,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129366882</v>
+        <v>129357163</v>
       </c>
       <c r="B69" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7609,22 +7609,19 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>430689</v>
+        <v>430645</v>
       </c>
       <c r="R69" t="n">
-        <v>6795544</v>
+        <v>6795744</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7662,19 +7659,18 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7684,7 +7680,7 @@
         <v>129357167</v>
       </c>
       <c r="B70" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7778,10 +7774,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129357163</v>
+        <v>129366882</v>
       </c>
       <c r="B71" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7807,19 +7803,22 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>430645</v>
+        <v>430689</v>
       </c>
       <c r="R71" t="n">
-        <v>6795744</v>
+        <v>6795544</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7857,18 +7856,19 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7878,7 +7878,7 @@
         <v>129366852</v>
       </c>
       <c r="B72" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7975,7 +7975,7 @@
         <v>129366837</v>
       </c>
       <c r="B73" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8072,7 +8072,7 @@
         <v>129366838</v>
       </c>
       <c r="B74" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8159,17 +8159,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129365286</v>
+        <v>129365290</v>
       </c>
       <c r="B75" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>430758</v>
+        <v>430688</v>
       </c>
       <c r="R75" t="n">
-        <v>6795794</v>
+        <v>6795513</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8263,10 +8263,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129365290</v>
+        <v>129365286</v>
       </c>
       <c r="B76" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>430688</v>
+        <v>430758</v>
       </c>
       <c r="R76" t="n">
-        <v>6795513</v>
+        <v>6795794</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8363,7 +8363,7 @@
         <v>129366849</v>
       </c>
       <c r="B77" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8460,7 +8460,7 @@
         <v>129366872</v>
       </c>
       <c r="B78" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8561,7 +8561,7 @@
         <v>129365291</v>
       </c>
       <c r="B79" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8655,10 +8655,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129357158</v>
+        <v>129366848</v>
       </c>
       <c r="B80" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8686,17 +8686,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>430587</v>
+        <v>430801</v>
       </c>
       <c r="R80" t="n">
-        <v>6795787</v>
+        <v>6795771</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8740,22 +8740,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129366868</v>
+        <v>129357158</v>
       </c>
       <c r="B81" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8781,22 +8781,19 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>430681</v>
+        <v>430587</v>
       </c>
       <c r="R81" t="n">
-        <v>6795699</v>
+        <v>6795787</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8834,29 +8831,28 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129357146</v>
+        <v>129366868</v>
       </c>
       <c r="B82" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8864,37 +8860,40 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>430723</v>
+        <v>430681</v>
       </c>
       <c r="R82" t="n">
-        <v>6795733</v>
+        <v>6795699</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8932,28 +8931,29 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129366848</v>
+        <v>129357146</v>
       </c>
       <c r="B83" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8961,37 +8961,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>430801</v>
+        <v>430723</v>
       </c>
       <c r="R83" t="n">
-        <v>6795771</v>
+        <v>6795733</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9035,12 +9035,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9050,7 +9050,7 @@
         <v>129366870</v>
       </c>
       <c r="B84" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9151,7 +9151,7 @@
         <v>129366887</v>
       </c>
       <c r="B85" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9252,7 +9252,7 @@
         <v>129366847</v>
       </c>
       <c r="B86" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9339,17 +9339,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129357156</v>
+        <v>129366844</v>
       </c>
       <c r="B87" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9377,17 +9377,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>430678</v>
+        <v>430858</v>
       </c>
       <c r="R87" t="n">
-        <v>6795768</v>
+        <v>6795532</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9431,22 +9431,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129366844</v>
+        <v>129366855</v>
       </c>
       <c r="B88" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9472,16 +9472,19 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>430858</v>
+        <v>430747</v>
       </c>
       <c r="R88" t="n">
-        <v>6795532</v>
+        <v>6795794</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9522,6 +9525,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9540,10 +9544,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129366855</v>
+        <v>129357156</v>
       </c>
       <c r="B89" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9569,22 +9573,19 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>430747</v>
+        <v>430678</v>
       </c>
       <c r="R89" t="n">
-        <v>6795794</v>
+        <v>6795768</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9622,29 +9623,28 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129357148</v>
+        <v>129357157</v>
       </c>
       <c r="B90" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9676,10 +9676,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>430712</v>
+        <v>430595</v>
       </c>
       <c r="R90" t="n">
-        <v>6795453</v>
+        <v>6795802</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9741,7 +9741,7 @@
         <v>129357152</v>
       </c>
       <c r="B91" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9835,10 +9835,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129357157</v>
+        <v>129357148</v>
       </c>
       <c r="B92" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9870,10 +9870,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>430595</v>
+        <v>430712</v>
       </c>
       <c r="R92" t="n">
-        <v>6795802</v>
+        <v>6795453</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9932,10 +9932,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129365277</v>
+        <v>129366879</v>
       </c>
       <c r="B93" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9943,37 +9943,40 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>430671</v>
+        <v>430705</v>
       </c>
       <c r="R93" t="n">
-        <v>6795716</v>
+        <v>6795565</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10011,18 +10014,19 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10032,7 +10036,7 @@
         <v>129366865</v>
       </c>
       <c r="B94" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10123,17 +10127,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129366879</v>
+        <v>129366843</v>
       </c>
       <c r="B95" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10159,19 +10163,16 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>430705</v>
+        <v>430875</v>
       </c>
       <c r="R95" t="n">
-        <v>6795565</v>
+        <v>6795544</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10212,7 +10213,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10231,10 +10231,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129366843</v>
+        <v>129365277</v>
       </c>
       <c r="B96" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10242,37 +10242,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>430875</v>
+        <v>430671</v>
       </c>
       <c r="R96" t="n">
-        <v>6795544</v>
+        <v>6795716</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10316,22 +10316,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129366835</v>
+        <v>129365282</v>
       </c>
       <c r="B97" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10359,17 +10359,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>430696</v>
+        <v>430792</v>
       </c>
       <c r="R97" t="n">
-        <v>6795393</v>
+        <v>6795496</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10413,22 +10413,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129365282</v>
+        <v>129357165</v>
       </c>
       <c r="B98" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>430792</v>
+        <v>430697</v>
       </c>
       <c r="R98" t="n">
-        <v>6795496</v>
+        <v>6795560</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10510,12 +10510,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10525,7 +10525,7 @@
         <v>129365289</v>
       </c>
       <c r="B99" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10619,10 +10619,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129357165</v>
+        <v>129365276</v>
       </c>
       <c r="B100" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10630,21 +10630,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10654,10 +10654,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>430697</v>
+        <v>430818</v>
       </c>
       <c r="R100" t="n">
-        <v>6795560</v>
+        <v>6795676</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10704,22 +10704,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129365276</v>
+        <v>129366835</v>
       </c>
       <c r="B101" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10727,37 +10727,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>430818</v>
+        <v>430696</v>
       </c>
       <c r="R101" t="n">
-        <v>6795676</v>
+        <v>6795393</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10801,22 +10801,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129357154</v>
+        <v>129366874</v>
       </c>
       <c r="B102" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10842,19 +10842,22 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>430735</v>
+        <v>430713</v>
       </c>
       <c r="R102" t="n">
-        <v>6795766</v>
+        <v>6795598</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10892,28 +10895,29 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129365274</v>
+        <v>129366878</v>
       </c>
       <c r="B103" t="n">
-        <v>83039</v>
+        <v>79075</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10921,37 +10925,40 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>430645</v>
+        <v>430709</v>
       </c>
       <c r="R103" t="n">
-        <v>6795789</v>
+        <v>6795590</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10989,28 +10996,29 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129366833</v>
+        <v>129366850</v>
       </c>
       <c r="B104" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11018,21 +11026,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11042,10 +11050,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>430797</v>
+        <v>430795</v>
       </c>
       <c r="R104" t="n">
-        <v>6795778</v>
+        <v>6795788</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11097,17 +11105,17 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129366832</v>
+        <v>129366861</v>
       </c>
       <c r="B105" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11115,34 +11123,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>430802</v>
+        <v>430639</v>
       </c>
       <c r="R105" t="n">
-        <v>6795767</v>
+        <v>6795711</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11183,6 +11194,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11201,10 +11213,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129366850</v>
+        <v>129357154</v>
       </c>
       <c r="B106" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11232,17 +11244,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>430795</v>
+        <v>430735</v>
       </c>
       <c r="R106" t="n">
-        <v>6795788</v>
+        <v>6795766</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11286,22 +11298,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129366861</v>
+        <v>129366832</v>
       </c>
       <c r="B107" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11309,37 +11321,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>430639</v>
+        <v>430802</v>
       </c>
       <c r="R107" t="n">
-        <v>6795711</v>
+        <v>6795767</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11380,7 +11389,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11399,10 +11407,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129366874</v>
+        <v>129365274</v>
       </c>
       <c r="B108" t="n">
-        <v>79070</v>
+        <v>83044</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11410,40 +11418,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>430713</v>
+        <v>430645</v>
       </c>
       <c r="R108" t="n">
-        <v>6795598</v>
+        <v>6795789</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11481,29 +11486,28 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129366878</v>
+        <v>129366833</v>
       </c>
       <c r="B109" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11511,37 +11515,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>430709</v>
+        <v>430797</v>
       </c>
       <c r="R109" t="n">
-        <v>6795590</v>
+        <v>6795778</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11582,7 +11583,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11601,10 +11601,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129366840</v>
+        <v>129366885</v>
       </c>
       <c r="B110" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11630,16 +11630,19 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>430748</v>
+        <v>430679</v>
       </c>
       <c r="R110" t="n">
-        <v>6795446</v>
+        <v>6795496</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11680,6 +11683,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11698,10 +11702,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129366885</v>
+        <v>129366840</v>
       </c>
       <c r="B111" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11727,19 +11731,16 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>430679</v>
+        <v>430748</v>
       </c>
       <c r="R111" t="n">
-        <v>6795496</v>
+        <v>6795446</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11780,7 +11781,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11802,7 +11802,7 @@
         <v>129357160</v>
       </c>
       <c r="B112" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>129357153</v>
       </c>
       <c r="B113" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>129366828</v>
       </c>
       <c r="B114" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12093,17 +12093,17 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129357166</v>
+        <v>129366836</v>
       </c>
       <c r="B115" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12131,17 +12131,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>430683</v>
+        <v>430712</v>
       </c>
       <c r="R115" t="n">
-        <v>6795520</v>
+        <v>6795414</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12185,12 +12185,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -12200,7 +12200,7 @@
         <v>129365280</v>
       </c>
       <c r="B116" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12294,10 +12294,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129366854</v>
+        <v>129366862</v>
       </c>
       <c r="B117" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12323,16 +12323,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>430775</v>
+        <v>430645</v>
       </c>
       <c r="R117" t="n">
-        <v>6795782</v>
+        <v>6795703</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -12373,6 +12376,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12391,10 +12395,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129366836</v>
+        <v>129366854</v>
       </c>
       <c r="B118" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12426,10 +12430,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>430712</v>
+        <v>430775</v>
       </c>
       <c r="R118" t="n">
-        <v>6795414</v>
+        <v>6795782</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12481,17 +12485,17 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129366862</v>
+        <v>129357166</v>
       </c>
       <c r="B119" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12517,22 +12521,19 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>430645</v>
+        <v>430683</v>
       </c>
       <c r="R119" t="n">
-        <v>6795703</v>
+        <v>6795520</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12570,19 +12571,18 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -12592,7 +12592,7 @@
         <v>129366867</v>
       </c>
       <c r="B120" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12683,17 +12683,17 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129366875</v>
+        <v>129366842</v>
       </c>
       <c r="B121" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12719,19 +12719,16 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>430714</v>
+        <v>430787</v>
       </c>
       <c r="R121" t="n">
-        <v>6795602</v>
+        <v>6795507</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -12772,7 +12769,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12791,10 +12787,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129366842</v>
+        <v>129366875</v>
       </c>
       <c r="B122" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12820,16 +12816,19 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>430787</v>
+        <v>430714</v>
       </c>
       <c r="R122" t="n">
-        <v>6795507</v>
+        <v>6795602</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -12870,6 +12869,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12891,7 +12891,7 @@
         <v>129366880</v>
       </c>
       <c r="B123" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12982,17 +12982,17 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129357145</v>
+        <v>129366864</v>
       </c>
       <c r="B124" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13000,37 +13000,40 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>430763</v>
+        <v>430653</v>
       </c>
       <c r="R124" t="n">
-        <v>6795787</v>
+        <v>6795703</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13068,18 +13071,19 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -13089,7 +13093,7 @@
         <v>129366881</v>
       </c>
       <c r="B125" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13180,17 +13184,17 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129357159</v>
+        <v>129365283</v>
       </c>
       <c r="B126" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13222,10 +13226,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>430603</v>
+        <v>430793</v>
       </c>
       <c r="R126" t="n">
-        <v>6795771</v>
+        <v>6795485</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13272,22 +13276,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129365283</v>
+        <v>129357159</v>
       </c>
       <c r="B127" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13319,10 +13323,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>430793</v>
+        <v>430603</v>
       </c>
       <c r="R127" t="n">
-        <v>6795485</v>
+        <v>6795771</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13369,22 +13373,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129366864</v>
+        <v>129366859</v>
       </c>
       <c r="B128" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13419,10 +13423,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>430653</v>
+        <v>430595</v>
       </c>
       <c r="R128" t="n">
-        <v>6795703</v>
+        <v>6795774</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -13475,17 +13479,17 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129366859</v>
+        <v>129357145</v>
       </c>
       <c r="B129" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13493,40 +13497,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>430595</v>
+        <v>430763</v>
       </c>
       <c r="R129" t="n">
-        <v>6795774</v>
+        <v>6795787</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13564,19 +13565,18 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -13586,7 +13586,7 @@
         <v>129366834</v>
       </c>
       <c r="B130" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>

--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -6303,7 +6303,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129366845</v>
+        <v>129366860</v>
       </c>
       <c r="B56" t="n">
         <v>79076</v>
@@ -6332,16 +6332,19 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>430816</v>
+        <v>430605</v>
       </c>
       <c r="R56" t="n">
-        <v>6795679</v>
+        <v>6795761</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6382,6 +6385,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6393,14 +6397,14 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129357164</v>
+        <v>129366845</v>
       </c>
       <c r="B57" t="n">
         <v>79076</v>
@@ -6431,17 +6435,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>430692</v>
+        <v>430816</v>
       </c>
       <c r="R57" t="n">
-        <v>6795567</v>
+        <v>6795679</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6485,19 +6489,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129365281</v>
+        <v>129357164</v>
       </c>
       <c r="B58" t="n">
         <v>79076</v>
@@ -6532,10 +6536,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>430773</v>
+        <v>430692</v>
       </c>
       <c r="R58" t="n">
-        <v>6795492</v>
+        <v>6795567</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6582,19 +6586,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129366860</v>
+        <v>129365281</v>
       </c>
       <c r="B59" t="n">
         <v>79076</v>
@@ -6623,22 +6627,19 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>430605</v>
+        <v>430773</v>
       </c>
       <c r="R59" t="n">
-        <v>6795761</v>
+        <v>6795492</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6676,19 +6677,18 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -8655,10 +8655,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129357146</v>
+        <v>129357158</v>
       </c>
       <c r="B80" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8666,21 +8666,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8690,10 +8690,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>430723</v>
+        <v>430587</v>
       </c>
       <c r="R80" t="n">
-        <v>6795733</v>
+        <v>6795787</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8752,7 +8752,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129357158</v>
+        <v>129366868</v>
       </c>
       <c r="B81" t="n">
         <v>79076</v>
@@ -8781,19 +8781,22 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>430587</v>
+        <v>430681</v>
       </c>
       <c r="R81" t="n">
-        <v>6795787</v>
+        <v>6795699</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8831,25 +8834,26 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129366868</v>
+        <v>129366848</v>
       </c>
       <c r="B82" t="n">
         <v>79076</v>
@@ -8878,19 +8882,16 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Åsdammen väster, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>430681</v>
+        <v>430801</v>
       </c>
       <c r="R82" t="n">
-        <v>6795699</v>
+        <v>6795771</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8931,7 +8932,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8943,17 +8943,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129366848</v>
+        <v>129357146</v>
       </c>
       <c r="B83" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8961,37 +8961,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Åsdammen väster, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>430801</v>
+        <v>430723</v>
       </c>
       <c r="R83" t="n">
-        <v>6795771</v>
+        <v>6795733</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9035,12 +9035,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -13685,10 +13685,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129773113</v>
+        <v>129773143</v>
       </c>
       <c r="B131" t="n">
-        <v>91609</v>
+        <v>78834</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13696,37 +13696,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>430833</v>
+        <v>430730</v>
       </c>
       <c r="R131" t="n">
-        <v>6796045</v>
+        <v>6795404</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13761,18 +13758,12 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>2 st på samma tall.</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13791,10 +13782,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129773143</v>
+        <v>129771737</v>
       </c>
       <c r="B132" t="n">
-        <v>78834</v>
+        <v>57733</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13802,34 +13793,42 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430730</v>
+        <v>430522</v>
       </c>
       <c r="R132" t="n">
-        <v>6795404</v>
+        <v>6795537</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13876,19 +13875,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129771737</v>
+        <v>129773137</v>
       </c>
       <c r="B133" t="n">
         <v>57733</v>
@@ -13921,7 +13920,7 @@
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -13931,10 +13930,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>430522</v>
+        <v>430851</v>
       </c>
       <c r="R133" t="n">
-        <v>6795537</v>
+        <v>6795824</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13981,19 +13980,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129773137</v>
+        <v>129773132</v>
       </c>
       <c r="B134" t="n">
         <v>57733</v>
@@ -14036,10 +14035,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>430851</v>
+        <v>430873</v>
       </c>
       <c r="R134" t="n">
-        <v>6795824</v>
+        <v>6795977</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14098,10 +14097,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129773132</v>
+        <v>129773214</v>
       </c>
       <c r="B135" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14109,42 +14108,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>430873</v>
+        <v>430777</v>
       </c>
       <c r="R135" t="n">
-        <v>6795977</v>
+        <v>6795822</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14203,10 +14194,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129773214</v>
+        <v>129771750</v>
       </c>
       <c r="B136" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14214,34 +14205,42 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>430777</v>
+        <v>430973</v>
       </c>
       <c r="R136" t="n">
-        <v>6795822</v>
+        <v>6795877</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14288,19 +14287,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129771750</v>
+        <v>129771741</v>
       </c>
       <c r="B137" t="n">
         <v>57733</v>
@@ -14333,7 +14332,7 @@
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -14343,10 +14342,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>430973</v>
+        <v>430784</v>
       </c>
       <c r="R137" t="n">
-        <v>6795877</v>
+        <v>6795567</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14405,10 +14404,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129771741</v>
+        <v>129771710</v>
       </c>
       <c r="B138" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14416,16 +14415,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -14448,10 +14447,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>430784</v>
+        <v>430669</v>
       </c>
       <c r="R138" t="n">
-        <v>6795567</v>
+        <v>6795823</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14510,32 +14509,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129771710</v>
+        <v>129771719</v>
       </c>
       <c r="B139" t="n">
-        <v>57736</v>
+        <v>56926</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14543,7 +14542,7 @@
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -14553,10 +14552,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>430669</v>
+        <v>430937</v>
       </c>
       <c r="R139" t="n">
-        <v>6795823</v>
+        <v>6796046</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14615,7 +14614,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129771719</v>
+        <v>129771724</v>
       </c>
       <c r="B140" t="n">
         <v>56926</v>
@@ -14658,10 +14657,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>430937</v>
+        <v>430884</v>
       </c>
       <c r="R140" t="n">
-        <v>6796046</v>
+        <v>6795785</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14720,53 +14719,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129771724</v>
+        <v>129773153</v>
       </c>
       <c r="B141" t="n">
-        <v>56926</v>
+        <v>78834</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>430884</v>
+        <v>430886</v>
       </c>
       <c r="R141" t="n">
-        <v>6795785</v>
+        <v>6796067</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14813,22 +14804,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129773153</v>
+        <v>129773113</v>
       </c>
       <c r="B142" t="n">
-        <v>78834</v>
+        <v>91609</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14836,34 +14827,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>430886</v>
+        <v>430833</v>
       </c>
       <c r="R142" t="n">
-        <v>6796067</v>
+        <v>6796045</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14898,12 +14892,18 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>2 st på samma tall.</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -17941,49 +17941,45 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129771819</v>
+        <v>129773179</v>
       </c>
       <c r="B173" t="n">
-        <v>92870</v>
+        <v>79076</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>430528</v>
+        <v>430611</v>
       </c>
       <c r="R173" t="n">
-        <v>6795564</v>
+        <v>6795443</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18024,29 +18020,28 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129773179</v>
+        <v>129773146</v>
       </c>
       <c r="B174" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18054,21 +18049,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18078,10 +18073,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>430611</v>
+        <v>430970</v>
       </c>
       <c r="R174" t="n">
-        <v>6795443</v>
+        <v>6795287</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18140,10 +18135,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129773146</v>
+        <v>129771790</v>
       </c>
       <c r="B175" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18151,21 +18146,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18175,10 +18170,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>430970</v>
+        <v>430957</v>
       </c>
       <c r="R175" t="n">
-        <v>6795287</v>
+        <v>6795608</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18225,19 +18220,19 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129771790</v>
+        <v>129773195</v>
       </c>
       <c r="B176" t="n">
         <v>79076</v>
@@ -18272,10 +18267,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>430957</v>
+        <v>431010</v>
       </c>
       <c r="R176" t="n">
-        <v>6795608</v>
+        <v>6795515</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18322,22 +18317,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129773195</v>
+        <v>129771757</v>
       </c>
       <c r="B177" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18345,21 +18340,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18369,10 +18364,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>431010</v>
+        <v>430923</v>
       </c>
       <c r="R177" t="n">
-        <v>6795515</v>
+        <v>6795582</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18419,22 +18414,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129771757</v>
+        <v>129773123</v>
       </c>
       <c r="B178" t="n">
-        <v>78834</v>
+        <v>57733</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18442,34 +18437,42 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>430923</v>
+        <v>430845</v>
       </c>
       <c r="R178" t="n">
-        <v>6795582</v>
+        <v>6795412</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18516,22 +18519,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129773123</v>
+        <v>129771811</v>
       </c>
       <c r="B179" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18539,42 +18542,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>430845</v>
+        <v>430910</v>
       </c>
       <c r="R179" t="n">
-        <v>6795412</v>
+        <v>6796078</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18621,19 +18616,19 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129771811</v>
+        <v>129773197</v>
       </c>
       <c r="B180" t="n">
         <v>79076</v>
@@ -18662,16 +18657,19 @@
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>430910</v>
+        <v>431062</v>
       </c>
       <c r="R180" t="n">
-        <v>6796078</v>
+        <v>6795533</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18712,28 +18710,29 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
+      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129773197</v>
+        <v>129773168</v>
       </c>
       <c r="B181" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18741,37 +18740,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>431062</v>
+        <v>430617</v>
       </c>
       <c r="R181" t="n">
-        <v>6795533</v>
+        <v>6795600</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18812,7 +18808,6 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
-      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
@@ -18831,10 +18826,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129773168</v>
+        <v>129771803</v>
       </c>
       <c r="B182" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18842,21 +18837,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18866,10 +18861,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>430617</v>
+        <v>430878</v>
       </c>
       <c r="R182" t="n">
-        <v>6795600</v>
+        <v>6795999</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18916,22 +18911,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129771803</v>
+        <v>129773150</v>
       </c>
       <c r="B183" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18939,21 +18934,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18963,10 +18958,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>430878</v>
+        <v>431067</v>
       </c>
       <c r="R183" t="n">
-        <v>6795999</v>
+        <v>6795549</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19013,22 +19008,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129773150</v>
+        <v>129773128</v>
       </c>
       <c r="B184" t="n">
-        <v>78834</v>
+        <v>57733</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19036,34 +19031,42 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>431067</v>
+        <v>430918</v>
       </c>
       <c r="R184" t="n">
-        <v>6795549</v>
+        <v>6795985</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19122,10 +19125,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129773128</v>
+        <v>129771766</v>
       </c>
       <c r="B185" t="n">
-        <v>57733</v>
+        <v>78833</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19133,42 +19136,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>430918</v>
+        <v>430922</v>
       </c>
       <c r="R185" t="n">
-        <v>6795985</v>
+        <v>6795638</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19215,22 +19210,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129771766</v>
+        <v>129771792</v>
       </c>
       <c r="B186" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19238,21 +19233,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19262,10 +19257,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>430922</v>
+        <v>430945</v>
       </c>
       <c r="R186" t="n">
-        <v>6795638</v>
+        <v>6795579</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19324,7 +19319,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129771792</v>
+        <v>129771812</v>
       </c>
       <c r="B187" t="n">
         <v>79076</v>
@@ -19359,10 +19354,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430945</v>
+        <v>430903</v>
       </c>
       <c r="R187" t="n">
-        <v>6795579</v>
+        <v>6796058</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19421,7 +19416,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129771812</v>
+        <v>129771807</v>
       </c>
       <c r="B188" t="n">
         <v>79076</v>
@@ -19456,10 +19451,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430903</v>
+        <v>430914</v>
       </c>
       <c r="R188" t="n">
-        <v>6796058</v>
+        <v>6796105</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19518,45 +19513,53 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129771807</v>
+        <v>129771764</v>
       </c>
       <c r="B189" t="n">
-        <v>79076</v>
+        <v>58106</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430914</v>
+        <v>430863</v>
       </c>
       <c r="R189" t="n">
-        <v>6796105</v>
+        <v>6795796</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19615,53 +19618,45 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129771764</v>
+        <v>129771729</v>
       </c>
       <c r="B190" t="n">
-        <v>58106</v>
+        <v>91609</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430863</v>
+        <v>430543</v>
       </c>
       <c r="R190" t="n">
-        <v>6795796</v>
+        <v>6795503</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19720,10 +19715,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129771729</v>
+        <v>129771728</v>
       </c>
       <c r="B191" t="n">
-        <v>91609</v>
+        <v>57896</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19731,34 +19726,42 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430543</v>
+        <v>430863</v>
       </c>
       <c r="R191" t="n">
-        <v>6795503</v>
+        <v>6795800</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19817,53 +19820,45 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129771728</v>
+        <v>129771703</v>
       </c>
       <c r="B192" t="n">
-        <v>57896</v>
+        <v>91552</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430863</v>
+        <v>430735</v>
       </c>
       <c r="R192" t="n">
-        <v>6795800</v>
+        <v>6795805</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19922,32 +19917,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129771703</v>
+        <v>129771707</v>
       </c>
       <c r="B193" t="n">
-        <v>91552</v>
+        <v>79695</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19957,10 +19952,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430735</v>
+        <v>430973</v>
       </c>
       <c r="R193" t="n">
-        <v>6795805</v>
+        <v>6795529</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20019,10 +20014,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129771707</v>
+        <v>129773122</v>
       </c>
       <c r="B194" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20030,34 +20025,42 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>430973</v>
+        <v>430702</v>
       </c>
       <c r="R194" t="n">
-        <v>6795529</v>
+        <v>6795444</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20104,22 +20107,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129773122</v>
+        <v>129773207</v>
       </c>
       <c r="B195" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20127,42 +20130,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430702</v>
+        <v>430947</v>
       </c>
       <c r="R195" t="n">
-        <v>6795444</v>
+        <v>6795977</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20221,10 +20216,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129773119</v>
+        <v>129771796</v>
       </c>
       <c r="B196" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20232,42 +20227,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430692</v>
+        <v>430984</v>
       </c>
       <c r="R196" t="n">
-        <v>6795373</v>
+        <v>6795518</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20314,19 +20301,19 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129773207</v>
+        <v>129771814</v>
       </c>
       <c r="B197" t="n">
         <v>79076</v>
@@ -20361,10 +20348,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>430947</v>
+        <v>430944</v>
       </c>
       <c r="R197" t="n">
-        <v>6795977</v>
+        <v>6796075</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20411,19 +20398,19 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129771796</v>
+        <v>129773211</v>
       </c>
       <c r="B198" t="n">
         <v>79076</v>
@@ -20458,10 +20445,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>430984</v>
+        <v>430815</v>
       </c>
       <c r="R198" t="n">
-        <v>6795518</v>
+        <v>6795818</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20508,57 +20495,66 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129771814</v>
+        <v>129771762</v>
       </c>
       <c r="B199" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>430944</v>
+        <v>430746</v>
       </c>
       <c r="R199" t="n">
-        <v>6796075</v>
+        <v>6795566</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20599,6 +20595,7 @@
       <c r="AE199" t="b">
         <v>0</v>
       </c>
+      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
@@ -20617,10 +20614,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129773211</v>
+        <v>129773119</v>
       </c>
       <c r="B200" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20628,34 +20625,42 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>430815</v>
+        <v>430692</v>
       </c>
       <c r="R200" t="n">
-        <v>6795818</v>
+        <v>6795373</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20714,7 +20719,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129771762</v>
+        <v>129773161</v>
       </c>
       <c r="B201" t="n">
         <v>8450</v>
@@ -20758,10 +20763,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>430746</v>
+        <v>430911</v>
       </c>
       <c r="R201" t="n">
-        <v>6795566</v>
+        <v>6795982</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20809,22 +20814,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129773161</v>
+        <v>129771725</v>
       </c>
       <c r="B202" t="n">
-        <v>8450</v>
+        <v>56926</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20832,30 +20837,29 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
@@ -20865,10 +20869,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>430911</v>
+        <v>430867</v>
       </c>
       <c r="R202" t="n">
-        <v>6795982</v>
+        <v>6795794</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20909,72 +20913,63 @@
       <c r="AE202" t="b">
         <v>0</v>
       </c>
-      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129771725</v>
+        <v>129771706</v>
       </c>
       <c r="B203" t="n">
-        <v>56926</v>
+        <v>79695</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>430867</v>
+        <v>430935</v>
       </c>
       <c r="R203" t="n">
-        <v>6795794</v>
+        <v>6795595</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21033,10 +21028,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129771706</v>
+        <v>129773205</v>
       </c>
       <c r="B204" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21044,21 +21039,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21068,10 +21063,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>430935</v>
+        <v>430907</v>
       </c>
       <c r="R204" t="n">
-        <v>6795595</v>
+        <v>6795973</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21118,22 +21113,22 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129773205</v>
+        <v>129773145</v>
       </c>
       <c r="B205" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21141,21 +21136,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21165,10 +21160,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>430907</v>
+        <v>430935</v>
       </c>
       <c r="R205" t="n">
-        <v>6795973</v>
+        <v>6795319</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21227,10 +21222,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129773145</v>
+        <v>129771808</v>
       </c>
       <c r="B206" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21238,21 +21233,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21262,10 +21257,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>430935</v>
+        <v>430894</v>
       </c>
       <c r="R206" t="n">
-        <v>6795319</v>
+        <v>6796093</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21312,22 +21307,22 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129771808</v>
+        <v>129771758</v>
       </c>
       <c r="B207" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21335,21 +21330,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21359,10 +21354,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>430894</v>
+        <v>430921</v>
       </c>
       <c r="R207" t="n">
-        <v>6796093</v>
+        <v>6795636</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21421,7 +21416,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129771758</v>
+        <v>129773142</v>
       </c>
       <c r="B208" t="n">
         <v>78834</v>
@@ -21456,10 +21451,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>430921</v>
+        <v>430602</v>
       </c>
       <c r="R208" t="n">
-        <v>6795636</v>
+        <v>6795431</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21506,22 +21501,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129773130</v>
+        <v>129771769</v>
       </c>
       <c r="B209" t="n">
-        <v>57733</v>
+        <v>78833</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21529,42 +21524,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>430893</v>
+        <v>430973</v>
       </c>
       <c r="R209" t="n">
-        <v>6796035</v>
+        <v>6795852</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21611,22 +21598,22 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129773142</v>
+        <v>129771795</v>
       </c>
       <c r="B210" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21634,21 +21621,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21658,10 +21645,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>430602</v>
+        <v>430956</v>
       </c>
       <c r="R210" t="n">
-        <v>6795431</v>
+        <v>6795564</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21708,22 +21695,22 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129771769</v>
+        <v>129771782</v>
       </c>
       <c r="B211" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21731,21 +21718,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21755,10 +21742,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>430973</v>
+        <v>430561</v>
       </c>
       <c r="R211" t="n">
-        <v>6795852</v>
+        <v>6795581</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21817,10 +21804,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129771795</v>
+        <v>129773130</v>
       </c>
       <c r="B212" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21828,34 +21815,42 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>430956</v>
+        <v>430893</v>
       </c>
       <c r="R212" t="n">
-        <v>6795564</v>
+        <v>6796035</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21902,19 +21897,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129771782</v>
+        <v>129773187</v>
       </c>
       <c r="B213" t="n">
         <v>79076</v>
@@ -21949,10 +21944,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>430561</v>
+        <v>430856</v>
       </c>
       <c r="R213" t="n">
-        <v>6795581</v>
+        <v>6795373</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21999,19 +21994,19 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129773187</v>
+        <v>129773186</v>
       </c>
       <c r="B214" t="n">
         <v>79076</v>
@@ -22046,10 +22041,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>430856</v>
+        <v>430861</v>
       </c>
       <c r="R214" t="n">
-        <v>6795373</v>
+        <v>6795429</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22108,7 +22103,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129773186</v>
+        <v>129773188</v>
       </c>
       <c r="B215" t="n">
         <v>79076</v>
@@ -22143,10 +22138,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>430861</v>
+        <v>430889</v>
       </c>
       <c r="R215" t="n">
-        <v>6795429</v>
+        <v>6795341</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22205,7 +22200,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129773188</v>
+        <v>129771798</v>
       </c>
       <c r="B216" t="n">
         <v>79076</v>
@@ -22240,10 +22235,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>430889</v>
+        <v>430982</v>
       </c>
       <c r="R216" t="n">
-        <v>6795341</v>
+        <v>6795567</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22290,19 +22285,19 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129771798</v>
+        <v>129773184</v>
       </c>
       <c r="B217" t="n">
         <v>79076</v>
@@ -22337,10 +22332,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>430982</v>
+        <v>430798</v>
       </c>
       <c r="R217" t="n">
-        <v>6795567</v>
+        <v>6795464</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22387,19 +22382,19 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129773184</v>
+        <v>129773206</v>
       </c>
       <c r="B218" t="n">
         <v>79076</v>
@@ -22434,10 +22429,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>430798</v>
+        <v>430918</v>
       </c>
       <c r="R218" t="n">
-        <v>6795464</v>
+        <v>6795974</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22496,7 +22491,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129773206</v>
+        <v>129773177</v>
       </c>
       <c r="B219" t="n">
         <v>79076</v>
@@ -22531,10 +22526,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>430918</v>
+        <v>430633</v>
       </c>
       <c r="R219" t="n">
-        <v>6795974</v>
+        <v>6795435</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22593,10 +22588,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129773177</v>
+        <v>129771736</v>
       </c>
       <c r="B220" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22604,34 +22599,42 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>430633</v>
+        <v>430531</v>
       </c>
       <c r="R220" t="n">
-        <v>6795435</v>
+        <v>6795488</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22678,22 +22681,22 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129771736</v>
+        <v>129773166</v>
       </c>
       <c r="B221" t="n">
-        <v>57733</v>
+        <v>78833</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22701,42 +22704,34 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>430531</v>
+        <v>430897</v>
       </c>
       <c r="R221" t="n">
-        <v>6795488</v>
+        <v>6795988</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22783,22 +22778,22 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129773166</v>
+        <v>129773189</v>
       </c>
       <c r="B222" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22806,21 +22801,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22830,10 +22825,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>430897</v>
+        <v>430904</v>
       </c>
       <c r="R222" t="n">
-        <v>6795988</v>
+        <v>6795339</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22892,10 +22887,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129773189</v>
+        <v>129771759</v>
       </c>
       <c r="B223" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22903,21 +22898,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -22927,10 +22922,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430904</v>
+        <v>430973</v>
       </c>
       <c r="R223" t="n">
-        <v>6795339</v>
+        <v>6795852</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22977,22 +22972,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129771759</v>
+        <v>129771813</v>
       </c>
       <c r="B224" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23000,21 +22995,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23024,10 +23019,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>430973</v>
+        <v>430910</v>
       </c>
       <c r="R224" t="n">
-        <v>6795852</v>
+        <v>6796073</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23086,10 +23081,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129771813</v>
+        <v>129771740</v>
       </c>
       <c r="B225" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23097,34 +23092,42 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>430910</v>
+        <v>430754</v>
       </c>
       <c r="R225" t="n">
-        <v>6796073</v>
+        <v>6795593</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23183,10 +23186,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129771740</v>
+        <v>129773190</v>
       </c>
       <c r="B226" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23194,42 +23197,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>430754</v>
+        <v>430984</v>
       </c>
       <c r="R226" t="n">
-        <v>6795593</v>
+        <v>6795313</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23276,19 +23271,19 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129773190</v>
+        <v>129771809</v>
       </c>
       <c r="B227" t="n">
         <v>79076</v>
@@ -23323,10 +23318,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>430984</v>
+        <v>430906</v>
       </c>
       <c r="R227" t="n">
-        <v>6795313</v>
+        <v>6796088</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23373,19 +23368,19 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129771809</v>
+        <v>129771781</v>
       </c>
       <c r="B228" t="n">
         <v>79076</v>
@@ -23420,10 +23415,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>430906</v>
+        <v>430497</v>
       </c>
       <c r="R228" t="n">
-        <v>6796088</v>
+        <v>6795553</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23482,7 +23477,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129771781</v>
+        <v>129773178</v>
       </c>
       <c r="B229" t="n">
         <v>79076</v>
@@ -23517,10 +23512,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>430497</v>
+        <v>430590</v>
       </c>
       <c r="R229" t="n">
-        <v>6795553</v>
+        <v>6795429</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23567,19 +23562,19 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129773178</v>
+        <v>129773201</v>
       </c>
       <c r="B230" t="n">
         <v>79076</v>
@@ -23614,10 +23609,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>430590</v>
+        <v>430907</v>
       </c>
       <c r="R230" t="n">
-        <v>6795429</v>
+        <v>6796028</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23676,10 +23671,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129773201</v>
+        <v>129773144</v>
       </c>
       <c r="B231" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23687,21 +23682,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -23714,7 +23709,7 @@
         <v>430907</v>
       </c>
       <c r="R231" t="n">
-        <v>6796028</v>
+        <v>6795330</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23773,10 +23768,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129773144</v>
+        <v>129771770</v>
       </c>
       <c r="B232" t="n">
-        <v>78834</v>
+        <v>78833</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23784,21 +23779,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23808,10 +23803,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>430907</v>
+        <v>430983</v>
       </c>
       <c r="R232" t="n">
-        <v>6795330</v>
+        <v>6795850</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23858,22 +23853,22 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129771770</v>
+        <v>129773217</v>
       </c>
       <c r="B233" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23881,21 +23876,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -23905,10 +23900,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>430983</v>
+        <v>430617</v>
       </c>
       <c r="R233" t="n">
-        <v>6795850</v>
+        <v>6795600</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23955,22 +23950,22 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129773217</v>
+        <v>129771708</v>
       </c>
       <c r="B234" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23978,21 +23973,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -24002,10 +23997,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>430617</v>
+        <v>430916</v>
       </c>
       <c r="R234" t="n">
-        <v>6795600</v>
+        <v>6796075</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24052,22 +24047,22 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129771708</v>
+        <v>129771752</v>
       </c>
       <c r="B235" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24075,34 +24070,42 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>430916</v>
+        <v>430801</v>
       </c>
       <c r="R235" t="n">
-        <v>6796075</v>
+        <v>6795756</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24161,40 +24164,41 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129771752</v>
+        <v>129773162</v>
       </c>
       <c r="B236" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr"/>
       <c r="M236" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N236" t="inlineStr"/>
@@ -24204,10 +24208,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>430801</v>
+        <v>430613</v>
       </c>
       <c r="R236" t="n">
-        <v>6795756</v>
+        <v>6795723</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24248,72 +24252,64 @@
       <c r="AE236" t="b">
         <v>0</v>
       </c>
+      <c r="AF236" t="inlineStr"/>
       <c r="AG236" t="b">
         <v>0</v>
       </c>
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129773162</v>
+        <v>129773101</v>
       </c>
       <c r="B237" t="n">
-        <v>8450</v>
+        <v>79666</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>430613</v>
+        <v>430763</v>
       </c>
       <c r="R237" t="n">
-        <v>6795723</v>
+        <v>6795472</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24354,7 +24350,6 @@
       <c r="AE237" t="b">
         <v>0</v>
       </c>
-      <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="b">
         <v>0</v>
       </c>
@@ -24373,10 +24368,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129773101</v>
+        <v>129771731</v>
       </c>
       <c r="B238" t="n">
-        <v>79666</v>
+        <v>91609</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24384,21 +24379,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -24408,10 +24403,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>430763</v>
+        <v>430961</v>
       </c>
       <c r="R238" t="n">
-        <v>6795472</v>
+        <v>6795616</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24458,22 +24453,22 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129771731</v>
+        <v>129771805</v>
       </c>
       <c r="B239" t="n">
-        <v>91609</v>
+        <v>79076</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24481,21 +24476,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24505,10 +24500,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>430961</v>
+        <v>430875</v>
       </c>
       <c r="R239" t="n">
-        <v>6795616</v>
+        <v>6796089</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24567,10 +24562,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129771805</v>
+        <v>129771747</v>
       </c>
       <c r="B240" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24578,34 +24573,42 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>430875</v>
+        <v>430947</v>
       </c>
       <c r="R240" t="n">
-        <v>6796089</v>
+        <v>6796064</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24664,7 +24667,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129771747</v>
+        <v>129771742</v>
       </c>
       <c r="B241" t="n">
         <v>57733</v>
@@ -24697,7 +24700,7 @@
       <c r="L241" t="inlineStr"/>
       <c r="M241" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N241" t="inlineStr"/>
@@ -24707,10 +24710,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>430947</v>
+        <v>430934</v>
       </c>
       <c r="R241" t="n">
-        <v>6796064</v>
+        <v>6795641</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24769,7 +24772,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129771742</v>
+        <v>129771746</v>
       </c>
       <c r="B242" t="n">
         <v>57733</v>
@@ -24802,7 +24805,7 @@
       <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N242" t="inlineStr"/>
@@ -24812,10 +24815,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>430934</v>
+        <v>430942</v>
       </c>
       <c r="R242" t="n">
-        <v>6795641</v>
+        <v>6796133</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24874,32 +24877,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129771746</v>
+        <v>129771716</v>
       </c>
       <c r="B243" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -24907,7 +24910,7 @@
       <c r="L243" t="inlineStr"/>
       <c r="M243" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N243" t="inlineStr"/>
@@ -24917,10 +24920,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>430942</v>
+        <v>430750</v>
       </c>
       <c r="R243" t="n">
-        <v>6796133</v>
+        <v>6795558</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24979,53 +24982,45 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129771716</v>
+        <v>129773213</v>
       </c>
       <c r="B244" t="n">
-        <v>56926</v>
+        <v>79076</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>430750</v>
+        <v>430783</v>
       </c>
       <c r="R244" t="n">
-        <v>6795558</v>
+        <v>6795818</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25072,19 +25067,19 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129773213</v>
+        <v>129771806</v>
       </c>
       <c r="B245" t="n">
         <v>79076</v>
@@ -25119,10 +25114,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>430783</v>
+        <v>430974</v>
       </c>
       <c r="R245" t="n">
-        <v>6795818</v>
+        <v>6796123</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25169,19 +25164,19 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>129771806</v>
+        <v>129771785</v>
       </c>
       <c r="B246" t="n">
         <v>79076</v>
@@ -25216,10 +25211,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>430974</v>
+        <v>430936</v>
       </c>
       <c r="R246" t="n">
-        <v>6796123</v>
+        <v>6795608</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25278,10 +25273,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>129771785</v>
+        <v>129771730</v>
       </c>
       <c r="B247" t="n">
-        <v>79076</v>
+        <v>91609</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25289,21 +25284,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25313,10 +25308,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>430936</v>
+        <v>430958</v>
       </c>
       <c r="R247" t="n">
-        <v>6795608</v>
+        <v>6795614</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25375,10 +25370,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129771730</v>
+        <v>129771739</v>
       </c>
       <c r="B248" t="n">
-        <v>91609</v>
+        <v>57733</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25386,34 +25381,42 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>430958</v>
+        <v>430752</v>
       </c>
       <c r="R248" t="n">
-        <v>6795614</v>
+        <v>6795559</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25472,10 +25475,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>129771739</v>
+        <v>129771784</v>
       </c>
       <c r="B249" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25483,42 +25486,34 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>430752</v>
+        <v>430920</v>
       </c>
       <c r="R249" t="n">
-        <v>6795559</v>
+        <v>6795536</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25577,10 +25572,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>129771784</v>
+        <v>129773121</v>
       </c>
       <c r="B250" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -25588,34 +25583,42 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>430920</v>
+        <v>430707</v>
       </c>
       <c r="R250" t="n">
-        <v>6795536</v>
+        <v>6795375</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25662,22 +25665,22 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129773121</v>
+        <v>129773202</v>
       </c>
       <c r="B251" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25685,42 +25688,34 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>430707</v>
+        <v>430858</v>
       </c>
       <c r="R251" t="n">
-        <v>6795375</v>
+        <v>6796064</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25779,10 +25774,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129773202</v>
+        <v>129773149</v>
       </c>
       <c r="B252" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -25790,21 +25785,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25814,10 +25809,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>430858</v>
+        <v>431021</v>
       </c>
       <c r="R252" t="n">
-        <v>6796064</v>
+        <v>6795524</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25876,10 +25871,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129773149</v>
+        <v>129771791</v>
       </c>
       <c r="B253" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -25887,21 +25882,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25911,10 +25906,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>431021</v>
+        <v>430959</v>
       </c>
       <c r="R253" t="n">
-        <v>6795524</v>
+        <v>6795606</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -25961,22 +25956,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>129771791</v>
+        <v>129771761</v>
       </c>
       <c r="B254" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -25984,21 +25979,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26008,10 +26003,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>430959</v>
+        <v>430865</v>
       </c>
       <c r="R254" t="n">
-        <v>6795606</v>
+        <v>6795798</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26070,10 +26065,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>129771761</v>
+        <v>129771738</v>
       </c>
       <c r="B255" t="n">
-        <v>78834</v>
+        <v>57733</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26081,34 +26076,42 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>430865</v>
+        <v>430655</v>
       </c>
       <c r="R255" t="n">
-        <v>6795798</v>
+        <v>6795565</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26167,32 +26170,32 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>129771738</v>
+        <v>129771714</v>
       </c>
       <c r="B256" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26200,7 +26203,7 @@
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N256" t="inlineStr"/>
@@ -26210,10 +26213,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>430655</v>
+        <v>430528</v>
       </c>
       <c r="R256" t="n">
-        <v>6795565</v>
+        <v>6795512</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26272,7 +26275,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>129771714</v>
+        <v>129771718</v>
       </c>
       <c r="B257" t="n">
         <v>56926</v>
@@ -26315,10 +26318,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>430528</v>
+        <v>430939</v>
       </c>
       <c r="R257" t="n">
-        <v>6795512</v>
+        <v>6796145</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26377,32 +26380,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>129771718</v>
+        <v>129773112</v>
       </c>
       <c r="B258" t="n">
-        <v>56926</v>
+        <v>57896</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26410,7 +26413,7 @@
       <c r="L258" t="inlineStr"/>
       <c r="M258" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N258" t="inlineStr"/>
@@ -26420,10 +26423,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>430939</v>
+        <v>430814</v>
       </c>
       <c r="R258" t="n">
-        <v>6796145</v>
+        <v>6795837</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26470,22 +26473,22 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>129773112</v>
+        <v>129773120</v>
       </c>
       <c r="B259" t="n">
-        <v>57896</v>
+        <v>57733</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26493,21 +26496,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -26515,7 +26518,7 @@
       <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N259" t="inlineStr"/>
@@ -26525,10 +26528,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>430814</v>
+        <v>430694</v>
       </c>
       <c r="R259" t="n">
-        <v>6795837</v>
+        <v>6795368</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -26587,10 +26590,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>129773120</v>
+        <v>129771786</v>
       </c>
       <c r="B260" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26598,42 +26601,34 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>430694</v>
+        <v>430927</v>
       </c>
       <c r="R260" t="n">
-        <v>6795368</v>
+        <v>6795611</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26680,22 +26675,22 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>129771786</v>
+        <v>129773135</v>
       </c>
       <c r="B261" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26703,34 +26698,42 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>430927</v>
+        <v>430938</v>
       </c>
       <c r="R261" t="n">
-        <v>6795611</v>
+        <v>6795967</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26777,22 +26780,22 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>129773135</v>
+        <v>129773182</v>
       </c>
       <c r="B262" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26800,42 +26803,34 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>430938</v>
+        <v>430740</v>
       </c>
       <c r="R262" t="n">
-        <v>6795967</v>
+        <v>6795371</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26894,10 +26889,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>129773182</v>
+        <v>129773156</v>
       </c>
       <c r="B263" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -26905,21 +26900,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -26929,10 +26924,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>430740</v>
+        <v>430787</v>
       </c>
       <c r="R263" t="n">
-        <v>6795371</v>
+        <v>6795816</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -26991,10 +26986,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>129773156</v>
+        <v>129771744</v>
       </c>
       <c r="B264" t="n">
-        <v>78834</v>
+        <v>57733</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27002,34 +26997,42 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>430787</v>
+        <v>430959</v>
       </c>
       <c r="R264" t="n">
-        <v>6795816</v>
+        <v>6795543</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27076,19 +27079,19 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>129771744</v>
+        <v>129773133</v>
       </c>
       <c r="B265" t="n">
         <v>57733</v>
@@ -27131,10 +27134,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>430959</v>
+        <v>430886</v>
       </c>
       <c r="R265" t="n">
-        <v>6795543</v>
+        <v>6795969</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27181,22 +27184,22 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>129773133</v>
+        <v>129773180</v>
       </c>
       <c r="B266" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27204,42 +27207,34 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>430886</v>
+        <v>430789</v>
       </c>
       <c r="R266" t="n">
-        <v>6795969</v>
+        <v>6795377</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27298,7 +27293,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>129773180</v>
+        <v>129771817</v>
       </c>
       <c r="B267" t="n">
         <v>79076</v>
@@ -27333,10 +27328,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>430789</v>
+        <v>430997</v>
       </c>
       <c r="R267" t="n">
-        <v>6795377</v>
+        <v>6795879</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27383,19 +27378,19 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>129771817</v>
+        <v>129771794</v>
       </c>
       <c r="B268" t="n">
         <v>79076</v>
@@ -27430,10 +27425,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>430997</v>
+        <v>430951</v>
       </c>
       <c r="R268" t="n">
-        <v>6795879</v>
+        <v>6795576</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27492,10 +27487,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>129771794</v>
+        <v>129773100</v>
       </c>
       <c r="B269" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -27503,21 +27498,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27527,10 +27522,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>430951</v>
+        <v>430941</v>
       </c>
       <c r="R269" t="n">
-        <v>6795576</v>
+        <v>6795869</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27577,57 +27572,65 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>129773100</v>
+        <v>129771715</v>
       </c>
       <c r="B270" t="n">
-        <v>79695</v>
+        <v>56926</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>430941</v>
+        <v>430568</v>
       </c>
       <c r="R270" t="n">
-        <v>6795869</v>
+        <v>6795570</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -27674,19 +27677,19 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>129771715</v>
+        <v>129771720</v>
       </c>
       <c r="B271" t="n">
         <v>56926</v>
@@ -27729,10 +27732,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>430568</v>
+        <v>430972</v>
       </c>
       <c r="R271" t="n">
-        <v>6795570</v>
+        <v>6796056</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27791,53 +27794,45 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>129771720</v>
+        <v>129771787</v>
       </c>
       <c r="B272" t="n">
-        <v>56926</v>
+        <v>79076</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>430972</v>
+        <v>430921</v>
       </c>
       <c r="R272" t="n">
-        <v>6796056</v>
+        <v>6795636</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27896,45 +27891,54 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>129771787</v>
+        <v>129773163</v>
       </c>
       <c r="B273" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>430921</v>
+        <v>430632</v>
       </c>
       <c r="R273" t="n">
-        <v>6795636</v>
+        <v>6795540</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27975,72 +27979,64 @@
       <c r="AE273" t="b">
         <v>0</v>
       </c>
+      <c r="AF273" t="inlineStr"/>
       <c r="AG273" t="b">
         <v>0</v>
       </c>
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>129773163</v>
+        <v>129771768</v>
       </c>
       <c r="B274" t="n">
-        <v>8450</v>
+        <v>78833</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>430632</v>
+        <v>430921</v>
       </c>
       <c r="R274" t="n">
-        <v>6795540</v>
+        <v>6796077</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28081,64 +28077,71 @@
       <c r="AE274" t="b">
         <v>0</v>
       </c>
-      <c r="AF274" t="inlineStr"/>
       <c r="AG274" t="b">
         <v>0</v>
       </c>
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>129771768</v>
+        <v>129773108</v>
       </c>
       <c r="B275" t="n">
-        <v>78833</v>
+        <v>56926</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>430921</v>
+        <v>430941</v>
       </c>
       <c r="R275" t="n">
-        <v>6796077</v>
+        <v>6795862</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28185,44 +28188,44 @@
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>129773108</v>
+        <v>129773125</v>
       </c>
       <c r="B276" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28230,7 +28233,7 @@
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N276" t="inlineStr"/>
@@ -28240,10 +28243,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>430941</v>
+        <v>430927</v>
       </c>
       <c r="R276" t="n">
-        <v>6795862</v>
+        <v>6795321</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28302,10 +28305,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>129773125</v>
+        <v>129773103</v>
       </c>
       <c r="B277" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -28313,16 +28316,16 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -28335,7 +28338,7 @@
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N277" t="inlineStr"/>
@@ -28345,10 +28348,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>430927</v>
+        <v>430952</v>
       </c>
       <c r="R277" t="n">
-        <v>6795321</v>
+        <v>6795876</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -28407,10 +28410,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>129773103</v>
+        <v>129771771</v>
       </c>
       <c r="B278" t="n">
-        <v>57736</v>
+        <v>78833</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28418,42 +28421,34 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>430952</v>
+        <v>430868</v>
       </c>
       <c r="R278" t="n">
-        <v>6795876</v>
+        <v>6795798</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28500,22 +28495,22 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>129771771</v>
+        <v>129771748</v>
       </c>
       <c r="B279" t="n">
-        <v>78833</v>
+        <v>57733</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28523,34 +28518,42 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>430868</v>
+        <v>430982</v>
       </c>
       <c r="R279" t="n">
-        <v>6795798</v>
+        <v>6795907</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28609,40 +28612,41 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>129771748</v>
+        <v>129773160</v>
       </c>
       <c r="B280" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N280" t="inlineStr"/>
@@ -28652,10 +28656,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>430982</v>
+        <v>430844</v>
       </c>
       <c r="R280" t="n">
-        <v>6795907</v>
+        <v>6796058</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28696,72 +28700,64 @@
       <c r="AE280" t="b">
         <v>0</v>
       </c>
+      <c r="AF280" t="inlineStr"/>
       <c r="AG280" t="b">
         <v>0</v>
       </c>
       <c r="AT280" t="inlineStr"/>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>129773160</v>
+        <v>129771800</v>
       </c>
       <c r="B281" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>430844</v>
+        <v>431011</v>
       </c>
       <c r="R281" t="n">
-        <v>6796058</v>
+        <v>6795579</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -28802,64 +28798,71 @@
       <c r="AE281" t="b">
         <v>0</v>
       </c>
-      <c r="AF281" t="inlineStr"/>
       <c r="AG281" t="b">
         <v>0</v>
       </c>
       <c r="AT281" t="inlineStr"/>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>129771800</v>
+        <v>129771723</v>
       </c>
       <c r="B282" t="n">
-        <v>79076</v>
+        <v>56926</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>431011</v>
+        <v>430890</v>
       </c>
       <c r="R282" t="n">
-        <v>6795579</v>
+        <v>6795825</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -28918,50 +28921,42 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>129771723</v>
+        <v>129773154</v>
       </c>
       <c r="B283" t="n">
-        <v>56926</v>
+        <v>78834</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>430890</v>
+        <v>430860</v>
       </c>
       <c r="R283" t="n">
         <v>6795825</v>
@@ -29011,19 +29006,19 @@
       <c r="AT283" t="inlineStr"/>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>129773154</v>
+        <v>129773157</v>
       </c>
       <c r="B284" t="n">
         <v>78834</v>
@@ -29058,10 +29053,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>430860</v>
+        <v>430617</v>
       </c>
       <c r="R284" t="n">
-        <v>6795825</v>
+        <v>6795600</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29120,45 +29115,53 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>129773157</v>
+        <v>129773105</v>
       </c>
       <c r="B285" t="n">
-        <v>78834</v>
+        <v>56926</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>430617</v>
+        <v>430923</v>
       </c>
       <c r="R285" t="n">
-        <v>6795600</v>
+        <v>6796012</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29217,32 +29220,32 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>129773105</v>
+        <v>129773129</v>
       </c>
       <c r="B286" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
@@ -29250,7 +29253,7 @@
       <c r="L286" t="inlineStr"/>
       <c r="M286" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N286" t="inlineStr"/>
@@ -29260,10 +29263,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>430923</v>
+        <v>430920</v>
       </c>
       <c r="R286" t="n">
-        <v>6796012</v>
+        <v>6796013</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -29322,7 +29325,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>129773129</v>
+        <v>129773115</v>
       </c>
       <c r="B287" t="n">
         <v>57733</v>
@@ -29365,10 +29368,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>430920</v>
+        <v>430594</v>
       </c>
       <c r="R287" t="n">
-        <v>6796013</v>
+        <v>6795423</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -29427,42 +29430,41 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>129773115</v>
+        <v>129771819</v>
       </c>
       <c r="B288" t="n">
-        <v>57733</v>
+        <v>92870</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
-      <c r="M288" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
         <is>
@@ -29470,10 +29472,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>430594</v>
+        <v>430528</v>
       </c>
       <c r="R288" t="n">
-        <v>6795423</v>
+        <v>6795564</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -29514,18 +29516,19 @@
       <c r="AE288" t="b">
         <v>0</v>
       </c>
+      <c r="AF288" t="inlineStr"/>
       <c r="AG288" t="b">
         <v>0</v>
       </c>
       <c r="AT288" t="inlineStr"/>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>

--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -13685,10 +13685,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129773214</v>
+        <v>129773137</v>
       </c>
       <c r="B131" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13696,34 +13696,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>430777</v>
+        <v>430851</v>
       </c>
       <c r="R131" t="n">
-        <v>6795822</v>
+        <v>6795824</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13782,10 +13790,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129773113</v>
+        <v>129771741</v>
       </c>
       <c r="B132" t="n">
-        <v>91614</v>
+        <v>57733</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13793,26 +13801,31 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -13820,10 +13833,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430833</v>
+        <v>430784</v>
       </c>
       <c r="R132" t="n">
-        <v>6796045</v>
+        <v>6795567</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13858,40 +13871,34 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>2 st på samma tall.</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129771737</v>
+        <v>129773143</v>
       </c>
       <c r="B133" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13899,42 +13906,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>430522</v>
+        <v>430730</v>
       </c>
       <c r="R133" t="n">
-        <v>6795537</v>
+        <v>6795404</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13981,22 +13980,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129773137</v>
+        <v>129773153</v>
       </c>
       <c r="B134" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14004,42 +14003,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>430851</v>
+        <v>430886</v>
       </c>
       <c r="R134" t="n">
-        <v>6795824</v>
+        <v>6796067</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14098,10 +14089,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129773132</v>
+        <v>129773113</v>
       </c>
       <c r="B135" t="n">
-        <v>57733</v>
+        <v>91618</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14109,31 +14100,26 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14141,10 +14127,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>430873</v>
+        <v>430833</v>
       </c>
       <c r="R135" t="n">
-        <v>6795977</v>
+        <v>6796045</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14179,12 +14165,18 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>2 st på samma tall.</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14203,7 +14195,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129771750</v>
+        <v>129771737</v>
       </c>
       <c r="B136" t="n">
         <v>57733</v>
@@ -14236,7 +14228,7 @@
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -14246,10 +14238,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>430973</v>
+        <v>430522</v>
       </c>
       <c r="R136" t="n">
-        <v>6795877</v>
+        <v>6795537</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14308,7 +14300,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129771741</v>
+        <v>129773132</v>
       </c>
       <c r="B137" t="n">
         <v>57733</v>
@@ -14341,7 +14333,7 @@
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -14351,10 +14343,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>430784</v>
+        <v>430873</v>
       </c>
       <c r="R137" t="n">
-        <v>6795567</v>
+        <v>6795977</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14401,22 +14393,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129771710</v>
+        <v>129771750</v>
       </c>
       <c r="B138" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14424,16 +14416,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -14446,7 +14438,7 @@
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -14456,10 +14448,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>430669</v>
+        <v>430973</v>
       </c>
       <c r="R138" t="n">
-        <v>6795823</v>
+        <v>6795877</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14518,32 +14510,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129771719</v>
+        <v>129771710</v>
       </c>
       <c r="B139" t="n">
-        <v>56926</v>
+        <v>57736</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14551,7 +14543,7 @@
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -14561,10 +14553,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>430937</v>
+        <v>430669</v>
       </c>
       <c r="R139" t="n">
-        <v>6796046</v>
+        <v>6795823</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14623,7 +14615,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129771724</v>
+        <v>129771719</v>
       </c>
       <c r="B140" t="n">
         <v>56926</v>
@@ -14666,10 +14658,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>430884</v>
+        <v>430937</v>
       </c>
       <c r="R140" t="n">
-        <v>6795785</v>
+        <v>6796046</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14728,45 +14720,53 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129773143</v>
+        <v>129771724</v>
       </c>
       <c r="B141" t="n">
-        <v>78839</v>
+        <v>56926</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>430730</v>
+        <v>430884</v>
       </c>
       <c r="R141" t="n">
-        <v>6795404</v>
+        <v>6795785</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14813,22 +14813,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129773153</v>
+        <v>129773214</v>
       </c>
       <c r="B142" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14836,21 +14836,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14860,10 +14860,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>430886</v>
+        <v>430777</v>
       </c>
       <c r="R142" t="n">
-        <v>6796067</v>
+        <v>6795822</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14922,10 +14922,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129771745</v>
+        <v>129771810</v>
       </c>
       <c r="B143" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14933,42 +14933,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>430945</v>
+        <v>430894</v>
       </c>
       <c r="R143" t="n">
-        <v>6796127</v>
+        <v>6796084</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15027,7 +15019,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129773196</v>
+        <v>129771783</v>
       </c>
       <c r="B144" t="n">
         <v>79081</v>
@@ -15062,10 +15054,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>431034</v>
+        <v>430787</v>
       </c>
       <c r="R144" t="n">
-        <v>6795525</v>
+        <v>6795560</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15112,19 +15104,19 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129773210</v>
+        <v>129773196</v>
       </c>
       <c r="B145" t="n">
         <v>79081</v>
@@ -15159,10 +15151,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>430968</v>
+        <v>431034</v>
       </c>
       <c r="R145" t="n">
-        <v>6795883</v>
+        <v>6795525</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15221,7 +15213,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129771810</v>
+        <v>129773210</v>
       </c>
       <c r="B146" t="n">
         <v>79081</v>
@@ -15256,10 +15248,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>430894</v>
+        <v>430968</v>
       </c>
       <c r="R146" t="n">
-        <v>6796084</v>
+        <v>6795883</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15306,22 +15298,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129771783</v>
+        <v>129771745</v>
       </c>
       <c r="B147" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15329,34 +15321,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>430787</v>
+        <v>430945</v>
       </c>
       <c r="R147" t="n">
-        <v>6795560</v>
+        <v>6796127</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15617,10 +15617,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129773155</v>
+        <v>129771751</v>
       </c>
       <c r="B150" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15628,34 +15628,42 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>430833</v>
+        <v>430983</v>
       </c>
       <c r="R150" t="n">
-        <v>6795830</v>
+        <v>6795850</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15702,19 +15710,19 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129771751</v>
+        <v>129773134</v>
       </c>
       <c r="B151" t="n">
         <v>57733</v>
@@ -15747,7 +15755,7 @@
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -15757,10 +15765,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>430983</v>
+        <v>430894</v>
       </c>
       <c r="R151" t="n">
-        <v>6795850</v>
+        <v>6795968</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15807,44 +15815,44 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129773134</v>
+        <v>129771717</v>
       </c>
       <c r="B152" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15852,7 +15860,7 @@
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -15862,10 +15870,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>430894</v>
+        <v>430918</v>
       </c>
       <c r="R152" t="n">
-        <v>6795968</v>
+        <v>6795982</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15912,19 +15920,19 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129771797</v>
+        <v>129773185</v>
       </c>
       <c r="B153" t="n">
         <v>79081</v>
@@ -15959,10 +15967,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>430960</v>
+        <v>430821</v>
       </c>
       <c r="R153" t="n">
-        <v>6795549</v>
+        <v>6795424</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16009,19 +16017,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129773185</v>
+        <v>129771797</v>
       </c>
       <c r="B154" t="n">
         <v>79081</v>
@@ -16056,10 +16064,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>430821</v>
+        <v>430960</v>
       </c>
       <c r="R154" t="n">
-        <v>6795424</v>
+        <v>6795549</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16106,12 +16114,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
@@ -16317,53 +16325,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129771717</v>
+        <v>129773155</v>
       </c>
       <c r="B157" t="n">
-        <v>56926</v>
+        <v>78839</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>430918</v>
+        <v>430833</v>
       </c>
       <c r="R157" t="n">
-        <v>6795982</v>
+        <v>6795830</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16410,65 +16410,57 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129771713</v>
+        <v>129771754</v>
       </c>
       <c r="B158" t="n">
-        <v>56926</v>
+        <v>92050</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>430542</v>
+        <v>430535</v>
       </c>
       <c r="R158" t="n">
-        <v>6795485</v>
+        <v>6795489</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16503,12 +16495,18 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -16527,45 +16525,53 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129771754</v>
+        <v>129773138</v>
       </c>
       <c r="B159" t="n">
-        <v>92046</v>
+        <v>57733</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>430535</v>
+        <v>430825</v>
       </c>
       <c r="R159" t="n">
-        <v>6795489</v>
+        <v>6795805</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16600,37 +16606,31 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129773138</v>
+        <v>129773124</v>
       </c>
       <c r="B160" t="n">
         <v>57733</v>
@@ -16673,10 +16673,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>430825</v>
+        <v>430865</v>
       </c>
       <c r="R160" t="n">
-        <v>6795805</v>
+        <v>6795387</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16735,7 +16735,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129773124</v>
+        <v>129771753</v>
       </c>
       <c r="B161" t="n">
         <v>57733</v>
@@ -16768,7 +16768,7 @@
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -16778,10 +16778,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>430865</v>
+        <v>430631</v>
       </c>
       <c r="R161" t="n">
-        <v>6795387</v>
+        <v>6795763</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16828,44 +16828,44 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129771753</v>
+        <v>129771713</v>
       </c>
       <c r="B162" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16873,7 +16873,7 @@
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -16883,10 +16883,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>430631</v>
+        <v>430542</v>
       </c>
       <c r="R162" t="n">
-        <v>6795763</v>
+        <v>6795485</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17440,10 +17440,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129773141</v>
+        <v>129773102</v>
       </c>
       <c r="B168" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17451,21 +17451,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17475,10 +17475,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>430600</v>
+        <v>431020</v>
       </c>
       <c r="R168" t="n">
-        <v>6795424</v>
+        <v>6795529</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17537,10 +17537,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129773102</v>
+        <v>129773141</v>
       </c>
       <c r="B169" t="n">
-        <v>79671</v>
+        <v>78839</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17548,21 +17548,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17572,10 +17572,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>431020</v>
+        <v>430600</v>
       </c>
       <c r="R169" t="n">
-        <v>6795529</v>
+        <v>6795424</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17634,10 +17634,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129771732</v>
+        <v>129773117</v>
       </c>
       <c r="B170" t="n">
-        <v>91614</v>
+        <v>57733</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17645,34 +17645,42 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>430972</v>
+        <v>430795</v>
       </c>
       <c r="R170" t="n">
-        <v>6795851</v>
+        <v>6795376</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17719,22 +17727,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129773146</v>
+        <v>129773123</v>
       </c>
       <c r="B171" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17742,34 +17750,42 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>430970</v>
+        <v>430845</v>
       </c>
       <c r="R171" t="n">
-        <v>6795287</v>
+        <v>6795412</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17828,10 +17844,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129771757</v>
+        <v>129771732</v>
       </c>
       <c r="B172" t="n">
-        <v>78839</v>
+        <v>91618</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17839,21 +17855,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17863,10 +17879,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>430923</v>
+        <v>430972</v>
       </c>
       <c r="R172" t="n">
-        <v>6795582</v>
+        <v>6795851</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17925,45 +17941,53 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129773179</v>
+        <v>129773109</v>
       </c>
       <c r="B173" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>430611</v>
+        <v>430816</v>
       </c>
       <c r="R173" t="n">
-        <v>6795443</v>
+        <v>6795834</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18022,10 +18046,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129773117</v>
+        <v>129773146</v>
       </c>
       <c r="B174" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18033,42 +18057,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>430795</v>
+        <v>430970</v>
       </c>
       <c r="R174" t="n">
-        <v>6795376</v>
+        <v>6795287</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18127,10 +18143,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129773123</v>
+        <v>129771757</v>
       </c>
       <c r="B175" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18138,42 +18154,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>430845</v>
+        <v>430923</v>
       </c>
       <c r="R175" t="n">
-        <v>6795412</v>
+        <v>6795582</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18220,19 +18228,19 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129771790</v>
+        <v>129773179</v>
       </c>
       <c r="B176" t="n">
         <v>79081</v>
@@ -18267,10 +18275,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>430957</v>
+        <v>430611</v>
       </c>
       <c r="R176" t="n">
-        <v>6795608</v>
+        <v>6795443</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18317,12 +18325,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
@@ -18426,53 +18434,45 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129773109</v>
+        <v>129771790</v>
       </c>
       <c r="B178" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>430816</v>
+        <v>430957</v>
       </c>
       <c r="R178" t="n">
-        <v>6795834</v>
+        <v>6795608</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18519,22 +18519,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129773128</v>
+        <v>129773150</v>
       </c>
       <c r="B179" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18542,42 +18542,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>430918</v>
+        <v>431067</v>
       </c>
       <c r="R179" t="n">
-        <v>6795985</v>
+        <v>6795549</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18636,10 +18628,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129771811</v>
+        <v>129773168</v>
       </c>
       <c r="B180" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18647,21 +18639,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18671,10 +18663,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>430910</v>
+        <v>430617</v>
       </c>
       <c r="R180" t="n">
-        <v>6796078</v>
+        <v>6795600</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18721,22 +18713,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129773197</v>
+        <v>129773128</v>
       </c>
       <c r="B181" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18744,26 +18736,31 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
@@ -18771,10 +18768,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>431062</v>
+        <v>430918</v>
       </c>
       <c r="R181" t="n">
-        <v>6795533</v>
+        <v>6795985</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18815,7 +18812,6 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
-      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
@@ -18834,10 +18830,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129773168</v>
+        <v>129771803</v>
       </c>
       <c r="B182" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18845,21 +18841,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18869,10 +18865,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>430617</v>
+        <v>430878</v>
       </c>
       <c r="R182" t="n">
-        <v>6795600</v>
+        <v>6795999</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18919,19 +18915,19 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129771803</v>
+        <v>129773197</v>
       </c>
       <c r="B183" t="n">
         <v>79081</v>
@@ -18960,16 +18956,19 @@
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>430878</v>
+        <v>431062</v>
       </c>
       <c r="R183" t="n">
-        <v>6795999</v>
+        <v>6795533</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19010,28 +19009,29 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129773150</v>
+        <v>129771811</v>
       </c>
       <c r="B184" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19039,21 +19039,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19063,10 +19063,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>431067</v>
+        <v>430910</v>
       </c>
       <c r="R184" t="n">
-        <v>6795549</v>
+        <v>6796078</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19113,44 +19113,44 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129771703</v>
+        <v>129771766</v>
       </c>
       <c r="B185" t="n">
-        <v>91557</v>
+        <v>78838</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19160,10 +19160,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>430735</v>
+        <v>430922</v>
       </c>
       <c r="R185" t="n">
-        <v>6795805</v>
+        <v>6795638</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19222,10 +19222,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129771766</v>
+        <v>129771707</v>
       </c>
       <c r="B186" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19233,21 +19233,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19257,10 +19257,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>430922</v>
+        <v>430973</v>
       </c>
       <c r="R186" t="n">
-        <v>6795638</v>
+        <v>6795529</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19319,7 +19319,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129771792</v>
+        <v>129771807</v>
       </c>
       <c r="B187" t="n">
         <v>79081</v>
@@ -19354,10 +19354,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430945</v>
+        <v>430914</v>
       </c>
       <c r="R187" t="n">
-        <v>6795579</v>
+        <v>6796105</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19416,7 +19416,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129771812</v>
+        <v>129771792</v>
       </c>
       <c r="B188" t="n">
         <v>79081</v>
@@ -19451,10 +19451,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430903</v>
+        <v>430945</v>
       </c>
       <c r="R188" t="n">
-        <v>6796058</v>
+        <v>6795579</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19513,7 +19513,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129771807</v>
+        <v>129771812</v>
       </c>
       <c r="B189" t="n">
         <v>79081</v>
@@ -19548,10 +19548,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430914</v>
+        <v>430903</v>
       </c>
       <c r="R189" t="n">
-        <v>6796105</v>
+        <v>6796058</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19610,10 +19610,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129771707</v>
+        <v>129771728</v>
       </c>
       <c r="B190" t="n">
-        <v>79700</v>
+        <v>57896</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19621,34 +19621,42 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430973</v>
+        <v>430863</v>
       </c>
       <c r="R190" t="n">
-        <v>6795529</v>
+        <v>6795800</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19707,10 +19715,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129771728</v>
+        <v>129771729</v>
       </c>
       <c r="B191" t="n">
-        <v>57896</v>
+        <v>91618</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19718,42 +19726,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430863</v>
+        <v>430543</v>
       </c>
       <c r="R191" t="n">
-        <v>6795800</v>
+        <v>6795503</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19812,10 +19812,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129771764</v>
+        <v>129771703</v>
       </c>
       <c r="B192" t="n">
-        <v>58106</v>
+        <v>91561</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19823,42 +19823,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430863</v>
+        <v>430735</v>
       </c>
       <c r="R192" t="n">
-        <v>6795796</v>
+        <v>6795805</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19917,10 +19909,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129771729</v>
+        <v>129773122</v>
       </c>
       <c r="B193" t="n">
-        <v>91614</v>
+        <v>57733</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19928,34 +19920,42 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430543</v>
+        <v>430702</v>
       </c>
       <c r="R193" t="n">
-        <v>6795503</v>
+        <v>6795444</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20002,39 +20002,39 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129773122</v>
+        <v>129771764</v>
       </c>
       <c r="B194" t="n">
-        <v>57733</v>
+        <v>58106</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -20047,7 +20047,7 @@
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N194" t="inlineStr"/>
@@ -20057,10 +20057,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>430702</v>
+        <v>430863</v>
       </c>
       <c r="R194" t="n">
-        <v>6795444</v>
+        <v>6795796</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20107,22 +20107,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129773119</v>
+        <v>129773207</v>
       </c>
       <c r="B195" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20130,42 +20130,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430692</v>
+        <v>430947</v>
       </c>
       <c r="R195" t="n">
-        <v>6795373</v>
+        <v>6795977</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20224,45 +20216,54 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129773207</v>
+        <v>129771762</v>
       </c>
       <c r="B196" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430947</v>
+        <v>430746</v>
       </c>
       <c r="R196" t="n">
-        <v>6795977</v>
+        <v>6795566</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20303,28 +20304,29 @@
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129771796</v>
+        <v>129773119</v>
       </c>
       <c r="B197" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20332,34 +20334,42 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>430984</v>
+        <v>430692</v>
       </c>
       <c r="R197" t="n">
-        <v>6795518</v>
+        <v>6795373</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20406,12 +20416,12 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
@@ -20515,7 +20525,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129773211</v>
+        <v>129771796</v>
       </c>
       <c r="B199" t="n">
         <v>79081</v>
@@ -20550,10 +20560,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>430815</v>
+        <v>430984</v>
       </c>
       <c r="R199" t="n">
-        <v>6795818</v>
+        <v>6795518</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20600,66 +20610,57 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129771762</v>
+        <v>129773211</v>
       </c>
       <c r="B200" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>430746</v>
+        <v>430815</v>
       </c>
       <c r="R200" t="n">
-        <v>6795566</v>
+        <v>6795818</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20700,19 +20701,18 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
@@ -20816,45 +20816,53 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129773205</v>
+        <v>129771725</v>
       </c>
       <c r="B202" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>430907</v>
+        <v>430867</v>
       </c>
       <c r="R202" t="n">
-        <v>6795973</v>
+        <v>6795794</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20901,19 +20909,19 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129771808</v>
+        <v>129773205</v>
       </c>
       <c r="B203" t="n">
         <v>79081</v>
@@ -20948,10 +20956,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>430894</v>
+        <v>430907</v>
       </c>
       <c r="R203" t="n">
-        <v>6796093</v>
+        <v>6795973</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20998,65 +21006,57 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129771725</v>
+        <v>129771808</v>
       </c>
       <c r="B204" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>430867</v>
+        <v>430894</v>
       </c>
       <c r="R204" t="n">
-        <v>6795794</v>
+        <v>6796093</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21115,54 +21115,45 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129773161</v>
+        <v>129773145</v>
       </c>
       <c r="B205" t="n">
-        <v>8450</v>
+        <v>78839</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>430911</v>
+        <v>430935</v>
       </c>
       <c r="R205" t="n">
-        <v>6795982</v>
+        <v>6795319</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21203,7 +21194,6 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
-      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
@@ -21222,7 +21212,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129773145</v>
+        <v>129771758</v>
       </c>
       <c r="B206" t="n">
         <v>78839</v>
@@ -21257,10 +21247,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>430935</v>
+        <v>430921</v>
       </c>
       <c r="R206" t="n">
-        <v>6795319</v>
+        <v>6795636</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21307,57 +21297,66 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129771758</v>
+        <v>129773161</v>
       </c>
       <c r="B207" t="n">
-        <v>78839</v>
+        <v>8450</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>430921</v>
+        <v>430911</v>
       </c>
       <c r="R207" t="n">
-        <v>6795636</v>
+        <v>6795982</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21398,28 +21397,29 @@
       <c r="AE207" t="b">
         <v>0</v>
       </c>
+      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129771769</v>
+        <v>129773130</v>
       </c>
       <c r="B208" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21427,34 +21427,42 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>430973</v>
+        <v>430893</v>
       </c>
       <c r="R208" t="n">
-        <v>6795852</v>
+        <v>6796035</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21501,12 +21509,12 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
@@ -21707,10 +21715,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129773130</v>
+        <v>129773142</v>
       </c>
       <c r="B211" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21718,42 +21726,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>430893</v>
+        <v>430602</v>
       </c>
       <c r="R211" t="n">
-        <v>6796035</v>
+        <v>6795431</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21812,10 +21812,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129773142</v>
+        <v>129771769</v>
       </c>
       <c r="B212" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21823,21 +21823,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21847,10 +21847,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>430602</v>
+        <v>430973</v>
       </c>
       <c r="R212" t="n">
-        <v>6795431</v>
+        <v>6795852</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21897,19 +21897,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129773187</v>
+        <v>129773206</v>
       </c>
       <c r="B213" t="n">
         <v>79081</v>
@@ -21944,10 +21944,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>430856</v>
+        <v>430918</v>
       </c>
       <c r="R213" t="n">
-        <v>6795373</v>
+        <v>6795974</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22006,7 +22006,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129773186</v>
+        <v>129773188</v>
       </c>
       <c r="B214" t="n">
         <v>79081</v>
@@ -22041,10 +22041,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>430861</v>
+        <v>430889</v>
       </c>
       <c r="R214" t="n">
-        <v>6795429</v>
+        <v>6795341</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22103,7 +22103,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129773206</v>
+        <v>129773186</v>
       </c>
       <c r="B215" t="n">
         <v>79081</v>
@@ -22138,10 +22138,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>430918</v>
+        <v>430861</v>
       </c>
       <c r="R215" t="n">
-        <v>6795974</v>
+        <v>6795429</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22200,7 +22200,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129773188</v>
+        <v>129773187</v>
       </c>
       <c r="B216" t="n">
         <v>79081</v>
@@ -22235,10 +22235,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>430889</v>
+        <v>430856</v>
       </c>
       <c r="R216" t="n">
-        <v>6795341</v>
+        <v>6795373</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22297,7 +22297,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129771798</v>
+        <v>129773184</v>
       </c>
       <c r="B217" t="n">
         <v>79081</v>
@@ -22332,10 +22332,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>430982</v>
+        <v>430798</v>
       </c>
       <c r="R217" t="n">
-        <v>6795567</v>
+        <v>6795464</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22382,19 +22382,19 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129773184</v>
+        <v>129771798</v>
       </c>
       <c r="B218" t="n">
         <v>79081</v>
@@ -22429,10 +22429,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>430798</v>
+        <v>430982</v>
       </c>
       <c r="R218" t="n">
-        <v>6795464</v>
+        <v>6795567</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22479,22 +22479,22 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129771736</v>
+        <v>129773166</v>
       </c>
       <c r="B219" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22502,42 +22502,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>430531</v>
+        <v>430897</v>
       </c>
       <c r="R219" t="n">
-        <v>6795488</v>
+        <v>6795988</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22584,22 +22576,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129771740</v>
+        <v>129773190</v>
       </c>
       <c r="B220" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22607,42 +22599,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>430754</v>
+        <v>430984</v>
       </c>
       <c r="R220" t="n">
-        <v>6795593</v>
+        <v>6795313</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22689,19 +22673,19 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129773177</v>
+        <v>129773189</v>
       </c>
       <c r="B221" t="n">
         <v>79081</v>
@@ -22736,10 +22720,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>430633</v>
+        <v>430904</v>
       </c>
       <c r="R221" t="n">
-        <v>6795435</v>
+        <v>6795339</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22798,10 +22782,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129773166</v>
+        <v>129771813</v>
       </c>
       <c r="B222" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22809,21 +22793,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22833,10 +22817,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>430897</v>
+        <v>430910</v>
       </c>
       <c r="R222" t="n">
-        <v>6795988</v>
+        <v>6796073</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22883,19 +22867,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129773189</v>
+        <v>129773177</v>
       </c>
       <c r="B223" t="n">
         <v>79081</v>
@@ -22930,10 +22914,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430904</v>
+        <v>430633</v>
       </c>
       <c r="R223" t="n">
-        <v>6795339</v>
+        <v>6795435</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22992,10 +22976,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129771813</v>
+        <v>129771736</v>
       </c>
       <c r="B224" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23003,34 +22987,42 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>430910</v>
+        <v>430531</v>
       </c>
       <c r="R224" t="n">
-        <v>6796073</v>
+        <v>6795488</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23089,10 +23081,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129773190</v>
+        <v>129771740</v>
       </c>
       <c r="B225" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23100,34 +23092,42 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>430984</v>
+        <v>430754</v>
       </c>
       <c r="R225" t="n">
-        <v>6795313</v>
+        <v>6795593</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23174,12 +23174,12 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
@@ -23283,10 +23283,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129773144</v>
+        <v>129771781</v>
       </c>
       <c r="B227" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23294,21 +23294,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23318,10 +23318,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>430907</v>
+        <v>430497</v>
       </c>
       <c r="R227" t="n">
-        <v>6795330</v>
+        <v>6795553</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23368,19 +23368,19 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129771809</v>
+        <v>129773217</v>
       </c>
       <c r="B228" t="n">
         <v>79081</v>
@@ -23415,10 +23415,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>430906</v>
+        <v>430617</v>
       </c>
       <c r="R228" t="n">
-        <v>6796088</v>
+        <v>6795600</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23465,19 +23465,19 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129771781</v>
+        <v>129773201</v>
       </c>
       <c r="B229" t="n">
         <v>79081</v>
@@ -23512,10 +23512,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>430497</v>
+        <v>430907</v>
       </c>
       <c r="R229" t="n">
-        <v>6795553</v>
+        <v>6796028</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23562,19 +23562,19 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129773178</v>
+        <v>129771809</v>
       </c>
       <c r="B230" t="n">
         <v>79081</v>
@@ -23609,10 +23609,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>430590</v>
+        <v>430906</v>
       </c>
       <c r="R230" t="n">
-        <v>6795429</v>
+        <v>6796088</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23659,19 +23659,19 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129773201</v>
+        <v>129773178</v>
       </c>
       <c r="B231" t="n">
         <v>79081</v>
@@ -23706,10 +23706,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>430907</v>
+        <v>430590</v>
       </c>
       <c r="R231" t="n">
-        <v>6796028</v>
+        <v>6795429</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23865,10 +23865,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129773217</v>
+        <v>129771708</v>
       </c>
       <c r="B233" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23876,21 +23876,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -23900,10 +23900,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>430617</v>
+        <v>430916</v>
       </c>
       <c r="R233" t="n">
-        <v>6795600</v>
+        <v>6796075</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23950,22 +23950,22 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129771708</v>
+        <v>129773144</v>
       </c>
       <c r="B234" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23973,21 +23973,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -23997,10 +23997,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>430916</v>
+        <v>430907</v>
       </c>
       <c r="R234" t="n">
-        <v>6796075</v>
+        <v>6795330</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24047,22 +24047,22 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129773101</v>
+        <v>129771731</v>
       </c>
       <c r="B235" t="n">
-        <v>79671</v>
+        <v>91618</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24070,21 +24070,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -24094,10 +24094,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>430763</v>
+        <v>430961</v>
       </c>
       <c r="R235" t="n">
-        <v>6795472</v>
+        <v>6795616</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24144,12 +24144,12 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
@@ -24261,45 +24261,54 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129771805</v>
+        <v>129773162</v>
       </c>
       <c r="B237" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>430875</v>
+        <v>430613</v>
       </c>
       <c r="R237" t="n">
-        <v>6796089</v>
+        <v>6795723</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24340,28 +24349,29 @@
       <c r="AE237" t="b">
         <v>0</v>
       </c>
+      <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="b">
         <v>0</v>
       </c>
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129771731</v>
+        <v>129771805</v>
       </c>
       <c r="B238" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24369,21 +24379,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -24393,10 +24403,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>430961</v>
+        <v>430875</v>
       </c>
       <c r="R238" t="n">
-        <v>6795616</v>
+        <v>6796089</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24455,54 +24465,45 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129773162</v>
+        <v>129773101</v>
       </c>
       <c r="B239" t="n">
-        <v>8450</v>
+        <v>79671</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>430613</v>
+        <v>430763</v>
       </c>
       <c r="R239" t="n">
-        <v>6795723</v>
+        <v>6795472</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24543,7 +24544,6 @@
       <c r="AE239" t="b">
         <v>0</v>
       </c>
-      <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="b">
         <v>0</v>
       </c>
@@ -24562,10 +24562,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129771747</v>
+        <v>129771730</v>
       </c>
       <c r="B240" t="n">
-        <v>57733</v>
+        <v>91618</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24573,42 +24573,34 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>430947</v>
+        <v>430958</v>
       </c>
       <c r="R240" t="n">
-        <v>6796064</v>
+        <v>6795614</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24772,7 +24764,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129771746</v>
+        <v>129771747</v>
       </c>
       <c r="B242" t="n">
         <v>57733</v>
@@ -24815,10 +24807,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>430942</v>
+        <v>430947</v>
       </c>
       <c r="R242" t="n">
-        <v>6796133</v>
+        <v>6796064</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24877,7 +24869,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129773121</v>
+        <v>129771746</v>
       </c>
       <c r="B243" t="n">
         <v>57733</v>
@@ -24920,10 +24912,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>430707</v>
+        <v>430942</v>
       </c>
       <c r="R243" t="n">
-        <v>6795375</v>
+        <v>6796133</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24970,19 +24962,19 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129771739</v>
+        <v>129773121</v>
       </c>
       <c r="B244" t="n">
         <v>57733</v>
@@ -25025,10 +25017,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>430752</v>
+        <v>430707</v>
       </c>
       <c r="R244" t="n">
-        <v>6795559</v>
+        <v>6795375</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25075,22 +25067,22 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129771730</v>
+        <v>129771739</v>
       </c>
       <c r="B245" t="n">
-        <v>91614</v>
+        <v>57733</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25098,34 +25090,42 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>430958</v>
+        <v>430752</v>
       </c>
       <c r="R245" t="n">
-        <v>6795614</v>
+        <v>6795559</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25184,45 +25184,53 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>129773213</v>
+        <v>129771716</v>
       </c>
       <c r="B246" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>430783</v>
+        <v>430750</v>
       </c>
       <c r="R246" t="n">
-        <v>6795818</v>
+        <v>6795558</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25269,19 +25277,19 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>129771806</v>
+        <v>129771785</v>
       </c>
       <c r="B247" t="n">
         <v>79081</v>
@@ -25316,10 +25324,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>430974</v>
+        <v>430936</v>
       </c>
       <c r="R247" t="n">
-        <v>6796123</v>
+        <v>6795608</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25378,7 +25386,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129771785</v>
+        <v>129771806</v>
       </c>
       <c r="B248" t="n">
         <v>79081</v>
@@ -25413,10 +25421,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>430936</v>
+        <v>430974</v>
       </c>
       <c r="R248" t="n">
-        <v>6795608</v>
+        <v>6796123</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25572,53 +25580,45 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>129771716</v>
+        <v>129773213</v>
       </c>
       <c r="B250" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>430750</v>
+        <v>430783</v>
       </c>
       <c r="R250" t="n">
-        <v>6795558</v>
+        <v>6795818</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25665,57 +25665,65 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129773149</v>
+        <v>129771714</v>
       </c>
       <c r="B251" t="n">
-        <v>78839</v>
+        <v>56926</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>431021</v>
+        <v>430528</v>
       </c>
       <c r="R251" t="n">
-        <v>6795524</v>
+        <v>6795512</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25762,57 +25770,65 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129771761</v>
+        <v>129771718</v>
       </c>
       <c r="B252" t="n">
-        <v>78839</v>
+        <v>56926</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>430865</v>
+        <v>430939</v>
       </c>
       <c r="R252" t="n">
-        <v>6795798</v>
+        <v>6796145</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25871,32 +25887,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129771714</v>
+        <v>129773112</v>
       </c>
       <c r="B253" t="n">
-        <v>56926</v>
+        <v>57896</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25904,7 +25920,7 @@
       <c r="L253" t="inlineStr"/>
       <c r="M253" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N253" t="inlineStr"/>
@@ -25914,10 +25930,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>430528</v>
+        <v>430814</v>
       </c>
       <c r="R253" t="n">
-        <v>6795512</v>
+        <v>6795837</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -25964,65 +25980,57 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>129771718</v>
+        <v>129773149</v>
       </c>
       <c r="B254" t="n">
-        <v>56926</v>
+        <v>78839</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>430939</v>
+        <v>431021</v>
       </c>
       <c r="R254" t="n">
-        <v>6796145</v>
+        <v>6795524</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26069,22 +26077,22 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>129773112</v>
+        <v>129771761</v>
       </c>
       <c r="B255" t="n">
-        <v>57896</v>
+        <v>78839</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26092,42 +26100,34 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>430814</v>
+        <v>430865</v>
       </c>
       <c r="R255" t="n">
-        <v>6795837</v>
+        <v>6795798</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26174,12 +26174,12 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
@@ -26485,10 +26485,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>129773156</v>
+        <v>129773120</v>
       </c>
       <c r="B259" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26496,34 +26496,42 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>430787</v>
+        <v>430694</v>
       </c>
       <c r="R259" t="n">
-        <v>6795816</v>
+        <v>6795368</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -26582,7 +26590,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>129773135</v>
+        <v>129773133</v>
       </c>
       <c r="B260" t="n">
         <v>57733</v>
@@ -26625,10 +26633,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>430938</v>
+        <v>430886</v>
       </c>
       <c r="R260" t="n">
-        <v>6795967</v>
+        <v>6795969</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26687,10 +26695,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>129773120</v>
+        <v>129773156</v>
       </c>
       <c r="B261" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26698,42 +26706,34 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>430694</v>
+        <v>430787</v>
       </c>
       <c r="R261" t="n">
-        <v>6795368</v>
+        <v>6795816</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26792,7 +26792,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>129771744</v>
+        <v>129773135</v>
       </c>
       <c r="B262" t="n">
         <v>57733</v>
@@ -26835,10 +26835,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>430959</v>
+        <v>430938</v>
       </c>
       <c r="R262" t="n">
-        <v>6795543</v>
+        <v>6795967</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26885,19 +26885,19 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>129773133</v>
+        <v>129771744</v>
       </c>
       <c r="B263" t="n">
         <v>57733</v>
@@ -26940,10 +26940,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>430886</v>
+        <v>430959</v>
       </c>
       <c r="R263" t="n">
-        <v>6795969</v>
+        <v>6795543</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -26990,12 +26990,12 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
@@ -27293,10 +27293,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>129773125</v>
+        <v>129771768</v>
       </c>
       <c r="B267" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -27304,42 +27304,34 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>430927</v>
+        <v>430921</v>
       </c>
       <c r="R267" t="n">
-        <v>6795321</v>
+        <v>6796077</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27386,53 +27378,52 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>129773163</v>
+        <v>129773125</v>
       </c>
       <c r="B268" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
-      <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr"/>
       <c r="M268" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N268" t="inlineStr"/>
@@ -27442,10 +27433,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>430632</v>
+        <v>430927</v>
       </c>
       <c r="R268" t="n">
-        <v>6795540</v>
+        <v>6795321</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27486,7 +27477,6 @@
       <c r="AE268" t="b">
         <v>0</v>
       </c>
-      <c r="AF268" t="inlineStr"/>
       <c r="AG268" t="b">
         <v>0</v>
       </c>
@@ -27505,45 +27495,53 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>129771817</v>
+        <v>129771715</v>
       </c>
       <c r="B269" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>430997</v>
+        <v>430568</v>
       </c>
       <c r="R269" t="n">
-        <v>6795879</v>
+        <v>6795570</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27602,45 +27600,53 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>129771794</v>
+        <v>129771720</v>
       </c>
       <c r="B270" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>430951</v>
+        <v>430972</v>
       </c>
       <c r="R270" t="n">
-        <v>6795576</v>
+        <v>6796056</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -27699,10 +27705,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>129773100</v>
+        <v>129773103</v>
       </c>
       <c r="B271" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27710,34 +27716,42 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>430941</v>
+        <v>430952</v>
       </c>
       <c r="R271" t="n">
-        <v>6795869</v>
+        <v>6795876</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27796,7 +27810,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>129771787</v>
+        <v>129771817</v>
       </c>
       <c r="B272" t="n">
         <v>79081</v>
@@ -27831,10 +27845,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>430921</v>
+        <v>430997</v>
       </c>
       <c r="R272" t="n">
-        <v>6795636</v>
+        <v>6795879</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27893,10 +27907,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>129771768</v>
+        <v>129771787</v>
       </c>
       <c r="B273" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -27904,21 +27918,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -27931,7 +27945,7 @@
         <v>430921</v>
       </c>
       <c r="R273" t="n">
-        <v>6796077</v>
+        <v>6795636</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27990,53 +28004,45 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>129773108</v>
+        <v>129771794</v>
       </c>
       <c r="B274" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>430941</v>
+        <v>430951</v>
       </c>
       <c r="R274" t="n">
-        <v>6795862</v>
+        <v>6795576</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28083,22 +28089,22 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>129771715</v>
+        <v>129773163</v>
       </c>
       <c r="B275" t="n">
-        <v>56926</v>
+        <v>8450</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -28106,29 +28112,30 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N275" t="inlineStr"/>
@@ -28138,10 +28145,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>430568</v>
+        <v>430632</v>
       </c>
       <c r="R275" t="n">
-        <v>6795570</v>
+        <v>6795540</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28182,71 +28189,64 @@
       <c r="AE275" t="b">
         <v>0</v>
       </c>
+      <c r="AF275" t="inlineStr"/>
       <c r="AG275" t="b">
         <v>0</v>
       </c>
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>129771720</v>
+        <v>129773100</v>
       </c>
       <c r="B276" t="n">
-        <v>56926</v>
+        <v>79700</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>430972</v>
+        <v>430941</v>
       </c>
       <c r="R276" t="n">
-        <v>6796056</v>
+        <v>6795869</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28293,44 +28293,44 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>129773103</v>
+        <v>129773108</v>
       </c>
       <c r="B277" t="n">
-        <v>57736</v>
+        <v>56926</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -28338,7 +28338,7 @@
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N277" t="inlineStr"/>
@@ -28348,10 +28348,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>430952</v>
+        <v>430941</v>
       </c>
       <c r="R277" t="n">
-        <v>6795876</v>
+        <v>6795862</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -28410,10 +28410,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>129773129</v>
+        <v>129771771</v>
       </c>
       <c r="B278" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28421,42 +28421,34 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>430920</v>
+        <v>430868</v>
       </c>
       <c r="R278" t="n">
-        <v>6796013</v>
+        <v>6795798</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28503,19 +28495,19 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>129773115</v>
+        <v>129773129</v>
       </c>
       <c r="B279" t="n">
         <v>57733</v>
@@ -28558,10 +28550,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>430594</v>
+        <v>430920</v>
       </c>
       <c r="R279" t="n">
-        <v>6795423</v>
+        <v>6796013</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28725,10 +28717,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>129773154</v>
+        <v>129773115</v>
       </c>
       <c r="B281" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28736,34 +28728,42 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>430860</v>
+        <v>430594</v>
       </c>
       <c r="R281" t="n">
-        <v>6795825</v>
+        <v>6795423</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -28822,45 +28822,53 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>129773157</v>
+        <v>129773105</v>
       </c>
       <c r="B282" t="n">
-        <v>78839</v>
+        <v>56926</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>430617</v>
+        <v>430923</v>
       </c>
       <c r="R282" t="n">
-        <v>6795600</v>
+        <v>6796012</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -28919,45 +28927,53 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>129771771</v>
+        <v>129771723</v>
       </c>
       <c r="B283" t="n">
-        <v>78838</v>
+        <v>56926</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>430868</v>
+        <v>430890</v>
       </c>
       <c r="R283" t="n">
-        <v>6795798</v>
+        <v>6795825</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -29113,10 +29129,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>129773105</v>
+        <v>129773160</v>
       </c>
       <c r="B285" t="n">
-        <v>56926</v>
+        <v>8450</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -29124,29 +29140,30 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr"/>
       <c r="M285" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N285" t="inlineStr"/>
@@ -29156,10 +29173,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>430923</v>
+        <v>430844</v>
       </c>
       <c r="R285" t="n">
-        <v>6796012</v>
+        <v>6796058</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29200,6 +29217,7 @@
       <c r="AE285" t="b">
         <v>0</v>
       </c>
+      <c r="AF285" t="inlineStr"/>
       <c r="AG285" t="b">
         <v>0</v>
       </c>
@@ -29218,50 +29236,42 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>129771723</v>
+        <v>129773154</v>
       </c>
       <c r="B286" t="n">
-        <v>56926</v>
+        <v>78839</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>430890</v>
+        <v>430860</v>
       </c>
       <c r="R286" t="n">
         <v>6795825</v>
@@ -29311,66 +29321,57 @@
       <c r="AT286" t="inlineStr"/>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>129773160</v>
+        <v>129773157</v>
       </c>
       <c r="B287" t="n">
-        <v>8450</v>
+        <v>78839</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
-      <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
-      <c r="M287" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>430844</v>
+        <v>430617</v>
       </c>
       <c r="R287" t="n">
-        <v>6796058</v>
+        <v>6795600</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -29411,7 +29412,6 @@
       <c r="AE287" t="b">
         <v>0</v>
       </c>
-      <c r="AF287" t="inlineStr"/>
       <c r="AG287" t="b">
         <v>0</v>
       </c>
@@ -29433,7 +29433,7 @@
         <v>129771819</v>
       </c>
       <c r="B288" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>

--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -13685,7 +13685,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129773137</v>
+        <v>129771737</v>
       </c>
       <c r="B131" t="n">
         <v>57733</v>
@@ -13718,7 +13718,7 @@
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -13728,10 +13728,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>430851</v>
+        <v>430522</v>
       </c>
       <c r="R131" t="n">
-        <v>6795824</v>
+        <v>6795537</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13778,19 +13778,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129771741</v>
+        <v>129773137</v>
       </c>
       <c r="B132" t="n">
         <v>57733</v>
@@ -13823,7 +13823,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -13833,10 +13833,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430784</v>
+        <v>430851</v>
       </c>
       <c r="R132" t="n">
-        <v>6795567</v>
+        <v>6795824</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13883,22 +13883,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129773143</v>
+        <v>129773132</v>
       </c>
       <c r="B133" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13906,34 +13906,42 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>430730</v>
+        <v>430873</v>
       </c>
       <c r="R133" t="n">
-        <v>6795404</v>
+        <v>6795977</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13992,10 +14000,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129773153</v>
+        <v>129771750</v>
       </c>
       <c r="B134" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14003,34 +14011,42 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>430886</v>
+        <v>430973</v>
       </c>
       <c r="R134" t="n">
-        <v>6796067</v>
+        <v>6795877</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14077,22 +14093,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129773113</v>
+        <v>129771741</v>
       </c>
       <c r="B135" t="n">
-        <v>91618</v>
+        <v>57733</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14100,26 +14116,31 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14127,10 +14148,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>430833</v>
+        <v>430784</v>
       </c>
       <c r="R135" t="n">
-        <v>6796045</v>
+        <v>6795567</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14165,40 +14186,34 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>2 st på samma tall.</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129771737</v>
+        <v>129773113</v>
       </c>
       <c r="B136" t="n">
-        <v>57733</v>
+        <v>91620</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14206,31 +14221,26 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -14238,10 +14248,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>430522</v>
+        <v>430833</v>
       </c>
       <c r="R136" t="n">
-        <v>6795537</v>
+        <v>6796045</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14276,34 +14286,40 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>2 st på samma tall.</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129773132</v>
+        <v>129773214</v>
       </c>
       <c r="B137" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14311,42 +14327,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>430873</v>
+        <v>430777</v>
       </c>
       <c r="R137" t="n">
-        <v>6795977</v>
+        <v>6795822</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14405,32 +14413,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129771750</v>
+        <v>129771724</v>
       </c>
       <c r="B138" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14438,7 +14446,7 @@
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -14448,10 +14456,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>430973</v>
+        <v>430884</v>
       </c>
       <c r="R138" t="n">
-        <v>6795877</v>
+        <v>6795785</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14720,53 +14728,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129771724</v>
+        <v>129773143</v>
       </c>
       <c r="B141" t="n">
-        <v>56926</v>
+        <v>78839</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>430884</v>
+        <v>430730</v>
       </c>
       <c r="R141" t="n">
-        <v>6795785</v>
+        <v>6795404</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14813,22 +14813,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129773214</v>
+        <v>129773153</v>
       </c>
       <c r="B142" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14836,21 +14836,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14860,10 +14860,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>430777</v>
+        <v>430886</v>
       </c>
       <c r="R142" t="n">
-        <v>6795822</v>
+        <v>6796067</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14922,7 +14922,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129771810</v>
+        <v>129773210</v>
       </c>
       <c r="B143" t="n">
         <v>79081</v>
@@ -14957,10 +14957,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>430894</v>
+        <v>430968</v>
       </c>
       <c r="R143" t="n">
-        <v>6796084</v>
+        <v>6795883</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15007,22 +15007,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129771783</v>
+        <v>129771745</v>
       </c>
       <c r="B144" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15030,34 +15030,42 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430787</v>
+        <v>430945</v>
       </c>
       <c r="R144" t="n">
-        <v>6795560</v>
+        <v>6796127</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15116,10 +15124,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129773196</v>
+        <v>129771743</v>
       </c>
       <c r="B145" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15127,34 +15135,42 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431034</v>
+        <v>430957</v>
       </c>
       <c r="R145" t="n">
-        <v>6795525</v>
+        <v>6795610</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15201,19 +15217,19 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129773210</v>
+        <v>129771810</v>
       </c>
       <c r="B146" t="n">
         <v>79081</v>
@@ -15248,10 +15264,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>430968</v>
+        <v>430894</v>
       </c>
       <c r="R146" t="n">
-        <v>6795883</v>
+        <v>6796084</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15298,22 +15314,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129771745</v>
+        <v>129771783</v>
       </c>
       <c r="B147" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15321,42 +15337,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>430945</v>
+        <v>430787</v>
       </c>
       <c r="R147" t="n">
-        <v>6796127</v>
+        <v>6795560</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15415,10 +15423,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129771743</v>
+        <v>129773196</v>
       </c>
       <c r="B148" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15426,42 +15434,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>430957</v>
+        <v>431034</v>
       </c>
       <c r="R148" t="n">
-        <v>6795610</v>
+        <v>6795525</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15508,12 +15508,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -16422,45 +16422,53 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129771754</v>
+        <v>129773138</v>
       </c>
       <c r="B158" t="n">
-        <v>92050</v>
+        <v>57733</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>430535</v>
+        <v>430825</v>
       </c>
       <c r="R158" t="n">
-        <v>6795489</v>
+        <v>6795805</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16495,37 +16503,31 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129773138</v>
+        <v>129773124</v>
       </c>
       <c r="B159" t="n">
         <v>57733</v>
@@ -16568,10 +16570,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>430825</v>
+        <v>430865</v>
       </c>
       <c r="R159" t="n">
-        <v>6795805</v>
+        <v>6795387</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16630,7 +16632,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129773124</v>
+        <v>129771753</v>
       </c>
       <c r="B160" t="n">
         <v>57733</v>
@@ -16663,7 +16665,7 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -16673,10 +16675,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>430865</v>
+        <v>430631</v>
       </c>
       <c r="R160" t="n">
-        <v>6795387</v>
+        <v>6795763</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16723,22 +16725,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129771753</v>
+        <v>129773204</v>
       </c>
       <c r="B161" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16746,42 +16748,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>430631</v>
+        <v>430881</v>
       </c>
       <c r="R161" t="n">
-        <v>6795763</v>
+        <v>6795985</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16828,65 +16822,57 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129771713</v>
+        <v>129773183</v>
       </c>
       <c r="B162" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>430542</v>
+        <v>430698</v>
       </c>
       <c r="R162" t="n">
-        <v>6795485</v>
+        <v>6795386</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16933,57 +16919,66 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129773204</v>
+        <v>129773158</v>
       </c>
       <c r="B163" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>430881</v>
+        <v>430704</v>
       </c>
       <c r="R163" t="n">
-        <v>6795985</v>
+        <v>6795457</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17024,6 +17019,7 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -17042,32 +17038,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129773183</v>
+        <v>129771754</v>
       </c>
       <c r="B164" t="n">
-        <v>79081</v>
+        <v>92052</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17077,10 +17073,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>430698</v>
+        <v>430535</v>
       </c>
       <c r="R164" t="n">
-        <v>6795386</v>
+        <v>6795489</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17115,34 +17111,40 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129773158</v>
+        <v>129771713</v>
       </c>
       <c r="B165" t="n">
-        <v>8450</v>
+        <v>56926</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17150,30 +17152,29 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -17183,10 +17184,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>430704</v>
+        <v>430542</v>
       </c>
       <c r="R165" t="n">
-        <v>6795457</v>
+        <v>6795485</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17227,19 +17228,18 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
@@ -17634,10 +17634,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129773117</v>
+        <v>129771732</v>
       </c>
       <c r="B170" t="n">
-        <v>57733</v>
+        <v>91620</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17645,42 +17645,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>430795</v>
+        <v>430972</v>
       </c>
       <c r="R170" t="n">
-        <v>6795376</v>
+        <v>6795851</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17727,22 +17719,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129773123</v>
+        <v>129773179</v>
       </c>
       <c r="B171" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17750,42 +17742,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>430845</v>
+        <v>430611</v>
       </c>
       <c r="R171" t="n">
-        <v>6795412</v>
+        <v>6795443</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17844,10 +17828,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129771732</v>
+        <v>129773195</v>
       </c>
       <c r="B172" t="n">
-        <v>91618</v>
+        <v>79081</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17855,21 +17839,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17879,10 +17863,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>430972</v>
+        <v>431010</v>
       </c>
       <c r="R172" t="n">
-        <v>6795851</v>
+        <v>6795515</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17929,65 +17913,57 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129773109</v>
+        <v>129771790</v>
       </c>
       <c r="B173" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>430816</v>
+        <v>430957</v>
       </c>
       <c r="R173" t="n">
-        <v>6795834</v>
+        <v>6795608</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18034,57 +18010,65 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129773146</v>
+        <v>129773109</v>
       </c>
       <c r="B174" t="n">
-        <v>78839</v>
+        <v>56926</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>430970</v>
+        <v>430816</v>
       </c>
       <c r="R174" t="n">
-        <v>6795287</v>
+        <v>6795834</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18143,7 +18127,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129771757</v>
+        <v>129773146</v>
       </c>
       <c r="B175" t="n">
         <v>78839</v>
@@ -18178,10 +18162,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>430923</v>
+        <v>430970</v>
       </c>
       <c r="R175" t="n">
-        <v>6795582</v>
+        <v>6795287</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18228,22 +18212,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129773179</v>
+        <v>129771757</v>
       </c>
       <c r="B176" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18251,21 +18235,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18275,10 +18259,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>430611</v>
+        <v>430923</v>
       </c>
       <c r="R176" t="n">
-        <v>6795443</v>
+        <v>6795582</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18325,22 +18309,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129773195</v>
+        <v>129773117</v>
       </c>
       <c r="B177" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18348,34 +18332,42 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>431010</v>
+        <v>430795</v>
       </c>
       <c r="R177" t="n">
-        <v>6795515</v>
+        <v>6795376</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18434,10 +18426,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129771790</v>
+        <v>129773123</v>
       </c>
       <c r="B178" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18445,34 +18437,42 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>430957</v>
+        <v>430845</v>
       </c>
       <c r="R178" t="n">
-        <v>6795608</v>
+        <v>6795412</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18519,22 +18519,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129773150</v>
+        <v>129773128</v>
       </c>
       <c r="B179" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18542,34 +18542,42 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>431067</v>
+        <v>430918</v>
       </c>
       <c r="R179" t="n">
-        <v>6795549</v>
+        <v>6795985</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18628,10 +18636,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129773168</v>
+        <v>129771803</v>
       </c>
       <c r="B180" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18639,21 +18647,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18663,10 +18671,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>430617</v>
+        <v>430878</v>
       </c>
       <c r="R180" t="n">
-        <v>6795600</v>
+        <v>6795999</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18713,22 +18721,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129773128</v>
+        <v>129773197</v>
       </c>
       <c r="B181" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18736,31 +18744,26 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
@@ -18768,10 +18771,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>430918</v>
+        <v>431062</v>
       </c>
       <c r="R181" t="n">
-        <v>6795985</v>
+        <v>6795533</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18812,6 +18815,7 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
+      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
@@ -18830,10 +18834,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129771803</v>
+        <v>129773168</v>
       </c>
       <c r="B182" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18841,21 +18845,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18865,10 +18869,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>430878</v>
+        <v>430617</v>
       </c>
       <c r="R182" t="n">
-        <v>6795999</v>
+        <v>6795600</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18915,19 +18919,19 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129773197</v>
+        <v>129771811</v>
       </c>
       <c r="B183" t="n">
         <v>79081</v>
@@ -18956,19 +18960,16 @@
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>431062</v>
+        <v>430910</v>
       </c>
       <c r="R183" t="n">
-        <v>6795533</v>
+        <v>6796078</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19009,29 +19010,28 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129771811</v>
+        <v>129773150</v>
       </c>
       <c r="B184" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19039,21 +19039,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19063,10 +19063,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>430910</v>
+        <v>431067</v>
       </c>
       <c r="R184" t="n">
-        <v>6796078</v>
+        <v>6795549</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19113,22 +19113,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129771766</v>
+        <v>129773122</v>
       </c>
       <c r="B185" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19136,34 +19136,42 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>430922</v>
+        <v>430702</v>
       </c>
       <c r="R185" t="n">
-        <v>6795638</v>
+        <v>6795444</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19210,57 +19218,65 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129771707</v>
+        <v>129771764</v>
       </c>
       <c r="B186" t="n">
-        <v>79700</v>
+        <v>58106</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>430973</v>
+        <v>430863</v>
       </c>
       <c r="R186" t="n">
-        <v>6795529</v>
+        <v>6795796</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19319,10 +19335,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129771807</v>
+        <v>129771729</v>
       </c>
       <c r="B187" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19330,21 +19346,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19354,10 +19370,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430914</v>
+        <v>430543</v>
       </c>
       <c r="R187" t="n">
-        <v>6796105</v>
+        <v>6795503</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19416,32 +19432,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129771792</v>
+        <v>129771703</v>
       </c>
       <c r="B188" t="n">
-        <v>79081</v>
+        <v>91563</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19451,10 +19467,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430945</v>
+        <v>430735</v>
       </c>
       <c r="R188" t="n">
-        <v>6795579</v>
+        <v>6795805</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19513,7 +19529,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129771812</v>
+        <v>129771807</v>
       </c>
       <c r="B189" t="n">
         <v>79081</v>
@@ -19548,10 +19564,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430903</v>
+        <v>430914</v>
       </c>
       <c r="R189" t="n">
-        <v>6796058</v>
+        <v>6796105</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19610,10 +19626,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129771728</v>
+        <v>129771792</v>
       </c>
       <c r="B190" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19621,42 +19637,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430863</v>
+        <v>430945</v>
       </c>
       <c r="R190" t="n">
-        <v>6795800</v>
+        <v>6795579</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19715,10 +19723,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129771729</v>
+        <v>129771766</v>
       </c>
       <c r="B191" t="n">
-        <v>91618</v>
+        <v>78838</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19726,21 +19734,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19750,10 +19758,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430543</v>
+        <v>430922</v>
       </c>
       <c r="R191" t="n">
-        <v>6795503</v>
+        <v>6795638</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19812,32 +19820,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129771703</v>
+        <v>129771812</v>
       </c>
       <c r="B192" t="n">
-        <v>91561</v>
+        <v>79081</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19847,10 +19855,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430735</v>
+        <v>430903</v>
       </c>
       <c r="R192" t="n">
-        <v>6795805</v>
+        <v>6796058</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19909,10 +19917,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129773122</v>
+        <v>129771707</v>
       </c>
       <c r="B193" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19920,42 +19928,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430702</v>
+        <v>430973</v>
       </c>
       <c r="R193" t="n">
-        <v>6795444</v>
+        <v>6795529</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20002,44 +20002,44 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129771764</v>
+        <v>129771728</v>
       </c>
       <c r="B194" t="n">
-        <v>58106</v>
+        <v>57896</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20047,7 +20047,7 @@
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N194" t="inlineStr"/>
@@ -20060,7 +20060,7 @@
         <v>430863</v>
       </c>
       <c r="R194" t="n">
-        <v>6795796</v>
+        <v>6795800</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20119,10 +20119,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129773207</v>
+        <v>129773119</v>
       </c>
       <c r="B195" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20130,34 +20130,42 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430947</v>
+        <v>430692</v>
       </c>
       <c r="R195" t="n">
-        <v>6795977</v>
+        <v>6795373</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20216,54 +20224,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129771762</v>
+        <v>129771814</v>
       </c>
       <c r="B196" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430746</v>
+        <v>430944</v>
       </c>
       <c r="R196" t="n">
-        <v>6795566</v>
+        <v>6796075</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20304,7 +20303,6 @@
       <c r="AE196" t="b">
         <v>0</v>
       </c>
-      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -20323,10 +20321,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129773119</v>
+        <v>129771796</v>
       </c>
       <c r="B197" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20334,42 +20332,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>430692</v>
+        <v>430984</v>
       </c>
       <c r="R197" t="n">
-        <v>6795373</v>
+        <v>6795518</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20416,19 +20406,19 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129771814</v>
+        <v>129773211</v>
       </c>
       <c r="B198" t="n">
         <v>79081</v>
@@ -20463,10 +20453,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>430944</v>
+        <v>430815</v>
       </c>
       <c r="R198" t="n">
-        <v>6796075</v>
+        <v>6795818</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20513,19 +20503,19 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129771796</v>
+        <v>129773207</v>
       </c>
       <c r="B199" t="n">
         <v>79081</v>
@@ -20560,10 +20550,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>430984</v>
+        <v>430947</v>
       </c>
       <c r="R199" t="n">
-        <v>6795518</v>
+        <v>6795977</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20610,57 +20600,66 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129773211</v>
+        <v>129771762</v>
       </c>
       <c r="B200" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>430815</v>
+        <v>430746</v>
       </c>
       <c r="R200" t="n">
-        <v>6795818</v>
+        <v>6795566</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20701,28 +20700,29 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129771706</v>
+        <v>129773205</v>
       </c>
       <c r="B201" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20730,21 +20730,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>430935</v>
+        <v>430907</v>
       </c>
       <c r="R201" t="n">
-        <v>6795595</v>
+        <v>6795973</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20804,65 +20804,57 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129771725</v>
+        <v>129771808</v>
       </c>
       <c r="B202" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>430867</v>
+        <v>430894</v>
       </c>
       <c r="R202" t="n">
-        <v>6795794</v>
+        <v>6796093</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20921,45 +20913,53 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129773205</v>
+        <v>129771725</v>
       </c>
       <c r="B203" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>430907</v>
+        <v>430867</v>
       </c>
       <c r="R203" t="n">
-        <v>6795973</v>
+        <v>6795794</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21006,22 +21006,22 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129771808</v>
+        <v>129771706</v>
       </c>
       <c r="B204" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21029,21 +21029,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21053,10 +21053,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>430894</v>
+        <v>430935</v>
       </c>
       <c r="R204" t="n">
-        <v>6796093</v>
+        <v>6795595</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21115,45 +21115,54 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129773145</v>
+        <v>129773161</v>
       </c>
       <c r="B205" t="n">
-        <v>78839</v>
+        <v>8450</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>430935</v>
+        <v>430911</v>
       </c>
       <c r="R205" t="n">
-        <v>6795319</v>
+        <v>6795982</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21194,6 +21203,7 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
+      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
@@ -21212,7 +21222,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129771758</v>
+        <v>129773145</v>
       </c>
       <c r="B206" t="n">
         <v>78839</v>
@@ -21247,10 +21257,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>430921</v>
+        <v>430935</v>
       </c>
       <c r="R206" t="n">
-        <v>6795636</v>
+        <v>6795319</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21297,66 +21307,57 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129773161</v>
+        <v>129771758</v>
       </c>
       <c r="B207" t="n">
-        <v>8450</v>
+        <v>78839</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>430911</v>
+        <v>430921</v>
       </c>
       <c r="R207" t="n">
-        <v>6795982</v>
+        <v>6795636</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21397,29 +21398,28 @@
       <c r="AE207" t="b">
         <v>0</v>
       </c>
-      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129773130</v>
+        <v>129771795</v>
       </c>
       <c r="B208" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21427,42 +21427,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>430893</v>
+        <v>430956</v>
       </c>
       <c r="R208" t="n">
-        <v>6796035</v>
+        <v>6795564</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21509,22 +21501,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129771795</v>
+        <v>129771769</v>
       </c>
       <c r="B209" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21532,21 +21524,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -21556,10 +21548,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>430956</v>
+        <v>430973</v>
       </c>
       <c r="R209" t="n">
-        <v>6795564</v>
+        <v>6795852</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21812,10 +21804,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129771769</v>
+        <v>129773130</v>
       </c>
       <c r="B212" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21823,34 +21815,42 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>430973</v>
+        <v>430893</v>
       </c>
       <c r="R212" t="n">
-        <v>6795852</v>
+        <v>6796035</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21897,12 +21897,12 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
@@ -22491,10 +22491,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129773166</v>
+        <v>129771759</v>
       </c>
       <c r="B219" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22502,21 +22502,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22526,10 +22526,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>430897</v>
+        <v>430973</v>
       </c>
       <c r="R219" t="n">
-        <v>6795988</v>
+        <v>6795852</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22576,22 +22576,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129773190</v>
+        <v>129773166</v>
       </c>
       <c r="B220" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22599,21 +22599,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22623,10 +22623,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>430984</v>
+        <v>430897</v>
       </c>
       <c r="R220" t="n">
-        <v>6795313</v>
+        <v>6795988</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22685,7 +22685,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129773189</v>
+        <v>129773190</v>
       </c>
       <c r="B221" t="n">
         <v>79081</v>
@@ -22720,10 +22720,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>430904</v>
+        <v>430984</v>
       </c>
       <c r="R221" t="n">
-        <v>6795339</v>
+        <v>6795313</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22782,7 +22782,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129771813</v>
+        <v>129773189</v>
       </c>
       <c r="B222" t="n">
         <v>79081</v>
@@ -22817,10 +22817,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>430910</v>
+        <v>430904</v>
       </c>
       <c r="R222" t="n">
-        <v>6796073</v>
+        <v>6795339</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22867,19 +22867,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129773177</v>
+        <v>129771813</v>
       </c>
       <c r="B223" t="n">
         <v>79081</v>
@@ -22914,10 +22914,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430633</v>
+        <v>430910</v>
       </c>
       <c r="R223" t="n">
-        <v>6795435</v>
+        <v>6796073</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22964,22 +22964,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129771736</v>
+        <v>129773177</v>
       </c>
       <c r="B224" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22987,42 +22987,34 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>430531</v>
+        <v>430633</v>
       </c>
       <c r="R224" t="n">
-        <v>6795488</v>
+        <v>6795435</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23069,19 +23061,19 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129771740</v>
+        <v>129771736</v>
       </c>
       <c r="B225" t="n">
         <v>57733</v>
@@ -23124,10 +23116,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>430754</v>
+        <v>430531</v>
       </c>
       <c r="R225" t="n">
-        <v>6795593</v>
+        <v>6795488</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23186,10 +23178,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129771759</v>
+        <v>129771740</v>
       </c>
       <c r="B226" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23197,34 +23189,42 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>430973</v>
+        <v>430754</v>
       </c>
       <c r="R226" t="n">
-        <v>6795852</v>
+        <v>6795593</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23477,10 +23477,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129773201</v>
+        <v>129771770</v>
       </c>
       <c r="B229" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23488,21 +23488,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23512,10 +23512,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>430907</v>
+        <v>430983</v>
       </c>
       <c r="R229" t="n">
-        <v>6796028</v>
+        <v>6795850</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23562,19 +23562,19 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129771809</v>
+        <v>129773201</v>
       </c>
       <c r="B230" t="n">
         <v>79081</v>
@@ -23609,10 +23609,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>430906</v>
+        <v>430907</v>
       </c>
       <c r="R230" t="n">
-        <v>6796088</v>
+        <v>6796028</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23659,19 +23659,19 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129773178</v>
+        <v>129771809</v>
       </c>
       <c r="B231" t="n">
         <v>79081</v>
@@ -23706,10 +23706,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>430590</v>
+        <v>430906</v>
       </c>
       <c r="R231" t="n">
-        <v>6795429</v>
+        <v>6796088</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23756,22 +23756,22 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129771770</v>
+        <v>129773178</v>
       </c>
       <c r="B232" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23779,21 +23779,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23803,10 +23803,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>430983</v>
+        <v>430590</v>
       </c>
       <c r="R232" t="n">
-        <v>6795850</v>
+        <v>6795429</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23853,12 +23853,12 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
@@ -24062,7 +24062,7 @@
         <v>129771731</v>
       </c>
       <c r="B235" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24156,40 +24156,41 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129771752</v>
+        <v>129773162</v>
       </c>
       <c r="B236" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr"/>
       <c r="M236" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N236" t="inlineStr"/>
@@ -24199,10 +24200,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>430801</v>
+        <v>430613</v>
       </c>
       <c r="R236" t="n">
-        <v>6795756</v>
+        <v>6795723</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24243,72 +24244,64 @@
       <c r="AE236" t="b">
         <v>0</v>
       </c>
+      <c r="AF236" t="inlineStr"/>
       <c r="AG236" t="b">
         <v>0</v>
       </c>
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129773162</v>
+        <v>129773101</v>
       </c>
       <c r="B237" t="n">
-        <v>8450</v>
+        <v>79671</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>430613</v>
+        <v>430763</v>
       </c>
       <c r="R237" t="n">
-        <v>6795723</v>
+        <v>6795472</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24349,7 +24342,6 @@
       <c r="AE237" t="b">
         <v>0</v>
       </c>
-      <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="b">
         <v>0</v>
       </c>
@@ -24368,10 +24360,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129771805</v>
+        <v>129771752</v>
       </c>
       <c r="B238" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24379,34 +24371,42 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>430875</v>
+        <v>430801</v>
       </c>
       <c r="R238" t="n">
-        <v>6796089</v>
+        <v>6795756</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24465,10 +24465,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129773101</v>
+        <v>129771805</v>
       </c>
       <c r="B239" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24476,21 +24476,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24500,10 +24500,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>430763</v>
+        <v>430875</v>
       </c>
       <c r="R239" t="n">
-        <v>6795472</v>
+        <v>6796089</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24550,12 +24550,12 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
@@ -24565,7 +24565,7 @@
         <v>129771730</v>
       </c>
       <c r="B240" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24659,10 +24659,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129771742</v>
+        <v>129771785</v>
       </c>
       <c r="B241" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24670,42 +24670,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>430934</v>
+        <v>430936</v>
       </c>
       <c r="R241" t="n">
-        <v>6795641</v>
+        <v>6795608</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24764,10 +24756,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129771747</v>
+        <v>129771806</v>
       </c>
       <c r="B242" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24775,42 +24767,34 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>430947</v>
+        <v>430974</v>
       </c>
       <c r="R242" t="n">
-        <v>6796064</v>
+        <v>6796123</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24869,10 +24853,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129771746</v>
+        <v>129771784</v>
       </c>
       <c r="B243" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24880,42 +24864,34 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>430942</v>
+        <v>430920</v>
       </c>
       <c r="R243" t="n">
-        <v>6796133</v>
+        <v>6795536</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24974,10 +24950,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129773121</v>
+        <v>129773213</v>
       </c>
       <c r="B244" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -24985,42 +24961,34 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>430707</v>
+        <v>430783</v>
       </c>
       <c r="R244" t="n">
-        <v>6795375</v>
+        <v>6795818</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25079,7 +25047,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129771739</v>
+        <v>129771747</v>
       </c>
       <c r="B245" t="n">
         <v>57733</v>
@@ -25122,10 +25090,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>430752</v>
+        <v>430947</v>
       </c>
       <c r="R245" t="n">
-        <v>6795559</v>
+        <v>6796064</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25184,32 +25152,32 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>129771716</v>
+        <v>129771742</v>
       </c>
       <c r="B246" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25217,7 +25185,7 @@
       <c r="L246" t="inlineStr"/>
       <c r="M246" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N246" t="inlineStr"/>
@@ -25227,10 +25195,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>430750</v>
+        <v>430934</v>
       </c>
       <c r="R246" t="n">
-        <v>6795558</v>
+        <v>6795641</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25289,10 +25257,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>129771785</v>
+        <v>129771746</v>
       </c>
       <c r="B247" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25300,34 +25268,42 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>430936</v>
+        <v>430942</v>
       </c>
       <c r="R247" t="n">
-        <v>6795608</v>
+        <v>6796133</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25386,10 +25362,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129771806</v>
+        <v>129773121</v>
       </c>
       <c r="B248" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25397,34 +25373,42 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>430974</v>
+        <v>430707</v>
       </c>
       <c r="R248" t="n">
-        <v>6796123</v>
+        <v>6795375</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25471,22 +25455,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>129771784</v>
+        <v>129771739</v>
       </c>
       <c r="B249" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25494,34 +25478,42 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>430920</v>
+        <v>430752</v>
       </c>
       <c r="R249" t="n">
-        <v>6795536</v>
+        <v>6795559</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25580,45 +25572,53 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>129773213</v>
+        <v>129771716</v>
       </c>
       <c r="B250" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>430783</v>
+        <v>430750</v>
       </c>
       <c r="R250" t="n">
-        <v>6795818</v>
+        <v>6795558</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25665,65 +25665,57 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129771714</v>
+        <v>129773202</v>
       </c>
       <c r="B251" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>430528</v>
+        <v>430858</v>
       </c>
       <c r="R251" t="n">
-        <v>6795512</v>
+        <v>6796064</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25770,65 +25762,57 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129771718</v>
+        <v>129771791</v>
       </c>
       <c r="B252" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>430939</v>
+        <v>430959</v>
       </c>
       <c r="R252" t="n">
-        <v>6796145</v>
+        <v>6795606</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25887,32 +25871,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129773112</v>
+        <v>129771714</v>
       </c>
       <c r="B253" t="n">
-        <v>57896</v>
+        <v>56926</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25920,7 +25904,7 @@
       <c r="L253" t="inlineStr"/>
       <c r="M253" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N253" t="inlineStr"/>
@@ -25930,10 +25914,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>430814</v>
+        <v>430528</v>
       </c>
       <c r="R253" t="n">
-        <v>6795837</v>
+        <v>6795512</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -25980,57 +25964,65 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>129773149</v>
+        <v>129771718</v>
       </c>
       <c r="B254" t="n">
-        <v>78839</v>
+        <v>56926</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>431021</v>
+        <v>430939</v>
       </c>
       <c r="R254" t="n">
-        <v>6795524</v>
+        <v>6796145</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26077,22 +26069,22 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>129771761</v>
+        <v>129773112</v>
       </c>
       <c r="B255" t="n">
-        <v>78839</v>
+        <v>57896</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26100,34 +26092,42 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>430865</v>
+        <v>430814</v>
       </c>
       <c r="R255" t="n">
-        <v>6795798</v>
+        <v>6795837</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26174,12 +26174,12 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
@@ -26291,10 +26291,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>129773202</v>
+        <v>129773149</v>
       </c>
       <c r="B257" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -26302,21 +26302,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26326,10 +26326,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>430858</v>
+        <v>431021</v>
       </c>
       <c r="R257" t="n">
-        <v>6796064</v>
+        <v>6795524</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26388,10 +26388,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>129771791</v>
+        <v>129771761</v>
       </c>
       <c r="B258" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26399,21 +26399,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26423,10 +26423,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>430959</v>
+        <v>430865</v>
       </c>
       <c r="R258" t="n">
-        <v>6795606</v>
+        <v>6795798</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26485,7 +26485,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>129773120</v>
+        <v>129773135</v>
       </c>
       <c r="B259" t="n">
         <v>57733</v>
@@ -26528,10 +26528,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>430694</v>
+        <v>430938</v>
       </c>
       <c r="R259" t="n">
-        <v>6795368</v>
+        <v>6795967</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -26590,7 +26590,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>129773133</v>
+        <v>129773120</v>
       </c>
       <c r="B260" t="n">
         <v>57733</v>
@@ -26633,10 +26633,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>430886</v>
+        <v>430694</v>
       </c>
       <c r="R260" t="n">
-        <v>6795969</v>
+        <v>6795368</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26695,10 +26695,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>129773156</v>
+        <v>129771744</v>
       </c>
       <c r="B261" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26706,34 +26706,42 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>430787</v>
+        <v>430959</v>
       </c>
       <c r="R261" t="n">
-        <v>6795816</v>
+        <v>6795543</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26780,19 +26788,19 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>129773135</v>
+        <v>129773133</v>
       </c>
       <c r="B262" t="n">
         <v>57733</v>
@@ -26835,10 +26843,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>430938</v>
+        <v>430886</v>
       </c>
       <c r="R262" t="n">
-        <v>6795967</v>
+        <v>6795969</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26897,10 +26905,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>129771744</v>
+        <v>129773180</v>
       </c>
       <c r="B263" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -26908,42 +26916,34 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>430959</v>
+        <v>430789</v>
       </c>
       <c r="R263" t="n">
-        <v>6795543</v>
+        <v>6795377</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -26990,12 +26990,12 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
@@ -27196,10 +27196,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>129773180</v>
+        <v>129773156</v>
       </c>
       <c r="B266" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27207,21 +27207,21 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -27231,10 +27231,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>430789</v>
+        <v>430787</v>
       </c>
       <c r="R266" t="n">
-        <v>6795377</v>
+        <v>6795816</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27293,45 +27293,54 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>129771768</v>
+        <v>129773163</v>
       </c>
       <c r="B267" t="n">
-        <v>78838</v>
+        <v>8450</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>430921</v>
+        <v>430632</v>
       </c>
       <c r="R267" t="n">
-        <v>6796077</v>
+        <v>6795540</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27372,18 +27381,19 @@
       <c r="AE267" t="b">
         <v>0</v>
       </c>
+      <c r="AF267" t="inlineStr"/>
       <c r="AG267" t="b">
         <v>0</v>
       </c>
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
@@ -27495,53 +27505,45 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>129771715</v>
+        <v>129771817</v>
       </c>
       <c r="B269" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>430568</v>
+        <v>430997</v>
       </c>
       <c r="R269" t="n">
-        <v>6795570</v>
+        <v>6795879</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27600,53 +27602,45 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>129771720</v>
+        <v>129771787</v>
       </c>
       <c r="B270" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>430972</v>
+        <v>430921</v>
       </c>
       <c r="R270" t="n">
-        <v>6796056</v>
+        <v>6795636</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -27705,10 +27699,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>129773103</v>
+        <v>129773100</v>
       </c>
       <c r="B271" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27716,42 +27710,34 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>430952</v>
+        <v>430941</v>
       </c>
       <c r="R271" t="n">
-        <v>6795876</v>
+        <v>6795869</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27810,7 +27796,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>129771817</v>
+        <v>129771794</v>
       </c>
       <c r="B272" t="n">
         <v>79081</v>
@@ -27845,10 +27831,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>430997</v>
+        <v>430951</v>
       </c>
       <c r="R272" t="n">
-        <v>6795879</v>
+        <v>6795576</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27907,10 +27893,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>129771787</v>
+        <v>129771768</v>
       </c>
       <c r="B273" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -27918,21 +27904,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -27945,7 +27931,7 @@
         <v>430921</v>
       </c>
       <c r="R273" t="n">
-        <v>6795636</v>
+        <v>6796077</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -28004,45 +27990,53 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>129771794</v>
+        <v>129773108</v>
       </c>
       <c r="B274" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>430951</v>
+        <v>430941</v>
       </c>
       <c r="R274" t="n">
-        <v>6795576</v>
+        <v>6795862</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28089,22 +28083,22 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>129773163</v>
+        <v>129771715</v>
       </c>
       <c r="B275" t="n">
-        <v>8450</v>
+        <v>56926</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -28112,30 +28106,29 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N275" t="inlineStr"/>
@@ -28145,10 +28138,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>430632</v>
+        <v>430568</v>
       </c>
       <c r="R275" t="n">
-        <v>6795540</v>
+        <v>6795570</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28189,64 +28182,71 @@
       <c r="AE275" t="b">
         <v>0</v>
       </c>
-      <c r="AF275" t="inlineStr"/>
       <c r="AG275" t="b">
         <v>0</v>
       </c>
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>129773100</v>
+        <v>129771720</v>
       </c>
       <c r="B276" t="n">
-        <v>79700</v>
+        <v>56926</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>430941</v>
+        <v>430972</v>
       </c>
       <c r="R276" t="n">
-        <v>6795869</v>
+        <v>6796056</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28293,44 +28293,44 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>129773108</v>
+        <v>129773103</v>
       </c>
       <c r="B277" t="n">
-        <v>56926</v>
+        <v>57736</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -28338,7 +28338,7 @@
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N277" t="inlineStr"/>
@@ -28348,10 +28348,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>430941</v>
+        <v>430952</v>
       </c>
       <c r="R277" t="n">
-        <v>6795862</v>
+        <v>6795876</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -28410,45 +28410,53 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>129771771</v>
+        <v>129773105</v>
       </c>
       <c r="B278" t="n">
-        <v>78838</v>
+        <v>56926</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>430868</v>
+        <v>430923</v>
       </c>
       <c r="R278" t="n">
-        <v>6795798</v>
+        <v>6796012</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28495,44 +28503,44 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>129773129</v>
+        <v>129771723</v>
       </c>
       <c r="B279" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28540,7 +28548,7 @@
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N279" t="inlineStr"/>
@@ -28550,10 +28558,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>430920</v>
+        <v>430890</v>
       </c>
       <c r="R279" t="n">
-        <v>6796013</v>
+        <v>6795825</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28600,52 +28608,53 @@
       <c r="AT279" t="inlineStr"/>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>129771748</v>
+        <v>129773160</v>
       </c>
       <c r="B280" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N280" t="inlineStr"/>
@@ -28655,10 +28664,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>430982</v>
+        <v>430844</v>
       </c>
       <c r="R280" t="n">
-        <v>6795907</v>
+        <v>6796058</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28699,25 +28708,26 @@
       <c r="AE280" t="b">
         <v>0</v>
       </c>
+      <c r="AF280" t="inlineStr"/>
       <c r="AG280" t="b">
         <v>0</v>
       </c>
       <c r="AT280" t="inlineStr"/>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>129773115</v>
+        <v>129773129</v>
       </c>
       <c r="B281" t="n">
         <v>57733</v>
@@ -28760,10 +28770,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>430594</v>
+        <v>430920</v>
       </c>
       <c r="R281" t="n">
-        <v>6795423</v>
+        <v>6796013</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -28822,32 +28832,32 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>129773105</v>
+        <v>129773115</v>
       </c>
       <c r="B282" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -28855,7 +28865,7 @@
       <c r="L282" t="inlineStr"/>
       <c r="M282" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N282" t="inlineStr"/>
@@ -28865,10 +28875,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>430923</v>
+        <v>430594</v>
       </c>
       <c r="R282" t="n">
-        <v>6796012</v>
+        <v>6795423</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -28927,32 +28937,32 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>129771723</v>
+        <v>129771748</v>
       </c>
       <c r="B283" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -28960,7 +28970,7 @@
       <c r="L283" t="inlineStr"/>
       <c r="M283" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N283" t="inlineStr"/>
@@ -28970,10 +28980,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>430890</v>
+        <v>430982</v>
       </c>
       <c r="R283" t="n">
-        <v>6795825</v>
+        <v>6795907</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -29032,10 +29042,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>129771800</v>
+        <v>129771771</v>
       </c>
       <c r="B284" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -29043,21 +29053,21 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29067,10 +29077,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>431011</v>
+        <v>430868</v>
       </c>
       <c r="R284" t="n">
-        <v>6795579</v>
+        <v>6795798</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29129,54 +29139,45 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>129773160</v>
+        <v>129771800</v>
       </c>
       <c r="B285" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
-      <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr"/>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>430844</v>
+        <v>431011</v>
       </c>
       <c r="R285" t="n">
-        <v>6796058</v>
+        <v>6795579</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29217,19 +29218,18 @@
       <c r="AE285" t="b">
         <v>0</v>
       </c>
-      <c r="AF285" t="inlineStr"/>
       <c r="AG285" t="b">
         <v>0</v>
       </c>
       <c r="AT285" t="inlineStr"/>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
@@ -29433,7 +29433,7 @@
         <v>129771819</v>
       </c>
       <c r="B288" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>

--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -14922,10 +14922,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129773210</v>
+        <v>129771745</v>
       </c>
       <c r="B143" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14933,34 +14933,42 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>430968</v>
+        <v>430945</v>
       </c>
       <c r="R143" t="n">
-        <v>6795883</v>
+        <v>6796127</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15007,19 +15015,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129771745</v>
+        <v>129771743</v>
       </c>
       <c r="B144" t="n">
         <v>57733</v>
@@ -15062,10 +15070,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430945</v>
+        <v>430957</v>
       </c>
       <c r="R144" t="n">
-        <v>6796127</v>
+        <v>6795610</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15124,10 +15132,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129771743</v>
+        <v>129771810</v>
       </c>
       <c r="B145" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15135,42 +15143,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>430957</v>
+        <v>430894</v>
       </c>
       <c r="R145" t="n">
-        <v>6795610</v>
+        <v>6796084</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15229,7 +15229,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129771810</v>
+        <v>129771783</v>
       </c>
       <c r="B146" t="n">
         <v>79081</v>
@@ -15264,10 +15264,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>430894</v>
+        <v>430787</v>
       </c>
       <c r="R146" t="n">
-        <v>6796084</v>
+        <v>6795560</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15326,7 +15326,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129771783</v>
+        <v>129773196</v>
       </c>
       <c r="B147" t="n">
         <v>79081</v>
@@ -15361,10 +15361,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>430787</v>
+        <v>431034</v>
       </c>
       <c r="R147" t="n">
-        <v>6795560</v>
+        <v>6795525</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15411,19 +15411,19 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129773196</v>
+        <v>129773210</v>
       </c>
       <c r="B148" t="n">
         <v>79081</v>
@@ -15458,10 +15458,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>431034</v>
+        <v>430968</v>
       </c>
       <c r="R148" t="n">
-        <v>6795525</v>
+        <v>6795883</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18636,10 +18636,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129771803</v>
+        <v>129773150</v>
       </c>
       <c r="B180" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18647,21 +18647,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18671,10 +18671,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>430878</v>
+        <v>431067</v>
       </c>
       <c r="R180" t="n">
-        <v>6795999</v>
+        <v>6795549</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18721,19 +18721,19 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129773197</v>
+        <v>129771803</v>
       </c>
       <c r="B181" t="n">
         <v>79081</v>
@@ -18762,19 +18762,16 @@
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>431062</v>
+        <v>430878</v>
       </c>
       <c r="R181" t="n">
-        <v>6795533</v>
+        <v>6795999</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18815,29 +18812,28 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
-      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129773168</v>
+        <v>129773197</v>
       </c>
       <c r="B182" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18845,34 +18841,37 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>430617</v>
+        <v>431062</v>
       </c>
       <c r="R182" t="n">
-        <v>6795600</v>
+        <v>6795533</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18913,6 +18912,7 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
+      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
@@ -18931,10 +18931,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129771811</v>
+        <v>129773168</v>
       </c>
       <c r="B183" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18942,21 +18942,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18966,10 +18966,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>430910</v>
+        <v>430617</v>
       </c>
       <c r="R183" t="n">
-        <v>6796078</v>
+        <v>6795600</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19016,22 +19016,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129773150</v>
+        <v>129771811</v>
       </c>
       <c r="B184" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19039,21 +19039,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19063,10 +19063,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>431067</v>
+        <v>430910</v>
       </c>
       <c r="R184" t="n">
-        <v>6795549</v>
+        <v>6796078</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19113,22 +19113,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129773122</v>
+        <v>129771728</v>
       </c>
       <c r="B185" t="n">
-        <v>57733</v>
+        <v>57896</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19136,21 +19136,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19158,7 +19158,7 @@
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N185" t="inlineStr"/>
@@ -19168,10 +19168,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>430702</v>
+        <v>430863</v>
       </c>
       <c r="R185" t="n">
-        <v>6795444</v>
+        <v>6795800</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19218,12 +19218,12 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -19335,10 +19335,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129771729</v>
+        <v>129773122</v>
       </c>
       <c r="B187" t="n">
-        <v>91620</v>
+        <v>57733</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19346,34 +19346,42 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430543</v>
+        <v>430702</v>
       </c>
       <c r="R187" t="n">
-        <v>6795503</v>
+        <v>6795444</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19420,44 +19428,44 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129771703</v>
+        <v>129771729</v>
       </c>
       <c r="B188" t="n">
-        <v>91563</v>
+        <v>91620</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19467,10 +19475,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430735</v>
+        <v>430543</v>
       </c>
       <c r="R188" t="n">
-        <v>6795805</v>
+        <v>6795503</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19529,32 +19537,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129771807</v>
+        <v>129771703</v>
       </c>
       <c r="B189" t="n">
-        <v>79081</v>
+        <v>91563</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19564,10 +19572,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430914</v>
+        <v>430735</v>
       </c>
       <c r="R189" t="n">
-        <v>6796105</v>
+        <v>6795805</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19626,7 +19634,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129771792</v>
+        <v>129771807</v>
       </c>
       <c r="B190" t="n">
         <v>79081</v>
@@ -19661,10 +19669,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430945</v>
+        <v>430914</v>
       </c>
       <c r="R190" t="n">
-        <v>6795579</v>
+        <v>6796105</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19723,10 +19731,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129771766</v>
+        <v>129771792</v>
       </c>
       <c r="B191" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19734,21 +19742,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19758,10 +19766,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430922</v>
+        <v>430945</v>
       </c>
       <c r="R191" t="n">
-        <v>6795638</v>
+        <v>6795579</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19820,10 +19828,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129771812</v>
+        <v>129771766</v>
       </c>
       <c r="B192" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19831,21 +19839,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19855,10 +19863,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430903</v>
+        <v>430922</v>
       </c>
       <c r="R192" t="n">
-        <v>6796058</v>
+        <v>6795638</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19917,10 +19925,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129771707</v>
+        <v>129771812</v>
       </c>
       <c r="B193" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19928,21 +19936,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19952,10 +19960,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430973</v>
+        <v>430903</v>
       </c>
       <c r="R193" t="n">
-        <v>6795529</v>
+        <v>6796058</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20014,10 +20022,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129771728</v>
+        <v>129771707</v>
       </c>
       <c r="B194" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20025,42 +20033,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>430863</v>
+        <v>430973</v>
       </c>
       <c r="R194" t="n">
-        <v>6795800</v>
+        <v>6795529</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20119,10 +20119,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129773119</v>
+        <v>129771814</v>
       </c>
       <c r="B195" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20130,42 +20130,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430692</v>
+        <v>430944</v>
       </c>
       <c r="R195" t="n">
-        <v>6795373</v>
+        <v>6796075</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20212,19 +20204,19 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129771814</v>
+        <v>129771796</v>
       </c>
       <c r="B196" t="n">
         <v>79081</v>
@@ -20259,10 +20251,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430944</v>
+        <v>430984</v>
       </c>
       <c r="R196" t="n">
-        <v>6796075</v>
+        <v>6795518</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20321,7 +20313,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129771796</v>
+        <v>129773211</v>
       </c>
       <c r="B197" t="n">
         <v>79081</v>
@@ -20356,10 +20348,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>430984</v>
+        <v>430815</v>
       </c>
       <c r="R197" t="n">
-        <v>6795518</v>
+        <v>6795818</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20406,19 +20398,19 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129773211</v>
+        <v>129773207</v>
       </c>
       <c r="B198" t="n">
         <v>79081</v>
@@ -20453,10 +20445,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>430815</v>
+        <v>430947</v>
       </c>
       <c r="R198" t="n">
-        <v>6795818</v>
+        <v>6795977</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20515,45 +20507,54 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129773207</v>
+        <v>129771762</v>
       </c>
       <c r="B199" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>430947</v>
+        <v>430746</v>
       </c>
       <c r="R199" t="n">
-        <v>6795977</v>
+        <v>6795566</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20594,59 +20595,59 @@
       <c r="AE199" t="b">
         <v>0</v>
       </c>
+      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129771762</v>
+        <v>129773119</v>
       </c>
       <c r="B200" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N200" t="inlineStr"/>
@@ -20656,10 +20657,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>430746</v>
+        <v>430692</v>
       </c>
       <c r="R200" t="n">
-        <v>6795566</v>
+        <v>6795373</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20700,19 +20701,18 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
@@ -21416,10 +21416,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129771795</v>
+        <v>129773142</v>
       </c>
       <c r="B208" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21427,21 +21427,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21451,10 +21451,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>430956</v>
+        <v>430602</v>
       </c>
       <c r="R208" t="n">
-        <v>6795564</v>
+        <v>6795431</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21501,22 +21501,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129771769</v>
+        <v>129771795</v>
       </c>
       <c r="B209" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21524,21 +21524,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -21548,10 +21548,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>430973</v>
+        <v>430956</v>
       </c>
       <c r="R209" t="n">
-        <v>6795852</v>
+        <v>6795564</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21610,10 +21610,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129771782</v>
+        <v>129771769</v>
       </c>
       <c r="B210" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21621,21 +21621,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21645,10 +21645,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>430561</v>
+        <v>430973</v>
       </c>
       <c r="R210" t="n">
-        <v>6795581</v>
+        <v>6795852</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21707,10 +21707,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129773142</v>
+        <v>129773130</v>
       </c>
       <c r="B211" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21718,34 +21718,42 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>430602</v>
+        <v>430893</v>
       </c>
       <c r="R211" t="n">
-        <v>6795431</v>
+        <v>6796035</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21804,10 +21812,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129773130</v>
+        <v>129771782</v>
       </c>
       <c r="B212" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21815,42 +21823,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>430893</v>
+        <v>430561</v>
       </c>
       <c r="R212" t="n">
-        <v>6796035</v>
+        <v>6795581</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21897,12 +21897,12 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
@@ -22491,10 +22491,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129771759</v>
+        <v>129771736</v>
       </c>
       <c r="B219" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22502,34 +22502,42 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>430973</v>
+        <v>430531</v>
       </c>
       <c r="R219" t="n">
-        <v>6795852</v>
+        <v>6795488</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22588,10 +22596,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129773166</v>
+        <v>129771740</v>
       </c>
       <c r="B220" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22599,34 +22607,42 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>430897</v>
+        <v>430754</v>
       </c>
       <c r="R220" t="n">
-        <v>6795988</v>
+        <v>6795593</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22673,22 +22689,22 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129773190</v>
+        <v>129773166</v>
       </c>
       <c r="B221" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22696,21 +22712,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22720,10 +22736,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>430984</v>
+        <v>430897</v>
       </c>
       <c r="R221" t="n">
-        <v>6795313</v>
+        <v>6795988</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22782,7 +22798,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129773189</v>
+        <v>129773190</v>
       </c>
       <c r="B222" t="n">
         <v>79081</v>
@@ -22817,10 +22833,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>430904</v>
+        <v>430984</v>
       </c>
       <c r="R222" t="n">
-        <v>6795339</v>
+        <v>6795313</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22879,7 +22895,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129771813</v>
+        <v>129773189</v>
       </c>
       <c r="B223" t="n">
         <v>79081</v>
@@ -22914,10 +22930,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430910</v>
+        <v>430904</v>
       </c>
       <c r="R223" t="n">
-        <v>6796073</v>
+        <v>6795339</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22964,19 +22980,19 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129773177</v>
+        <v>129771813</v>
       </c>
       <c r="B224" t="n">
         <v>79081</v>
@@ -23011,10 +23027,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>430633</v>
+        <v>430910</v>
       </c>
       <c r="R224" t="n">
-        <v>6795435</v>
+        <v>6796073</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23061,22 +23077,22 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129771736</v>
+        <v>129773177</v>
       </c>
       <c r="B225" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23084,42 +23100,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>430531</v>
+        <v>430633</v>
       </c>
       <c r="R225" t="n">
-        <v>6795488</v>
+        <v>6795435</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23166,22 +23174,22 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129771740</v>
+        <v>129771759</v>
       </c>
       <c r="B226" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23189,42 +23197,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>430754</v>
+        <v>430973</v>
       </c>
       <c r="R226" t="n">
-        <v>6795593</v>
+        <v>6795852</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24059,10 +24059,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129771731</v>
+        <v>129773101</v>
       </c>
       <c r="B235" t="n">
-        <v>91620</v>
+        <v>79671</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24070,21 +24070,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -24094,10 +24094,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>430961</v>
+        <v>430763</v>
       </c>
       <c r="R235" t="n">
-        <v>6795616</v>
+        <v>6795472</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24144,66 +24144,57 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129773162</v>
+        <v>129771805</v>
       </c>
       <c r="B236" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>430613</v>
+        <v>430875</v>
       </c>
       <c r="R236" t="n">
-        <v>6795723</v>
+        <v>6796089</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24244,29 +24235,28 @@
       <c r="AE236" t="b">
         <v>0</v>
       </c>
-      <c r="AF236" t="inlineStr"/>
       <c r="AG236" t="b">
         <v>0</v>
       </c>
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129773101</v>
+        <v>129771752</v>
       </c>
       <c r="B237" t="n">
-        <v>79671</v>
+        <v>57733</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24274,34 +24264,42 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>430763</v>
+        <v>430801</v>
       </c>
       <c r="R237" t="n">
-        <v>6795472</v>
+        <v>6795756</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24348,22 +24346,22 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129771752</v>
+        <v>129771731</v>
       </c>
       <c r="B238" t="n">
-        <v>57733</v>
+        <v>91620</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24371,42 +24369,34 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>430801</v>
+        <v>430961</v>
       </c>
       <c r="R238" t="n">
-        <v>6795756</v>
+        <v>6795616</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24465,45 +24455,54 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129771805</v>
+        <v>129773162</v>
       </c>
       <c r="B239" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>430875</v>
+        <v>430613</v>
       </c>
       <c r="R239" t="n">
-        <v>6796089</v>
+        <v>6795723</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24544,28 +24543,29 @@
       <c r="AE239" t="b">
         <v>0</v>
       </c>
+      <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="b">
         <v>0</v>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129771730</v>
+        <v>129771747</v>
       </c>
       <c r="B240" t="n">
-        <v>91620</v>
+        <v>57733</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24573,34 +24573,42 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>430958</v>
+        <v>430947</v>
       </c>
       <c r="R240" t="n">
-        <v>6795614</v>
+        <v>6796064</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24659,10 +24667,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129771785</v>
+        <v>129771742</v>
       </c>
       <c r="B241" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24670,34 +24678,42 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>430936</v>
+        <v>430934</v>
       </c>
       <c r="R241" t="n">
-        <v>6795608</v>
+        <v>6795641</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24756,10 +24772,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129771806</v>
+        <v>129771746</v>
       </c>
       <c r="B242" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24767,34 +24783,42 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>430974</v>
+        <v>430942</v>
       </c>
       <c r="R242" t="n">
-        <v>6796123</v>
+        <v>6796133</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24853,10 +24877,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129771784</v>
+        <v>129773121</v>
       </c>
       <c r="B243" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24864,34 +24888,42 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>430920</v>
+        <v>430707</v>
       </c>
       <c r="R243" t="n">
-        <v>6795536</v>
+        <v>6795375</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24938,22 +24970,22 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129773213</v>
+        <v>129771739</v>
       </c>
       <c r="B244" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -24961,34 +24993,42 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>430783</v>
+        <v>430752</v>
       </c>
       <c r="R244" t="n">
-        <v>6795818</v>
+        <v>6795559</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25035,44 +25075,44 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129771747</v>
+        <v>129771716</v>
       </c>
       <c r="B245" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25080,7 +25120,7 @@
       <c r="L245" t="inlineStr"/>
       <c r="M245" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N245" t="inlineStr"/>
@@ -25090,10 +25130,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>430947</v>
+        <v>430750</v>
       </c>
       <c r="R245" t="n">
-        <v>6796064</v>
+        <v>6795558</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25152,10 +25192,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>129771742</v>
+        <v>129771730</v>
       </c>
       <c r="B246" t="n">
-        <v>57733</v>
+        <v>91620</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25163,42 +25203,34 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>430934</v>
+        <v>430958</v>
       </c>
       <c r="R246" t="n">
-        <v>6795641</v>
+        <v>6795614</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25257,10 +25289,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>129771746</v>
+        <v>129771785</v>
       </c>
       <c r="B247" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25268,42 +25300,34 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>430942</v>
+        <v>430936</v>
       </c>
       <c r="R247" t="n">
-        <v>6796133</v>
+        <v>6795608</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25362,10 +25386,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129773121</v>
+        <v>129771806</v>
       </c>
       <c r="B248" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25373,42 +25397,34 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>430707</v>
+        <v>430974</v>
       </c>
       <c r="R248" t="n">
-        <v>6795375</v>
+        <v>6796123</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25455,22 +25471,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>129771739</v>
+        <v>129771784</v>
       </c>
       <c r="B249" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25478,42 +25494,34 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>430752</v>
+        <v>430920</v>
       </c>
       <c r="R249" t="n">
-        <v>6795559</v>
+        <v>6795536</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25572,53 +25580,45 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>129771716</v>
+        <v>129773213</v>
       </c>
       <c r="B250" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>430750</v>
+        <v>430783</v>
       </c>
       <c r="R250" t="n">
-        <v>6795558</v>
+        <v>6795818</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25665,12 +25665,12 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
@@ -26485,10 +26485,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>129773135</v>
+        <v>129773180</v>
       </c>
       <c r="B259" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26496,42 +26496,34 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>430938</v>
+        <v>430789</v>
       </c>
       <c r="R259" t="n">
-        <v>6795967</v>
+        <v>6795377</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -26590,10 +26582,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>129773120</v>
+        <v>129773156</v>
       </c>
       <c r="B260" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26601,42 +26593,34 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>430694</v>
+        <v>430787</v>
       </c>
       <c r="R260" t="n">
-        <v>6795368</v>
+        <v>6795816</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26695,7 +26679,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>129771744</v>
+        <v>129773135</v>
       </c>
       <c r="B261" t="n">
         <v>57733</v>
@@ -26738,10 +26722,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>430959</v>
+        <v>430938</v>
       </c>
       <c r="R261" t="n">
-        <v>6795543</v>
+        <v>6795967</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26788,19 +26772,19 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>129773133</v>
+        <v>129773120</v>
       </c>
       <c r="B262" t="n">
         <v>57733</v>
@@ -26843,10 +26827,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>430886</v>
+        <v>430694</v>
       </c>
       <c r="R262" t="n">
-        <v>6795969</v>
+        <v>6795368</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26905,10 +26889,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>129773180</v>
+        <v>129771744</v>
       </c>
       <c r="B263" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -26916,34 +26900,42 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>430789</v>
+        <v>430959</v>
       </c>
       <c r="R263" t="n">
-        <v>6795377</v>
+        <v>6795543</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -26990,22 +26982,22 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>129771786</v>
+        <v>129773133</v>
       </c>
       <c r="B264" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27013,34 +27005,42 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>430927</v>
+        <v>430886</v>
       </c>
       <c r="R264" t="n">
-        <v>6795611</v>
+        <v>6795969</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27087,19 +27087,19 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>129773182</v>
+        <v>129771786</v>
       </c>
       <c r="B265" t="n">
         <v>79081</v>
@@ -27134,10 +27134,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>430740</v>
+        <v>430927</v>
       </c>
       <c r="R265" t="n">
-        <v>6795371</v>
+        <v>6795611</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27184,22 +27184,22 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>129773156</v>
+        <v>129773182</v>
       </c>
       <c r="B266" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27207,21 +27207,21 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -27231,10 +27231,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>430787</v>
+        <v>430740</v>
       </c>
       <c r="R266" t="n">
-        <v>6795816</v>
+        <v>6795371</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>

--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -14922,10 +14922,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129771745</v>
+        <v>129773210</v>
       </c>
       <c r="B143" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14933,42 +14933,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>430945</v>
+        <v>430968</v>
       </c>
       <c r="R143" t="n">
-        <v>6796127</v>
+        <v>6795883</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15015,19 +15007,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129771743</v>
+        <v>129771745</v>
       </c>
       <c r="B144" t="n">
         <v>57733</v>
@@ -15070,10 +15062,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430957</v>
+        <v>430945</v>
       </c>
       <c r="R144" t="n">
-        <v>6795610</v>
+        <v>6796127</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15132,10 +15124,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129771810</v>
+        <v>129771743</v>
       </c>
       <c r="B145" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15143,34 +15135,42 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>430894</v>
+        <v>430957</v>
       </c>
       <c r="R145" t="n">
-        <v>6796084</v>
+        <v>6795610</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15229,7 +15229,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129771783</v>
+        <v>129771810</v>
       </c>
       <c r="B146" t="n">
         <v>79081</v>
@@ -15264,10 +15264,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>430787</v>
+        <v>430894</v>
       </c>
       <c r="R146" t="n">
-        <v>6795560</v>
+        <v>6796084</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15326,7 +15326,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129773196</v>
+        <v>129771783</v>
       </c>
       <c r="B147" t="n">
         <v>79081</v>
@@ -15361,10 +15361,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431034</v>
+        <v>430787</v>
       </c>
       <c r="R147" t="n">
-        <v>6795525</v>
+        <v>6795560</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15411,19 +15411,19 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129773210</v>
+        <v>129773196</v>
       </c>
       <c r="B148" t="n">
         <v>79081</v>
@@ -15458,10 +15458,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>430968</v>
+        <v>431034</v>
       </c>
       <c r="R148" t="n">
-        <v>6795883</v>
+        <v>6795525</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15722,10 +15722,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129773134</v>
+        <v>129773185</v>
       </c>
       <c r="B151" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15733,42 +15733,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>430894</v>
+        <v>430821</v>
       </c>
       <c r="R151" t="n">
-        <v>6795968</v>
+        <v>6795424</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15827,53 +15819,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129771717</v>
+        <v>129771797</v>
       </c>
       <c r="B152" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>430918</v>
+        <v>430960</v>
       </c>
       <c r="R152" t="n">
-        <v>6795982</v>
+        <v>6795549</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15932,7 +15916,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129773185</v>
+        <v>129771788</v>
       </c>
       <c r="B153" t="n">
         <v>79081</v>
@@ -15967,10 +15951,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>430821</v>
+        <v>430957</v>
       </c>
       <c r="R153" t="n">
-        <v>6795424</v>
+        <v>6795628</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16005,6 +15989,11 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 10 m</t>
+        </is>
+      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -16017,19 +16006,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129771797</v>
+        <v>129771804</v>
       </c>
       <c r="B154" t="n">
         <v>79081</v>
@@ -16064,10 +16053,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>430960</v>
+        <v>430865</v>
       </c>
       <c r="R154" t="n">
-        <v>6795549</v>
+        <v>6796072</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16126,45 +16115,53 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129771788</v>
+        <v>129771717</v>
       </c>
       <c r="B155" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>430957</v>
+        <v>430918</v>
       </c>
       <c r="R155" t="n">
-        <v>6795628</v>
+        <v>6795982</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16197,11 +16194,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 10 m</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16228,10 +16220,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129771804</v>
+        <v>129773134</v>
       </c>
       <c r="B156" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16239,34 +16231,42 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>430865</v>
+        <v>430894</v>
       </c>
       <c r="R156" t="n">
-        <v>6796072</v>
+        <v>6795968</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16313,12 +16313,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -16422,53 +16422,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129773138</v>
+        <v>129771754</v>
       </c>
       <c r="B158" t="n">
-        <v>57733</v>
+        <v>92052</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>430825</v>
+        <v>430535</v>
       </c>
       <c r="R158" t="n">
-        <v>6795805</v>
+        <v>6795489</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16503,64 +16495,71 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129773124</v>
+        <v>129773158</v>
       </c>
       <c r="B159" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
@@ -16570,10 +16569,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>430865</v>
+        <v>430704</v>
       </c>
       <c r="R159" t="n">
-        <v>6795387</v>
+        <v>6795457</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16614,6 +16613,7 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -16632,7 +16632,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129771753</v>
+        <v>129773138</v>
       </c>
       <c r="B160" t="n">
         <v>57733</v>
@@ -16665,7 +16665,7 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -16675,10 +16675,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>430631</v>
+        <v>430825</v>
       </c>
       <c r="R160" t="n">
-        <v>6795763</v>
+        <v>6795805</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16725,22 +16725,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129773204</v>
+        <v>129773124</v>
       </c>
       <c r="B161" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16748,34 +16748,42 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>430881</v>
+        <v>430865</v>
       </c>
       <c r="R161" t="n">
-        <v>6795985</v>
+        <v>6795387</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16834,10 +16842,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129773183</v>
+        <v>129771753</v>
       </c>
       <c r="B162" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16845,34 +16853,42 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>430698</v>
+        <v>430631</v>
       </c>
       <c r="R162" t="n">
-        <v>6795386</v>
+        <v>6795763</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16919,66 +16935,57 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129773158</v>
+        <v>129773204</v>
       </c>
       <c r="B163" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>430704</v>
+        <v>430881</v>
       </c>
       <c r="R163" t="n">
-        <v>6795457</v>
+        <v>6795985</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17019,7 +17026,6 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -17038,32 +17044,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129771754</v>
+        <v>129773183</v>
       </c>
       <c r="B164" t="n">
-        <v>92052</v>
+        <v>79081</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17073,10 +17079,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>430535</v>
+        <v>430698</v>
       </c>
       <c r="R164" t="n">
-        <v>6795489</v>
+        <v>6795386</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17111,30 +17117,24 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -19125,10 +19125,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129771728</v>
+        <v>129773122</v>
       </c>
       <c r="B185" t="n">
-        <v>57896</v>
+        <v>57733</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19136,21 +19136,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19158,7 +19158,7 @@
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N185" t="inlineStr"/>
@@ -19168,10 +19168,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>430863</v>
+        <v>430702</v>
       </c>
       <c r="R185" t="n">
-        <v>6795800</v>
+        <v>6795444</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19218,12 +19218,12 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -19335,10 +19335,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129773122</v>
+        <v>129771729</v>
       </c>
       <c r="B187" t="n">
-        <v>57733</v>
+        <v>91620</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19346,42 +19346,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430702</v>
+        <v>430543</v>
       </c>
       <c r="R187" t="n">
-        <v>6795444</v>
+        <v>6795503</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19428,44 +19420,44 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129771729</v>
+        <v>129771703</v>
       </c>
       <c r="B188" t="n">
-        <v>91620</v>
+        <v>91563</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19475,10 +19467,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430543</v>
+        <v>430735</v>
       </c>
       <c r="R188" t="n">
-        <v>6795503</v>
+        <v>6795805</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19537,32 +19529,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129771703</v>
+        <v>129771807</v>
       </c>
       <c r="B189" t="n">
-        <v>91563</v>
+        <v>79081</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19572,10 +19564,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430735</v>
+        <v>430914</v>
       </c>
       <c r="R189" t="n">
-        <v>6795805</v>
+        <v>6796105</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19634,7 +19626,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129771807</v>
+        <v>129771792</v>
       </c>
       <c r="B190" t="n">
         <v>79081</v>
@@ -19669,10 +19661,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430914</v>
+        <v>430945</v>
       </c>
       <c r="R190" t="n">
-        <v>6796105</v>
+        <v>6795579</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19731,10 +19723,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129771792</v>
+        <v>129771766</v>
       </c>
       <c r="B191" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19742,21 +19734,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19766,10 +19758,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430945</v>
+        <v>430922</v>
       </c>
       <c r="R191" t="n">
-        <v>6795579</v>
+        <v>6795638</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19828,10 +19820,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129771766</v>
+        <v>129771812</v>
       </c>
       <c r="B192" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19839,21 +19831,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19863,10 +19855,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430922</v>
+        <v>430903</v>
       </c>
       <c r="R192" t="n">
-        <v>6795638</v>
+        <v>6796058</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19925,10 +19917,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129771812</v>
+        <v>129771707</v>
       </c>
       <c r="B193" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19936,21 +19928,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19960,10 +19952,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430903</v>
+        <v>430973</v>
       </c>
       <c r="R193" t="n">
-        <v>6796058</v>
+        <v>6795529</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20022,10 +20014,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129771707</v>
+        <v>129771728</v>
       </c>
       <c r="B194" t="n">
-        <v>79700</v>
+        <v>57896</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20033,34 +20025,42 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>430973</v>
+        <v>430863</v>
       </c>
       <c r="R194" t="n">
-        <v>6795529</v>
+        <v>6795800</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21416,10 +21416,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129773142</v>
+        <v>129771795</v>
       </c>
       <c r="B208" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21427,21 +21427,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21451,10 +21451,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>430602</v>
+        <v>430956</v>
       </c>
       <c r="R208" t="n">
-        <v>6795431</v>
+        <v>6795564</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21501,22 +21501,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129771795</v>
+        <v>129771769</v>
       </c>
       <c r="B209" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21524,21 +21524,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -21548,10 +21548,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>430956</v>
+        <v>430973</v>
       </c>
       <c r="R209" t="n">
-        <v>6795564</v>
+        <v>6795852</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21610,10 +21610,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129771769</v>
+        <v>129771782</v>
       </c>
       <c r="B210" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21621,21 +21621,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21645,10 +21645,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>430973</v>
+        <v>430561</v>
       </c>
       <c r="R210" t="n">
-        <v>6795852</v>
+        <v>6795581</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21707,10 +21707,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129773130</v>
+        <v>129773142</v>
       </c>
       <c r="B211" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21718,42 +21718,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>430893</v>
+        <v>430602</v>
       </c>
       <c r="R211" t="n">
-        <v>6796035</v>
+        <v>6795431</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21812,10 +21804,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129771782</v>
+        <v>129773130</v>
       </c>
       <c r="B212" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21823,34 +21815,42 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>430561</v>
+        <v>430893</v>
       </c>
       <c r="R212" t="n">
-        <v>6795581</v>
+        <v>6796035</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21897,12 +21897,12 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
@@ -26485,10 +26485,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>129773180</v>
+        <v>129773135</v>
       </c>
       <c r="B259" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26496,34 +26496,42 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>430789</v>
+        <v>430938</v>
       </c>
       <c r="R259" t="n">
-        <v>6795377</v>
+        <v>6795967</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -26582,10 +26590,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>129773156</v>
+        <v>129773120</v>
       </c>
       <c r="B260" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26593,34 +26601,42 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>430787</v>
+        <v>430694</v>
       </c>
       <c r="R260" t="n">
-        <v>6795816</v>
+        <v>6795368</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26679,7 +26695,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>129773135</v>
+        <v>129771744</v>
       </c>
       <c r="B261" t="n">
         <v>57733</v>
@@ -26722,10 +26738,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>430938</v>
+        <v>430959</v>
       </c>
       <c r="R261" t="n">
-        <v>6795967</v>
+        <v>6795543</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26772,19 +26788,19 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>129773120</v>
+        <v>129773133</v>
       </c>
       <c r="B262" t="n">
         <v>57733</v>
@@ -26827,10 +26843,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>430694</v>
+        <v>430886</v>
       </c>
       <c r="R262" t="n">
-        <v>6795368</v>
+        <v>6795969</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26889,10 +26905,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>129771744</v>
+        <v>129771786</v>
       </c>
       <c r="B263" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -26900,42 +26916,34 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>430959</v>
+        <v>430927</v>
       </c>
       <c r="R263" t="n">
-        <v>6795543</v>
+        <v>6795611</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -26994,10 +27002,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>129773133</v>
+        <v>129773182</v>
       </c>
       <c r="B264" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27005,42 +27013,34 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>430886</v>
+        <v>430740</v>
       </c>
       <c r="R264" t="n">
-        <v>6795969</v>
+        <v>6795371</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27099,7 +27099,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>129771786</v>
+        <v>129773180</v>
       </c>
       <c r="B265" t="n">
         <v>79081</v>
@@ -27134,10 +27134,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>430927</v>
+        <v>430789</v>
       </c>
       <c r="R265" t="n">
-        <v>6795611</v>
+        <v>6795377</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27184,22 +27184,22 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>129773182</v>
+        <v>129773156</v>
       </c>
       <c r="B266" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27207,21 +27207,21 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -27231,10 +27231,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>430740</v>
+        <v>430787</v>
       </c>
       <c r="R266" t="n">
-        <v>6795371</v>
+        <v>6795816</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>

--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -14922,10 +14922,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129773210</v>
+        <v>129771745</v>
       </c>
       <c r="B143" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14933,34 +14933,42 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>430968</v>
+        <v>430945</v>
       </c>
       <c r="R143" t="n">
-        <v>6795883</v>
+        <v>6796127</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15007,19 +15015,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129771745</v>
+        <v>129771743</v>
       </c>
       <c r="B144" t="n">
         <v>57733</v>
@@ -15062,10 +15070,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430945</v>
+        <v>430957</v>
       </c>
       <c r="R144" t="n">
-        <v>6796127</v>
+        <v>6795610</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15124,10 +15132,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129771743</v>
+        <v>129771810</v>
       </c>
       <c r="B145" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15135,42 +15143,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>430957</v>
+        <v>430894</v>
       </c>
       <c r="R145" t="n">
-        <v>6795610</v>
+        <v>6796084</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15229,7 +15229,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129771810</v>
+        <v>129771783</v>
       </c>
       <c r="B146" t="n">
         <v>79081</v>
@@ -15264,10 +15264,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>430894</v>
+        <v>430787</v>
       </c>
       <c r="R146" t="n">
-        <v>6796084</v>
+        <v>6795560</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15326,7 +15326,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129771783</v>
+        <v>129773196</v>
       </c>
       <c r="B147" t="n">
         <v>79081</v>
@@ -15361,10 +15361,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>430787</v>
+        <v>431034</v>
       </c>
       <c r="R147" t="n">
-        <v>6795560</v>
+        <v>6795525</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15411,19 +15411,19 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129773196</v>
+        <v>129773210</v>
       </c>
       <c r="B148" t="n">
         <v>79081</v>
@@ -15458,10 +15458,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>431034</v>
+        <v>430968</v>
       </c>
       <c r="R148" t="n">
-        <v>6795525</v>
+        <v>6795883</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -20119,45 +20119,54 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129771814</v>
+        <v>129771762</v>
       </c>
       <c r="B195" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430944</v>
+        <v>430746</v>
       </c>
       <c r="R195" t="n">
-        <v>6796075</v>
+        <v>6795566</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20198,6 +20207,7 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -20216,10 +20226,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129771796</v>
+        <v>129773119</v>
       </c>
       <c r="B196" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20227,34 +20237,42 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430984</v>
+        <v>430692</v>
       </c>
       <c r="R196" t="n">
-        <v>6795518</v>
+        <v>6795373</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20301,19 +20319,19 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129773211</v>
+        <v>129771814</v>
       </c>
       <c r="B197" t="n">
         <v>79081</v>
@@ -20348,10 +20366,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>430815</v>
+        <v>430944</v>
       </c>
       <c r="R197" t="n">
-        <v>6795818</v>
+        <v>6796075</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20398,19 +20416,19 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129773207</v>
+        <v>129771796</v>
       </c>
       <c r="B198" t="n">
         <v>79081</v>
@@ -20445,10 +20463,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>430947</v>
+        <v>430984</v>
       </c>
       <c r="R198" t="n">
-        <v>6795977</v>
+        <v>6795518</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20495,66 +20513,57 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129771762</v>
+        <v>129773211</v>
       </c>
       <c r="B199" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>430746</v>
+        <v>430815</v>
       </c>
       <c r="R199" t="n">
-        <v>6795566</v>
+        <v>6795818</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20595,29 +20604,28 @@
       <c r="AE199" t="b">
         <v>0</v>
       </c>
-      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129773119</v>
+        <v>129773207</v>
       </c>
       <c r="B200" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20625,42 +20633,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>430692</v>
+        <v>430947</v>
       </c>
       <c r="R200" t="n">
-        <v>6795373</v>
+        <v>6795977</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -24059,10 +24059,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129773101</v>
+        <v>129771731</v>
       </c>
       <c r="B235" t="n">
-        <v>79671</v>
+        <v>91620</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24070,21 +24070,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -24094,10 +24094,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>430763</v>
+        <v>430961</v>
       </c>
       <c r="R235" t="n">
-        <v>6795472</v>
+        <v>6795616</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24144,57 +24144,66 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129771805</v>
+        <v>129773162</v>
       </c>
       <c r="B236" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>430875</v>
+        <v>430613</v>
       </c>
       <c r="R236" t="n">
-        <v>6796089</v>
+        <v>6795723</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24235,28 +24244,29 @@
       <c r="AE236" t="b">
         <v>0</v>
       </c>
+      <c r="AF236" t="inlineStr"/>
       <c r="AG236" t="b">
         <v>0</v>
       </c>
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129771752</v>
+        <v>129773101</v>
       </c>
       <c r="B237" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24264,42 +24274,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>430801</v>
+        <v>430763</v>
       </c>
       <c r="R237" t="n">
-        <v>6795756</v>
+        <v>6795472</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24346,22 +24348,22 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129771731</v>
+        <v>129771752</v>
       </c>
       <c r="B238" t="n">
-        <v>91620</v>
+        <v>57733</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24369,34 +24371,42 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>430961</v>
+        <v>430801</v>
       </c>
       <c r="R238" t="n">
-        <v>6795616</v>
+        <v>6795756</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24455,54 +24465,45 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129773162</v>
+        <v>129771805</v>
       </c>
       <c r="B239" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>430613</v>
+        <v>430875</v>
       </c>
       <c r="R239" t="n">
-        <v>6795723</v>
+        <v>6796089</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24543,19 +24544,18 @@
       <c r="AE239" t="b">
         <v>0</v>
       </c>
-      <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="b">
         <v>0</v>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>

--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -13685,10 +13685,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129771737</v>
+        <v>129773214</v>
       </c>
       <c r="B131" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13696,42 +13696,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>430522</v>
+        <v>430777</v>
       </c>
       <c r="R131" t="n">
-        <v>6795537</v>
+        <v>6795822</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13778,19 +13770,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129773137</v>
+        <v>129771737</v>
       </c>
       <c r="B132" t="n">
         <v>57733</v>
@@ -13823,7 +13815,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -13833,10 +13825,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430851</v>
+        <v>430522</v>
       </c>
       <c r="R132" t="n">
-        <v>6795824</v>
+        <v>6795537</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13883,19 +13875,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129773132</v>
+        <v>129771741</v>
       </c>
       <c r="B133" t="n">
         <v>57733</v>
@@ -13928,7 +13920,7 @@
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -13938,10 +13930,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>430873</v>
+        <v>430784</v>
       </c>
       <c r="R133" t="n">
-        <v>6795977</v>
+        <v>6795567</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13988,19 +13980,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129771750</v>
+        <v>129773137</v>
       </c>
       <c r="B134" t="n">
         <v>57733</v>
@@ -14043,10 +14035,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>430973</v>
+        <v>430851</v>
       </c>
       <c r="R134" t="n">
-        <v>6795877</v>
+        <v>6795824</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14093,19 +14085,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129771741</v>
+        <v>129773132</v>
       </c>
       <c r="B135" t="n">
         <v>57733</v>
@@ -14138,7 +14130,7 @@
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -14148,10 +14140,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>430784</v>
+        <v>430873</v>
       </c>
       <c r="R135" t="n">
-        <v>6795567</v>
+        <v>6795977</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14198,22 +14190,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129773113</v>
+        <v>129771750</v>
       </c>
       <c r="B136" t="n">
-        <v>91620</v>
+        <v>57733</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14221,26 +14213,31 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -14248,10 +14245,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>430833</v>
+        <v>430973</v>
       </c>
       <c r="R136" t="n">
-        <v>6796045</v>
+        <v>6795877</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14286,40 +14283,34 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>2 st på samma tall.</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129773214</v>
+        <v>129773143</v>
       </c>
       <c r="B137" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14327,21 +14318,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14351,10 +14342,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>430777</v>
+        <v>430730</v>
       </c>
       <c r="R137" t="n">
-        <v>6795822</v>
+        <v>6795404</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14413,53 +14404,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129771724</v>
+        <v>129773153</v>
       </c>
       <c r="B138" t="n">
-        <v>56926</v>
+        <v>78839</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>430884</v>
+        <v>430886</v>
       </c>
       <c r="R138" t="n">
-        <v>6795785</v>
+        <v>6796067</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14506,22 +14489,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129771710</v>
+        <v>129773113</v>
       </c>
       <c r="B139" t="n">
-        <v>57736</v>
+        <v>91620</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14529,31 +14512,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -14561,10 +14539,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>430669</v>
+        <v>430833</v>
       </c>
       <c r="R139" t="n">
-        <v>6795823</v>
+        <v>6796045</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14599,56 +14577,62 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>2 st på samma tall.</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129771719</v>
+        <v>129771710</v>
       </c>
       <c r="B140" t="n">
-        <v>56926</v>
+        <v>57736</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14656,7 +14640,7 @@
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -14666,10 +14650,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>430937</v>
+        <v>430669</v>
       </c>
       <c r="R140" t="n">
-        <v>6796046</v>
+        <v>6795823</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14728,45 +14712,53 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129773143</v>
+        <v>129771719</v>
       </c>
       <c r="B141" t="n">
-        <v>78839</v>
+        <v>56926</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>430730</v>
+        <v>430937</v>
       </c>
       <c r="R141" t="n">
-        <v>6795404</v>
+        <v>6796046</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14813,57 +14805,65 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129773153</v>
+        <v>129771724</v>
       </c>
       <c r="B142" t="n">
-        <v>78839</v>
+        <v>56926</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>430886</v>
+        <v>430884</v>
       </c>
       <c r="R142" t="n">
-        <v>6796067</v>
+        <v>6795785</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14910,22 +14910,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129771745</v>
+        <v>129773196</v>
       </c>
       <c r="B143" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14933,42 +14933,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>430945</v>
+        <v>431034</v>
       </c>
       <c r="R143" t="n">
-        <v>6796127</v>
+        <v>6795525</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15015,22 +15007,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129771743</v>
+        <v>129771810</v>
       </c>
       <c r="B144" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15038,42 +15030,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430957</v>
+        <v>430894</v>
       </c>
       <c r="R144" t="n">
-        <v>6795610</v>
+        <v>6796084</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15132,7 +15116,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129771810</v>
+        <v>129771783</v>
       </c>
       <c r="B145" t="n">
         <v>79081</v>
@@ -15167,10 +15151,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>430894</v>
+        <v>430787</v>
       </c>
       <c r="R145" t="n">
-        <v>6796084</v>
+        <v>6795560</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15229,7 +15213,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129771783</v>
+        <v>129773210</v>
       </c>
       <c r="B146" t="n">
         <v>79081</v>
@@ -15264,10 +15248,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>430787</v>
+        <v>430968</v>
       </c>
       <c r="R146" t="n">
-        <v>6795560</v>
+        <v>6795883</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15314,22 +15298,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129773196</v>
+        <v>129771745</v>
       </c>
       <c r="B147" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15337,34 +15321,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431034</v>
+        <v>430945</v>
       </c>
       <c r="R147" t="n">
-        <v>6795525</v>
+        <v>6796127</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15411,22 +15403,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129773210</v>
+        <v>129771743</v>
       </c>
       <c r="B148" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15434,34 +15426,42 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>430968</v>
+        <v>430957</v>
       </c>
       <c r="R148" t="n">
-        <v>6795883</v>
+        <v>6795610</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15508,12 +15508,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -15722,10 +15722,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129773185</v>
+        <v>129773134</v>
       </c>
       <c r="B151" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15733,34 +15733,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>430821</v>
+        <v>430894</v>
       </c>
       <c r="R151" t="n">
-        <v>6795424</v>
+        <v>6795968</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15819,45 +15827,53 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129771797</v>
+        <v>129771717</v>
       </c>
       <c r="B152" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>430960</v>
+        <v>430918</v>
       </c>
       <c r="R152" t="n">
-        <v>6795549</v>
+        <v>6795982</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15916,10 +15932,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129771788</v>
+        <v>129773155</v>
       </c>
       <c r="B153" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15927,21 +15943,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15951,10 +15967,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>430957</v>
+        <v>430833</v>
       </c>
       <c r="R153" t="n">
-        <v>6795628</v>
+        <v>6795830</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15989,11 +16005,6 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 10 m</t>
-        </is>
-      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -16006,19 +16017,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129771804</v>
+        <v>129771797</v>
       </c>
       <c r="B154" t="n">
         <v>79081</v>
@@ -16053,10 +16064,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>430865</v>
+        <v>430960</v>
       </c>
       <c r="R154" t="n">
-        <v>6796072</v>
+        <v>6795549</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16115,53 +16126,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129771717</v>
+        <v>129773185</v>
       </c>
       <c r="B155" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>430918</v>
+        <v>430821</v>
       </c>
       <c r="R155" t="n">
-        <v>6795982</v>
+        <v>6795424</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16208,22 +16211,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129773134</v>
+        <v>129771788</v>
       </c>
       <c r="B156" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16231,42 +16234,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>430894</v>
+        <v>430957</v>
       </c>
       <c r="R156" t="n">
-        <v>6795968</v>
+        <v>6795628</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16301,6 +16296,11 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 10 m</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
@@ -16313,22 +16313,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129773155</v>
+        <v>129771804</v>
       </c>
       <c r="B157" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16336,21 +16336,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16360,10 +16360,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>430833</v>
+        <v>430865</v>
       </c>
       <c r="R157" t="n">
-        <v>6795830</v>
+        <v>6796072</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16410,57 +16410,65 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129771754</v>
+        <v>129773138</v>
       </c>
       <c r="B158" t="n">
-        <v>92052</v>
+        <v>57733</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>430535</v>
+        <v>430825</v>
       </c>
       <c r="R158" t="n">
-        <v>6795489</v>
+        <v>6795805</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16495,71 +16503,64 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129773158</v>
+        <v>129773124</v>
       </c>
       <c r="B159" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
@@ -16569,10 +16570,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>430704</v>
+        <v>430865</v>
       </c>
       <c r="R159" t="n">
-        <v>6795457</v>
+        <v>6795387</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16613,7 +16614,6 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -16632,32 +16632,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129773138</v>
+        <v>129771713</v>
       </c>
       <c r="B160" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16665,7 +16665,7 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -16675,10 +16675,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>430825</v>
+        <v>430542</v>
       </c>
       <c r="R160" t="n">
-        <v>6795805</v>
+        <v>6795485</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16725,22 +16725,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129773124</v>
+        <v>129773204</v>
       </c>
       <c r="B161" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16748,42 +16748,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>430865</v>
+        <v>430881</v>
       </c>
       <c r="R161" t="n">
-        <v>6795387</v>
+        <v>6795985</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16842,10 +16834,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129771753</v>
+        <v>129773183</v>
       </c>
       <c r="B162" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16853,42 +16845,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>430631</v>
+        <v>430698</v>
       </c>
       <c r="R162" t="n">
-        <v>6795763</v>
+        <v>6795386</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16935,44 +16919,44 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129773204</v>
+        <v>129771754</v>
       </c>
       <c r="B163" t="n">
-        <v>79081</v>
+        <v>92052</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16982,10 +16966,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>430881</v>
+        <v>430535</v>
       </c>
       <c r="R163" t="n">
-        <v>6795985</v>
+        <v>6795489</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17020,34 +17004,40 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129773183</v>
+        <v>129771753</v>
       </c>
       <c r="B164" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17055,34 +17045,42 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>430698</v>
+        <v>430631</v>
       </c>
       <c r="R164" t="n">
-        <v>6795386</v>
+        <v>6795763</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17129,22 +17127,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129771713</v>
+        <v>129773158</v>
       </c>
       <c r="B165" t="n">
-        <v>56926</v>
+        <v>8450</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17152,29 +17150,30 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -17184,10 +17183,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>430542</v>
+        <v>430704</v>
       </c>
       <c r="R165" t="n">
-        <v>6795485</v>
+        <v>6795457</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17228,18 +17227,19 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
@@ -17440,10 +17440,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129773102</v>
+        <v>129773141</v>
       </c>
       <c r="B168" t="n">
-        <v>79671</v>
+        <v>78839</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17451,21 +17451,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17475,10 +17475,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>431020</v>
+        <v>430600</v>
       </c>
       <c r="R168" t="n">
-        <v>6795529</v>
+        <v>6795424</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17537,10 +17537,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129773141</v>
+        <v>129773102</v>
       </c>
       <c r="B169" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17548,21 +17548,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17572,10 +17572,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>430600</v>
+        <v>431020</v>
       </c>
       <c r="R169" t="n">
-        <v>6795424</v>
+        <v>6795529</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17828,7 +17828,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129773195</v>
+        <v>129771790</v>
       </c>
       <c r="B172" t="n">
         <v>79081</v>
@@ -17863,10 +17863,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>431010</v>
+        <v>430957</v>
       </c>
       <c r="R172" t="n">
-        <v>6795515</v>
+        <v>6795608</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17913,19 +17913,19 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129771790</v>
+        <v>129773195</v>
       </c>
       <c r="B173" t="n">
         <v>79081</v>
@@ -17960,10 +17960,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>430957</v>
+        <v>431010</v>
       </c>
       <c r="R173" t="n">
-        <v>6795608</v>
+        <v>6795515</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18010,44 +18010,44 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129773109</v>
+        <v>129773117</v>
       </c>
       <c r="B174" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18055,7 +18055,7 @@
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -18065,10 +18065,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>430816</v>
+        <v>430795</v>
       </c>
       <c r="R174" t="n">
-        <v>6795834</v>
+        <v>6795376</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18127,45 +18127,53 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129773146</v>
+        <v>129773109</v>
       </c>
       <c r="B175" t="n">
-        <v>78839</v>
+        <v>56926</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>430970</v>
+        <v>430816</v>
       </c>
       <c r="R175" t="n">
-        <v>6795287</v>
+        <v>6795834</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18224,10 +18232,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129771757</v>
+        <v>129773123</v>
       </c>
       <c r="B176" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18235,34 +18243,42 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>430923</v>
+        <v>430845</v>
       </c>
       <c r="R176" t="n">
-        <v>6795582</v>
+        <v>6795412</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18309,22 +18325,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129773117</v>
+        <v>129773146</v>
       </c>
       <c r="B177" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18332,42 +18348,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>430795</v>
+        <v>430970</v>
       </c>
       <c r="R177" t="n">
-        <v>6795376</v>
+        <v>6795287</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18426,10 +18434,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129773123</v>
+        <v>129771757</v>
       </c>
       <c r="B178" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18437,42 +18445,34 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>430845</v>
+        <v>430923</v>
       </c>
       <c r="R178" t="n">
-        <v>6795412</v>
+        <v>6795582</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18519,22 +18519,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129773128</v>
+        <v>129771803</v>
       </c>
       <c r="B179" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18542,42 +18542,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>430918</v>
+        <v>430878</v>
       </c>
       <c r="R179" t="n">
-        <v>6795985</v>
+        <v>6795999</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18624,22 +18616,22 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129773150</v>
+        <v>129773168</v>
       </c>
       <c r="B180" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18647,21 +18639,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18671,10 +18663,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>431067</v>
+        <v>430617</v>
       </c>
       <c r="R180" t="n">
-        <v>6795549</v>
+        <v>6795600</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18733,7 +18725,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129771803</v>
+        <v>129771811</v>
       </c>
       <c r="B181" t="n">
         <v>79081</v>
@@ -18768,10 +18760,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>430878</v>
+        <v>430910</v>
       </c>
       <c r="R181" t="n">
-        <v>6795999</v>
+        <v>6796078</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18931,10 +18923,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129773168</v>
+        <v>129773128</v>
       </c>
       <c r="B183" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18942,34 +18934,42 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>430617</v>
+        <v>430918</v>
       </c>
       <c r="R183" t="n">
-        <v>6795600</v>
+        <v>6795985</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19028,10 +19028,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129771811</v>
+        <v>129773150</v>
       </c>
       <c r="B184" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19039,21 +19039,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19063,10 +19063,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>430910</v>
+        <v>431067</v>
       </c>
       <c r="R184" t="n">
-        <v>6796078</v>
+        <v>6795549</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19113,22 +19113,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129773122</v>
+        <v>129771792</v>
       </c>
       <c r="B185" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19136,42 +19136,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>430702</v>
+        <v>430945</v>
       </c>
       <c r="R185" t="n">
-        <v>6795444</v>
+        <v>6795579</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19218,65 +19210,57 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129771764</v>
+        <v>129771766</v>
       </c>
       <c r="B186" t="n">
-        <v>58106</v>
+        <v>78838</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>103015</v>
+        <v>6446</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>430863</v>
+        <v>430922</v>
       </c>
       <c r="R186" t="n">
-        <v>6795796</v>
+        <v>6795638</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19335,10 +19319,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129771729</v>
+        <v>129771707</v>
       </c>
       <c r="B187" t="n">
-        <v>91620</v>
+        <v>79700</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19346,21 +19330,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19370,10 +19354,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430543</v>
+        <v>430973</v>
       </c>
       <c r="R187" t="n">
-        <v>6795503</v>
+        <v>6795529</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19432,32 +19416,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129771703</v>
+        <v>129771812</v>
       </c>
       <c r="B188" t="n">
-        <v>91563</v>
+        <v>79081</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19467,10 +19451,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430735</v>
+        <v>430903</v>
       </c>
       <c r="R188" t="n">
-        <v>6795805</v>
+        <v>6796058</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19626,10 +19610,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129771792</v>
+        <v>129771729</v>
       </c>
       <c r="B190" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19637,21 +19621,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19661,10 +19645,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430945</v>
+        <v>430543</v>
       </c>
       <c r="R190" t="n">
-        <v>6795579</v>
+        <v>6795503</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19723,32 +19707,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129771766</v>
+        <v>129771703</v>
       </c>
       <c r="B191" t="n">
-        <v>78838</v>
+        <v>91563</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19758,10 +19742,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430922</v>
+        <v>430735</v>
       </c>
       <c r="R191" t="n">
-        <v>6795638</v>
+        <v>6795805</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19820,10 +19804,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129771812</v>
+        <v>129773122</v>
       </c>
       <c r="B192" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19831,34 +19815,42 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430903</v>
+        <v>430702</v>
       </c>
       <c r="R192" t="n">
-        <v>6796058</v>
+        <v>6795444</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19905,22 +19897,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129771707</v>
+        <v>129771728</v>
       </c>
       <c r="B193" t="n">
-        <v>79700</v>
+        <v>57896</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19928,34 +19920,42 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430973</v>
+        <v>430863</v>
       </c>
       <c r="R193" t="n">
-        <v>6795529</v>
+        <v>6795800</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20014,32 +20014,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129771728</v>
+        <v>129771764</v>
       </c>
       <c r="B194" t="n">
-        <v>57896</v>
+        <v>58106</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20047,7 +20047,7 @@
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N194" t="inlineStr"/>
@@ -20060,7 +20060,7 @@
         <v>430863</v>
       </c>
       <c r="R194" t="n">
-        <v>6795800</v>
+        <v>6795796</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20119,41 +20119,40 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129771762</v>
+        <v>129773119</v>
       </c>
       <c r="B195" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N195" t="inlineStr"/>
@@ -20163,10 +20162,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430746</v>
+        <v>430692</v>
       </c>
       <c r="R195" t="n">
-        <v>6795566</v>
+        <v>6795373</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20207,29 +20206,28 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129773119</v>
+        <v>129773211</v>
       </c>
       <c r="B196" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20237,42 +20235,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430692</v>
+        <v>430815</v>
       </c>
       <c r="R196" t="n">
-        <v>6795373</v>
+        <v>6795818</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20525,7 +20515,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129773211</v>
+        <v>129773207</v>
       </c>
       <c r="B199" t="n">
         <v>79081</v>
@@ -20560,10 +20550,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>430815</v>
+        <v>430947</v>
       </c>
       <c r="R199" t="n">
-        <v>6795818</v>
+        <v>6795977</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20622,45 +20612,54 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129773207</v>
+        <v>129771762</v>
       </c>
       <c r="B200" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>430947</v>
+        <v>430746</v>
       </c>
       <c r="R200" t="n">
-        <v>6795977</v>
+        <v>6795566</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20701,18 +20700,19 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
@@ -20816,10 +20816,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129771808</v>
+        <v>129771706</v>
       </c>
       <c r="B202" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20827,21 +20827,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20851,10 +20851,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>430894</v>
+        <v>430935</v>
       </c>
       <c r="R202" t="n">
-        <v>6796093</v>
+        <v>6795595</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20913,53 +20913,45 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129771725</v>
+        <v>129771808</v>
       </c>
       <c r="B203" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>430867</v>
+        <v>430894</v>
       </c>
       <c r="R203" t="n">
-        <v>6795794</v>
+        <v>6796093</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21018,45 +21010,54 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129771706</v>
+        <v>129773161</v>
       </c>
       <c r="B204" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>430935</v>
+        <v>430911</v>
       </c>
       <c r="R204" t="n">
-        <v>6795595</v>
+        <v>6795982</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21097,28 +21098,29 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
+      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129773161</v>
+        <v>129771725</v>
       </c>
       <c r="B205" t="n">
-        <v>8450</v>
+        <v>56926</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21126,30 +21128,29 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N205" t="inlineStr"/>
@@ -21159,10 +21160,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>430911</v>
+        <v>430867</v>
       </c>
       <c r="R205" t="n">
-        <v>6795982</v>
+        <v>6795794</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21203,19 +21204,18 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
-      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
@@ -21416,7 +21416,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129771795</v>
+        <v>129771782</v>
       </c>
       <c r="B208" t="n">
         <v>79081</v>
@@ -21451,10 +21451,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>430956</v>
+        <v>430561</v>
       </c>
       <c r="R208" t="n">
-        <v>6795564</v>
+        <v>6795581</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21513,10 +21513,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129771769</v>
+        <v>129771795</v>
       </c>
       <c r="B209" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21524,21 +21524,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -21548,10 +21548,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>430973</v>
+        <v>430956</v>
       </c>
       <c r="R209" t="n">
-        <v>6795852</v>
+        <v>6795564</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21610,10 +21610,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129771782</v>
+        <v>129771769</v>
       </c>
       <c r="B210" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21621,21 +21621,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21645,10 +21645,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>430561</v>
+        <v>430973</v>
       </c>
       <c r="R210" t="n">
-        <v>6795581</v>
+        <v>6795852</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21909,7 +21909,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129773206</v>
+        <v>129773188</v>
       </c>
       <c r="B213" t="n">
         <v>79081</v>
@@ -21944,10 +21944,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>430918</v>
+        <v>430889</v>
       </c>
       <c r="R213" t="n">
-        <v>6795974</v>
+        <v>6795341</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22006,7 +22006,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129773188</v>
+        <v>129773206</v>
       </c>
       <c r="B214" t="n">
         <v>79081</v>
@@ -22041,10 +22041,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>430889</v>
+        <v>430918</v>
       </c>
       <c r="R214" t="n">
-        <v>6795341</v>
+        <v>6795974</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22491,10 +22491,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129771736</v>
+        <v>129773177</v>
       </c>
       <c r="B219" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22502,42 +22502,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>430531</v>
+        <v>430633</v>
       </c>
       <c r="R219" t="n">
-        <v>6795488</v>
+        <v>6795435</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22584,22 +22576,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129771740</v>
+        <v>129773166</v>
       </c>
       <c r="B220" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22607,42 +22599,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>430754</v>
+        <v>430897</v>
       </c>
       <c r="R220" t="n">
-        <v>6795593</v>
+        <v>6795988</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22689,22 +22673,22 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129773166</v>
+        <v>129773190</v>
       </c>
       <c r="B221" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22712,21 +22696,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22736,10 +22720,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>430897</v>
+        <v>430984</v>
       </c>
       <c r="R221" t="n">
-        <v>6795988</v>
+        <v>6795313</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22798,7 +22782,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129773190</v>
+        <v>129773189</v>
       </c>
       <c r="B222" t="n">
         <v>79081</v>
@@ -22833,10 +22817,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>430984</v>
+        <v>430904</v>
       </c>
       <c r="R222" t="n">
-        <v>6795313</v>
+        <v>6795339</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22895,7 +22879,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129773189</v>
+        <v>129771813</v>
       </c>
       <c r="B223" t="n">
         <v>79081</v>
@@ -22930,10 +22914,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430904</v>
+        <v>430910</v>
       </c>
       <c r="R223" t="n">
-        <v>6795339</v>
+        <v>6796073</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22980,22 +22964,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129771813</v>
+        <v>129771740</v>
       </c>
       <c r="B224" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23003,34 +22987,42 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>430910</v>
+        <v>430754</v>
       </c>
       <c r="R224" t="n">
-        <v>6796073</v>
+        <v>6795593</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23089,10 +23081,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129773177</v>
+        <v>129771736</v>
       </c>
       <c r="B225" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23100,34 +23092,42 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>430633</v>
+        <v>430531</v>
       </c>
       <c r="R225" t="n">
-        <v>6795435</v>
+        <v>6795488</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23174,12 +23174,12 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
@@ -23283,10 +23283,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129771781</v>
+        <v>129773144</v>
       </c>
       <c r="B227" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23294,21 +23294,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23318,10 +23318,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>430497</v>
+        <v>430907</v>
       </c>
       <c r="R227" t="n">
-        <v>6795553</v>
+        <v>6795330</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23368,19 +23368,19 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129773217</v>
+        <v>129773178</v>
       </c>
       <c r="B228" t="n">
         <v>79081</v>
@@ -23415,10 +23415,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>430617</v>
+        <v>430590</v>
       </c>
       <c r="R228" t="n">
-        <v>6795600</v>
+        <v>6795429</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23477,10 +23477,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129771770</v>
+        <v>129773201</v>
       </c>
       <c r="B229" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23488,21 +23488,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23512,10 +23512,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>430983</v>
+        <v>430907</v>
       </c>
       <c r="R229" t="n">
-        <v>6795850</v>
+        <v>6796028</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23562,19 +23562,19 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129773201</v>
+        <v>129771781</v>
       </c>
       <c r="B230" t="n">
         <v>79081</v>
@@ -23609,10 +23609,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>430907</v>
+        <v>430497</v>
       </c>
       <c r="R230" t="n">
-        <v>6796028</v>
+        <v>6795553</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23659,19 +23659,19 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129771809</v>
+        <v>129773217</v>
       </c>
       <c r="B231" t="n">
         <v>79081</v>
@@ -23706,10 +23706,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>430906</v>
+        <v>430617</v>
       </c>
       <c r="R231" t="n">
-        <v>6796088</v>
+        <v>6795600</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23756,22 +23756,22 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129773178</v>
+        <v>129771770</v>
       </c>
       <c r="B232" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23779,21 +23779,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23803,10 +23803,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>430590</v>
+        <v>430983</v>
       </c>
       <c r="R232" t="n">
-        <v>6795429</v>
+        <v>6795850</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23853,22 +23853,22 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129771708</v>
+        <v>129771809</v>
       </c>
       <c r="B233" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23876,21 +23876,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -23900,10 +23900,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>430916</v>
+        <v>430906</v>
       </c>
       <c r="R233" t="n">
-        <v>6796075</v>
+        <v>6796088</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23962,10 +23962,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129773144</v>
+        <v>129771708</v>
       </c>
       <c r="B234" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23973,21 +23973,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -23997,10 +23997,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>430907</v>
+        <v>430916</v>
       </c>
       <c r="R234" t="n">
-        <v>6795330</v>
+        <v>6796075</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24047,12 +24047,12 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
@@ -24156,54 +24156,45 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129773162</v>
+        <v>129771805</v>
       </c>
       <c r="B236" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>430613</v>
+        <v>430875</v>
       </c>
       <c r="R236" t="n">
-        <v>6795723</v>
+        <v>6796089</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24244,29 +24235,28 @@
       <c r="AE236" t="b">
         <v>0</v>
       </c>
-      <c r="AF236" t="inlineStr"/>
       <c r="AG236" t="b">
         <v>0</v>
       </c>
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129773101</v>
+        <v>129771752</v>
       </c>
       <c r="B237" t="n">
-        <v>79671</v>
+        <v>57733</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24274,34 +24264,42 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>430763</v>
+        <v>430801</v>
       </c>
       <c r="R237" t="n">
-        <v>6795472</v>
+        <v>6795756</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24348,22 +24346,22 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129771752</v>
+        <v>129773101</v>
       </c>
       <c r="B238" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24371,42 +24369,34 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>430801</v>
+        <v>430763</v>
       </c>
       <c r="R238" t="n">
-        <v>6795756</v>
+        <v>6795472</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24453,57 +24443,66 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129771805</v>
+        <v>129773162</v>
       </c>
       <c r="B239" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>430875</v>
+        <v>430613</v>
       </c>
       <c r="R239" t="n">
-        <v>6796089</v>
+        <v>6795723</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24544,28 +24543,29 @@
       <c r="AE239" t="b">
         <v>0</v>
       </c>
+      <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="b">
         <v>0</v>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129771747</v>
+        <v>129771785</v>
       </c>
       <c r="B240" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24573,42 +24573,34 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>430947</v>
+        <v>430936</v>
       </c>
       <c r="R240" t="n">
-        <v>6796064</v>
+        <v>6795608</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24667,10 +24659,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129771742</v>
+        <v>129771806</v>
       </c>
       <c r="B241" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24678,42 +24670,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>430934</v>
+        <v>430974</v>
       </c>
       <c r="R241" t="n">
-        <v>6795641</v>
+        <v>6796123</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24772,10 +24756,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129771746</v>
+        <v>129773213</v>
       </c>
       <c r="B242" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24783,42 +24767,34 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>430942</v>
+        <v>430783</v>
       </c>
       <c r="R242" t="n">
-        <v>6796133</v>
+        <v>6795818</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24865,22 +24841,22 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129773121</v>
+        <v>129771730</v>
       </c>
       <c r="B243" t="n">
-        <v>57733</v>
+        <v>91620</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24888,42 +24864,34 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>430707</v>
+        <v>430958</v>
       </c>
       <c r="R243" t="n">
-        <v>6795375</v>
+        <v>6795614</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24970,22 +24938,22 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129771739</v>
+        <v>129771784</v>
       </c>
       <c r="B244" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -24993,42 +24961,34 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>430752</v>
+        <v>430920</v>
       </c>
       <c r="R244" t="n">
-        <v>6795559</v>
+        <v>6795536</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25087,32 +25047,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129771716</v>
+        <v>129771747</v>
       </c>
       <c r="B245" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25120,7 +25080,7 @@
       <c r="L245" t="inlineStr"/>
       <c r="M245" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N245" t="inlineStr"/>
@@ -25130,10 +25090,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>430750</v>
+        <v>430947</v>
       </c>
       <c r="R245" t="n">
-        <v>6795558</v>
+        <v>6796064</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25192,10 +25152,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>129771730</v>
+        <v>129771742</v>
       </c>
       <c r="B246" t="n">
-        <v>91620</v>
+        <v>57733</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25203,34 +25163,42 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>430958</v>
+        <v>430934</v>
       </c>
       <c r="R246" t="n">
-        <v>6795614</v>
+        <v>6795641</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25289,10 +25257,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>129771785</v>
+        <v>129771746</v>
       </c>
       <c r="B247" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25300,34 +25268,42 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>430936</v>
+        <v>430942</v>
       </c>
       <c r="R247" t="n">
-        <v>6795608</v>
+        <v>6796133</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25386,10 +25362,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129771806</v>
+        <v>129773121</v>
       </c>
       <c r="B248" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25397,34 +25373,42 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>430974</v>
+        <v>430707</v>
       </c>
       <c r="R248" t="n">
-        <v>6796123</v>
+        <v>6795375</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25471,22 +25455,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>129771784</v>
+        <v>129771739</v>
       </c>
       <c r="B249" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25494,34 +25478,42 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>430920</v>
+        <v>430752</v>
       </c>
       <c r="R249" t="n">
-        <v>6795536</v>
+        <v>6795559</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25580,45 +25572,53 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>129773213</v>
+        <v>129771716</v>
       </c>
       <c r="B250" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>430783</v>
+        <v>430750</v>
       </c>
       <c r="R250" t="n">
-        <v>6795818</v>
+        <v>6795558</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25665,22 +25665,22 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129773202</v>
+        <v>129771738</v>
       </c>
       <c r="B251" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25688,34 +25688,42 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>430858</v>
+        <v>430655</v>
       </c>
       <c r="R251" t="n">
-        <v>6796064</v>
+        <v>6795565</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25762,22 +25770,22 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129771791</v>
+        <v>129773149</v>
       </c>
       <c r="B252" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -25785,21 +25793,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25809,10 +25817,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>430959</v>
+        <v>431021</v>
       </c>
       <c r="R252" t="n">
-        <v>6795606</v>
+        <v>6795524</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25859,65 +25867,57 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129771714</v>
+        <v>129771761</v>
       </c>
       <c r="B253" t="n">
-        <v>56926</v>
+        <v>78839</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>430528</v>
+        <v>430865</v>
       </c>
       <c r="R253" t="n">
-        <v>6795512</v>
+        <v>6795798</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -25976,53 +25976,45 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>129771718</v>
+        <v>129773202</v>
       </c>
       <c r="B254" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>430939</v>
+        <v>430858</v>
       </c>
       <c r="R254" t="n">
-        <v>6796145</v>
+        <v>6796064</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26069,22 +26061,22 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>129773112</v>
+        <v>129771791</v>
       </c>
       <c r="B255" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26092,42 +26084,34 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>430814</v>
+        <v>430959</v>
       </c>
       <c r="R255" t="n">
-        <v>6795837</v>
+        <v>6795606</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26174,44 +26158,44 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>129771738</v>
+        <v>129771714</v>
       </c>
       <c r="B256" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26219,7 +26203,7 @@
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N256" t="inlineStr"/>
@@ -26229,10 +26213,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>430655</v>
+        <v>430528</v>
       </c>
       <c r="R256" t="n">
-        <v>6795565</v>
+        <v>6795512</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26291,45 +26275,53 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>129773149</v>
+        <v>129771718</v>
       </c>
       <c r="B257" t="n">
-        <v>78839</v>
+        <v>56926</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>431021</v>
+        <v>430939</v>
       </c>
       <c r="R257" t="n">
-        <v>6795524</v>
+        <v>6796145</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26376,22 +26368,22 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>129771761</v>
+        <v>129773112</v>
       </c>
       <c r="B258" t="n">
-        <v>78839</v>
+        <v>57896</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26399,34 +26391,42 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>430865</v>
+        <v>430814</v>
       </c>
       <c r="R258" t="n">
-        <v>6795798</v>
+        <v>6795837</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26473,22 +26473,22 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>129773135</v>
+        <v>129773182</v>
       </c>
       <c r="B259" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26496,42 +26496,34 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>430938</v>
+        <v>430740</v>
       </c>
       <c r="R259" t="n">
-        <v>6795967</v>
+        <v>6795371</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -26590,10 +26582,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>129773120</v>
+        <v>129773180</v>
       </c>
       <c r="B260" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26601,42 +26593,34 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>430694</v>
+        <v>430789</v>
       </c>
       <c r="R260" t="n">
-        <v>6795368</v>
+        <v>6795377</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26695,7 +26679,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>129771744</v>
+        <v>129773135</v>
       </c>
       <c r="B261" t="n">
         <v>57733</v>
@@ -26738,10 +26722,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>430959</v>
+        <v>430938</v>
       </c>
       <c r="R261" t="n">
-        <v>6795543</v>
+        <v>6795967</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26788,19 +26772,19 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>129773133</v>
+        <v>129773120</v>
       </c>
       <c r="B262" t="n">
         <v>57733</v>
@@ -26843,10 +26827,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>430886</v>
+        <v>430694</v>
       </c>
       <c r="R262" t="n">
-        <v>6795969</v>
+        <v>6795368</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26905,10 +26889,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>129771786</v>
+        <v>129771744</v>
       </c>
       <c r="B263" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -26916,34 +26900,42 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>430927</v>
+        <v>430959</v>
       </c>
       <c r="R263" t="n">
-        <v>6795611</v>
+        <v>6795543</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27002,10 +26994,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>129773182</v>
+        <v>129773133</v>
       </c>
       <c r="B264" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27013,34 +27005,42 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>430740</v>
+        <v>430886</v>
       </c>
       <c r="R264" t="n">
-        <v>6795371</v>
+        <v>6795969</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27099,7 +27099,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>129773180</v>
+        <v>129771786</v>
       </c>
       <c r="B265" t="n">
         <v>79081</v>
@@ -27134,10 +27134,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>430789</v>
+        <v>430927</v>
       </c>
       <c r="R265" t="n">
-        <v>6795377</v>
+        <v>6795611</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27184,12 +27184,12 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
@@ -27293,54 +27293,45 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>129773163</v>
+        <v>129771817</v>
       </c>
       <c r="B267" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
-      <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>430632</v>
+        <v>430997</v>
       </c>
       <c r="R267" t="n">
-        <v>6795540</v>
+        <v>6795879</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27381,29 +27372,28 @@
       <c r="AE267" t="b">
         <v>0</v>
       </c>
-      <c r="AF267" t="inlineStr"/>
       <c r="AG267" t="b">
         <v>0</v>
       </c>
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>129773125</v>
+        <v>129771787</v>
       </c>
       <c r="B268" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -27411,42 +27401,34 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>430927</v>
+        <v>430921</v>
       </c>
       <c r="R268" t="n">
-        <v>6795321</v>
+        <v>6795636</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27493,22 +27475,22 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>129771817</v>
+        <v>129773100</v>
       </c>
       <c r="B269" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -27516,21 +27498,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27540,10 +27522,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>430997</v>
+        <v>430941</v>
       </c>
       <c r="R269" t="n">
-        <v>6795879</v>
+        <v>6795869</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27590,19 +27572,19 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>129771787</v>
+        <v>129771794</v>
       </c>
       <c r="B270" t="n">
         <v>79081</v>
@@ -27637,10 +27619,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>430921</v>
+        <v>430951</v>
       </c>
       <c r="R270" t="n">
-        <v>6795636</v>
+        <v>6795576</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -27699,10 +27681,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>129773100</v>
+        <v>129771768</v>
       </c>
       <c r="B271" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27710,21 +27692,21 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -27734,10 +27716,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>430941</v>
+        <v>430921</v>
       </c>
       <c r="R271" t="n">
-        <v>6795869</v>
+        <v>6796077</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27784,22 +27766,22 @@
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>129771794</v>
+        <v>129773125</v>
       </c>
       <c r="B272" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -27807,34 +27789,42 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>430951</v>
+        <v>430927</v>
       </c>
       <c r="R272" t="n">
-        <v>6795576</v>
+        <v>6795321</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27881,57 +27871,65 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>129771768</v>
+        <v>129773108</v>
       </c>
       <c r="B273" t="n">
-        <v>78838</v>
+        <v>56926</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>430921</v>
+        <v>430941</v>
       </c>
       <c r="R273" t="n">
-        <v>6796077</v>
+        <v>6795862</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27978,19 +27976,19 @@
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>129773108</v>
+        <v>129771715</v>
       </c>
       <c r="B274" t="n">
         <v>56926</v>
@@ -28033,10 +28031,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>430941</v>
+        <v>430568</v>
       </c>
       <c r="R274" t="n">
-        <v>6795862</v>
+        <v>6795570</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28083,19 +28081,19 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>129771715</v>
+        <v>129771720</v>
       </c>
       <c r="B275" t="n">
         <v>56926</v>
@@ -28138,10 +28136,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>430568</v>
+        <v>430972</v>
       </c>
       <c r="R275" t="n">
-        <v>6795570</v>
+        <v>6796056</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28200,32 +28198,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>129771720</v>
+        <v>129773103</v>
       </c>
       <c r="B276" t="n">
-        <v>56926</v>
+        <v>57736</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28233,7 +28231,7 @@
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N276" t="inlineStr"/>
@@ -28243,10 +28241,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>430972</v>
+        <v>430952</v>
       </c>
       <c r="R276" t="n">
-        <v>6796056</v>
+        <v>6795876</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28293,52 +28291,53 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>129773103</v>
+        <v>129773163</v>
       </c>
       <c r="B277" t="n">
-        <v>57736</v>
+        <v>8450</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N277" t="inlineStr"/>
@@ -28348,10 +28347,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>430952</v>
+        <v>430632</v>
       </c>
       <c r="R277" t="n">
-        <v>6795876</v>
+        <v>6795540</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -28392,6 +28391,7 @@
       <c r="AE277" t="b">
         <v>0</v>
       </c>
+      <c r="AF277" t="inlineStr"/>
       <c r="AG277" t="b">
         <v>0</v>
       </c>
@@ -28410,32 +28410,32 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>129773105</v>
+        <v>129773129</v>
       </c>
       <c r="B278" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -28443,7 +28443,7 @@
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N278" t="inlineStr"/>
@@ -28453,10 +28453,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>430923</v>
+        <v>430920</v>
       </c>
       <c r="R278" t="n">
-        <v>6796012</v>
+        <v>6796013</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28515,32 +28515,32 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>129771723</v>
+        <v>129773115</v>
       </c>
       <c r="B279" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28548,7 +28548,7 @@
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N279" t="inlineStr"/>
@@ -28558,10 +28558,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>430890</v>
+        <v>430594</v>
       </c>
       <c r="R279" t="n">
-        <v>6795825</v>
+        <v>6795423</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28608,53 +28608,52 @@
       <c r="AT279" t="inlineStr"/>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>129773160</v>
+        <v>129771748</v>
       </c>
       <c r="B280" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N280" t="inlineStr"/>
@@ -28664,10 +28663,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>430844</v>
+        <v>430982</v>
       </c>
       <c r="R280" t="n">
-        <v>6796058</v>
+        <v>6795907</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28708,29 +28707,28 @@
       <c r="AE280" t="b">
         <v>0</v>
       </c>
-      <c r="AF280" t="inlineStr"/>
       <c r="AG280" t="b">
         <v>0</v>
       </c>
       <c r="AT280" t="inlineStr"/>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>129773129</v>
+        <v>129773154</v>
       </c>
       <c r="B281" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28738,42 +28736,34 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>430920</v>
+        <v>430860</v>
       </c>
       <c r="R281" t="n">
-        <v>6796013</v>
+        <v>6795825</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -28832,10 +28822,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>129773115</v>
+        <v>129773157</v>
       </c>
       <c r="B282" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -28843,42 +28833,34 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
-      <c r="K282" t="inlineStr"/>
-      <c r="L282" t="inlineStr"/>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>430594</v>
+        <v>430617</v>
       </c>
       <c r="R282" t="n">
-        <v>6795423</v>
+        <v>6795600</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -28937,10 +28919,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>129771748</v>
+        <v>129771771</v>
       </c>
       <c r="B283" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -28948,42 +28930,34 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>430982</v>
+        <v>430868</v>
       </c>
       <c r="R283" t="n">
-        <v>6795907</v>
+        <v>6795798</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -29042,10 +29016,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>129771771</v>
+        <v>129771800</v>
       </c>
       <c r="B284" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -29053,21 +29027,21 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29077,10 +29051,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>430868</v>
+        <v>431011</v>
       </c>
       <c r="R284" t="n">
-        <v>6795798</v>
+        <v>6795579</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29139,45 +29113,53 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>129771800</v>
+        <v>129773105</v>
       </c>
       <c r="B285" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>431011</v>
+        <v>430923</v>
       </c>
       <c r="R285" t="n">
-        <v>6795579</v>
+        <v>6796012</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29224,54 +29206,62 @@
       <c r="AT285" t="inlineStr"/>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>129773154</v>
+        <v>129771723</v>
       </c>
       <c r="B286" t="n">
-        <v>78839</v>
+        <v>56926</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>430860</v>
+        <v>430890</v>
       </c>
       <c r="R286" t="n">
         <v>6795825</v>
@@ -29321,57 +29311,66 @@
       <c r="AT286" t="inlineStr"/>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>129773157</v>
+        <v>129773160</v>
       </c>
       <c r="B287" t="n">
-        <v>78839</v>
+        <v>8450</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
+      <c r="J287" t="inlineStr"/>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>430617</v>
+        <v>430844</v>
       </c>
       <c r="R287" t="n">
-        <v>6795600</v>
+        <v>6796058</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -29412,6 +29411,7 @@
       <c r="AE287" t="b">
         <v>0</v>
       </c>
+      <c r="AF287" t="inlineStr"/>
       <c r="AG287" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -13782,7 +13782,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129771737</v>
+        <v>129773137</v>
       </c>
       <c r="B132" t="n">
         <v>57733</v>
@@ -13815,7 +13815,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -13825,10 +13825,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430522</v>
+        <v>430851</v>
       </c>
       <c r="R132" t="n">
-        <v>6795537</v>
+        <v>6795824</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13875,19 +13875,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129771741</v>
+        <v>129773132</v>
       </c>
       <c r="B133" t="n">
         <v>57733</v>
@@ -13920,7 +13920,7 @@
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -13930,10 +13930,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>430784</v>
+        <v>430873</v>
       </c>
       <c r="R133" t="n">
-        <v>6795567</v>
+        <v>6795977</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13980,19 +13980,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129773137</v>
+        <v>129771750</v>
       </c>
       <c r="B134" t="n">
         <v>57733</v>
@@ -14035,10 +14035,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>430851</v>
+        <v>430973</v>
       </c>
       <c r="R134" t="n">
-        <v>6795824</v>
+        <v>6795877</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14085,22 +14085,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129773132</v>
+        <v>129773113</v>
       </c>
       <c r="B135" t="n">
-        <v>57733</v>
+        <v>91620</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14108,31 +14108,26 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14140,10 +14135,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>430873</v>
+        <v>430833</v>
       </c>
       <c r="R135" t="n">
-        <v>6795977</v>
+        <v>6796045</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14178,12 +14173,18 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>2 st på samma tall.</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14202,7 +14203,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129771750</v>
+        <v>129771737</v>
       </c>
       <c r="B136" t="n">
         <v>57733</v>
@@ -14235,7 +14236,7 @@
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -14245,10 +14246,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>430973</v>
+        <v>430522</v>
       </c>
       <c r="R136" t="n">
-        <v>6795877</v>
+        <v>6795537</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14307,10 +14308,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129773143</v>
+        <v>129771741</v>
       </c>
       <c r="B137" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14318,34 +14319,42 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>430730</v>
+        <v>430784</v>
       </c>
       <c r="R137" t="n">
-        <v>6795404</v>
+        <v>6795567</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14392,22 +14401,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129773153</v>
+        <v>129771710</v>
       </c>
       <c r="B138" t="n">
-        <v>78839</v>
+        <v>57736</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14415,34 +14424,42 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>430886</v>
+        <v>430669</v>
       </c>
       <c r="R138" t="n">
-        <v>6796067</v>
+        <v>6795823</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14489,49 +14506,54 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129773113</v>
+        <v>129771719</v>
       </c>
       <c r="B139" t="n">
-        <v>91620</v>
+        <v>56926</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -14539,10 +14561,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>430833</v>
+        <v>430937</v>
       </c>
       <c r="R139" t="n">
-        <v>6796045</v>
+        <v>6796046</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14577,62 +14599,56 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>2 st på samma tall.</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129771710</v>
+        <v>129771724</v>
       </c>
       <c r="B140" t="n">
-        <v>57736</v>
+        <v>56926</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14640,7 +14656,7 @@
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -14650,10 +14666,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>430669</v>
+        <v>430884</v>
       </c>
       <c r="R140" t="n">
-        <v>6795823</v>
+        <v>6795785</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14712,53 +14728,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129771719</v>
+        <v>129773143</v>
       </c>
       <c r="B141" t="n">
-        <v>56926</v>
+        <v>78839</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>430937</v>
+        <v>430730</v>
       </c>
       <c r="R141" t="n">
-        <v>6796046</v>
+        <v>6795404</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14805,65 +14813,57 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129771724</v>
+        <v>129773153</v>
       </c>
       <c r="B142" t="n">
-        <v>56926</v>
+        <v>78839</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>430884</v>
+        <v>430886</v>
       </c>
       <c r="R142" t="n">
-        <v>6795785</v>
+        <v>6796067</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14910,12 +14910,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -18531,7 +18531,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129771803</v>
+        <v>129771811</v>
       </c>
       <c r="B179" t="n">
         <v>79081</v>
@@ -18566,10 +18566,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>430878</v>
+        <v>430910</v>
       </c>
       <c r="R179" t="n">
-        <v>6795999</v>
+        <v>6796078</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18628,10 +18628,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129773168</v>
+        <v>129773197</v>
       </c>
       <c r="B180" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18639,34 +18639,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>430617</v>
+        <v>431062</v>
       </c>
       <c r="R180" t="n">
-        <v>6795600</v>
+        <v>6795533</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18707,6 +18710,7 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
+      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
@@ -18725,10 +18729,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129771811</v>
+        <v>129773128</v>
       </c>
       <c r="B181" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18736,34 +18740,42 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>430910</v>
+        <v>430918</v>
       </c>
       <c r="R181" t="n">
-        <v>6796078</v>
+        <v>6795985</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18810,22 +18822,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129773197</v>
+        <v>129773150</v>
       </c>
       <c r="B182" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18833,37 +18845,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>431062</v>
+        <v>431067</v>
       </c>
       <c r="R182" t="n">
-        <v>6795533</v>
+        <v>6795549</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18904,7 +18913,6 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
@@ -18923,10 +18931,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129773128</v>
+        <v>129771803</v>
       </c>
       <c r="B183" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18934,42 +18942,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>430918</v>
+        <v>430878</v>
       </c>
       <c r="R183" t="n">
-        <v>6795985</v>
+        <v>6795999</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19016,22 +19016,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129773150</v>
+        <v>129773168</v>
       </c>
       <c r="B184" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19039,21 +19039,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19063,10 +19063,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>431067</v>
+        <v>430617</v>
       </c>
       <c r="R184" t="n">
-        <v>6795549</v>
+        <v>6795600</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19416,10 +19416,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129771812</v>
+        <v>129773122</v>
       </c>
       <c r="B188" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19427,34 +19427,42 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430903</v>
+        <v>430702</v>
       </c>
       <c r="R188" t="n">
-        <v>6796058</v>
+        <v>6795444</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19501,22 +19509,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129771807</v>
+        <v>129771728</v>
       </c>
       <c r="B189" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19524,34 +19532,42 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430914</v>
+        <v>430863</v>
       </c>
       <c r="R189" t="n">
-        <v>6796105</v>
+        <v>6795800</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19610,10 +19626,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129771729</v>
+        <v>129771812</v>
       </c>
       <c r="B190" t="n">
-        <v>91620</v>
+        <v>79081</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19621,21 +19637,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19645,10 +19661,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430543</v>
+        <v>430903</v>
       </c>
       <c r="R190" t="n">
-        <v>6795503</v>
+        <v>6796058</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19707,32 +19723,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129771703</v>
+        <v>129771807</v>
       </c>
       <c r="B191" t="n">
-        <v>91563</v>
+        <v>79081</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19742,10 +19758,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430735</v>
+        <v>430914</v>
       </c>
       <c r="R191" t="n">
-        <v>6795805</v>
+        <v>6796105</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19804,10 +19820,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129773122</v>
+        <v>129771729</v>
       </c>
       <c r="B192" t="n">
-        <v>57733</v>
+        <v>91620</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19815,42 +19831,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430702</v>
+        <v>430543</v>
       </c>
       <c r="R192" t="n">
-        <v>6795444</v>
+        <v>6795503</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19897,65 +19905,57 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129771728</v>
+        <v>129771703</v>
       </c>
       <c r="B193" t="n">
-        <v>57896</v>
+        <v>91563</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430863</v>
+        <v>430735</v>
       </c>
       <c r="R193" t="n">
-        <v>6795800</v>
+        <v>6795805</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20119,10 +20119,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129773119</v>
+        <v>129773211</v>
       </c>
       <c r="B195" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20130,42 +20130,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430692</v>
+        <v>430815</v>
       </c>
       <c r="R195" t="n">
-        <v>6795373</v>
+        <v>6795818</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20224,7 +20216,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129773211</v>
+        <v>129771814</v>
       </c>
       <c r="B196" t="n">
         <v>79081</v>
@@ -20259,10 +20251,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430815</v>
+        <v>430944</v>
       </c>
       <c r="R196" t="n">
-        <v>6795818</v>
+        <v>6796075</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20309,19 +20301,19 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129771814</v>
+        <v>129771796</v>
       </c>
       <c r="B197" t="n">
         <v>79081</v>
@@ -20356,10 +20348,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>430944</v>
+        <v>430984</v>
       </c>
       <c r="R197" t="n">
-        <v>6796075</v>
+        <v>6795518</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20418,7 +20410,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129771796</v>
+        <v>129773207</v>
       </c>
       <c r="B198" t="n">
         <v>79081</v>
@@ -20453,10 +20445,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>430984</v>
+        <v>430947</v>
       </c>
       <c r="R198" t="n">
-        <v>6795518</v>
+        <v>6795977</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20503,22 +20495,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129773207</v>
+        <v>129773119</v>
       </c>
       <c r="B199" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20526,34 +20518,42 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>430947</v>
+        <v>430692</v>
       </c>
       <c r="R199" t="n">
-        <v>6795977</v>
+        <v>6795373</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20816,45 +20816,53 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129771706</v>
+        <v>129771725</v>
       </c>
       <c r="B202" t="n">
-        <v>79700</v>
+        <v>56926</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>430935</v>
+        <v>430867</v>
       </c>
       <c r="R202" t="n">
-        <v>6795595</v>
+        <v>6795794</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20913,10 +20921,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129771808</v>
+        <v>129773145</v>
       </c>
       <c r="B203" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20924,21 +20932,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20948,10 +20956,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>430894</v>
+        <v>430935</v>
       </c>
       <c r="R203" t="n">
-        <v>6796093</v>
+        <v>6795319</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20998,66 +21006,57 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129773161</v>
+        <v>129771758</v>
       </c>
       <c r="B204" t="n">
-        <v>8450</v>
+        <v>78839</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>430911</v>
+        <v>430921</v>
       </c>
       <c r="R204" t="n">
-        <v>6795982</v>
+        <v>6795636</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21098,72 +21097,63 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
-      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129771725</v>
+        <v>129771706</v>
       </c>
       <c r="B205" t="n">
-        <v>56926</v>
+        <v>79700</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>430867</v>
+        <v>430935</v>
       </c>
       <c r="R205" t="n">
-        <v>6795794</v>
+        <v>6795595</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21222,10 +21212,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129773145</v>
+        <v>129771808</v>
       </c>
       <c r="B206" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21233,21 +21223,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21257,10 +21247,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>430935</v>
+        <v>430894</v>
       </c>
       <c r="R206" t="n">
-        <v>6795319</v>
+        <v>6796093</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21307,57 +21297,66 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129771758</v>
+        <v>129773161</v>
       </c>
       <c r="B207" t="n">
-        <v>78839</v>
+        <v>8450</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>430921</v>
+        <v>430911</v>
       </c>
       <c r="R207" t="n">
-        <v>6795636</v>
+        <v>6795982</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21398,18 +21397,19 @@
       <c r="AE207" t="b">
         <v>0</v>
       </c>
+      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
@@ -22491,10 +22491,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129773177</v>
+        <v>129773166</v>
       </c>
       <c r="B219" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22502,21 +22502,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22526,10 +22526,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>430633</v>
+        <v>430897</v>
       </c>
       <c r="R219" t="n">
-        <v>6795435</v>
+        <v>6795988</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22588,10 +22588,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129773166</v>
+        <v>129773190</v>
       </c>
       <c r="B220" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22599,21 +22599,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22623,10 +22623,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>430897</v>
+        <v>430984</v>
       </c>
       <c r="R220" t="n">
-        <v>6795988</v>
+        <v>6795313</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22685,7 +22685,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129773190</v>
+        <v>129773189</v>
       </c>
       <c r="B221" t="n">
         <v>79081</v>
@@ -22720,10 +22720,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>430984</v>
+        <v>430904</v>
       </c>
       <c r="R221" t="n">
-        <v>6795313</v>
+        <v>6795339</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22782,7 +22782,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129773189</v>
+        <v>129771813</v>
       </c>
       <c r="B222" t="n">
         <v>79081</v>
@@ -22817,10 +22817,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>430904</v>
+        <v>430910</v>
       </c>
       <c r="R222" t="n">
-        <v>6795339</v>
+        <v>6796073</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22867,19 +22867,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129771813</v>
+        <v>129773177</v>
       </c>
       <c r="B223" t="n">
         <v>79081</v>
@@ -22914,10 +22914,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430910</v>
+        <v>430633</v>
       </c>
       <c r="R223" t="n">
-        <v>6796073</v>
+        <v>6795435</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22964,12 +22964,12 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
@@ -24562,10 +24562,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129771785</v>
+        <v>129771747</v>
       </c>
       <c r="B240" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24573,34 +24573,42 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>430936</v>
+        <v>430947</v>
       </c>
       <c r="R240" t="n">
-        <v>6795608</v>
+        <v>6796064</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24659,10 +24667,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129771806</v>
+        <v>129771742</v>
       </c>
       <c r="B241" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24670,34 +24678,42 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>430974</v>
+        <v>430934</v>
       </c>
       <c r="R241" t="n">
-        <v>6796123</v>
+        <v>6795641</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24756,10 +24772,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129773213</v>
+        <v>129771746</v>
       </c>
       <c r="B242" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24767,34 +24783,42 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>430783</v>
+        <v>430942</v>
       </c>
       <c r="R242" t="n">
-        <v>6795818</v>
+        <v>6796133</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24841,22 +24865,22 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129771730</v>
+        <v>129773121</v>
       </c>
       <c r="B243" t="n">
-        <v>91620</v>
+        <v>57733</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24864,34 +24888,42 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>430958</v>
+        <v>430707</v>
       </c>
       <c r="R243" t="n">
-        <v>6795614</v>
+        <v>6795375</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24938,22 +24970,22 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129771784</v>
+        <v>129771739</v>
       </c>
       <c r="B244" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -24961,34 +24993,42 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>430920</v>
+        <v>430752</v>
       </c>
       <c r="R244" t="n">
-        <v>6795536</v>
+        <v>6795559</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25047,10 +25087,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129771747</v>
+        <v>129771730</v>
       </c>
       <c r="B245" t="n">
-        <v>57733</v>
+        <v>91620</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25058,42 +25098,34 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>430947</v>
+        <v>430958</v>
       </c>
       <c r="R245" t="n">
-        <v>6796064</v>
+        <v>6795614</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25152,10 +25184,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>129771742</v>
+        <v>129771784</v>
       </c>
       <c r="B246" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25163,42 +25195,34 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>430934</v>
+        <v>430920</v>
       </c>
       <c r="R246" t="n">
-        <v>6795641</v>
+        <v>6795536</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25257,10 +25281,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>129771746</v>
+        <v>129771785</v>
       </c>
       <c r="B247" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25268,42 +25292,34 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>430942</v>
+        <v>430936</v>
       </c>
       <c r="R247" t="n">
-        <v>6796133</v>
+        <v>6795608</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25362,10 +25378,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129773121</v>
+        <v>129771806</v>
       </c>
       <c r="B248" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25373,42 +25389,34 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>430707</v>
+        <v>430974</v>
       </c>
       <c r="R248" t="n">
-        <v>6795375</v>
+        <v>6796123</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25455,22 +25463,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>129771739</v>
+        <v>129773213</v>
       </c>
       <c r="B249" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25478,42 +25486,34 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>430752</v>
+        <v>430783</v>
       </c>
       <c r="R249" t="n">
-        <v>6795559</v>
+        <v>6795818</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25560,12 +25560,12 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
@@ -25677,10 +25677,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129771738</v>
+        <v>129771791</v>
       </c>
       <c r="B251" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25688,42 +25688,34 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>430655</v>
+        <v>430959</v>
       </c>
       <c r="R251" t="n">
-        <v>6795565</v>
+        <v>6795606</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25782,10 +25774,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129773149</v>
+        <v>129773202</v>
       </c>
       <c r="B252" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -25793,21 +25785,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25817,10 +25809,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>431021</v>
+        <v>430858</v>
       </c>
       <c r="R252" t="n">
-        <v>6795524</v>
+        <v>6796064</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25879,10 +25871,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129771761</v>
+        <v>129771738</v>
       </c>
       <c r="B253" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -25890,34 +25882,42 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>430865</v>
+        <v>430655</v>
       </c>
       <c r="R253" t="n">
-        <v>6795798</v>
+        <v>6795565</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -25976,45 +25976,53 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>129773202</v>
+        <v>129771714</v>
       </c>
       <c r="B254" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>430858</v>
+        <v>430528</v>
       </c>
       <c r="R254" t="n">
-        <v>6796064</v>
+        <v>6795512</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26061,57 +26069,65 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>129771791</v>
+        <v>129771718</v>
       </c>
       <c r="B255" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>430959</v>
+        <v>430939</v>
       </c>
       <c r="R255" t="n">
-        <v>6795606</v>
+        <v>6796145</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26170,32 +26186,32 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>129771714</v>
+        <v>129773112</v>
       </c>
       <c r="B256" t="n">
-        <v>56926</v>
+        <v>57896</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26203,7 +26219,7 @@
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N256" t="inlineStr"/>
@@ -26213,10 +26229,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>430528</v>
+        <v>430814</v>
       </c>
       <c r="R256" t="n">
-        <v>6795512</v>
+        <v>6795837</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26263,65 +26279,57 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>129771718</v>
+        <v>129773149</v>
       </c>
       <c r="B257" t="n">
-        <v>56926</v>
+        <v>78839</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>430939</v>
+        <v>431021</v>
       </c>
       <c r="R257" t="n">
-        <v>6796145</v>
+        <v>6795524</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26368,22 +26376,22 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>129773112</v>
+        <v>129771761</v>
       </c>
       <c r="B258" t="n">
-        <v>57896</v>
+        <v>78839</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26391,42 +26399,34 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>430814</v>
+        <v>430865</v>
       </c>
       <c r="R258" t="n">
-        <v>6795837</v>
+        <v>6795798</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26473,12 +26473,12 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
@@ -27293,45 +27293,54 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>129771817</v>
+        <v>129773163</v>
       </c>
       <c r="B267" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>430997</v>
+        <v>430632</v>
       </c>
       <c r="R267" t="n">
-        <v>6795879</v>
+        <v>6795540</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27372,25 +27381,26 @@
       <c r="AE267" t="b">
         <v>0</v>
       </c>
+      <c r="AF267" t="inlineStr"/>
       <c r="AG267" t="b">
         <v>0</v>
       </c>
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>129771787</v>
+        <v>129771817</v>
       </c>
       <c r="B268" t="n">
         <v>79081</v>
@@ -27425,10 +27435,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>430921</v>
+        <v>430997</v>
       </c>
       <c r="R268" t="n">
-        <v>6795636</v>
+        <v>6795879</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27487,10 +27497,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>129773100</v>
+        <v>129771787</v>
       </c>
       <c r="B269" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -27498,21 +27508,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27522,10 +27532,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>430941</v>
+        <v>430921</v>
       </c>
       <c r="R269" t="n">
-        <v>6795869</v>
+        <v>6795636</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27572,22 +27582,22 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>129771794</v>
+        <v>129773100</v>
       </c>
       <c r="B270" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27595,21 +27605,21 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -27619,10 +27629,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>430951</v>
+        <v>430941</v>
       </c>
       <c r="R270" t="n">
-        <v>6795576</v>
+        <v>6795869</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -27669,22 +27679,22 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>129771768</v>
+        <v>129771794</v>
       </c>
       <c r="B271" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27692,21 +27702,21 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -27716,10 +27726,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>430921</v>
+        <v>430951</v>
       </c>
       <c r="R271" t="n">
-        <v>6796077</v>
+        <v>6795576</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27778,10 +27788,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>129773125</v>
+        <v>129771768</v>
       </c>
       <c r="B272" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -27789,42 +27799,34 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>430927</v>
+        <v>430921</v>
       </c>
       <c r="R272" t="n">
-        <v>6795321</v>
+        <v>6796077</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27871,44 +27873,44 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>129773108</v>
+        <v>129773125</v>
       </c>
       <c r="B273" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -27916,7 +27918,7 @@
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N273" t="inlineStr"/>
@@ -27926,10 +27928,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>430941</v>
+        <v>430927</v>
       </c>
       <c r="R273" t="n">
-        <v>6795862</v>
+        <v>6795321</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27988,7 +27990,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>129771715</v>
+        <v>129773108</v>
       </c>
       <c r="B274" t="n">
         <v>56926</v>
@@ -28031,10 +28033,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>430568</v>
+        <v>430941</v>
       </c>
       <c r="R274" t="n">
-        <v>6795570</v>
+        <v>6795862</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28081,19 +28083,19 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>129771720</v>
+        <v>129771715</v>
       </c>
       <c r="B275" t="n">
         <v>56926</v>
@@ -28136,10 +28138,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>430972</v>
+        <v>430568</v>
       </c>
       <c r="R275" t="n">
-        <v>6796056</v>
+        <v>6795570</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28198,32 +28200,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>129773103</v>
+        <v>129771720</v>
       </c>
       <c r="B276" t="n">
-        <v>57736</v>
+        <v>56926</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28231,7 +28233,7 @@
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N276" t="inlineStr"/>
@@ -28241,10 +28243,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>430952</v>
+        <v>430972</v>
       </c>
       <c r="R276" t="n">
-        <v>6795876</v>
+        <v>6796056</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28291,53 +28293,52 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>129773163</v>
+        <v>129773103</v>
       </c>
       <c r="B277" t="n">
-        <v>8450</v>
+        <v>57736</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N277" t="inlineStr"/>
@@ -28347,10 +28348,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>430632</v>
+        <v>430952</v>
       </c>
       <c r="R277" t="n">
-        <v>6795540</v>
+        <v>6795876</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -28391,7 +28392,6 @@
       <c r="AE277" t="b">
         <v>0</v>
       </c>
-      <c r="AF277" t="inlineStr"/>
       <c r="AG277" t="b">
         <v>0</v>
       </c>
@@ -28410,10 +28410,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>129773129</v>
+        <v>129771771</v>
       </c>
       <c r="B278" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28421,42 +28421,34 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>430920</v>
+        <v>430868</v>
       </c>
       <c r="R278" t="n">
-        <v>6796013</v>
+        <v>6795798</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28503,22 +28495,22 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>129773115</v>
+        <v>129771800</v>
       </c>
       <c r="B279" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -28526,42 +28518,34 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>430594</v>
+        <v>431011</v>
       </c>
       <c r="R279" t="n">
-        <v>6795423</v>
+        <v>6795579</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28608,19 +28592,19 @@
       <c r="AT279" t="inlineStr"/>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>129771748</v>
+        <v>129773129</v>
       </c>
       <c r="B280" t="n">
         <v>57733</v>
@@ -28653,7 +28637,7 @@
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N280" t="inlineStr"/>
@@ -28663,10 +28647,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>430982</v>
+        <v>430920</v>
       </c>
       <c r="R280" t="n">
-        <v>6795907</v>
+        <v>6796013</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28713,22 +28697,22 @@
       <c r="AT280" t="inlineStr"/>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>129773154</v>
+        <v>129773115</v>
       </c>
       <c r="B281" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28736,34 +28720,42 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>430860</v>
+        <v>430594</v>
       </c>
       <c r="R281" t="n">
-        <v>6795825</v>
+        <v>6795423</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -28822,10 +28814,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>129773157</v>
+        <v>129771748</v>
       </c>
       <c r="B282" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -28833,34 +28825,42 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>430617</v>
+        <v>430982</v>
       </c>
       <c r="R282" t="n">
-        <v>6795600</v>
+        <v>6795907</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -28907,57 +28907,65 @@
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>129771771</v>
+        <v>129773105</v>
       </c>
       <c r="B283" t="n">
-        <v>78838</v>
+        <v>56926</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>430868</v>
+        <v>430923</v>
       </c>
       <c r="R283" t="n">
-        <v>6795798</v>
+        <v>6796012</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -29004,57 +29012,65 @@
       <c r="AT283" t="inlineStr"/>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>129771800</v>
+        <v>129771723</v>
       </c>
       <c r="B284" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr"/>
       <c r="P284" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>431011</v>
+        <v>430890</v>
       </c>
       <c r="R284" t="n">
-        <v>6795579</v>
+        <v>6795825</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29113,53 +29129,45 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>129773105</v>
+        <v>129773157</v>
       </c>
       <c r="B285" t="n">
-        <v>56926</v>
+        <v>78839</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
-      <c r="K285" t="inlineStr"/>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>430923</v>
+        <v>430617</v>
       </c>
       <c r="R285" t="n">
-        <v>6796012</v>
+        <v>6795600</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29218,10 +29226,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>129771723</v>
+        <v>129773160</v>
       </c>
       <c r="B286" t="n">
-        <v>56926</v>
+        <v>8450</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -29229,29 +29237,30 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
+      <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr"/>
       <c r="M286" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N286" t="inlineStr"/>
@@ -29261,10 +29270,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>430890</v>
+        <v>430844</v>
       </c>
       <c r="R286" t="n">
-        <v>6795825</v>
+        <v>6796058</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -29305,72 +29314,64 @@
       <c r="AE286" t="b">
         <v>0</v>
       </c>
+      <c r="AF286" t="inlineStr"/>
       <c r="AG286" t="b">
         <v>0</v>
       </c>
       <c r="AT286" t="inlineStr"/>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>129773160</v>
+        <v>129773154</v>
       </c>
       <c r="B287" t="n">
-        <v>8450</v>
+        <v>78839</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
-      <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
-      <c r="M287" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>430844</v>
+        <v>430860</v>
       </c>
       <c r="R287" t="n">
-        <v>6796058</v>
+        <v>6795825</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -29411,7 +29412,6 @@
       <c r="AE287" t="b">
         <v>0</v>
       </c>
-      <c r="AF287" t="inlineStr"/>
       <c r="AG287" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -13685,45 +13685,53 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129773214</v>
+        <v>129771719</v>
       </c>
       <c r="B131" t="n">
-        <v>79081</v>
+        <v>56927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>430777</v>
+        <v>430937</v>
       </c>
       <c r="R131" t="n">
-        <v>6795822</v>
+        <v>6796046</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13770,44 +13778,44 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129773137</v>
+        <v>129771724</v>
       </c>
       <c r="B132" t="n">
-        <v>57733</v>
+        <v>56927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13815,7 +13823,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -13825,10 +13833,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430851</v>
+        <v>430884</v>
       </c>
       <c r="R132" t="n">
-        <v>6795824</v>
+        <v>6795785</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13875,22 +13883,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129773132</v>
+        <v>129771710</v>
       </c>
       <c r="B133" t="n">
-        <v>57733</v>
+        <v>57737</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13898,16 +13906,16 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -13920,7 +13928,7 @@
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -13930,10 +13938,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>430873</v>
+        <v>430669</v>
       </c>
       <c r="R133" t="n">
-        <v>6795977</v>
+        <v>6795823</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13980,22 +13988,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129771750</v>
+        <v>129771737</v>
       </c>
       <c r="B134" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14025,7 +14033,7 @@
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -14035,10 +14043,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>430973</v>
+        <v>430522</v>
       </c>
       <c r="R134" t="n">
-        <v>6795877</v>
+        <v>6795537</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14097,10 +14105,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129773113</v>
+        <v>129773137</v>
       </c>
       <c r="B135" t="n">
-        <v>91620</v>
+        <v>57734</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14108,26 +14116,31 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14135,10 +14148,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>430833</v>
+        <v>430851</v>
       </c>
       <c r="R135" t="n">
-        <v>6796045</v>
+        <v>6795824</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14173,18 +14186,12 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>2 st på samma tall.</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14203,10 +14210,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129771737</v>
+        <v>129773132</v>
       </c>
       <c r="B136" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14236,7 +14243,7 @@
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -14246,10 +14253,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>430522</v>
+        <v>430873</v>
       </c>
       <c r="R136" t="n">
-        <v>6795537</v>
+        <v>6795977</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14296,22 +14303,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129771741</v>
+        <v>129771750</v>
       </c>
       <c r="B137" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14341,7 +14348,7 @@
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -14351,10 +14358,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>430784</v>
+        <v>430973</v>
       </c>
       <c r="R137" t="n">
-        <v>6795567</v>
+        <v>6795877</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14413,10 +14420,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129771710</v>
+        <v>129771741</v>
       </c>
       <c r="B138" t="n">
-        <v>57736</v>
+        <v>57734</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14424,16 +14431,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -14456,10 +14463,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>430669</v>
+        <v>430784</v>
       </c>
       <c r="R138" t="n">
-        <v>6795823</v>
+        <v>6795567</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14518,42 +14525,37 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129771719</v>
+        <v>129773113</v>
       </c>
       <c r="B139" t="n">
-        <v>56926</v>
+        <v>91623</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -14561,10 +14563,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>430937</v>
+        <v>430833</v>
       </c>
       <c r="R139" t="n">
-        <v>6796046</v>
+        <v>6796045</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14599,77 +14601,75 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>2 st på samma tall.</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129771724</v>
+        <v>129773214</v>
       </c>
       <c r="B140" t="n">
-        <v>56926</v>
+        <v>79084</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>430884</v>
+        <v>430777</v>
       </c>
       <c r="R140" t="n">
-        <v>6795785</v>
+        <v>6795822</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14716,12 +14716,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -14731,7 +14731,7 @@
         <v>129773143</v>
       </c>
       <c r="B141" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>129773153</v>
       </c>
       <c r="B142" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14922,10 +14922,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129773196</v>
+        <v>129771745</v>
       </c>
       <c r="B143" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14933,34 +14933,42 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431034</v>
+        <v>430945</v>
       </c>
       <c r="R143" t="n">
-        <v>6795525</v>
+        <v>6796127</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15007,22 +15015,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129771810</v>
+        <v>129771743</v>
       </c>
       <c r="B144" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15030,34 +15038,42 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430894</v>
+        <v>430957</v>
       </c>
       <c r="R144" t="n">
-        <v>6796084</v>
+        <v>6795610</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15116,10 +15132,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129771783</v>
+        <v>129773196</v>
       </c>
       <c r="B145" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15151,10 +15167,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>430787</v>
+        <v>431034</v>
       </c>
       <c r="R145" t="n">
-        <v>6795560</v>
+        <v>6795525</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15201,12 +15217,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -15216,7 +15232,7 @@
         <v>129773210</v>
       </c>
       <c r="B146" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15310,10 +15326,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129771745</v>
+        <v>129771810</v>
       </c>
       <c r="B147" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15321,42 +15337,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>430945</v>
+        <v>430894</v>
       </c>
       <c r="R147" t="n">
-        <v>6796127</v>
+        <v>6796084</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15415,10 +15423,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129771743</v>
+        <v>129771783</v>
       </c>
       <c r="B148" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15426,42 +15434,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>430957</v>
+        <v>430787</v>
       </c>
       <c r="R148" t="n">
-        <v>6795610</v>
+        <v>6795560</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15523,7 +15523,7 @@
         <v>129771760</v>
       </c>
       <c r="B149" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15617,10 +15617,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129771751</v>
+        <v>129771797</v>
       </c>
       <c r="B150" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15628,42 +15628,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>430983</v>
+        <v>430960</v>
       </c>
       <c r="R150" t="n">
-        <v>6795850</v>
+        <v>6795549</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15722,10 +15714,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129773134</v>
+        <v>129773185</v>
       </c>
       <c r="B151" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15733,42 +15725,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>430894</v>
+        <v>430821</v>
       </c>
       <c r="R151" t="n">
-        <v>6795968</v>
+        <v>6795424</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15827,53 +15811,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129771717</v>
+        <v>129771788</v>
       </c>
       <c r="B152" t="n">
-        <v>56926</v>
+        <v>79084</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>430918</v>
+        <v>430957</v>
       </c>
       <c r="R152" t="n">
-        <v>6795982</v>
+        <v>6795628</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15906,6 +15882,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 10 m</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15932,10 +15913,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129773155</v>
+        <v>129771804</v>
       </c>
       <c r="B153" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15943,21 +15924,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15967,10 +15948,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>430833</v>
+        <v>430865</v>
       </c>
       <c r="R153" t="n">
-        <v>6795830</v>
+        <v>6796072</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16017,22 +15998,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129771797</v>
+        <v>129771751</v>
       </c>
       <c r="B154" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16040,34 +16021,42 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>430960</v>
+        <v>430983</v>
       </c>
       <c r="R154" t="n">
-        <v>6795549</v>
+        <v>6795850</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16126,10 +16115,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129773185</v>
+        <v>129773134</v>
       </c>
       <c r="B155" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16137,34 +16126,42 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>430821</v>
+        <v>430894</v>
       </c>
       <c r="R155" t="n">
-        <v>6795424</v>
+        <v>6795968</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16223,45 +16220,53 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129771788</v>
+        <v>129771717</v>
       </c>
       <c r="B156" t="n">
-        <v>79081</v>
+        <v>56927</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>430957</v>
+        <v>430918</v>
       </c>
       <c r="R156" t="n">
-        <v>6795628</v>
+        <v>6795982</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16294,11 +16299,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 10 m</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16325,10 +16325,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129771804</v>
+        <v>129773155</v>
       </c>
       <c r="B157" t="n">
-        <v>79081</v>
+        <v>78842</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16336,21 +16336,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16360,10 +16360,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>430865</v>
+        <v>430833</v>
       </c>
       <c r="R157" t="n">
-        <v>6796072</v>
+        <v>6795830</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16410,52 +16410,53 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129773138</v>
+        <v>129773158</v>
       </c>
       <c r="B158" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -16465,10 +16466,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>430825</v>
+        <v>430704</v>
       </c>
       <c r="R158" t="n">
-        <v>6795805</v>
+        <v>6795457</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16509,6 +16510,7 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -16527,10 +16529,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129773124</v>
+        <v>129773204</v>
       </c>
       <c r="B159" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16538,42 +16540,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>430865</v>
+        <v>430881</v>
       </c>
       <c r="R159" t="n">
-        <v>6795387</v>
+        <v>6795985</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16632,53 +16626,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129771713</v>
+        <v>129773183</v>
       </c>
       <c r="B160" t="n">
-        <v>56926</v>
+        <v>79084</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>430542</v>
+        <v>430698</v>
       </c>
       <c r="R160" t="n">
-        <v>6795485</v>
+        <v>6795386</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16725,44 +16711,44 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129773204</v>
+        <v>129771754</v>
       </c>
       <c r="B161" t="n">
-        <v>79081</v>
+        <v>92055</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16772,10 +16758,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>430881</v>
+        <v>430535</v>
       </c>
       <c r="R161" t="n">
-        <v>6795985</v>
+        <v>6795489</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16810,34 +16796,40 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129773183</v>
+        <v>129773138</v>
       </c>
       <c r="B162" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16845,34 +16837,42 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>430698</v>
+        <v>430825</v>
       </c>
       <c r="R162" t="n">
-        <v>6795386</v>
+        <v>6795805</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16931,45 +16931,53 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129771754</v>
+        <v>129773124</v>
       </c>
       <c r="B163" t="n">
-        <v>92052</v>
+        <v>57734</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>430535</v>
+        <v>430865</v>
       </c>
       <c r="R163" t="n">
-        <v>6795489</v>
+        <v>6795387</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17004,30 +17012,24 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
@@ -17037,7 +17039,7 @@
         <v>129771753</v>
       </c>
       <c r="B164" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17139,10 +17141,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129773158</v>
+        <v>129771713</v>
       </c>
       <c r="B165" t="n">
-        <v>8450</v>
+        <v>56927</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17150,30 +17152,29 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -17183,10 +17184,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>430704</v>
+        <v>430542</v>
       </c>
       <c r="R165" t="n">
-        <v>6795457</v>
+        <v>6795485</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17227,29 +17228,28 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129771799</v>
+        <v>129773102</v>
       </c>
       <c r="B166" t="n">
-        <v>79081</v>
+        <v>79674</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17257,21 +17257,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17281,10 +17281,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>431001</v>
+        <v>431020</v>
       </c>
       <c r="R166" t="n">
-        <v>6795561</v>
+        <v>6795529</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17331,22 +17331,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129771793</v>
+        <v>129773141</v>
       </c>
       <c r="B167" t="n">
-        <v>79081</v>
+        <v>78842</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17354,21 +17354,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17378,10 +17378,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>430946</v>
+        <v>430600</v>
       </c>
       <c r="R167" t="n">
-        <v>6795572</v>
+        <v>6795424</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17428,22 +17428,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129773141</v>
+        <v>129771799</v>
       </c>
       <c r="B168" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17451,21 +17451,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17475,10 +17475,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>430600</v>
+        <v>431001</v>
       </c>
       <c r="R168" t="n">
-        <v>6795424</v>
+        <v>6795561</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17525,22 +17525,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129773102</v>
+        <v>129771793</v>
       </c>
       <c r="B169" t="n">
-        <v>79671</v>
+        <v>79084</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17548,21 +17548,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17572,10 +17572,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>431020</v>
+        <v>430946</v>
       </c>
       <c r="R169" t="n">
-        <v>6795529</v>
+        <v>6795572</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17622,22 +17622,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129771732</v>
+        <v>129773117</v>
       </c>
       <c r="B170" t="n">
-        <v>91620</v>
+        <v>57734</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17645,34 +17645,42 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>430972</v>
+        <v>430795</v>
       </c>
       <c r="R170" t="n">
-        <v>6795851</v>
+        <v>6795376</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17719,22 +17727,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129773179</v>
+        <v>129773123</v>
       </c>
       <c r="B171" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17742,34 +17750,42 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>430611</v>
+        <v>430845</v>
       </c>
       <c r="R171" t="n">
-        <v>6795443</v>
+        <v>6795412</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17828,10 +17844,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129771790</v>
+        <v>129773146</v>
       </c>
       <c r="B172" t="n">
-        <v>79081</v>
+        <v>78842</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17839,21 +17855,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17863,10 +17879,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>430957</v>
+        <v>430970</v>
       </c>
       <c r="R172" t="n">
-        <v>6795608</v>
+        <v>6795287</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17913,22 +17929,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129773195</v>
+        <v>129771757</v>
       </c>
       <c r="B173" t="n">
-        <v>79081</v>
+        <v>78842</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17936,21 +17952,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17960,10 +17976,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>431010</v>
+        <v>430923</v>
       </c>
       <c r="R173" t="n">
-        <v>6795515</v>
+        <v>6795582</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18010,22 +18026,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129773117</v>
+        <v>129771732</v>
       </c>
       <c r="B174" t="n">
-        <v>57733</v>
+        <v>91623</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18033,42 +18049,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>430795</v>
+        <v>430972</v>
       </c>
       <c r="R174" t="n">
-        <v>6795376</v>
+        <v>6795851</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18115,65 +18123,57 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129773109</v>
+        <v>129773179</v>
       </c>
       <c r="B175" t="n">
-        <v>56926</v>
+        <v>79084</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>430816</v>
+        <v>430611</v>
       </c>
       <c r="R175" t="n">
-        <v>6795834</v>
+        <v>6795443</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18232,10 +18232,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129773123</v>
+        <v>129771790</v>
       </c>
       <c r="B176" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18243,42 +18243,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>430845</v>
+        <v>430957</v>
       </c>
       <c r="R176" t="n">
-        <v>6795412</v>
+        <v>6795608</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18325,22 +18317,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129773146</v>
+        <v>129773195</v>
       </c>
       <c r="B177" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18348,21 +18340,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18372,10 +18364,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>430970</v>
+        <v>431010</v>
       </c>
       <c r="R177" t="n">
-        <v>6795287</v>
+        <v>6795515</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18434,45 +18426,53 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129771757</v>
+        <v>129773109</v>
       </c>
       <c r="B178" t="n">
-        <v>78839</v>
+        <v>56927</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>430923</v>
+        <v>430816</v>
       </c>
       <c r="R178" t="n">
-        <v>6795582</v>
+        <v>6795834</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18519,22 +18519,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129771811</v>
+        <v>129773168</v>
       </c>
       <c r="B179" t="n">
-        <v>79081</v>
+        <v>78841</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18542,21 +18542,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18566,10 +18566,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>430910</v>
+        <v>430617</v>
       </c>
       <c r="R179" t="n">
-        <v>6796078</v>
+        <v>6795600</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18616,22 +18616,22 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129773197</v>
+        <v>129773128</v>
       </c>
       <c r="B180" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18639,26 +18639,31 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
@@ -18666,10 +18671,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>431062</v>
+        <v>430918</v>
       </c>
       <c r="R180" t="n">
-        <v>6795533</v>
+        <v>6795985</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18710,7 +18715,6 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
-      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
@@ -18729,10 +18733,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129773128</v>
+        <v>129773150</v>
       </c>
       <c r="B181" t="n">
-        <v>57733</v>
+        <v>78842</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18740,42 +18744,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>430918</v>
+        <v>431067</v>
       </c>
       <c r="R181" t="n">
-        <v>6795985</v>
+        <v>6795549</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18834,10 +18830,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129773150</v>
+        <v>129771811</v>
       </c>
       <c r="B182" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18845,21 +18841,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18869,10 +18865,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>431067</v>
+        <v>430910</v>
       </c>
       <c r="R182" t="n">
-        <v>6795549</v>
+        <v>6796078</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18919,22 +18915,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129771803</v>
+        <v>129773197</v>
       </c>
       <c r="B183" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18960,16 +18956,19 @@
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>430878</v>
+        <v>431062</v>
       </c>
       <c r="R183" t="n">
-        <v>6795999</v>
+        <v>6795533</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19010,28 +19009,29 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129773168</v>
+        <v>129771803</v>
       </c>
       <c r="B184" t="n">
-        <v>78838</v>
+        <v>79084</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19039,21 +19039,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19063,10 +19063,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>430617</v>
+        <v>430878</v>
       </c>
       <c r="R184" t="n">
-        <v>6795600</v>
+        <v>6795999</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19113,22 +19113,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129771792</v>
+        <v>129773122</v>
       </c>
       <c r="B185" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19136,34 +19136,42 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>430945</v>
+        <v>430702</v>
       </c>
       <c r="R185" t="n">
-        <v>6795579</v>
+        <v>6795444</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19210,57 +19218,65 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129771766</v>
+        <v>129771764</v>
       </c>
       <c r="B186" t="n">
-        <v>78838</v>
+        <v>58108</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>430922</v>
+        <v>430863</v>
       </c>
       <c r="R186" t="n">
-        <v>6795638</v>
+        <v>6795796</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19319,10 +19335,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129771707</v>
+        <v>129771728</v>
       </c>
       <c r="B187" t="n">
-        <v>79700</v>
+        <v>57895</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19330,34 +19346,42 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430973</v>
+        <v>430863</v>
       </c>
       <c r="R187" t="n">
-        <v>6795529</v>
+        <v>6795800</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19416,10 +19440,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129773122</v>
+        <v>129771792</v>
       </c>
       <c r="B188" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19427,42 +19451,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430702</v>
+        <v>430945</v>
       </c>
       <c r="R188" t="n">
-        <v>6795444</v>
+        <v>6795579</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19509,22 +19525,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129771728</v>
+        <v>129771812</v>
       </c>
       <c r="B189" t="n">
-        <v>57896</v>
+        <v>79084</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19532,42 +19548,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430863</v>
+        <v>430903</v>
       </c>
       <c r="R189" t="n">
-        <v>6795800</v>
+        <v>6796058</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19626,10 +19634,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129771812</v>
+        <v>129771807</v>
       </c>
       <c r="B190" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19661,10 +19669,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430903</v>
+        <v>430914</v>
       </c>
       <c r="R190" t="n">
-        <v>6796058</v>
+        <v>6796105</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19723,10 +19731,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129771807</v>
+        <v>129771729</v>
       </c>
       <c r="B191" t="n">
-        <v>79081</v>
+        <v>91623</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19734,21 +19742,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19758,10 +19766,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430914</v>
+        <v>430543</v>
       </c>
       <c r="R191" t="n">
-        <v>6796105</v>
+        <v>6795503</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19820,32 +19828,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129771729</v>
+        <v>129771703</v>
       </c>
       <c r="B192" t="n">
-        <v>91620</v>
+        <v>91566</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19855,10 +19863,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430543</v>
+        <v>430735</v>
       </c>
       <c r="R192" t="n">
-        <v>6795503</v>
+        <v>6795805</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19917,32 +19925,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129771703</v>
+        <v>129771766</v>
       </c>
       <c r="B193" t="n">
-        <v>91563</v>
+        <v>78841</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19952,10 +19960,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430735</v>
+        <v>430922</v>
       </c>
       <c r="R193" t="n">
-        <v>6795805</v>
+        <v>6795638</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20014,53 +20022,45 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129771764</v>
+        <v>129771707</v>
       </c>
       <c r="B194" t="n">
-        <v>58106</v>
+        <v>79703</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>430863</v>
+        <v>430973</v>
       </c>
       <c r="R194" t="n">
-        <v>6795796</v>
+        <v>6795529</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20119,10 +20119,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129773211</v>
+        <v>129771796</v>
       </c>
       <c r="B195" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20154,10 +20154,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430815</v>
+        <v>430984</v>
       </c>
       <c r="R195" t="n">
-        <v>6795818</v>
+        <v>6795518</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20204,12 +20204,12 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
@@ -20219,7 +20219,7 @@
         <v>129771814</v>
       </c>
       <c r="B196" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20313,10 +20313,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129771796</v>
+        <v>129773207</v>
       </c>
       <c r="B197" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20348,10 +20348,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>430984</v>
+        <v>430947</v>
       </c>
       <c r="R197" t="n">
-        <v>6795518</v>
+        <v>6795977</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20398,22 +20398,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129773207</v>
+        <v>129773211</v>
       </c>
       <c r="B198" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20445,10 +20445,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>430947</v>
+        <v>430815</v>
       </c>
       <c r="R198" t="n">
-        <v>6795977</v>
+        <v>6795818</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20510,7 +20510,7 @@
         <v>129773119</v>
       </c>
       <c r="B199" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20719,10 +20719,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129773205</v>
+        <v>129771706</v>
       </c>
       <c r="B201" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20730,21 +20730,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>430907</v>
+        <v>430935</v>
       </c>
       <c r="R201" t="n">
-        <v>6795973</v>
+        <v>6795595</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20804,65 +20804,57 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129771725</v>
+        <v>129773205</v>
       </c>
       <c r="B202" t="n">
-        <v>56926</v>
+        <v>79084</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>430867</v>
+        <v>430907</v>
       </c>
       <c r="R202" t="n">
-        <v>6795794</v>
+        <v>6795973</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20909,22 +20901,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129773145</v>
+        <v>129771808</v>
       </c>
       <c r="B203" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20932,21 +20924,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20956,10 +20948,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>430935</v>
+        <v>430894</v>
       </c>
       <c r="R203" t="n">
-        <v>6795319</v>
+        <v>6796093</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21006,57 +20998,65 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129771758</v>
+        <v>129771725</v>
       </c>
       <c r="B204" t="n">
-        <v>78839</v>
+        <v>56927</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>430921</v>
+        <v>430867</v>
       </c>
       <c r="R204" t="n">
-        <v>6795636</v>
+        <v>6795794</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21115,45 +21115,54 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129771706</v>
+        <v>129773161</v>
       </c>
       <c r="B205" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>430935</v>
+        <v>430911</v>
       </c>
       <c r="R205" t="n">
-        <v>6795595</v>
+        <v>6795982</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21194,28 +21203,29 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
+      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129771808</v>
+        <v>129773145</v>
       </c>
       <c r="B206" t="n">
-        <v>79081</v>
+        <v>78842</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21223,21 +21233,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21247,10 +21257,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>430894</v>
+        <v>430935</v>
       </c>
       <c r="R206" t="n">
-        <v>6796093</v>
+        <v>6795319</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21297,66 +21307,57 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129773161</v>
+        <v>129771758</v>
       </c>
       <c r="B207" t="n">
-        <v>8450</v>
+        <v>78842</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>430911</v>
+        <v>430921</v>
       </c>
       <c r="R207" t="n">
-        <v>6795982</v>
+        <v>6795636</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21397,29 +21398,28 @@
       <c r="AE207" t="b">
         <v>0</v>
       </c>
-      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129771782</v>
+        <v>129771769</v>
       </c>
       <c r="B208" t="n">
-        <v>79081</v>
+        <v>78841</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21427,21 +21427,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21451,10 +21451,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>430561</v>
+        <v>430973</v>
       </c>
       <c r="R208" t="n">
-        <v>6795581</v>
+        <v>6795852</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21513,10 +21513,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129771795</v>
+        <v>129773130</v>
       </c>
       <c r="B209" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21524,34 +21524,42 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>430956</v>
+        <v>430893</v>
       </c>
       <c r="R209" t="n">
-        <v>6795564</v>
+        <v>6796035</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21598,22 +21606,22 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129771769</v>
+        <v>129771795</v>
       </c>
       <c r="B210" t="n">
-        <v>78838</v>
+        <v>79084</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21621,21 +21629,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21645,10 +21653,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>430973</v>
+        <v>430956</v>
       </c>
       <c r="R210" t="n">
-        <v>6795852</v>
+        <v>6795564</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21707,10 +21715,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129773142</v>
+        <v>129771782</v>
       </c>
       <c r="B211" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21718,21 +21726,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21742,10 +21750,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>430602</v>
+        <v>430561</v>
       </c>
       <c r="R211" t="n">
-        <v>6795431</v>
+        <v>6795581</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21792,22 +21800,22 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129773130</v>
+        <v>129773142</v>
       </c>
       <c r="B212" t="n">
-        <v>57733</v>
+        <v>78842</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21815,42 +21823,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>430893</v>
+        <v>430602</v>
       </c>
       <c r="R212" t="n">
-        <v>6796035</v>
+        <v>6795431</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21909,10 +21909,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129773188</v>
+        <v>129773187</v>
       </c>
       <c r="B213" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21944,10 +21944,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>430889</v>
+        <v>430856</v>
       </c>
       <c r="R213" t="n">
-        <v>6795341</v>
+        <v>6795373</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22006,10 +22006,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129773206</v>
+        <v>129773186</v>
       </c>
       <c r="B214" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22041,10 +22041,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>430918</v>
+        <v>430861</v>
       </c>
       <c r="R214" t="n">
-        <v>6795974</v>
+        <v>6795429</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22103,10 +22103,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129773186</v>
+        <v>129773188</v>
       </c>
       <c r="B215" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22138,10 +22138,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>430861</v>
+        <v>430889</v>
       </c>
       <c r="R215" t="n">
-        <v>6795429</v>
+        <v>6795341</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22200,10 +22200,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129773187</v>
+        <v>129771798</v>
       </c>
       <c r="B216" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22235,10 +22235,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>430856</v>
+        <v>430982</v>
       </c>
       <c r="R216" t="n">
-        <v>6795373</v>
+        <v>6795567</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22285,12 +22285,12 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
@@ -22300,7 +22300,7 @@
         <v>129773184</v>
       </c>
       <c r="B217" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22394,10 +22394,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129771798</v>
+        <v>129773206</v>
       </c>
       <c r="B218" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22429,10 +22429,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>430982</v>
+        <v>430918</v>
       </c>
       <c r="R218" t="n">
-        <v>6795567</v>
+        <v>6795974</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22479,22 +22479,22 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129773166</v>
+        <v>129773177</v>
       </c>
       <c r="B219" t="n">
-        <v>78838</v>
+        <v>79084</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22502,21 +22502,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22526,10 +22526,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>430897</v>
+        <v>430633</v>
       </c>
       <c r="R219" t="n">
-        <v>6795988</v>
+        <v>6795435</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22588,10 +22588,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129773190</v>
+        <v>129773189</v>
       </c>
       <c r="B220" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22623,10 +22623,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>430984</v>
+        <v>430904</v>
       </c>
       <c r="R220" t="n">
-        <v>6795313</v>
+        <v>6795339</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22685,10 +22685,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129773189</v>
+        <v>129771813</v>
       </c>
       <c r="B221" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22720,10 +22720,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>430904</v>
+        <v>430910</v>
       </c>
       <c r="R221" t="n">
-        <v>6795339</v>
+        <v>6796073</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22770,22 +22770,22 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129771813</v>
+        <v>129773190</v>
       </c>
       <c r="B222" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22817,10 +22817,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>430910</v>
+        <v>430984</v>
       </c>
       <c r="R222" t="n">
-        <v>6796073</v>
+        <v>6795313</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22867,22 +22867,22 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129773177</v>
+        <v>129773166</v>
       </c>
       <c r="B223" t="n">
-        <v>79081</v>
+        <v>78841</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22890,21 +22890,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -22914,10 +22914,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430633</v>
+        <v>430897</v>
       </c>
       <c r="R223" t="n">
-        <v>6795435</v>
+        <v>6795988</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22976,10 +22976,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129771740</v>
+        <v>129771736</v>
       </c>
       <c r="B224" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23019,10 +23019,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>430754</v>
+        <v>430531</v>
       </c>
       <c r="R224" t="n">
-        <v>6795593</v>
+        <v>6795488</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23081,10 +23081,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129771736</v>
+        <v>129771740</v>
       </c>
       <c r="B225" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23124,10 +23124,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>430531</v>
+        <v>430754</v>
       </c>
       <c r="R225" t="n">
-        <v>6795488</v>
+        <v>6795593</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23189,7 +23189,7 @@
         <v>129771759</v>
       </c>
       <c r="B226" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23283,10 +23283,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129773144</v>
+        <v>129771809</v>
       </c>
       <c r="B227" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23294,21 +23294,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23318,10 +23318,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>430907</v>
+        <v>430906</v>
       </c>
       <c r="R227" t="n">
-        <v>6795330</v>
+        <v>6796088</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23368,22 +23368,22 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129773178</v>
+        <v>129771781</v>
       </c>
       <c r="B228" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23415,10 +23415,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>430590</v>
+        <v>430497</v>
       </c>
       <c r="R228" t="n">
-        <v>6795429</v>
+        <v>6795553</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23465,22 +23465,22 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129773201</v>
+        <v>129773178</v>
       </c>
       <c r="B229" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23512,10 +23512,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>430907</v>
+        <v>430590</v>
       </c>
       <c r="R229" t="n">
-        <v>6796028</v>
+        <v>6795429</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23574,10 +23574,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129771781</v>
+        <v>129773201</v>
       </c>
       <c r="B230" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23609,10 +23609,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>430497</v>
+        <v>430907</v>
       </c>
       <c r="R230" t="n">
-        <v>6795553</v>
+        <v>6796028</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23659,12 +23659,12 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
@@ -23674,7 +23674,7 @@
         <v>129773217</v>
       </c>
       <c r="B231" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>129771770</v>
       </c>
       <c r="B232" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23865,10 +23865,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129771809</v>
+        <v>129771708</v>
       </c>
       <c r="B233" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23876,21 +23876,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -23900,10 +23900,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>430906</v>
+        <v>430916</v>
       </c>
       <c r="R233" t="n">
-        <v>6796088</v>
+        <v>6796075</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23962,10 +23962,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129771708</v>
+        <v>129773144</v>
       </c>
       <c r="B234" t="n">
-        <v>79700</v>
+        <v>78842</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23973,21 +23973,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -23997,10 +23997,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>430916</v>
+        <v>430907</v>
       </c>
       <c r="R234" t="n">
-        <v>6796075</v>
+        <v>6795330</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24047,22 +24047,22 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129771731</v>
+        <v>129771752</v>
       </c>
       <c r="B235" t="n">
-        <v>91620</v>
+        <v>57734</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24070,34 +24070,42 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>430961</v>
+        <v>430801</v>
       </c>
       <c r="R235" t="n">
-        <v>6795616</v>
+        <v>6795756</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24156,10 +24164,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129771805</v>
+        <v>129771731</v>
       </c>
       <c r="B236" t="n">
-        <v>79081</v>
+        <v>91623</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24167,21 +24175,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -24191,10 +24199,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>430875</v>
+        <v>430961</v>
       </c>
       <c r="R236" t="n">
-        <v>6796089</v>
+        <v>6795616</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24253,10 +24261,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129771752</v>
+        <v>129771805</v>
       </c>
       <c r="B237" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24264,42 +24272,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>430801</v>
+        <v>430875</v>
       </c>
       <c r="R237" t="n">
-        <v>6795756</v>
+        <v>6796089</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24358,45 +24358,54 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129773101</v>
+        <v>129773162</v>
       </c>
       <c r="B238" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>430763</v>
+        <v>430613</v>
       </c>
       <c r="R238" t="n">
-        <v>6795472</v>
+        <v>6795723</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24437,6 +24446,7 @@
       <c r="AE238" t="b">
         <v>0</v>
       </c>
+      <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="b">
         <v>0</v>
       </c>
@@ -24455,54 +24465,45 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129773162</v>
+        <v>129773101</v>
       </c>
       <c r="B239" t="n">
-        <v>8450</v>
+        <v>79674</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>430613</v>
+        <v>430763</v>
       </c>
       <c r="R239" t="n">
-        <v>6795723</v>
+        <v>6795472</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24543,7 +24544,6 @@
       <c r="AE239" t="b">
         <v>0</v>
       </c>
-      <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="b">
         <v>0</v>
       </c>
@@ -24562,10 +24562,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129771747</v>
+        <v>129773213</v>
       </c>
       <c r="B240" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24573,42 +24573,34 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>430947</v>
+        <v>430783</v>
       </c>
       <c r="R240" t="n">
-        <v>6796064</v>
+        <v>6795818</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24655,22 +24647,22 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129771742</v>
+        <v>129771806</v>
       </c>
       <c r="B241" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24678,42 +24670,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>430934</v>
+        <v>430974</v>
       </c>
       <c r="R241" t="n">
-        <v>6795641</v>
+        <v>6796123</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24772,10 +24756,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129771746</v>
+        <v>129771785</v>
       </c>
       <c r="B242" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24783,42 +24767,34 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>430942</v>
+        <v>430936</v>
       </c>
       <c r="R242" t="n">
-        <v>6796133</v>
+        <v>6795608</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24877,10 +24853,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129773121</v>
+        <v>129771730</v>
       </c>
       <c r="B243" t="n">
-        <v>57733</v>
+        <v>91623</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24888,42 +24864,34 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>430707</v>
+        <v>430958</v>
       </c>
       <c r="R243" t="n">
-        <v>6795375</v>
+        <v>6795614</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24970,22 +24938,22 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129771739</v>
+        <v>129771784</v>
       </c>
       <c r="B244" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -24993,42 +24961,34 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>430752</v>
+        <v>430920</v>
       </c>
       <c r="R244" t="n">
-        <v>6795559</v>
+        <v>6795536</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25087,10 +25047,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129771730</v>
+        <v>129771747</v>
       </c>
       <c r="B245" t="n">
-        <v>91620</v>
+        <v>57734</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25098,34 +25058,42 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>430958</v>
+        <v>430947</v>
       </c>
       <c r="R245" t="n">
-        <v>6795614</v>
+        <v>6796064</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25184,10 +25152,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>129771784</v>
+        <v>129771742</v>
       </c>
       <c r="B246" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25195,34 +25163,42 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>430920</v>
+        <v>430934</v>
       </c>
       <c r="R246" t="n">
-        <v>6795536</v>
+        <v>6795641</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25281,10 +25257,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>129771785</v>
+        <v>129771746</v>
       </c>
       <c r="B247" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25292,34 +25268,42 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>430936</v>
+        <v>430942</v>
       </c>
       <c r="R247" t="n">
-        <v>6795608</v>
+        <v>6796133</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25378,10 +25362,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129771806</v>
+        <v>129773121</v>
       </c>
       <c r="B248" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25389,34 +25373,42 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>430974</v>
+        <v>430707</v>
       </c>
       <c r="R248" t="n">
-        <v>6796123</v>
+        <v>6795375</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25463,22 +25455,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>129773213</v>
+        <v>129771739</v>
       </c>
       <c r="B249" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25486,34 +25478,42 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>430783</v>
+        <v>430752</v>
       </c>
       <c r="R249" t="n">
-        <v>6795818</v>
+        <v>6795559</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25560,12 +25560,12 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
@@ -25575,7 +25575,7 @@
         <v>129771716</v>
       </c>
       <c r="B250" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -25677,10 +25677,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129771791</v>
+        <v>129773112</v>
       </c>
       <c r="B251" t="n">
-        <v>79081</v>
+        <v>57895</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -25688,34 +25688,42 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>430959</v>
+        <v>430814</v>
       </c>
       <c r="R251" t="n">
-        <v>6795606</v>
+        <v>6795837</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25762,57 +25770,65 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129773202</v>
+        <v>129771714</v>
       </c>
       <c r="B252" t="n">
-        <v>79081</v>
+        <v>56927</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>430858</v>
+        <v>430528</v>
       </c>
       <c r="R252" t="n">
-        <v>6796064</v>
+        <v>6795512</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25859,44 +25875,44 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129771738</v>
+        <v>129771718</v>
       </c>
       <c r="B253" t="n">
-        <v>57733</v>
+        <v>56927</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25904,7 +25920,7 @@
       <c r="L253" t="inlineStr"/>
       <c r="M253" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N253" t="inlineStr"/>
@@ -25914,10 +25930,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>430655</v>
+        <v>430939</v>
       </c>
       <c r="R253" t="n">
-        <v>6795565</v>
+        <v>6796145</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -25976,53 +25992,45 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>129771714</v>
+        <v>129773202</v>
       </c>
       <c r="B254" t="n">
-        <v>56926</v>
+        <v>79084</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>430528</v>
+        <v>430858</v>
       </c>
       <c r="R254" t="n">
-        <v>6795512</v>
+        <v>6796064</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26069,65 +26077,57 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>129771718</v>
+        <v>129771791</v>
       </c>
       <c r="B255" t="n">
-        <v>56926</v>
+        <v>79084</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>430939</v>
+        <v>430959</v>
       </c>
       <c r="R255" t="n">
-        <v>6796145</v>
+        <v>6795606</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26186,10 +26186,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>129773112</v>
+        <v>129771738</v>
       </c>
       <c r="B256" t="n">
-        <v>57896</v>
+        <v>57734</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -26197,21 +26197,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26219,7 +26219,7 @@
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N256" t="inlineStr"/>
@@ -26229,10 +26229,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>430814</v>
+        <v>430655</v>
       </c>
       <c r="R256" t="n">
-        <v>6795837</v>
+        <v>6795565</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26279,12 +26279,12 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
@@ -26294,7 +26294,7 @@
         <v>129773149</v>
       </c>
       <c r="B257" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>129771761</v>
       </c>
       <c r="B258" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -26485,10 +26485,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>129773182</v>
+        <v>129773180</v>
       </c>
       <c r="B259" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26520,10 +26520,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>430740</v>
+        <v>430789</v>
       </c>
       <c r="R259" t="n">
-        <v>6795371</v>
+        <v>6795377</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -26582,10 +26582,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>129773180</v>
+        <v>129771786</v>
       </c>
       <c r="B260" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26617,10 +26617,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>430789</v>
+        <v>430927</v>
       </c>
       <c r="R260" t="n">
-        <v>6795377</v>
+        <v>6795611</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26667,22 +26667,22 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>129773135</v>
+        <v>129773182</v>
       </c>
       <c r="B261" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26690,42 +26690,34 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>430938</v>
+        <v>430740</v>
       </c>
       <c r="R261" t="n">
-        <v>6795967</v>
+        <v>6795371</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26784,10 +26776,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>129773120</v>
+        <v>129773135</v>
       </c>
       <c r="B262" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26827,10 +26819,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>430694</v>
+        <v>430938</v>
       </c>
       <c r="R262" t="n">
-        <v>6795368</v>
+        <v>6795967</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26889,10 +26881,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>129771744</v>
+        <v>129773120</v>
       </c>
       <c r="B263" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -26932,10 +26924,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>430959</v>
+        <v>430694</v>
       </c>
       <c r="R263" t="n">
-        <v>6795543</v>
+        <v>6795368</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -26982,22 +26974,22 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>129773133</v>
+        <v>129771744</v>
       </c>
       <c r="B264" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27037,10 +27029,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>430886</v>
+        <v>430959</v>
       </c>
       <c r="R264" t="n">
-        <v>6795969</v>
+        <v>6795543</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27087,22 +27079,22 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>129771786</v>
+        <v>129773133</v>
       </c>
       <c r="B265" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -27110,34 +27102,42 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>430927</v>
+        <v>430886</v>
       </c>
       <c r="R265" t="n">
-        <v>6795611</v>
+        <v>6795969</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27184,12 +27184,12 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
@@ -27199,7 +27199,7 @@
         <v>129773156</v>
       </c>
       <c r="B266" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27293,54 +27293,45 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>129773163</v>
+        <v>129771817</v>
       </c>
       <c r="B267" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
-      <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>430632</v>
+        <v>430997</v>
       </c>
       <c r="R267" t="n">
-        <v>6795540</v>
+        <v>6795879</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27381,29 +27372,28 @@
       <c r="AE267" t="b">
         <v>0</v>
       </c>
-      <c r="AF267" t="inlineStr"/>
       <c r="AG267" t="b">
         <v>0</v>
       </c>
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>129771817</v>
+        <v>129771794</v>
       </c>
       <c r="B268" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -27435,10 +27425,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>430997</v>
+        <v>430951</v>
       </c>
       <c r="R268" t="n">
-        <v>6795879</v>
+        <v>6795576</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27500,7 +27490,7 @@
         <v>129771787</v>
       </c>
       <c r="B269" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -27597,7 +27587,7 @@
         <v>129773100</v>
       </c>
       <c r="B270" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27691,10 +27681,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>129771794</v>
+        <v>129771768</v>
       </c>
       <c r="B271" t="n">
-        <v>79081</v>
+        <v>78841</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27702,21 +27692,21 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -27726,10 +27716,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>430951</v>
+        <v>430921</v>
       </c>
       <c r="R271" t="n">
-        <v>6795576</v>
+        <v>6796077</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27788,45 +27778,53 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>129771768</v>
+        <v>129773108</v>
       </c>
       <c r="B272" t="n">
-        <v>78838</v>
+        <v>56927</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>430921</v>
+        <v>430941</v>
       </c>
       <c r="R272" t="n">
-        <v>6796077</v>
+        <v>6795862</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27873,44 +27871,44 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>129773125</v>
+        <v>129771715</v>
       </c>
       <c r="B273" t="n">
-        <v>57733</v>
+        <v>56927</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -27918,7 +27916,7 @@
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N273" t="inlineStr"/>
@@ -27928,10 +27926,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>430927</v>
+        <v>430568</v>
       </c>
       <c r="R273" t="n">
-        <v>6795321</v>
+        <v>6795570</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27978,22 +27976,22 @@
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>129773108</v>
+        <v>129771720</v>
       </c>
       <c r="B274" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -28033,10 +28031,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>430941</v>
+        <v>430972</v>
       </c>
       <c r="R274" t="n">
-        <v>6795862</v>
+        <v>6796056</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28083,44 +28081,44 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>129771715</v>
+        <v>129773125</v>
       </c>
       <c r="B275" t="n">
-        <v>56926</v>
+        <v>57734</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28128,7 +28126,7 @@
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N275" t="inlineStr"/>
@@ -28138,10 +28136,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>430568</v>
+        <v>430927</v>
       </c>
       <c r="R275" t="n">
-        <v>6795570</v>
+        <v>6795321</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28188,44 +28186,44 @@
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>129771720</v>
+        <v>129773103</v>
       </c>
       <c r="B276" t="n">
-        <v>56926</v>
+        <v>57737</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28233,7 +28231,7 @@
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N276" t="inlineStr"/>
@@ -28243,10 +28241,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>430972</v>
+        <v>430952</v>
       </c>
       <c r="R276" t="n">
-        <v>6796056</v>
+        <v>6795876</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28293,52 +28291,53 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>129773103</v>
+        <v>129773163</v>
       </c>
       <c r="B277" t="n">
-        <v>57736</v>
+        <v>8450</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N277" t="inlineStr"/>
@@ -28348,10 +28347,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>430952</v>
+        <v>430632</v>
       </c>
       <c r="R277" t="n">
-        <v>6795876</v>
+        <v>6795540</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -28392,6 +28391,7 @@
       <c r="AE277" t="b">
         <v>0</v>
       </c>
+      <c r="AF277" t="inlineStr"/>
       <c r="AG277" t="b">
         <v>0</v>
       </c>
@@ -28413,7 +28413,7 @@
         <v>129771771</v>
       </c>
       <c r="B278" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28507,45 +28507,53 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>129771800</v>
+        <v>129773105</v>
       </c>
       <c r="B279" t="n">
-        <v>79081</v>
+        <v>56927</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>431011</v>
+        <v>430923</v>
       </c>
       <c r="R279" t="n">
-        <v>6795579</v>
+        <v>6796012</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28592,22 +28600,22 @@
       <c r="AT279" t="inlineStr"/>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>129773129</v>
+        <v>129771800</v>
       </c>
       <c r="B280" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28615,42 +28623,34 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>430920</v>
+        <v>431011</v>
       </c>
       <c r="R280" t="n">
-        <v>6796013</v>
+        <v>6795579</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28697,22 +28697,22 @@
       <c r="AT280" t="inlineStr"/>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>129773115</v>
+        <v>129773129</v>
       </c>
       <c r="B281" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28752,10 +28752,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>430594</v>
+        <v>430920</v>
       </c>
       <c r="R281" t="n">
-        <v>6795423</v>
+        <v>6796013</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -28814,10 +28814,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>129771748</v>
+        <v>129773115</v>
       </c>
       <c r="B282" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
       <c r="L282" t="inlineStr"/>
       <c r="M282" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N282" t="inlineStr"/>
@@ -28857,10 +28857,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>430982</v>
+        <v>430594</v>
       </c>
       <c r="R282" t="n">
-        <v>6795907</v>
+        <v>6795423</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -28907,44 +28907,44 @@
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>129773105</v>
+        <v>129771748</v>
       </c>
       <c r="B283" t="n">
-        <v>56926</v>
+        <v>57734</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -28952,7 +28952,7 @@
       <c r="L283" t="inlineStr"/>
       <c r="M283" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N283" t="inlineStr"/>
@@ -28962,10 +28962,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>430923</v>
+        <v>430982</v>
       </c>
       <c r="R283" t="n">
-        <v>6796012</v>
+        <v>6795907</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -29012,12 +29012,12 @@
       <c r="AT283" t="inlineStr"/>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
@@ -29027,7 +29027,7 @@
         <v>129771723</v>
       </c>
       <c r="B284" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -29129,45 +29129,54 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>129773157</v>
+        <v>129773160</v>
       </c>
       <c r="B285" t="n">
-        <v>78839</v>
+        <v>8450</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>430617</v>
+        <v>430844</v>
       </c>
       <c r="R285" t="n">
-        <v>6795600</v>
+        <v>6796058</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29208,6 +29217,7 @@
       <c r="AE285" t="b">
         <v>0</v>
       </c>
+      <c r="AF285" t="inlineStr"/>
       <c r="AG285" t="b">
         <v>0</v>
       </c>
@@ -29226,54 +29236,45 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>129773160</v>
+        <v>129773154</v>
       </c>
       <c r="B286" t="n">
-        <v>8450</v>
+        <v>78842</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
-      <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>430844</v>
+        <v>430860</v>
       </c>
       <c r="R286" t="n">
-        <v>6796058</v>
+        <v>6795825</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -29314,7 +29315,6 @@
       <c r="AE286" t="b">
         <v>0</v>
       </c>
-      <c r="AF286" t="inlineStr"/>
       <c r="AG286" t="b">
         <v>0</v>
       </c>
@@ -29333,10 +29333,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>129773154</v>
+        <v>129773157</v>
       </c>
       <c r="B287" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -29368,10 +29368,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>430860</v>
+        <v>430617</v>
       </c>
       <c r="R287" t="n">
-        <v>6795825</v>
+        <v>6795600</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -29433,7 +29433,7 @@
         <v>129771819</v>
       </c>
       <c r="B288" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>

--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -13685,53 +13685,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129771719</v>
+        <v>129773143</v>
       </c>
       <c r="B131" t="n">
-        <v>56927</v>
+        <v>78842</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>430937</v>
+        <v>430730</v>
       </c>
       <c r="R131" t="n">
-        <v>6796046</v>
+        <v>6795404</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13778,65 +13770,57 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129771724</v>
+        <v>129773153</v>
       </c>
       <c r="B132" t="n">
-        <v>56927</v>
+        <v>78842</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430884</v>
+        <v>430886</v>
       </c>
       <c r="R132" t="n">
-        <v>6795785</v>
+        <v>6796067</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13883,22 +13867,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129771710</v>
+        <v>129771737</v>
       </c>
       <c r="B133" t="n">
-        <v>57737</v>
+        <v>57734</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13906,16 +13890,16 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -13938,10 +13922,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>430669</v>
+        <v>430522</v>
       </c>
       <c r="R133" t="n">
-        <v>6795823</v>
+        <v>6795537</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14000,7 +13984,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129771737</v>
+        <v>129773137</v>
       </c>
       <c r="B134" t="n">
         <v>57734</v>
@@ -14033,7 +14017,7 @@
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -14043,10 +14027,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>430522</v>
+        <v>430851</v>
       </c>
       <c r="R134" t="n">
-        <v>6795537</v>
+        <v>6795824</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14093,19 +14077,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129773137</v>
+        <v>129773132</v>
       </c>
       <c r="B135" t="n">
         <v>57734</v>
@@ -14148,10 +14132,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>430851</v>
+        <v>430873</v>
       </c>
       <c r="R135" t="n">
-        <v>6795824</v>
+        <v>6795977</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14210,7 +14194,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129773132</v>
+        <v>129771750</v>
       </c>
       <c r="B136" t="n">
         <v>57734</v>
@@ -14253,10 +14237,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>430873</v>
+        <v>430973</v>
       </c>
       <c r="R136" t="n">
-        <v>6795977</v>
+        <v>6795877</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14303,19 +14287,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129771750</v>
+        <v>129771741</v>
       </c>
       <c r="B137" t="n">
         <v>57734</v>
@@ -14348,7 +14332,7 @@
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -14358,10 +14342,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>430973</v>
+        <v>430784</v>
       </c>
       <c r="R137" t="n">
-        <v>6795877</v>
+        <v>6795567</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14420,10 +14404,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129771741</v>
+        <v>129773113</v>
       </c>
       <c r="B138" t="n">
-        <v>57734</v>
+        <v>91623</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14431,31 +14415,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
@@ -14463,10 +14442,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>430784</v>
+        <v>430833</v>
       </c>
       <c r="R138" t="n">
-        <v>6795567</v>
+        <v>6796045</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14501,34 +14480,40 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>2 st på samma tall.</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129773113</v>
+        <v>129773214</v>
       </c>
       <c r="B139" t="n">
-        <v>91623</v>
+        <v>79084</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14536,37 +14521,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>430833</v>
+        <v>430777</v>
       </c>
       <c r="R139" t="n">
-        <v>6796045</v>
+        <v>6795822</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14601,18 +14583,12 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>2 st på samma tall.</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14631,45 +14607,53 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129773214</v>
+        <v>129771719</v>
       </c>
       <c r="B140" t="n">
-        <v>79084</v>
+        <v>56927</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>430777</v>
+        <v>430937</v>
       </c>
       <c r="R140" t="n">
-        <v>6795822</v>
+        <v>6796046</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14716,57 +14700,65 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129773143</v>
+        <v>129771724</v>
       </c>
       <c r="B141" t="n">
-        <v>78842</v>
+        <v>56927</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>430730</v>
+        <v>430884</v>
       </c>
       <c r="R141" t="n">
-        <v>6795404</v>
+        <v>6795785</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14813,22 +14805,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129773153</v>
+        <v>129771710</v>
       </c>
       <c r="B142" t="n">
-        <v>78842</v>
+        <v>57737</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14836,34 +14828,42 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>430886</v>
+        <v>430669</v>
       </c>
       <c r="R142" t="n">
-        <v>6796067</v>
+        <v>6795823</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14910,12 +14910,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -15027,10 +15027,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129771743</v>
+        <v>129771760</v>
       </c>
       <c r="B144" t="n">
-        <v>57734</v>
+        <v>78842</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15038,42 +15038,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430957</v>
+        <v>430983</v>
       </c>
       <c r="R144" t="n">
-        <v>6795610</v>
+        <v>6795850</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15520,10 +15512,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129771760</v>
+        <v>129771743</v>
       </c>
       <c r="B149" t="n">
-        <v>78842</v>
+        <v>57734</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15531,34 +15523,42 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>430983</v>
+        <v>430957</v>
       </c>
       <c r="R149" t="n">
-        <v>6795850</v>
+        <v>6795610</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15617,45 +15617,53 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129771797</v>
+        <v>129771717</v>
       </c>
       <c r="B150" t="n">
-        <v>79084</v>
+        <v>56927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>430960</v>
+        <v>430918</v>
       </c>
       <c r="R150" t="n">
-        <v>6795549</v>
+        <v>6795982</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15714,10 +15722,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129773185</v>
+        <v>129771751</v>
       </c>
       <c r="B151" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15725,34 +15733,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>430821</v>
+        <v>430983</v>
       </c>
       <c r="R151" t="n">
-        <v>6795424</v>
+        <v>6795850</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15799,22 +15815,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129771788</v>
+        <v>129773155</v>
       </c>
       <c r="B152" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15822,21 +15838,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15846,10 +15862,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>430957</v>
+        <v>430833</v>
       </c>
       <c r="R152" t="n">
-        <v>6795628</v>
+        <v>6795830</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15884,11 +15900,6 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 10 m</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
@@ -15901,19 +15912,19 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129771804</v>
+        <v>129771797</v>
       </c>
       <c r="B153" t="n">
         <v>79084</v>
@@ -15948,10 +15959,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>430865</v>
+        <v>430960</v>
       </c>
       <c r="R153" t="n">
-        <v>6796072</v>
+        <v>6795549</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16010,10 +16021,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129771751</v>
+        <v>129771788</v>
       </c>
       <c r="B154" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16021,42 +16032,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>430983</v>
+        <v>430957</v>
       </c>
       <c r="R154" t="n">
-        <v>6795850</v>
+        <v>6795628</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16089,6 +16092,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 10 m</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16115,10 +16123,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129773134</v>
+        <v>129771804</v>
       </c>
       <c r="B155" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16126,42 +16134,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>430894</v>
+        <v>430865</v>
       </c>
       <c r="R155" t="n">
-        <v>6795968</v>
+        <v>6796072</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16208,44 +16208,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129771717</v>
+        <v>129773134</v>
       </c>
       <c r="B156" t="n">
-        <v>56927</v>
+        <v>57734</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16253,7 +16253,7 @@
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
@@ -16263,10 +16263,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>430918</v>
+        <v>430894</v>
       </c>
       <c r="R156" t="n">
-        <v>6795982</v>
+        <v>6795968</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16313,22 +16313,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129773155</v>
+        <v>129773185</v>
       </c>
       <c r="B157" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16336,21 +16336,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16360,10 +16360,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>430833</v>
+        <v>430821</v>
       </c>
       <c r="R157" t="n">
-        <v>6795830</v>
+        <v>6795424</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16422,10 +16422,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129773158</v>
+        <v>129771713</v>
       </c>
       <c r="B158" t="n">
-        <v>8450</v>
+        <v>56927</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16433,30 +16433,29 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -16466,10 +16465,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>430704</v>
+        <v>430542</v>
       </c>
       <c r="R158" t="n">
-        <v>6795457</v>
+        <v>6795485</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16510,29 +16509,28 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129773204</v>
+        <v>129773138</v>
       </c>
       <c r="B159" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16540,34 +16538,42 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>430881</v>
+        <v>430825</v>
       </c>
       <c r="R159" t="n">
-        <v>6795985</v>
+        <v>6795805</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16626,32 +16632,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129773183</v>
+        <v>129771754</v>
       </c>
       <c r="B160" t="n">
-        <v>79084</v>
+        <v>92055</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16661,10 +16667,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>430698</v>
+        <v>430535</v>
       </c>
       <c r="R160" t="n">
-        <v>6795386</v>
+        <v>6795489</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16699,69 +16705,84 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129771754</v>
+        <v>129773158</v>
       </c>
       <c r="B161" t="n">
-        <v>92055</v>
+        <v>8450</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1209</v>
+        <v>106545</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>430535</v>
+        <v>430704</v>
       </c>
       <c r="R161" t="n">
-        <v>6795489</v>
+        <v>6795457</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16796,11 +16817,6 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
@@ -16814,19 +16830,19 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129773138</v>
+        <v>129773124</v>
       </c>
       <c r="B162" t="n">
         <v>57734</v>
@@ -16869,10 +16885,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>430825</v>
+        <v>430865</v>
       </c>
       <c r="R162" t="n">
-        <v>6795805</v>
+        <v>6795387</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16931,7 +16947,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129773124</v>
+        <v>129771753</v>
       </c>
       <c r="B163" t="n">
         <v>57734</v>
@@ -16964,7 +16980,7 @@
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -16974,10 +16990,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>430865</v>
+        <v>430631</v>
       </c>
       <c r="R163" t="n">
-        <v>6795387</v>
+        <v>6795763</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17024,22 +17040,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129771753</v>
+        <v>129773204</v>
       </c>
       <c r="B164" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17047,42 +17063,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>430631</v>
+        <v>430881</v>
       </c>
       <c r="R164" t="n">
-        <v>6795763</v>
+        <v>6795985</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17129,65 +17137,57 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129771713</v>
+        <v>129773183</v>
       </c>
       <c r="B165" t="n">
-        <v>56927</v>
+        <v>79084</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>430542</v>
+        <v>430698</v>
       </c>
       <c r="R165" t="n">
-        <v>6795485</v>
+        <v>6795386</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17234,22 +17234,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129773102</v>
+        <v>129771799</v>
       </c>
       <c r="B166" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17257,21 +17257,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17281,10 +17281,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>431020</v>
+        <v>431001</v>
       </c>
       <c r="R166" t="n">
-        <v>6795529</v>
+        <v>6795561</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17331,22 +17331,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129773141</v>
+        <v>129771793</v>
       </c>
       <c r="B167" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17354,21 +17354,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17378,10 +17378,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>430600</v>
+        <v>430946</v>
       </c>
       <c r="R167" t="n">
-        <v>6795424</v>
+        <v>6795572</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17428,22 +17428,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129771799</v>
+        <v>129773102</v>
       </c>
       <c r="B168" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17451,21 +17451,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17475,10 +17475,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>431001</v>
+        <v>431020</v>
       </c>
       <c r="R168" t="n">
-        <v>6795561</v>
+        <v>6795529</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17525,22 +17525,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129771793</v>
+        <v>129773141</v>
       </c>
       <c r="B169" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17548,21 +17548,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17572,10 +17572,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>430946</v>
+        <v>430600</v>
       </c>
       <c r="R169" t="n">
-        <v>6795572</v>
+        <v>6795424</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17622,19 +17622,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129773117</v>
+        <v>129773123</v>
       </c>
       <c r="B170" t="n">
         <v>57734</v>
@@ -17677,10 +17677,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>430795</v>
+        <v>430845</v>
       </c>
       <c r="R170" t="n">
-        <v>6795376</v>
+        <v>6795412</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17739,10 +17739,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129773123</v>
+        <v>129773179</v>
       </c>
       <c r="B171" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17750,42 +17750,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>430845</v>
+        <v>430611</v>
       </c>
       <c r="R171" t="n">
-        <v>6795412</v>
+        <v>6795443</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17844,45 +17836,53 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129773146</v>
+        <v>129773109</v>
       </c>
       <c r="B172" t="n">
-        <v>78842</v>
+        <v>56927</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>430970</v>
+        <v>430816</v>
       </c>
       <c r="R172" t="n">
-        <v>6795287</v>
+        <v>6795834</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17941,10 +17941,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129771757</v>
+        <v>129771732</v>
       </c>
       <c r="B173" t="n">
-        <v>78842</v>
+        <v>91623</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17952,21 +17952,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17976,10 +17976,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>430923</v>
+        <v>430972</v>
       </c>
       <c r="R173" t="n">
-        <v>6795582</v>
+        <v>6795851</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18038,10 +18038,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129771732</v>
+        <v>129771790</v>
       </c>
       <c r="B174" t="n">
-        <v>91623</v>
+        <v>79084</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18049,21 +18049,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18073,10 +18073,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>430972</v>
+        <v>430957</v>
       </c>
       <c r="R174" t="n">
-        <v>6795851</v>
+        <v>6795608</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18135,7 +18135,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129773179</v>
+        <v>129773195</v>
       </c>
       <c r="B175" t="n">
         <v>79084</v>
@@ -18170,10 +18170,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>430611</v>
+        <v>431010</v>
       </c>
       <c r="R175" t="n">
-        <v>6795443</v>
+        <v>6795515</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18232,10 +18232,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129771790</v>
+        <v>129773117</v>
       </c>
       <c r="B176" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18243,34 +18243,42 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>430957</v>
+        <v>430795</v>
       </c>
       <c r="R176" t="n">
-        <v>6795608</v>
+        <v>6795376</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18317,22 +18325,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129773195</v>
+        <v>129773146</v>
       </c>
       <c r="B177" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18340,21 +18348,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18364,10 +18372,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>431010</v>
+        <v>430970</v>
       </c>
       <c r="R177" t="n">
-        <v>6795515</v>
+        <v>6795287</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18426,53 +18434,45 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129773109</v>
+        <v>129771757</v>
       </c>
       <c r="B178" t="n">
-        <v>56927</v>
+        <v>78842</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>430816</v>
+        <v>430923</v>
       </c>
       <c r="R178" t="n">
-        <v>6795834</v>
+        <v>6795582</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18519,22 +18519,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129773168</v>
+        <v>129773197</v>
       </c>
       <c r="B179" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18542,34 +18542,37 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>430617</v>
+        <v>431062</v>
       </c>
       <c r="R179" t="n">
-        <v>6795600</v>
+        <v>6795533</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18610,6 +18613,7 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -18628,10 +18632,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129773128</v>
+        <v>129773168</v>
       </c>
       <c r="B180" t="n">
-        <v>57734</v>
+        <v>78841</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18639,42 +18643,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>430918</v>
+        <v>430617</v>
       </c>
       <c r="R180" t="n">
-        <v>6795985</v>
+        <v>6795600</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18927,7 +18923,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129773197</v>
+        <v>129771803</v>
       </c>
       <c r="B183" t="n">
         <v>79084</v>
@@ -18956,19 +18952,16 @@
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>431062</v>
+        <v>430878</v>
       </c>
       <c r="R183" t="n">
-        <v>6795533</v>
+        <v>6795999</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19009,29 +19002,28 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129771803</v>
+        <v>129773128</v>
       </c>
       <c r="B184" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19039,34 +19031,42 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>430878</v>
+        <v>430918</v>
       </c>
       <c r="R184" t="n">
-        <v>6795999</v>
+        <v>6795985</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19113,12 +19113,12 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
@@ -19230,32 +19230,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129771764</v>
+        <v>129771728</v>
       </c>
       <c r="B186" t="n">
-        <v>58108</v>
+        <v>57895</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19263,7 +19263,7 @@
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N186" t="inlineStr"/>
@@ -19276,7 +19276,7 @@
         <v>430863</v>
       </c>
       <c r="R186" t="n">
-        <v>6795796</v>
+        <v>6795800</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19335,10 +19335,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129771728</v>
+        <v>129771792</v>
       </c>
       <c r="B187" t="n">
-        <v>57895</v>
+        <v>79084</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19346,42 +19346,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430863</v>
+        <v>430945</v>
       </c>
       <c r="R187" t="n">
-        <v>6795800</v>
+        <v>6795579</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19440,7 +19432,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129771792</v>
+        <v>129771812</v>
       </c>
       <c r="B188" t="n">
         <v>79084</v>
@@ -19475,10 +19467,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430945</v>
+        <v>430903</v>
       </c>
       <c r="R188" t="n">
-        <v>6795579</v>
+        <v>6796058</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19537,7 +19529,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129771812</v>
+        <v>129771807</v>
       </c>
       <c r="B189" t="n">
         <v>79084</v>
@@ -19572,10 +19564,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430903</v>
+        <v>430914</v>
       </c>
       <c r="R189" t="n">
-        <v>6796058</v>
+        <v>6796105</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19634,10 +19626,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129771807</v>
+        <v>129771729</v>
       </c>
       <c r="B190" t="n">
-        <v>79084</v>
+        <v>91623</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19645,21 +19637,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19669,10 +19661,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430914</v>
+        <v>430543</v>
       </c>
       <c r="R190" t="n">
-        <v>6796105</v>
+        <v>6795503</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19731,32 +19723,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129771729</v>
+        <v>129771703</v>
       </c>
       <c r="B191" t="n">
-        <v>91623</v>
+        <v>91566</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19766,10 +19758,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430543</v>
+        <v>430735</v>
       </c>
       <c r="R191" t="n">
-        <v>6795503</v>
+        <v>6795805</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19828,32 +19820,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129771703</v>
+        <v>129771766</v>
       </c>
       <c r="B192" t="n">
-        <v>91566</v>
+        <v>78841</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19863,10 +19855,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430735</v>
+        <v>430922</v>
       </c>
       <c r="R192" t="n">
-        <v>6795805</v>
+        <v>6795638</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19925,10 +19917,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129771766</v>
+        <v>129771707</v>
       </c>
       <c r="B193" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19936,21 +19928,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19960,10 +19952,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430922</v>
+        <v>430973</v>
       </c>
       <c r="R193" t="n">
-        <v>6795638</v>
+        <v>6795529</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20022,45 +20014,53 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129771707</v>
+        <v>129771764</v>
       </c>
       <c r="B194" t="n">
-        <v>79703</v>
+        <v>58108</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>430973</v>
+        <v>430863</v>
       </c>
       <c r="R194" t="n">
-        <v>6795529</v>
+        <v>6795796</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20119,45 +20119,54 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129771796</v>
+        <v>129771762</v>
       </c>
       <c r="B195" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430984</v>
+        <v>430746</v>
       </c>
       <c r="R195" t="n">
-        <v>6795518</v>
+        <v>6795566</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20198,6 +20207,7 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -20216,10 +20226,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129771814</v>
+        <v>129773119</v>
       </c>
       <c r="B196" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20227,34 +20237,42 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430944</v>
+        <v>430692</v>
       </c>
       <c r="R196" t="n">
-        <v>6796075</v>
+        <v>6795373</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20301,12 +20319,12 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
@@ -20410,7 +20428,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129773211</v>
+        <v>129771796</v>
       </c>
       <c r="B198" t="n">
         <v>79084</v>
@@ -20445,10 +20463,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>430815</v>
+        <v>430984</v>
       </c>
       <c r="R198" t="n">
-        <v>6795818</v>
+        <v>6795518</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20495,22 +20513,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129773119</v>
+        <v>129771814</v>
       </c>
       <c r="B199" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20518,42 +20536,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>430692</v>
+        <v>430944</v>
       </c>
       <c r="R199" t="n">
-        <v>6795373</v>
+        <v>6796075</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20600,66 +20610,57 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129771762</v>
+        <v>129773211</v>
       </c>
       <c r="B200" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>430746</v>
+        <v>430815</v>
       </c>
       <c r="R200" t="n">
-        <v>6795566</v>
+        <v>6795818</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20700,64 +20701,71 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129771706</v>
+        <v>129771725</v>
       </c>
       <c r="B201" t="n">
-        <v>79703</v>
+        <v>56927</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>430935</v>
+        <v>430867</v>
       </c>
       <c r="R201" t="n">
-        <v>6795595</v>
+        <v>6795794</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20816,7 +20824,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129773205</v>
+        <v>129771808</v>
       </c>
       <c r="B202" t="n">
         <v>79084</v>
@@ -20851,10 +20859,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>430907</v>
+        <v>430894</v>
       </c>
       <c r="R202" t="n">
-        <v>6795973</v>
+        <v>6796093</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20901,19 +20909,19 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129771808</v>
+        <v>129773205</v>
       </c>
       <c r="B203" t="n">
         <v>79084</v>
@@ -20948,10 +20956,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>430894</v>
+        <v>430907</v>
       </c>
       <c r="R203" t="n">
-        <v>6796093</v>
+        <v>6795973</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20998,65 +21006,57 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129771725</v>
+        <v>129771706</v>
       </c>
       <c r="B204" t="n">
-        <v>56927</v>
+        <v>79703</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>430867</v>
+        <v>430935</v>
       </c>
       <c r="R204" t="n">
-        <v>6795794</v>
+        <v>6795595</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22103,7 +22103,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129773188</v>
+        <v>129771798</v>
       </c>
       <c r="B215" t="n">
         <v>79084</v>
@@ -22138,10 +22138,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>430889</v>
+        <v>430982</v>
       </c>
       <c r="R215" t="n">
-        <v>6795341</v>
+        <v>6795567</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22188,19 +22188,19 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129771798</v>
+        <v>129773184</v>
       </c>
       <c r="B216" t="n">
         <v>79084</v>
@@ -22235,10 +22235,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>430982</v>
+        <v>430798</v>
       </c>
       <c r="R216" t="n">
-        <v>6795567</v>
+        <v>6795464</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22285,19 +22285,19 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129773184</v>
+        <v>129773206</v>
       </c>
       <c r="B217" t="n">
         <v>79084</v>
@@ -22332,10 +22332,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>430798</v>
+        <v>430918</v>
       </c>
       <c r="R217" t="n">
-        <v>6795464</v>
+        <v>6795974</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22394,7 +22394,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129773206</v>
+        <v>129773188</v>
       </c>
       <c r="B218" t="n">
         <v>79084</v>
@@ -22429,10 +22429,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>430918</v>
+        <v>430889</v>
       </c>
       <c r="R218" t="n">
-        <v>6795974</v>
+        <v>6795341</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22588,7 +22588,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129773189</v>
+        <v>129771813</v>
       </c>
       <c r="B220" t="n">
         <v>79084</v>
@@ -22623,10 +22623,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>430904</v>
+        <v>430910</v>
       </c>
       <c r="R220" t="n">
-        <v>6795339</v>
+        <v>6796073</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22673,19 +22673,19 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129771813</v>
+        <v>129773190</v>
       </c>
       <c r="B221" t="n">
         <v>79084</v>
@@ -22720,10 +22720,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>430910</v>
+        <v>430984</v>
       </c>
       <c r="R221" t="n">
-        <v>6796073</v>
+        <v>6795313</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22770,22 +22770,22 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129773190</v>
+        <v>129773166</v>
       </c>
       <c r="B222" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22793,21 +22793,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22817,10 +22817,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>430984</v>
+        <v>430897</v>
       </c>
       <c r="R222" t="n">
-        <v>6795313</v>
+        <v>6795988</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22879,10 +22879,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129773166</v>
+        <v>129773189</v>
       </c>
       <c r="B223" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22890,21 +22890,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -22914,10 +22914,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430897</v>
+        <v>430904</v>
       </c>
       <c r="R223" t="n">
-        <v>6795988</v>
+        <v>6795339</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22976,10 +22976,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129771736</v>
+        <v>129771759</v>
       </c>
       <c r="B224" t="n">
-        <v>57734</v>
+        <v>78842</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22987,42 +22987,34 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>430531</v>
+        <v>430973</v>
       </c>
       <c r="R224" t="n">
-        <v>6795488</v>
+        <v>6795852</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23081,7 +23073,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129771740</v>
+        <v>129771736</v>
       </c>
       <c r="B225" t="n">
         <v>57734</v>
@@ -23124,10 +23116,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>430754</v>
+        <v>430531</v>
       </c>
       <c r="R225" t="n">
-        <v>6795593</v>
+        <v>6795488</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23186,10 +23178,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129771759</v>
+        <v>129771740</v>
       </c>
       <c r="B226" t="n">
-        <v>78842</v>
+        <v>57734</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23197,34 +23189,42 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>430973</v>
+        <v>430754</v>
       </c>
       <c r="R226" t="n">
-        <v>6795852</v>
+        <v>6795593</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23283,10 +23283,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129771809</v>
+        <v>129771770</v>
       </c>
       <c r="B227" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23294,21 +23294,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23318,10 +23318,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>430906</v>
+        <v>430983</v>
       </c>
       <c r="R227" t="n">
-        <v>6796088</v>
+        <v>6795850</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23380,7 +23380,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129771781</v>
+        <v>129773201</v>
       </c>
       <c r="B228" t="n">
         <v>79084</v>
@@ -23415,10 +23415,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>430497</v>
+        <v>430907</v>
       </c>
       <c r="R228" t="n">
-        <v>6795553</v>
+        <v>6796028</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23465,22 +23465,22 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129773178</v>
+        <v>129771708</v>
       </c>
       <c r="B229" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23488,21 +23488,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23512,10 +23512,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>430590</v>
+        <v>430916</v>
       </c>
       <c r="R229" t="n">
-        <v>6795429</v>
+        <v>6796075</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23562,22 +23562,22 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129773201</v>
+        <v>129773144</v>
       </c>
       <c r="B230" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23585,21 +23585,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -23612,7 +23612,7 @@
         <v>430907</v>
       </c>
       <c r="R230" t="n">
-        <v>6796028</v>
+        <v>6795330</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23671,7 +23671,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129773217</v>
+        <v>129771809</v>
       </c>
       <c r="B231" t="n">
         <v>79084</v>
@@ -23706,10 +23706,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>430617</v>
+        <v>430906</v>
       </c>
       <c r="R231" t="n">
-        <v>6795600</v>
+        <v>6796088</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23756,22 +23756,22 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129771770</v>
+        <v>129771781</v>
       </c>
       <c r="B232" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23779,21 +23779,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23803,10 +23803,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>430983</v>
+        <v>430497</v>
       </c>
       <c r="R232" t="n">
-        <v>6795850</v>
+        <v>6795553</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23865,10 +23865,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129771708</v>
+        <v>129773178</v>
       </c>
       <c r="B233" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23876,21 +23876,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -23900,10 +23900,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>430916</v>
+        <v>430590</v>
       </c>
       <c r="R233" t="n">
-        <v>6796075</v>
+        <v>6795429</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23950,22 +23950,22 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129773144</v>
+        <v>129773217</v>
       </c>
       <c r="B234" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23973,21 +23973,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -23997,10 +23997,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>430907</v>
+        <v>430617</v>
       </c>
       <c r="R234" t="n">
-        <v>6795330</v>
+        <v>6795600</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24562,45 +24562,53 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129773213</v>
+        <v>129771716</v>
       </c>
       <c r="B240" t="n">
-        <v>79084</v>
+        <v>56927</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>430783</v>
+        <v>430750</v>
       </c>
       <c r="R240" t="n">
-        <v>6795818</v>
+        <v>6795558</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24647,22 +24655,22 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129771806</v>
+        <v>129771742</v>
       </c>
       <c r="B241" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24670,34 +24678,42 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>430974</v>
+        <v>430934</v>
       </c>
       <c r="R241" t="n">
-        <v>6796123</v>
+        <v>6795641</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24756,10 +24772,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129771785</v>
+        <v>129771746</v>
       </c>
       <c r="B242" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24767,34 +24783,42 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>430936</v>
+        <v>430942</v>
       </c>
       <c r="R242" t="n">
-        <v>6795608</v>
+        <v>6796133</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24853,10 +24877,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129771730</v>
+        <v>129771739</v>
       </c>
       <c r="B243" t="n">
-        <v>91623</v>
+        <v>57734</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24864,34 +24888,42 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>430958</v>
+        <v>430752</v>
       </c>
       <c r="R243" t="n">
-        <v>6795614</v>
+        <v>6795559</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24950,10 +24982,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129771784</v>
+        <v>129771747</v>
       </c>
       <c r="B244" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -24961,34 +24993,42 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>430920</v>
+        <v>430947</v>
       </c>
       <c r="R244" t="n">
-        <v>6795536</v>
+        <v>6796064</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25047,7 +25087,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129771747</v>
+        <v>129773121</v>
       </c>
       <c r="B245" t="n">
         <v>57734</v>
@@ -25090,10 +25130,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>430947</v>
+        <v>430707</v>
       </c>
       <c r="R245" t="n">
-        <v>6796064</v>
+        <v>6795375</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25140,22 +25180,22 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>129771742</v>
+        <v>129771806</v>
       </c>
       <c r="B246" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25163,42 +25203,34 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>430934</v>
+        <v>430974</v>
       </c>
       <c r="R246" t="n">
-        <v>6795641</v>
+        <v>6796123</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25257,10 +25289,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>129771746</v>
+        <v>129771785</v>
       </c>
       <c r="B247" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25268,42 +25300,34 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>430942</v>
+        <v>430936</v>
       </c>
       <c r="R247" t="n">
-        <v>6796133</v>
+        <v>6795608</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25362,10 +25386,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129773121</v>
+        <v>129771730</v>
       </c>
       <c r="B248" t="n">
-        <v>57734</v>
+        <v>91623</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25373,42 +25397,34 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>430707</v>
+        <v>430958</v>
       </c>
       <c r="R248" t="n">
-        <v>6795375</v>
+        <v>6795614</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25455,22 +25471,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>129771739</v>
+        <v>129771784</v>
       </c>
       <c r="B249" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25478,42 +25494,34 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>430752</v>
+        <v>430920</v>
       </c>
       <c r="R249" t="n">
-        <v>6795559</v>
+        <v>6795536</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25572,53 +25580,45 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>129771716</v>
+        <v>129773213</v>
       </c>
       <c r="B250" t="n">
-        <v>56927</v>
+        <v>79084</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>430750</v>
+        <v>430783</v>
       </c>
       <c r="R250" t="n">
-        <v>6795558</v>
+        <v>6795818</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25665,44 +25665,44 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129773112</v>
+        <v>129771714</v>
       </c>
       <c r="B251" t="n">
-        <v>57895</v>
+        <v>56927</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25710,7 +25710,7 @@
       <c r="L251" t="inlineStr"/>
       <c r="M251" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N251" t="inlineStr"/>
@@ -25720,10 +25720,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>430814</v>
+        <v>430528</v>
       </c>
       <c r="R251" t="n">
-        <v>6795837</v>
+        <v>6795512</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25770,19 +25770,19 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129771714</v>
+        <v>129771718</v>
       </c>
       <c r="B252" t="n">
         <v>56927</v>
@@ -25825,10 +25825,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>430528</v>
+        <v>430939</v>
       </c>
       <c r="R252" t="n">
-        <v>6795512</v>
+        <v>6796145</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25887,32 +25887,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129771718</v>
+        <v>129771738</v>
       </c>
       <c r="B253" t="n">
-        <v>56927</v>
+        <v>57734</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -25920,7 +25920,7 @@
       <c r="L253" t="inlineStr"/>
       <c r="M253" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N253" t="inlineStr"/>
@@ -25930,10 +25930,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>430939</v>
+        <v>430655</v>
       </c>
       <c r="R253" t="n">
-        <v>6796145</v>
+        <v>6795565</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26186,10 +26186,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>129771738</v>
+        <v>129773112</v>
       </c>
       <c r="B256" t="n">
-        <v>57734</v>
+        <v>57895</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -26197,21 +26197,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26219,7 +26219,7 @@
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N256" t="inlineStr"/>
@@ -26229,10 +26229,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>430655</v>
+        <v>430814</v>
       </c>
       <c r="R256" t="n">
-        <v>6795565</v>
+        <v>6795837</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26279,12 +26279,12 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
@@ -26485,10 +26485,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>129773180</v>
+        <v>129771744</v>
       </c>
       <c r="B259" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -26496,34 +26496,42 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>430789</v>
+        <v>430959</v>
       </c>
       <c r="R259" t="n">
-        <v>6795377</v>
+        <v>6795543</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -26570,22 +26578,22 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>129771786</v>
+        <v>129773133</v>
       </c>
       <c r="B260" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26593,34 +26601,42 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>430927</v>
+        <v>430886</v>
       </c>
       <c r="R260" t="n">
-        <v>6795611</v>
+        <v>6795969</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26667,22 +26683,22 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>129773182</v>
+        <v>129773135</v>
       </c>
       <c r="B261" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26690,34 +26706,42 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>430740</v>
+        <v>430938</v>
       </c>
       <c r="R261" t="n">
-        <v>6795371</v>
+        <v>6795967</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26776,10 +26800,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>129773135</v>
+        <v>129771786</v>
       </c>
       <c r="B262" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26787,42 +26811,34 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>430938</v>
+        <v>430927</v>
       </c>
       <c r="R262" t="n">
-        <v>6795967</v>
+        <v>6795611</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26869,22 +26885,22 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>129773120</v>
+        <v>129773182</v>
       </c>
       <c r="B263" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -26892,42 +26908,34 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>430694</v>
+        <v>430740</v>
       </c>
       <c r="R263" t="n">
-        <v>6795368</v>
+        <v>6795371</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -26986,10 +26994,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>129771744</v>
+        <v>129773180</v>
       </c>
       <c r="B264" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -26997,42 +27005,34 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>430959</v>
+        <v>430789</v>
       </c>
       <c r="R264" t="n">
-        <v>6795543</v>
+        <v>6795377</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27079,19 +27079,19 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>129773133</v>
+        <v>129773120</v>
       </c>
       <c r="B265" t="n">
         <v>57734</v>
@@ -27134,10 +27134,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>430886</v>
+        <v>430694</v>
       </c>
       <c r="R265" t="n">
-        <v>6795969</v>
+        <v>6795368</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27293,10 +27293,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>129771817</v>
+        <v>129773125</v>
       </c>
       <c r="B267" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -27304,34 +27304,42 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>430997</v>
+        <v>430927</v>
       </c>
       <c r="R267" t="n">
-        <v>6795879</v>
+        <v>6795321</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27378,22 +27386,22 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>129771794</v>
+        <v>129773103</v>
       </c>
       <c r="B268" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -27401,34 +27409,42 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>430951</v>
+        <v>430952</v>
       </c>
       <c r="R268" t="n">
-        <v>6795576</v>
+        <v>6795876</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27475,57 +27491,65 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>129771787</v>
+        <v>129773108</v>
       </c>
       <c r="B269" t="n">
-        <v>79084</v>
+        <v>56927</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>430921</v>
+        <v>430941</v>
       </c>
       <c r="R269" t="n">
-        <v>6795636</v>
+        <v>6795862</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27572,57 +27596,65 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>129773100</v>
+        <v>129771715</v>
       </c>
       <c r="B270" t="n">
-        <v>79703</v>
+        <v>56927</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>430941</v>
+        <v>430568</v>
       </c>
       <c r="R270" t="n">
-        <v>6795869</v>
+        <v>6795570</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -27669,57 +27701,65 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>129771768</v>
+        <v>129771720</v>
       </c>
       <c r="B271" t="n">
-        <v>78841</v>
+        <v>56927</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>430921</v>
+        <v>430972</v>
       </c>
       <c r="R271" t="n">
-        <v>6796077</v>
+        <v>6796056</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27778,53 +27818,45 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>129773108</v>
+        <v>129771817</v>
       </c>
       <c r="B272" t="n">
-        <v>56927</v>
+        <v>79084</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>430941</v>
+        <v>430997</v>
       </c>
       <c r="R272" t="n">
-        <v>6795862</v>
+        <v>6795879</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27871,65 +27903,57 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>129771715</v>
+        <v>129771794</v>
       </c>
       <c r="B273" t="n">
-        <v>56927</v>
+        <v>79084</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>430568</v>
+        <v>430951</v>
       </c>
       <c r="R273" t="n">
-        <v>6795570</v>
+        <v>6795576</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27988,53 +28012,45 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>129771720</v>
+        <v>129771787</v>
       </c>
       <c r="B274" t="n">
-        <v>56927</v>
+        <v>79084</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>430972</v>
+        <v>430921</v>
       </c>
       <c r="R274" t="n">
-        <v>6796056</v>
+        <v>6795636</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28093,10 +28109,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>129773125</v>
+        <v>129773100</v>
       </c>
       <c r="B275" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -28104,42 +28120,34 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>430927</v>
+        <v>430941</v>
       </c>
       <c r="R275" t="n">
-        <v>6795321</v>
+        <v>6795869</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28198,10 +28206,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>129773103</v>
+        <v>129771768</v>
       </c>
       <c r="B276" t="n">
-        <v>57737</v>
+        <v>78841</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -28209,42 +28217,34 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>430952</v>
+        <v>430921</v>
       </c>
       <c r="R276" t="n">
-        <v>6795876</v>
+        <v>6796077</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28291,12 +28291,12 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
@@ -28410,10 +28410,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>129771771</v>
+        <v>129773154</v>
       </c>
       <c r="B278" t="n">
-        <v>78841</v>
+        <v>78842</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -28421,21 +28421,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -28445,10 +28445,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>430868</v>
+        <v>430860</v>
       </c>
       <c r="R278" t="n">
-        <v>6795798</v>
+        <v>6795825</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28495,65 +28495,57 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>129773105</v>
+        <v>129773157</v>
       </c>
       <c r="B279" t="n">
-        <v>56927</v>
+        <v>78842</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>430923</v>
+        <v>430617</v>
       </c>
       <c r="R279" t="n">
-        <v>6796012</v>
+        <v>6795600</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -28612,10 +28604,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>129771800</v>
+        <v>129773115</v>
       </c>
       <c r="B280" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -28623,34 +28615,42 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>431011</v>
+        <v>430594</v>
       </c>
       <c r="R280" t="n">
-        <v>6795579</v>
+        <v>6795423</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -28697,44 +28697,44 @@
       <c r="AT280" t="inlineStr"/>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>129773129</v>
+        <v>129773105</v>
       </c>
       <c r="B281" t="n">
-        <v>57734</v>
+        <v>56927</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -28742,7 +28742,7 @@
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N281" t="inlineStr"/>
@@ -28752,10 +28752,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>430920</v>
+        <v>430923</v>
       </c>
       <c r="R281" t="n">
-        <v>6796013</v>
+        <v>6796012</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -28814,32 +28814,32 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>129773115</v>
+        <v>129771723</v>
       </c>
       <c r="B282" t="n">
-        <v>57734</v>
+        <v>56927</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -28847,7 +28847,7 @@
       <c r="L282" t="inlineStr"/>
       <c r="M282" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N282" t="inlineStr"/>
@@ -28857,10 +28857,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>430594</v>
+        <v>430890</v>
       </c>
       <c r="R282" t="n">
-        <v>6795423</v>
+        <v>6795825</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -28907,19 +28907,19 @@
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>129771748</v>
+        <v>129773129</v>
       </c>
       <c r="B283" t="n">
         <v>57734</v>
@@ -28952,7 +28952,7 @@
       <c r="L283" t="inlineStr"/>
       <c r="M283" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N283" t="inlineStr"/>
@@ -28962,10 +28962,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>430982</v>
+        <v>430920</v>
       </c>
       <c r="R283" t="n">
-        <v>6795907</v>
+        <v>6796013</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -29012,44 +29012,44 @@
       <c r="AT283" t="inlineStr"/>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>129771723</v>
+        <v>129771748</v>
       </c>
       <c r="B284" t="n">
-        <v>56927</v>
+        <v>57734</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29057,7 +29057,7 @@
       <c r="L284" t="inlineStr"/>
       <c r="M284" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N284" t="inlineStr"/>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>430890</v>
+        <v>430982</v>
       </c>
       <c r="R284" t="n">
-        <v>6795825</v>
+        <v>6795907</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29129,54 +29129,45 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>129773160</v>
+        <v>129771800</v>
       </c>
       <c r="B285" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
-      <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr"/>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>430844</v>
+        <v>431011</v>
       </c>
       <c r="R285" t="n">
-        <v>6796058</v>
+        <v>6795579</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29217,29 +29208,28 @@
       <c r="AE285" t="b">
         <v>0</v>
       </c>
-      <c r="AF285" t="inlineStr"/>
       <c r="AG285" t="b">
         <v>0</v>
       </c>
       <c r="AT285" t="inlineStr"/>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>129773154</v>
+        <v>129771771</v>
       </c>
       <c r="B286" t="n">
-        <v>78842</v>
+        <v>78841</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -29247,21 +29237,21 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
@@ -29271,10 +29261,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>430860</v>
+        <v>430868</v>
       </c>
       <c r="R286" t="n">
-        <v>6795825</v>
+        <v>6795798</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -29321,57 +29311,66 @@
       <c r="AT286" t="inlineStr"/>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>129773157</v>
+        <v>129773160</v>
       </c>
       <c r="B287" t="n">
-        <v>78842</v>
+        <v>8450</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
+      <c r="J287" t="inlineStr"/>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>430617</v>
+        <v>430844</v>
       </c>
       <c r="R287" t="n">
-        <v>6795600</v>
+        <v>6796058</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -29412,6 +29411,7 @@
       <c r="AE287" t="b">
         <v>0</v>
       </c>
+      <c r="AF287" t="inlineStr"/>
       <c r="AG287" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50497-2025 artfynd.xlsx
+++ b/artfynd/A 50497-2025 artfynd.xlsx
@@ -13685,45 +13685,53 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129773143</v>
+        <v>129771719</v>
       </c>
       <c r="B131" t="n">
-        <v>78842</v>
+        <v>56927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>430730</v>
+        <v>430937</v>
       </c>
       <c r="R131" t="n">
-        <v>6795404</v>
+        <v>6796046</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13770,57 +13778,65 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129773153</v>
+        <v>129771724</v>
       </c>
       <c r="B132" t="n">
-        <v>78842</v>
+        <v>56927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430886</v>
+        <v>430884</v>
       </c>
       <c r="R132" t="n">
-        <v>6796067</v>
+        <v>6795785</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13867,19 +13883,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129771737</v>
+        <v>129773137</v>
       </c>
       <c r="B133" t="n">
         <v>57734</v>
@@ -13912,7 +13928,7 @@
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -13922,10 +13938,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>430522</v>
+        <v>430851</v>
       </c>
       <c r="R133" t="n">
-        <v>6795537</v>
+        <v>6795824</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13972,19 +13988,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129773137</v>
+        <v>129773132</v>
       </c>
       <c r="B134" t="n">
         <v>57734</v>
@@ -14027,10 +14043,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>430851</v>
+        <v>430873</v>
       </c>
       <c r="R134" t="n">
-        <v>6795824</v>
+        <v>6795977</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14089,7 +14105,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129773132</v>
+        <v>129771750</v>
       </c>
       <c r="B135" t="n">
         <v>57734</v>
@@ -14132,10 +14148,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>430873</v>
+        <v>430973</v>
       </c>
       <c r="R135" t="n">
-        <v>6795977</v>
+        <v>6795877</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14182,22 +14198,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129771750</v>
+        <v>129773113</v>
       </c>
       <c r="B136" t="n">
-        <v>57734</v>
+        <v>91623</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14205,31 +14221,26 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -14237,10 +14248,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>430973</v>
+        <v>430833</v>
       </c>
       <c r="R136" t="n">
-        <v>6795877</v>
+        <v>6796045</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14275,34 +14286,40 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>2 st på samma tall.</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129771741</v>
+        <v>129773214</v>
       </c>
       <c r="B137" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14310,42 +14327,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>430784</v>
+        <v>430777</v>
       </c>
       <c r="R137" t="n">
-        <v>6795567</v>
+        <v>6795822</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14392,22 +14401,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129773113</v>
+        <v>129773143</v>
       </c>
       <c r="B138" t="n">
-        <v>91623</v>
+        <v>78842</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14415,37 +14424,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>430833</v>
+        <v>430730</v>
       </c>
       <c r="R138" t="n">
-        <v>6796045</v>
+        <v>6795404</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14480,18 +14486,12 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>2 st på samma tall.</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14510,10 +14510,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129773214</v>
+        <v>129773153</v>
       </c>
       <c r="B139" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
    